--- a/primer/primer_gosti.xlsx
+++ b/primer/primer_gosti.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Uputstvo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gosti'!$A$1:$H$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gosti'!$A$1:$I$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,18 +513,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col hidden="1" outlineLevel="1" width="8" customWidth="1" min="9" max="12"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col hidden="1" outlineLevel="1" width="8" customWidth="1" min="10" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,45 +546,50 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Datum</t>
+          <t>Dolazak</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RAZLOG</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PROVERA JMBG</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>zbir</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>kontrolna</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>godina</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dat.rođ.</t>
         </is>
@@ -607,30 +613,34 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>05.10-10.10</t>
+          <t>05.10.2026</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="4">
+        <f>IF(A2="","",5)</f>
+        <v/>
+      </c>
+      <c r="F2" s="4" t="n"/>
       <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2">
-        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(J2="","JMBG sadrži nešto što nije cifra",IF(L2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;J2,"Pogrešna kontrolna cifra — treba "&amp;J2,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I2">
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2">
+        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(K2="","JMBG sadrži nešto što nije cifra",IF(M2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;K2,"Pogrešna kontrolna cifra — treba "&amp;K2,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J2">
         <f>IFERROR(IF(LEN(C2)&lt;&gt;13,"",7*(VALUE(MID(C2,1,1))+VALUE(MID(C2,7,1)))+6*(VALUE(MID(C2,2,1))+VALUE(MID(C2,8,1)))+5*(VALUE(MID(C2,3,1))+VALUE(MID(C2,9,1)))+4*(VALUE(MID(C2,4,1))+VALUE(MID(C2,10,1)))+3*(VALUE(MID(C2,5,1))+VALUE(MID(C2,11,1)))+2*(VALUE(MID(C2,6,1))+VALUE(MID(C2,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J2">
-        <f>IF(I2="","",IF(11-MOD(I2,11)&gt;9,0,11-MOD(I2,11)))</f>
-        <v/>
-      </c>
       <c r="K2">
+        <f>IF(J2="","",IF(11-MOD(J2,11)&gt;9,0,11-MOD(J2,11)))</f>
+        <v/>
+      </c>
+      <c r="L2">
         <f>IFERROR(IF(LEN(C2)&lt;&gt;13,"",IF(VALUE(MID(C2,5,3))&gt;=800,1000,2000)+VALUE(MID(C2,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L2">
-        <f>IFERROR(IF(K2="","",IF(AND(DAY(DATE(K2,VALUE(MID(C2,3,2)),VALUE(MID(C2,1,2))))=VALUE(MID(C2,1,2)),MONTH(DATE(K2,VALUE(MID(C2,3,2)),VALUE(MID(C2,1,2))))=VALUE(MID(C2,3,2))),DATE(K2,VALUE(MID(C2,3,2)),VALUE(MID(C2,1,2))),"")),"")</f>
+      <c r="M2">
+        <f>IFERROR(IF(L2="","",IF(AND(DAY(DATE(L2,VALUE(MID(C2,3,2)),VALUE(MID(C2,1,2))))=VALUE(MID(C2,1,2)),MONTH(DATE(L2,VALUE(MID(C2,3,2)),VALUE(MID(C2,1,2))))=VALUE(MID(C2,3,2))),DATE(L2,VALUE(MID(C2,3,2)),VALUE(MID(C2,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -652,30 +662,34 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>05.10-10.10</t>
+          <t>05.10.2026</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="4">
+        <f>IF(A3="","",5)</f>
+        <v/>
+      </c>
+      <c r="F3" s="4" t="n"/>
       <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2">
-        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(J3="","JMBG sadrži nešto što nije cifra",IF(L3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;J3,"Pogrešna kontrolna cifra — treba "&amp;J3,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I3">
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2">
+        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(K3="","JMBG sadrži nešto što nije cifra",IF(M3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;K3,"Pogrešna kontrolna cifra — treba "&amp;K3,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J3">
         <f>IFERROR(IF(LEN(C3)&lt;&gt;13,"",7*(VALUE(MID(C3,1,1))+VALUE(MID(C3,7,1)))+6*(VALUE(MID(C3,2,1))+VALUE(MID(C3,8,1)))+5*(VALUE(MID(C3,3,1))+VALUE(MID(C3,9,1)))+4*(VALUE(MID(C3,4,1))+VALUE(MID(C3,10,1)))+3*(VALUE(MID(C3,5,1))+VALUE(MID(C3,11,1)))+2*(VALUE(MID(C3,6,1))+VALUE(MID(C3,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J3">
-        <f>IF(I3="","",IF(11-MOD(I3,11)&gt;9,0,11-MOD(I3,11)))</f>
-        <v/>
-      </c>
       <c r="K3">
+        <f>IF(J3="","",IF(11-MOD(J3,11)&gt;9,0,11-MOD(J3,11)))</f>
+        <v/>
+      </c>
+      <c r="L3">
         <f>IFERROR(IF(LEN(C3)&lt;&gt;13,"",IF(VALUE(MID(C3,5,3))&gt;=800,1000,2000)+VALUE(MID(C3,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L3">
-        <f>IFERROR(IF(K3="","",IF(AND(DAY(DATE(K3,VALUE(MID(C3,3,2)),VALUE(MID(C3,1,2))))=VALUE(MID(C3,1,2)),MONTH(DATE(K3,VALUE(MID(C3,3,2)),VALUE(MID(C3,1,2))))=VALUE(MID(C3,3,2))),DATE(K3,VALUE(MID(C3,3,2)),VALUE(MID(C3,1,2))),"")),"")</f>
+      <c r="M3">
+        <f>IFERROR(IF(L3="","",IF(AND(DAY(DATE(L3,VALUE(MID(C3,3,2)),VALUE(MID(C3,1,2))))=VALUE(MID(C3,1,2)),MONTH(DATE(L3,VALUE(MID(C3,3,2)),VALUE(MID(C3,1,2))))=VALUE(MID(C3,3,2))),DATE(L3,VALUE(MID(C3,3,2)),VALUE(MID(C3,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -697,30 +711,33 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>06.10-12.10</t>
+          <t>06.10.2026</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="n"/>
       <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2">
-        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(J4="","JMBG sadrži nešto što nije cifra",IF(L4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;J4,"Pogrešna kontrolna cifra — treba "&amp;J4,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I4">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2">
+        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(K4="","JMBG sadrži nešto što nije cifra",IF(M4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;K4,"Pogrešna kontrolna cifra — treba "&amp;K4,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J4">
         <f>IFERROR(IF(LEN(C4)&lt;&gt;13,"",7*(VALUE(MID(C4,1,1))+VALUE(MID(C4,7,1)))+6*(VALUE(MID(C4,2,1))+VALUE(MID(C4,8,1)))+5*(VALUE(MID(C4,3,1))+VALUE(MID(C4,9,1)))+4*(VALUE(MID(C4,4,1))+VALUE(MID(C4,10,1)))+3*(VALUE(MID(C4,5,1))+VALUE(MID(C4,11,1)))+2*(VALUE(MID(C4,6,1))+VALUE(MID(C4,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J4">
-        <f>IF(I4="","",IF(11-MOD(I4,11)&gt;9,0,11-MOD(I4,11)))</f>
-        <v/>
-      </c>
       <c r="K4">
+        <f>IF(J4="","",IF(11-MOD(J4,11)&gt;9,0,11-MOD(J4,11)))</f>
+        <v/>
+      </c>
+      <c r="L4">
         <f>IFERROR(IF(LEN(C4)&lt;&gt;13,"",IF(VALUE(MID(C4,5,3))&gt;=800,1000,2000)+VALUE(MID(C4,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L4">
-        <f>IFERROR(IF(K4="","",IF(AND(DAY(DATE(K4,VALUE(MID(C4,3,2)),VALUE(MID(C4,1,2))))=VALUE(MID(C4,1,2)),MONTH(DATE(K4,VALUE(MID(C4,3,2)),VALUE(MID(C4,1,2))))=VALUE(MID(C4,3,2))),DATE(K4,VALUE(MID(C4,3,2)),VALUE(MID(C4,1,2))),"")),"")</f>
+      <c r="M4">
+        <f>IFERROR(IF(L4="","",IF(AND(DAY(DATE(L4,VALUE(MID(C4,3,2)),VALUE(MID(C4,1,2))))=VALUE(MID(C4,1,2)),MONTH(DATE(L4,VALUE(MID(C4,3,2)),VALUE(MID(C4,1,2))))=VALUE(MID(C4,3,2))),DATE(L4,VALUE(MID(C4,3,2)),VALUE(MID(C4,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -742,30 +759,34 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06.10-12.10</t>
+          <t>06.10.2026</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="4">
+        <f>IF(A5="","",5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="n"/>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2">
-        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(J5="","JMBG sadrži nešto što nije cifra",IF(L5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;J5,"Pogrešna kontrolna cifra — treba "&amp;J5,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I5">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2">
+        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(K5="","JMBG sadrži nešto što nije cifra",IF(M5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;K5,"Pogrešna kontrolna cifra — treba "&amp;K5,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J5">
         <f>IFERROR(IF(LEN(C5)&lt;&gt;13,"",7*(VALUE(MID(C5,1,1))+VALUE(MID(C5,7,1)))+6*(VALUE(MID(C5,2,1))+VALUE(MID(C5,8,1)))+5*(VALUE(MID(C5,3,1))+VALUE(MID(C5,9,1)))+4*(VALUE(MID(C5,4,1))+VALUE(MID(C5,10,1)))+3*(VALUE(MID(C5,5,1))+VALUE(MID(C5,11,1)))+2*(VALUE(MID(C5,6,1))+VALUE(MID(C5,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J5">
-        <f>IF(I5="","",IF(11-MOD(I5,11)&gt;9,0,11-MOD(I5,11)))</f>
-        <v/>
-      </c>
       <c r="K5">
+        <f>IF(J5="","",IF(11-MOD(J5,11)&gt;9,0,11-MOD(J5,11)))</f>
+        <v/>
+      </c>
+      <c r="L5">
         <f>IFERROR(IF(LEN(C5)&lt;&gt;13,"",IF(VALUE(MID(C5,5,3))&gt;=800,1000,2000)+VALUE(MID(C5,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L5">
-        <f>IFERROR(IF(K5="","",IF(AND(DAY(DATE(K5,VALUE(MID(C5,3,2)),VALUE(MID(C5,1,2))))=VALUE(MID(C5,1,2)),MONTH(DATE(K5,VALUE(MID(C5,3,2)),VALUE(MID(C5,1,2))))=VALUE(MID(C5,3,2))),DATE(K5,VALUE(MID(C5,3,2)),VALUE(MID(C5,1,2))),"")),"")</f>
+      <c r="M5">
+        <f>IFERROR(IF(L5="","",IF(AND(DAY(DATE(L5,VALUE(MID(C5,3,2)),VALUE(MID(C5,1,2))))=VALUE(MID(C5,1,2)),MONTH(DATE(L5,VALUE(MID(C5,3,2)),VALUE(MID(C5,1,2))))=VALUE(MID(C5,3,2))),DATE(L5,VALUE(MID(C5,3,2)),VALUE(MID(C5,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -787,30 +808,33 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>07.10-14.10</t>
+          <t>07.10.2026</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="n"/>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2">
-        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(J6="","JMBG sadrži nešto što nije cifra",IF(L6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;J6,"Pogrešna kontrolna cifra — treba "&amp;J6,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I6">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2">
+        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(K6="","JMBG sadrži nešto što nije cifra",IF(M6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;K6,"Pogrešna kontrolna cifra — treba "&amp;K6,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J6">
         <f>IFERROR(IF(LEN(C6)&lt;&gt;13,"",7*(VALUE(MID(C6,1,1))+VALUE(MID(C6,7,1)))+6*(VALUE(MID(C6,2,1))+VALUE(MID(C6,8,1)))+5*(VALUE(MID(C6,3,1))+VALUE(MID(C6,9,1)))+4*(VALUE(MID(C6,4,1))+VALUE(MID(C6,10,1)))+3*(VALUE(MID(C6,5,1))+VALUE(MID(C6,11,1)))+2*(VALUE(MID(C6,6,1))+VALUE(MID(C6,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J6">
-        <f>IF(I6="","",IF(11-MOD(I6,11)&gt;9,0,11-MOD(I6,11)))</f>
-        <v/>
-      </c>
       <c r="K6">
+        <f>IF(J6="","",IF(11-MOD(J6,11)&gt;9,0,11-MOD(J6,11)))</f>
+        <v/>
+      </c>
+      <c r="L6">
         <f>IFERROR(IF(LEN(C6)&lt;&gt;13,"",IF(VALUE(MID(C6,5,3))&gt;=800,1000,2000)+VALUE(MID(C6,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L6">
-        <f>IFERROR(IF(K6="","",IF(AND(DAY(DATE(K6,VALUE(MID(C6,3,2)),VALUE(MID(C6,1,2))))=VALUE(MID(C6,1,2)),MONTH(DATE(K6,VALUE(MID(C6,3,2)),VALUE(MID(C6,1,2))))=VALUE(MID(C6,3,2))),DATE(K6,VALUE(MID(C6,3,2)),VALUE(MID(C6,1,2))),"")),"")</f>
+      <c r="M6">
+        <f>IFERROR(IF(L6="","",IF(AND(DAY(DATE(L6,VALUE(MID(C6,3,2)),VALUE(MID(C6,1,2))))=VALUE(MID(C6,1,2)),MONTH(DATE(L6,VALUE(MID(C6,3,2)),VALUE(MID(C6,1,2))))=VALUE(MID(C6,3,2))),DATE(L6,VALUE(MID(C6,3,2)),VALUE(MID(C6,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -832,30 +856,34 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>07.10-14.10</t>
+          <t>07.10.2026</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="4">
+        <f>IF(A7="","",5)</f>
+        <v/>
+      </c>
+      <c r="F7" s="4" t="n"/>
       <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2">
-        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(J7="","JMBG sadrži nešto što nije cifra",IF(L7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;J7,"Pogrešna kontrolna cifra — treba "&amp;J7,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I7">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2">
+        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(K7="","JMBG sadrži nešto što nije cifra",IF(M7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;K7,"Pogrešna kontrolna cifra — treba "&amp;K7,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J7">
         <f>IFERROR(IF(LEN(C7)&lt;&gt;13,"",7*(VALUE(MID(C7,1,1))+VALUE(MID(C7,7,1)))+6*(VALUE(MID(C7,2,1))+VALUE(MID(C7,8,1)))+5*(VALUE(MID(C7,3,1))+VALUE(MID(C7,9,1)))+4*(VALUE(MID(C7,4,1))+VALUE(MID(C7,10,1)))+3*(VALUE(MID(C7,5,1))+VALUE(MID(C7,11,1)))+2*(VALUE(MID(C7,6,1))+VALUE(MID(C7,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J7">
-        <f>IF(I7="","",IF(11-MOD(I7,11)&gt;9,0,11-MOD(I7,11)))</f>
-        <v/>
-      </c>
       <c r="K7">
+        <f>IF(J7="","",IF(11-MOD(J7,11)&gt;9,0,11-MOD(J7,11)))</f>
+        <v/>
+      </c>
+      <c r="L7">
         <f>IFERROR(IF(LEN(C7)&lt;&gt;13,"",IF(VALUE(MID(C7,5,3))&gt;=800,1000,2000)+VALUE(MID(C7,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L7">
-        <f>IFERROR(IF(K7="","",IF(AND(DAY(DATE(K7,VALUE(MID(C7,3,2)),VALUE(MID(C7,1,2))))=VALUE(MID(C7,1,2)),MONTH(DATE(K7,VALUE(MID(C7,3,2)),VALUE(MID(C7,1,2))))=VALUE(MID(C7,3,2))),DATE(K7,VALUE(MID(C7,3,2)),VALUE(MID(C7,1,2))),"")),"")</f>
+      <c r="M7">
+        <f>IFERROR(IF(L7="","",IF(AND(DAY(DATE(L7,VALUE(MID(C7,3,2)),VALUE(MID(C7,1,2))))=VALUE(MID(C7,1,2)),MONTH(DATE(L7,VALUE(MID(C7,3,2)),VALUE(MID(C7,1,2))))=VALUE(MID(C7,3,2))),DATE(L7,VALUE(MID(C7,3,2)),VALUE(MID(C7,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -877,30 +905,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>08.10-15.10</t>
+          <t>08.10.2026</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="4">
+        <f>IF(A8="","",5)</f>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2">
-        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(J8="","JMBG sadrži nešto što nije cifra",IF(L8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;J8,"Pogrešna kontrolna cifra — treba "&amp;J8,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I8">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2">
+        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(K8="","JMBG sadrži nešto što nije cifra",IF(M8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;K8,"Pogrešna kontrolna cifra — treba "&amp;K8,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J8">
         <f>IFERROR(IF(LEN(C8)&lt;&gt;13,"",7*(VALUE(MID(C8,1,1))+VALUE(MID(C8,7,1)))+6*(VALUE(MID(C8,2,1))+VALUE(MID(C8,8,1)))+5*(VALUE(MID(C8,3,1))+VALUE(MID(C8,9,1)))+4*(VALUE(MID(C8,4,1))+VALUE(MID(C8,10,1)))+3*(VALUE(MID(C8,5,1))+VALUE(MID(C8,11,1)))+2*(VALUE(MID(C8,6,1))+VALUE(MID(C8,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J8">
-        <f>IF(I8="","",IF(11-MOD(I8,11)&gt;9,0,11-MOD(I8,11)))</f>
-        <v/>
-      </c>
       <c r="K8">
+        <f>IF(J8="","",IF(11-MOD(J8,11)&gt;9,0,11-MOD(J8,11)))</f>
+        <v/>
+      </c>
+      <c r="L8">
         <f>IFERROR(IF(LEN(C8)&lt;&gt;13,"",IF(VALUE(MID(C8,5,3))&gt;=800,1000,2000)+VALUE(MID(C8,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L8">
-        <f>IFERROR(IF(K8="","",IF(AND(DAY(DATE(K8,VALUE(MID(C8,3,2)),VALUE(MID(C8,1,2))))=VALUE(MID(C8,1,2)),MONTH(DATE(K8,VALUE(MID(C8,3,2)),VALUE(MID(C8,1,2))))=VALUE(MID(C8,3,2))),DATE(K8,VALUE(MID(C8,3,2)),VALUE(MID(C8,1,2))),"")),"")</f>
+      <c r="M8">
+        <f>IFERROR(IF(L8="","",IF(AND(DAY(DATE(L8,VALUE(MID(C8,3,2)),VALUE(MID(C8,1,2))))=VALUE(MID(C8,1,2)),MONTH(DATE(L8,VALUE(MID(C8,3,2)),VALUE(MID(C8,1,2))))=VALUE(MID(C8,3,2))),DATE(L8,VALUE(MID(C8,3,2)),VALUE(MID(C8,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -909,27 +941,31 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="2" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="2" t="n"/>
+      <c r="E9" s="4">
+        <f>IF(A9="","",5)</f>
+        <v/>
+      </c>
+      <c r="F9" s="4" t="n"/>
       <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2">
-        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(J9="","JMBG sadrži nešto što nije cifra",IF(L9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;J9,"Pogrešna kontrolna cifra — treba "&amp;J9,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I9">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2">
+        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(K9="","JMBG sadrži nešto što nije cifra",IF(M9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;K9,"Pogrešna kontrolna cifra — treba "&amp;K9,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J9">
         <f>IFERROR(IF(LEN(C9)&lt;&gt;13,"",7*(VALUE(MID(C9,1,1))+VALUE(MID(C9,7,1)))+6*(VALUE(MID(C9,2,1))+VALUE(MID(C9,8,1)))+5*(VALUE(MID(C9,3,1))+VALUE(MID(C9,9,1)))+4*(VALUE(MID(C9,4,1))+VALUE(MID(C9,10,1)))+3*(VALUE(MID(C9,5,1))+VALUE(MID(C9,11,1)))+2*(VALUE(MID(C9,6,1))+VALUE(MID(C9,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J9">
-        <f>IF(I9="","",IF(11-MOD(I9,11)&gt;9,0,11-MOD(I9,11)))</f>
-        <v/>
-      </c>
       <c r="K9">
+        <f>IF(J9="","",IF(11-MOD(J9,11)&gt;9,0,11-MOD(J9,11)))</f>
+        <v/>
+      </c>
+      <c r="L9">
         <f>IFERROR(IF(LEN(C9)&lt;&gt;13,"",IF(VALUE(MID(C9,5,3))&gt;=800,1000,2000)+VALUE(MID(C9,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L9">
-        <f>IFERROR(IF(K9="","",IF(AND(DAY(DATE(K9,VALUE(MID(C9,3,2)),VALUE(MID(C9,1,2))))=VALUE(MID(C9,1,2)),MONTH(DATE(K9,VALUE(MID(C9,3,2)),VALUE(MID(C9,1,2))))=VALUE(MID(C9,3,2))),DATE(K9,VALUE(MID(C9,3,2)),VALUE(MID(C9,1,2))),"")),"")</f>
+      <c r="M9">
+        <f>IFERROR(IF(L9="","",IF(AND(DAY(DATE(L9,VALUE(MID(C9,3,2)),VALUE(MID(C9,1,2))))=VALUE(MID(C9,1,2)),MONTH(DATE(L9,VALUE(MID(C9,3,2)),VALUE(MID(C9,1,2))))=VALUE(MID(C9,3,2))),DATE(L9,VALUE(MID(C9,3,2)),VALUE(MID(C9,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -938,27 +974,31 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="2" t="n"/>
+      <c r="E10" s="4">
+        <f>IF(A10="","",5)</f>
+        <v/>
+      </c>
+      <c r="F10" s="4" t="n"/>
       <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2">
-        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(J10="","JMBG sadrži nešto što nije cifra",IF(L10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;J10,"Pogrešna kontrolna cifra — treba "&amp;J10,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I10">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2">
+        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(K10="","JMBG sadrži nešto što nije cifra",IF(M10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;K10,"Pogrešna kontrolna cifra — treba "&amp;K10,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J10">
         <f>IFERROR(IF(LEN(C10)&lt;&gt;13,"",7*(VALUE(MID(C10,1,1))+VALUE(MID(C10,7,1)))+6*(VALUE(MID(C10,2,1))+VALUE(MID(C10,8,1)))+5*(VALUE(MID(C10,3,1))+VALUE(MID(C10,9,1)))+4*(VALUE(MID(C10,4,1))+VALUE(MID(C10,10,1)))+3*(VALUE(MID(C10,5,1))+VALUE(MID(C10,11,1)))+2*(VALUE(MID(C10,6,1))+VALUE(MID(C10,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J10">
-        <f>IF(I10="","",IF(11-MOD(I10,11)&gt;9,0,11-MOD(I10,11)))</f>
-        <v/>
-      </c>
       <c r="K10">
+        <f>IF(J10="","",IF(11-MOD(J10,11)&gt;9,0,11-MOD(J10,11)))</f>
+        <v/>
+      </c>
+      <c r="L10">
         <f>IFERROR(IF(LEN(C10)&lt;&gt;13,"",IF(VALUE(MID(C10,5,3))&gt;=800,1000,2000)+VALUE(MID(C10,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L10">
-        <f>IFERROR(IF(K10="","",IF(AND(DAY(DATE(K10,VALUE(MID(C10,3,2)),VALUE(MID(C10,1,2))))=VALUE(MID(C10,1,2)),MONTH(DATE(K10,VALUE(MID(C10,3,2)),VALUE(MID(C10,1,2))))=VALUE(MID(C10,3,2))),DATE(K10,VALUE(MID(C10,3,2)),VALUE(MID(C10,1,2))),"")),"")</f>
+      <c r="M10">
+        <f>IFERROR(IF(L10="","",IF(AND(DAY(DATE(L10,VALUE(MID(C10,3,2)),VALUE(MID(C10,1,2))))=VALUE(MID(C10,1,2)),MONTH(DATE(L10,VALUE(MID(C10,3,2)),VALUE(MID(C10,1,2))))=VALUE(MID(C10,3,2))),DATE(L10,VALUE(MID(C10,3,2)),VALUE(MID(C10,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -967,27 +1007,31 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="2" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="E11" s="4">
+        <f>IF(A11="","",5)</f>
+        <v/>
+      </c>
+      <c r="F11" s="4" t="n"/>
       <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2">
-        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(J11="","JMBG sadrži nešto što nije cifra",IF(L11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;J11,"Pogrešna kontrolna cifra — treba "&amp;J11,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I11">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2">
+        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(K11="","JMBG sadrži nešto što nije cifra",IF(M11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;K11,"Pogrešna kontrolna cifra — treba "&amp;K11,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J11">
         <f>IFERROR(IF(LEN(C11)&lt;&gt;13,"",7*(VALUE(MID(C11,1,1))+VALUE(MID(C11,7,1)))+6*(VALUE(MID(C11,2,1))+VALUE(MID(C11,8,1)))+5*(VALUE(MID(C11,3,1))+VALUE(MID(C11,9,1)))+4*(VALUE(MID(C11,4,1))+VALUE(MID(C11,10,1)))+3*(VALUE(MID(C11,5,1))+VALUE(MID(C11,11,1)))+2*(VALUE(MID(C11,6,1))+VALUE(MID(C11,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J11">
-        <f>IF(I11="","",IF(11-MOD(I11,11)&gt;9,0,11-MOD(I11,11)))</f>
-        <v/>
-      </c>
       <c r="K11">
+        <f>IF(J11="","",IF(11-MOD(J11,11)&gt;9,0,11-MOD(J11,11)))</f>
+        <v/>
+      </c>
+      <c r="L11">
         <f>IFERROR(IF(LEN(C11)&lt;&gt;13,"",IF(VALUE(MID(C11,5,3))&gt;=800,1000,2000)+VALUE(MID(C11,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L11">
-        <f>IFERROR(IF(K11="","",IF(AND(DAY(DATE(K11,VALUE(MID(C11,3,2)),VALUE(MID(C11,1,2))))=VALUE(MID(C11,1,2)),MONTH(DATE(K11,VALUE(MID(C11,3,2)),VALUE(MID(C11,1,2))))=VALUE(MID(C11,3,2))),DATE(K11,VALUE(MID(C11,3,2)),VALUE(MID(C11,1,2))),"")),"")</f>
+      <c r="M11">
+        <f>IFERROR(IF(L11="","",IF(AND(DAY(DATE(L11,VALUE(MID(C11,3,2)),VALUE(MID(C11,1,2))))=VALUE(MID(C11,1,2)),MONTH(DATE(L11,VALUE(MID(C11,3,2)),VALUE(MID(C11,1,2))))=VALUE(MID(C11,3,2))),DATE(L11,VALUE(MID(C11,3,2)),VALUE(MID(C11,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -996,27 +1040,31 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="2" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="E12" s="4">
+        <f>IF(A12="","",5)</f>
+        <v/>
+      </c>
+      <c r="F12" s="4" t="n"/>
       <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2">
-        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(J12="","JMBG sadrži nešto što nije cifra",IF(L12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;J12,"Pogrešna kontrolna cifra — treba "&amp;J12,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I12">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2">
+        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(K12="","JMBG sadrži nešto što nije cifra",IF(M12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;K12,"Pogrešna kontrolna cifra — treba "&amp;K12,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J12">
         <f>IFERROR(IF(LEN(C12)&lt;&gt;13,"",7*(VALUE(MID(C12,1,1))+VALUE(MID(C12,7,1)))+6*(VALUE(MID(C12,2,1))+VALUE(MID(C12,8,1)))+5*(VALUE(MID(C12,3,1))+VALUE(MID(C12,9,1)))+4*(VALUE(MID(C12,4,1))+VALUE(MID(C12,10,1)))+3*(VALUE(MID(C12,5,1))+VALUE(MID(C12,11,1)))+2*(VALUE(MID(C12,6,1))+VALUE(MID(C12,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J12">
-        <f>IF(I12="","",IF(11-MOD(I12,11)&gt;9,0,11-MOD(I12,11)))</f>
-        <v/>
-      </c>
       <c r="K12">
+        <f>IF(J12="","",IF(11-MOD(J12,11)&gt;9,0,11-MOD(J12,11)))</f>
+        <v/>
+      </c>
+      <c r="L12">
         <f>IFERROR(IF(LEN(C12)&lt;&gt;13,"",IF(VALUE(MID(C12,5,3))&gt;=800,1000,2000)+VALUE(MID(C12,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L12">
-        <f>IFERROR(IF(K12="","",IF(AND(DAY(DATE(K12,VALUE(MID(C12,3,2)),VALUE(MID(C12,1,2))))=VALUE(MID(C12,1,2)),MONTH(DATE(K12,VALUE(MID(C12,3,2)),VALUE(MID(C12,1,2))))=VALUE(MID(C12,3,2))),DATE(K12,VALUE(MID(C12,3,2)),VALUE(MID(C12,1,2))),"")),"")</f>
+      <c r="M12">
+        <f>IFERROR(IF(L12="","",IF(AND(DAY(DATE(L12,VALUE(MID(C12,3,2)),VALUE(MID(C12,1,2))))=VALUE(MID(C12,1,2)),MONTH(DATE(L12,VALUE(MID(C12,3,2)),VALUE(MID(C12,1,2))))=VALUE(MID(C12,3,2))),DATE(L12,VALUE(MID(C12,3,2)),VALUE(MID(C12,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1025,27 +1073,31 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="2" t="n"/>
+      <c r="E13" s="4">
+        <f>IF(A13="","",5)</f>
+        <v/>
+      </c>
+      <c r="F13" s="4" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2">
-        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(J13="","JMBG sadrži nešto što nije cifra",IF(L13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;J13,"Pogrešna kontrolna cifra — treba "&amp;J13,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I13">
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2">
+        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(K13="","JMBG sadrži nešto što nije cifra",IF(M13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;K13,"Pogrešna kontrolna cifra — treba "&amp;K13,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J13">
         <f>IFERROR(IF(LEN(C13)&lt;&gt;13,"",7*(VALUE(MID(C13,1,1))+VALUE(MID(C13,7,1)))+6*(VALUE(MID(C13,2,1))+VALUE(MID(C13,8,1)))+5*(VALUE(MID(C13,3,1))+VALUE(MID(C13,9,1)))+4*(VALUE(MID(C13,4,1))+VALUE(MID(C13,10,1)))+3*(VALUE(MID(C13,5,1))+VALUE(MID(C13,11,1)))+2*(VALUE(MID(C13,6,1))+VALUE(MID(C13,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J13">
-        <f>IF(I13="","",IF(11-MOD(I13,11)&gt;9,0,11-MOD(I13,11)))</f>
-        <v/>
-      </c>
       <c r="K13">
+        <f>IF(J13="","",IF(11-MOD(J13,11)&gt;9,0,11-MOD(J13,11)))</f>
+        <v/>
+      </c>
+      <c r="L13">
         <f>IFERROR(IF(LEN(C13)&lt;&gt;13,"",IF(VALUE(MID(C13,5,3))&gt;=800,1000,2000)+VALUE(MID(C13,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L13">
-        <f>IFERROR(IF(K13="","",IF(AND(DAY(DATE(K13,VALUE(MID(C13,3,2)),VALUE(MID(C13,1,2))))=VALUE(MID(C13,1,2)),MONTH(DATE(K13,VALUE(MID(C13,3,2)),VALUE(MID(C13,1,2))))=VALUE(MID(C13,3,2))),DATE(K13,VALUE(MID(C13,3,2)),VALUE(MID(C13,1,2))),"")),"")</f>
+      <c r="M13">
+        <f>IFERROR(IF(L13="","",IF(AND(DAY(DATE(L13,VALUE(MID(C13,3,2)),VALUE(MID(C13,1,2))))=VALUE(MID(C13,1,2)),MONTH(DATE(L13,VALUE(MID(C13,3,2)),VALUE(MID(C13,1,2))))=VALUE(MID(C13,3,2))),DATE(L13,VALUE(MID(C13,3,2)),VALUE(MID(C13,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1054,27 +1106,31 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="E14" s="4">
+        <f>IF(A14="","",5)</f>
+        <v/>
+      </c>
+      <c r="F14" s="4" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2">
-        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(J14="","JMBG sadrži nešto što nije cifra",IF(L14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;J14,"Pogrešna kontrolna cifra — treba "&amp;J14,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I14">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2">
+        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(K14="","JMBG sadrži nešto što nije cifra",IF(M14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;K14,"Pogrešna kontrolna cifra — treba "&amp;K14,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J14">
         <f>IFERROR(IF(LEN(C14)&lt;&gt;13,"",7*(VALUE(MID(C14,1,1))+VALUE(MID(C14,7,1)))+6*(VALUE(MID(C14,2,1))+VALUE(MID(C14,8,1)))+5*(VALUE(MID(C14,3,1))+VALUE(MID(C14,9,1)))+4*(VALUE(MID(C14,4,1))+VALUE(MID(C14,10,1)))+3*(VALUE(MID(C14,5,1))+VALUE(MID(C14,11,1)))+2*(VALUE(MID(C14,6,1))+VALUE(MID(C14,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J14">
-        <f>IF(I14="","",IF(11-MOD(I14,11)&gt;9,0,11-MOD(I14,11)))</f>
-        <v/>
-      </c>
       <c r="K14">
+        <f>IF(J14="","",IF(11-MOD(J14,11)&gt;9,0,11-MOD(J14,11)))</f>
+        <v/>
+      </c>
+      <c r="L14">
         <f>IFERROR(IF(LEN(C14)&lt;&gt;13,"",IF(VALUE(MID(C14,5,3))&gt;=800,1000,2000)+VALUE(MID(C14,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L14">
-        <f>IFERROR(IF(K14="","",IF(AND(DAY(DATE(K14,VALUE(MID(C14,3,2)),VALUE(MID(C14,1,2))))=VALUE(MID(C14,1,2)),MONTH(DATE(K14,VALUE(MID(C14,3,2)),VALUE(MID(C14,1,2))))=VALUE(MID(C14,3,2))),DATE(K14,VALUE(MID(C14,3,2)),VALUE(MID(C14,1,2))),"")),"")</f>
+      <c r="M14">
+        <f>IFERROR(IF(L14="","",IF(AND(DAY(DATE(L14,VALUE(MID(C14,3,2)),VALUE(MID(C14,1,2))))=VALUE(MID(C14,1,2)),MONTH(DATE(L14,VALUE(MID(C14,3,2)),VALUE(MID(C14,1,2))))=VALUE(MID(C14,3,2))),DATE(L14,VALUE(MID(C14,3,2)),VALUE(MID(C14,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1083,27 +1139,31 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="2" t="n"/>
+      <c r="E15" s="4">
+        <f>IF(A15="","",5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="4" t="n"/>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2">
-        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(J15="","JMBG sadrži nešto što nije cifra",IF(L15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;J15,"Pogrešna kontrolna cifra — treba "&amp;J15,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I15">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2">
+        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(K15="","JMBG sadrži nešto što nije cifra",IF(M15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;K15,"Pogrešna kontrolna cifra — treba "&amp;K15,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J15">
         <f>IFERROR(IF(LEN(C15)&lt;&gt;13,"",7*(VALUE(MID(C15,1,1))+VALUE(MID(C15,7,1)))+6*(VALUE(MID(C15,2,1))+VALUE(MID(C15,8,1)))+5*(VALUE(MID(C15,3,1))+VALUE(MID(C15,9,1)))+4*(VALUE(MID(C15,4,1))+VALUE(MID(C15,10,1)))+3*(VALUE(MID(C15,5,1))+VALUE(MID(C15,11,1)))+2*(VALUE(MID(C15,6,1))+VALUE(MID(C15,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J15">
-        <f>IF(I15="","",IF(11-MOD(I15,11)&gt;9,0,11-MOD(I15,11)))</f>
-        <v/>
-      </c>
       <c r="K15">
+        <f>IF(J15="","",IF(11-MOD(J15,11)&gt;9,0,11-MOD(J15,11)))</f>
+        <v/>
+      </c>
+      <c r="L15">
         <f>IFERROR(IF(LEN(C15)&lt;&gt;13,"",IF(VALUE(MID(C15,5,3))&gt;=800,1000,2000)+VALUE(MID(C15,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L15">
-        <f>IFERROR(IF(K15="","",IF(AND(DAY(DATE(K15,VALUE(MID(C15,3,2)),VALUE(MID(C15,1,2))))=VALUE(MID(C15,1,2)),MONTH(DATE(K15,VALUE(MID(C15,3,2)),VALUE(MID(C15,1,2))))=VALUE(MID(C15,3,2))),DATE(K15,VALUE(MID(C15,3,2)),VALUE(MID(C15,1,2))),"")),"")</f>
+      <c r="M15">
+        <f>IFERROR(IF(L15="","",IF(AND(DAY(DATE(L15,VALUE(MID(C15,3,2)),VALUE(MID(C15,1,2))))=VALUE(MID(C15,1,2)),MONTH(DATE(L15,VALUE(MID(C15,3,2)),VALUE(MID(C15,1,2))))=VALUE(MID(C15,3,2))),DATE(L15,VALUE(MID(C15,3,2)),VALUE(MID(C15,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1112,27 +1172,31 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="2" t="n"/>
+      <c r="E16" s="4">
+        <f>IF(A16="","",5)</f>
+        <v/>
+      </c>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2">
-        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(J16="","JMBG sadrži nešto što nije cifra",IF(L16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;J16,"Pogrešna kontrolna cifra — treba "&amp;J16,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I16">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2">
+        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(K16="","JMBG sadrži nešto što nije cifra",IF(M16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;K16,"Pogrešna kontrolna cifra — treba "&amp;K16,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J16">
         <f>IFERROR(IF(LEN(C16)&lt;&gt;13,"",7*(VALUE(MID(C16,1,1))+VALUE(MID(C16,7,1)))+6*(VALUE(MID(C16,2,1))+VALUE(MID(C16,8,1)))+5*(VALUE(MID(C16,3,1))+VALUE(MID(C16,9,1)))+4*(VALUE(MID(C16,4,1))+VALUE(MID(C16,10,1)))+3*(VALUE(MID(C16,5,1))+VALUE(MID(C16,11,1)))+2*(VALUE(MID(C16,6,1))+VALUE(MID(C16,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J16">
-        <f>IF(I16="","",IF(11-MOD(I16,11)&gt;9,0,11-MOD(I16,11)))</f>
-        <v/>
-      </c>
       <c r="K16">
+        <f>IF(J16="","",IF(11-MOD(J16,11)&gt;9,0,11-MOD(J16,11)))</f>
+        <v/>
+      </c>
+      <c r="L16">
         <f>IFERROR(IF(LEN(C16)&lt;&gt;13,"",IF(VALUE(MID(C16,5,3))&gt;=800,1000,2000)+VALUE(MID(C16,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L16">
-        <f>IFERROR(IF(K16="","",IF(AND(DAY(DATE(K16,VALUE(MID(C16,3,2)),VALUE(MID(C16,1,2))))=VALUE(MID(C16,1,2)),MONTH(DATE(K16,VALUE(MID(C16,3,2)),VALUE(MID(C16,1,2))))=VALUE(MID(C16,3,2))),DATE(K16,VALUE(MID(C16,3,2)),VALUE(MID(C16,1,2))),"")),"")</f>
+      <c r="M16">
+        <f>IFERROR(IF(L16="","",IF(AND(DAY(DATE(L16,VALUE(MID(C16,3,2)),VALUE(MID(C16,1,2))))=VALUE(MID(C16,1,2)),MONTH(DATE(L16,VALUE(MID(C16,3,2)),VALUE(MID(C16,1,2))))=VALUE(MID(C16,3,2))),DATE(L16,VALUE(MID(C16,3,2)),VALUE(MID(C16,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1141,27 +1205,31 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="2" t="n"/>
+      <c r="E17" s="4">
+        <f>IF(A17="","",5)</f>
+        <v/>
+      </c>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2">
-        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(J17="","JMBG sadrži nešto što nije cifra",IF(L17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;J17,"Pogrešna kontrolna cifra — treba "&amp;J17,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I17">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2">
+        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(K17="","JMBG sadrži nešto što nije cifra",IF(M17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;K17,"Pogrešna kontrolna cifra — treba "&amp;K17,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J17">
         <f>IFERROR(IF(LEN(C17)&lt;&gt;13,"",7*(VALUE(MID(C17,1,1))+VALUE(MID(C17,7,1)))+6*(VALUE(MID(C17,2,1))+VALUE(MID(C17,8,1)))+5*(VALUE(MID(C17,3,1))+VALUE(MID(C17,9,1)))+4*(VALUE(MID(C17,4,1))+VALUE(MID(C17,10,1)))+3*(VALUE(MID(C17,5,1))+VALUE(MID(C17,11,1)))+2*(VALUE(MID(C17,6,1))+VALUE(MID(C17,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J17">
-        <f>IF(I17="","",IF(11-MOD(I17,11)&gt;9,0,11-MOD(I17,11)))</f>
-        <v/>
-      </c>
       <c r="K17">
+        <f>IF(J17="","",IF(11-MOD(J17,11)&gt;9,0,11-MOD(J17,11)))</f>
+        <v/>
+      </c>
+      <c r="L17">
         <f>IFERROR(IF(LEN(C17)&lt;&gt;13,"",IF(VALUE(MID(C17,5,3))&gt;=800,1000,2000)+VALUE(MID(C17,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L17">
-        <f>IFERROR(IF(K17="","",IF(AND(DAY(DATE(K17,VALUE(MID(C17,3,2)),VALUE(MID(C17,1,2))))=VALUE(MID(C17,1,2)),MONTH(DATE(K17,VALUE(MID(C17,3,2)),VALUE(MID(C17,1,2))))=VALUE(MID(C17,3,2))),DATE(K17,VALUE(MID(C17,3,2)),VALUE(MID(C17,1,2))),"")),"")</f>
+      <c r="M17">
+        <f>IFERROR(IF(L17="","",IF(AND(DAY(DATE(L17,VALUE(MID(C17,3,2)),VALUE(MID(C17,1,2))))=VALUE(MID(C17,1,2)),MONTH(DATE(L17,VALUE(MID(C17,3,2)),VALUE(MID(C17,1,2))))=VALUE(MID(C17,3,2))),DATE(L17,VALUE(MID(C17,3,2)),VALUE(MID(C17,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1170,27 +1238,31 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="2" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="2" t="n"/>
+      <c r="E18" s="4">
+        <f>IF(A18="","",5)</f>
+        <v/>
+      </c>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2">
-        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(J18="","JMBG sadrži nešto što nije cifra",IF(L18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;J18,"Pogrešna kontrolna cifra — treba "&amp;J18,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I18">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2">
+        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(K18="","JMBG sadrži nešto što nije cifra",IF(M18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;K18,"Pogrešna kontrolna cifra — treba "&amp;K18,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J18">
         <f>IFERROR(IF(LEN(C18)&lt;&gt;13,"",7*(VALUE(MID(C18,1,1))+VALUE(MID(C18,7,1)))+6*(VALUE(MID(C18,2,1))+VALUE(MID(C18,8,1)))+5*(VALUE(MID(C18,3,1))+VALUE(MID(C18,9,1)))+4*(VALUE(MID(C18,4,1))+VALUE(MID(C18,10,1)))+3*(VALUE(MID(C18,5,1))+VALUE(MID(C18,11,1)))+2*(VALUE(MID(C18,6,1))+VALUE(MID(C18,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J18">
-        <f>IF(I18="","",IF(11-MOD(I18,11)&gt;9,0,11-MOD(I18,11)))</f>
-        <v/>
-      </c>
       <c r="K18">
+        <f>IF(J18="","",IF(11-MOD(J18,11)&gt;9,0,11-MOD(J18,11)))</f>
+        <v/>
+      </c>
+      <c r="L18">
         <f>IFERROR(IF(LEN(C18)&lt;&gt;13,"",IF(VALUE(MID(C18,5,3))&gt;=800,1000,2000)+VALUE(MID(C18,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L18">
-        <f>IFERROR(IF(K18="","",IF(AND(DAY(DATE(K18,VALUE(MID(C18,3,2)),VALUE(MID(C18,1,2))))=VALUE(MID(C18,1,2)),MONTH(DATE(K18,VALUE(MID(C18,3,2)),VALUE(MID(C18,1,2))))=VALUE(MID(C18,3,2))),DATE(K18,VALUE(MID(C18,3,2)),VALUE(MID(C18,1,2))),"")),"")</f>
+      <c r="M18">
+        <f>IFERROR(IF(L18="","",IF(AND(DAY(DATE(L18,VALUE(MID(C18,3,2)),VALUE(MID(C18,1,2))))=VALUE(MID(C18,1,2)),MONTH(DATE(L18,VALUE(MID(C18,3,2)),VALUE(MID(C18,1,2))))=VALUE(MID(C18,3,2))),DATE(L18,VALUE(MID(C18,3,2)),VALUE(MID(C18,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1199,27 +1271,31 @@
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="2" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="E19" s="4">
+        <f>IF(A19="","",5)</f>
+        <v/>
+      </c>
+      <c r="F19" s="4" t="n"/>
       <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2">
-        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(J19="","JMBG sadrži nešto što nije cifra",IF(L19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;J19,"Pogrešna kontrolna cifra — treba "&amp;J19,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I19">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2">
+        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(K19="","JMBG sadrži nešto što nije cifra",IF(M19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;K19,"Pogrešna kontrolna cifra — treba "&amp;K19,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J19">
         <f>IFERROR(IF(LEN(C19)&lt;&gt;13,"",7*(VALUE(MID(C19,1,1))+VALUE(MID(C19,7,1)))+6*(VALUE(MID(C19,2,1))+VALUE(MID(C19,8,1)))+5*(VALUE(MID(C19,3,1))+VALUE(MID(C19,9,1)))+4*(VALUE(MID(C19,4,1))+VALUE(MID(C19,10,1)))+3*(VALUE(MID(C19,5,1))+VALUE(MID(C19,11,1)))+2*(VALUE(MID(C19,6,1))+VALUE(MID(C19,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J19">
-        <f>IF(I19="","",IF(11-MOD(I19,11)&gt;9,0,11-MOD(I19,11)))</f>
-        <v/>
-      </c>
       <c r="K19">
+        <f>IF(J19="","",IF(11-MOD(J19,11)&gt;9,0,11-MOD(J19,11)))</f>
+        <v/>
+      </c>
+      <c r="L19">
         <f>IFERROR(IF(LEN(C19)&lt;&gt;13,"",IF(VALUE(MID(C19,5,3))&gt;=800,1000,2000)+VALUE(MID(C19,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L19">
-        <f>IFERROR(IF(K19="","",IF(AND(DAY(DATE(K19,VALUE(MID(C19,3,2)),VALUE(MID(C19,1,2))))=VALUE(MID(C19,1,2)),MONTH(DATE(K19,VALUE(MID(C19,3,2)),VALUE(MID(C19,1,2))))=VALUE(MID(C19,3,2))),DATE(K19,VALUE(MID(C19,3,2)),VALUE(MID(C19,1,2))),"")),"")</f>
+      <c r="M19">
+        <f>IFERROR(IF(L19="","",IF(AND(DAY(DATE(L19,VALUE(MID(C19,3,2)),VALUE(MID(C19,1,2))))=VALUE(MID(C19,1,2)),MONTH(DATE(L19,VALUE(MID(C19,3,2)),VALUE(MID(C19,1,2))))=VALUE(MID(C19,3,2))),DATE(L19,VALUE(MID(C19,3,2)),VALUE(MID(C19,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1228,27 +1304,31 @@
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="2" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="2" t="n"/>
+      <c r="E20" s="4">
+        <f>IF(A20="","",5)</f>
+        <v/>
+      </c>
+      <c r="F20" s="4" t="n"/>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2">
-        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(J20="","JMBG sadrži nešto što nije cifra",IF(L20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;J20,"Pogrešna kontrolna cifra — treba "&amp;J20,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I20">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2">
+        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(K20="","JMBG sadrži nešto što nije cifra",IF(M20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;K20,"Pogrešna kontrolna cifra — treba "&amp;K20,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J20">
         <f>IFERROR(IF(LEN(C20)&lt;&gt;13,"",7*(VALUE(MID(C20,1,1))+VALUE(MID(C20,7,1)))+6*(VALUE(MID(C20,2,1))+VALUE(MID(C20,8,1)))+5*(VALUE(MID(C20,3,1))+VALUE(MID(C20,9,1)))+4*(VALUE(MID(C20,4,1))+VALUE(MID(C20,10,1)))+3*(VALUE(MID(C20,5,1))+VALUE(MID(C20,11,1)))+2*(VALUE(MID(C20,6,1))+VALUE(MID(C20,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J20">
-        <f>IF(I20="","",IF(11-MOD(I20,11)&gt;9,0,11-MOD(I20,11)))</f>
-        <v/>
-      </c>
       <c r="K20">
+        <f>IF(J20="","",IF(11-MOD(J20,11)&gt;9,0,11-MOD(J20,11)))</f>
+        <v/>
+      </c>
+      <c r="L20">
         <f>IFERROR(IF(LEN(C20)&lt;&gt;13,"",IF(VALUE(MID(C20,5,3))&gt;=800,1000,2000)+VALUE(MID(C20,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L20">
-        <f>IFERROR(IF(K20="","",IF(AND(DAY(DATE(K20,VALUE(MID(C20,3,2)),VALUE(MID(C20,1,2))))=VALUE(MID(C20,1,2)),MONTH(DATE(K20,VALUE(MID(C20,3,2)),VALUE(MID(C20,1,2))))=VALUE(MID(C20,3,2))),DATE(K20,VALUE(MID(C20,3,2)),VALUE(MID(C20,1,2))),"")),"")</f>
+      <c r="M20">
+        <f>IFERROR(IF(L20="","",IF(AND(DAY(DATE(L20,VALUE(MID(C20,3,2)),VALUE(MID(C20,1,2))))=VALUE(MID(C20,1,2)),MONTH(DATE(L20,VALUE(MID(C20,3,2)),VALUE(MID(C20,1,2))))=VALUE(MID(C20,3,2))),DATE(L20,VALUE(MID(C20,3,2)),VALUE(MID(C20,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1257,27 +1337,31 @@
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="2" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="E21" s="4">
+        <f>IF(A21="","",5)</f>
+        <v/>
+      </c>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2">
-        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(J21="","JMBG sadrži nešto što nije cifra",IF(L21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;J21,"Pogrešna kontrolna cifra — treba "&amp;J21,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I21">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2">
+        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(K21="","JMBG sadrži nešto što nije cifra",IF(M21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;K21,"Pogrešna kontrolna cifra — treba "&amp;K21,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J21">
         <f>IFERROR(IF(LEN(C21)&lt;&gt;13,"",7*(VALUE(MID(C21,1,1))+VALUE(MID(C21,7,1)))+6*(VALUE(MID(C21,2,1))+VALUE(MID(C21,8,1)))+5*(VALUE(MID(C21,3,1))+VALUE(MID(C21,9,1)))+4*(VALUE(MID(C21,4,1))+VALUE(MID(C21,10,1)))+3*(VALUE(MID(C21,5,1))+VALUE(MID(C21,11,1)))+2*(VALUE(MID(C21,6,1))+VALUE(MID(C21,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J21">
-        <f>IF(I21="","",IF(11-MOD(I21,11)&gt;9,0,11-MOD(I21,11)))</f>
-        <v/>
-      </c>
       <c r="K21">
+        <f>IF(J21="","",IF(11-MOD(J21,11)&gt;9,0,11-MOD(J21,11)))</f>
+        <v/>
+      </c>
+      <c r="L21">
         <f>IFERROR(IF(LEN(C21)&lt;&gt;13,"",IF(VALUE(MID(C21,5,3))&gt;=800,1000,2000)+VALUE(MID(C21,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L21">
-        <f>IFERROR(IF(K21="","",IF(AND(DAY(DATE(K21,VALUE(MID(C21,3,2)),VALUE(MID(C21,1,2))))=VALUE(MID(C21,1,2)),MONTH(DATE(K21,VALUE(MID(C21,3,2)),VALUE(MID(C21,1,2))))=VALUE(MID(C21,3,2))),DATE(K21,VALUE(MID(C21,3,2)),VALUE(MID(C21,1,2))),"")),"")</f>
+      <c r="M21">
+        <f>IFERROR(IF(L21="","",IF(AND(DAY(DATE(L21,VALUE(MID(C21,3,2)),VALUE(MID(C21,1,2))))=VALUE(MID(C21,1,2)),MONTH(DATE(L21,VALUE(MID(C21,3,2)),VALUE(MID(C21,1,2))))=VALUE(MID(C21,3,2))),DATE(L21,VALUE(MID(C21,3,2)),VALUE(MID(C21,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1286,27 +1370,31 @@
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="2" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="2" t="n"/>
+      <c r="E22" s="4">
+        <f>IF(A22="","",5)</f>
+        <v/>
+      </c>
+      <c r="F22" s="4" t="n"/>
       <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2">
-        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(J22="","JMBG sadrži nešto što nije cifra",IF(L22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;J22,"Pogrešna kontrolna cifra — treba "&amp;J22,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I22">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2">
+        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(K22="","JMBG sadrži nešto što nije cifra",IF(M22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;K22,"Pogrešna kontrolna cifra — treba "&amp;K22,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J22">
         <f>IFERROR(IF(LEN(C22)&lt;&gt;13,"",7*(VALUE(MID(C22,1,1))+VALUE(MID(C22,7,1)))+6*(VALUE(MID(C22,2,1))+VALUE(MID(C22,8,1)))+5*(VALUE(MID(C22,3,1))+VALUE(MID(C22,9,1)))+4*(VALUE(MID(C22,4,1))+VALUE(MID(C22,10,1)))+3*(VALUE(MID(C22,5,1))+VALUE(MID(C22,11,1)))+2*(VALUE(MID(C22,6,1))+VALUE(MID(C22,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J22">
-        <f>IF(I22="","",IF(11-MOD(I22,11)&gt;9,0,11-MOD(I22,11)))</f>
-        <v/>
-      </c>
       <c r="K22">
+        <f>IF(J22="","",IF(11-MOD(J22,11)&gt;9,0,11-MOD(J22,11)))</f>
+        <v/>
+      </c>
+      <c r="L22">
         <f>IFERROR(IF(LEN(C22)&lt;&gt;13,"",IF(VALUE(MID(C22,5,3))&gt;=800,1000,2000)+VALUE(MID(C22,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L22">
-        <f>IFERROR(IF(K22="","",IF(AND(DAY(DATE(K22,VALUE(MID(C22,3,2)),VALUE(MID(C22,1,2))))=VALUE(MID(C22,1,2)),MONTH(DATE(K22,VALUE(MID(C22,3,2)),VALUE(MID(C22,1,2))))=VALUE(MID(C22,3,2))),DATE(K22,VALUE(MID(C22,3,2)),VALUE(MID(C22,1,2))),"")),"")</f>
+      <c r="M22">
+        <f>IFERROR(IF(L22="","",IF(AND(DAY(DATE(L22,VALUE(MID(C22,3,2)),VALUE(MID(C22,1,2))))=VALUE(MID(C22,1,2)),MONTH(DATE(L22,VALUE(MID(C22,3,2)),VALUE(MID(C22,1,2))))=VALUE(MID(C22,3,2))),DATE(L22,VALUE(MID(C22,3,2)),VALUE(MID(C22,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1315,27 +1403,31 @@
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="E23" s="4">
+        <f>IF(A23="","",5)</f>
+        <v/>
+      </c>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2">
-        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(J23="","JMBG sadrži nešto što nije cifra",IF(L23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;J23,"Pogrešna kontrolna cifra — treba "&amp;J23,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I23">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2">
+        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(K23="","JMBG sadrži nešto što nije cifra",IF(M23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;K23,"Pogrešna kontrolna cifra — treba "&amp;K23,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J23">
         <f>IFERROR(IF(LEN(C23)&lt;&gt;13,"",7*(VALUE(MID(C23,1,1))+VALUE(MID(C23,7,1)))+6*(VALUE(MID(C23,2,1))+VALUE(MID(C23,8,1)))+5*(VALUE(MID(C23,3,1))+VALUE(MID(C23,9,1)))+4*(VALUE(MID(C23,4,1))+VALUE(MID(C23,10,1)))+3*(VALUE(MID(C23,5,1))+VALUE(MID(C23,11,1)))+2*(VALUE(MID(C23,6,1))+VALUE(MID(C23,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J23">
-        <f>IF(I23="","",IF(11-MOD(I23,11)&gt;9,0,11-MOD(I23,11)))</f>
-        <v/>
-      </c>
       <c r="K23">
+        <f>IF(J23="","",IF(11-MOD(J23,11)&gt;9,0,11-MOD(J23,11)))</f>
+        <v/>
+      </c>
+      <c r="L23">
         <f>IFERROR(IF(LEN(C23)&lt;&gt;13,"",IF(VALUE(MID(C23,5,3))&gt;=800,1000,2000)+VALUE(MID(C23,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L23">
-        <f>IFERROR(IF(K23="","",IF(AND(DAY(DATE(K23,VALUE(MID(C23,3,2)),VALUE(MID(C23,1,2))))=VALUE(MID(C23,1,2)),MONTH(DATE(K23,VALUE(MID(C23,3,2)),VALUE(MID(C23,1,2))))=VALUE(MID(C23,3,2))),DATE(K23,VALUE(MID(C23,3,2)),VALUE(MID(C23,1,2))),"")),"")</f>
+      <c r="M23">
+        <f>IFERROR(IF(L23="","",IF(AND(DAY(DATE(L23,VALUE(MID(C23,3,2)),VALUE(MID(C23,1,2))))=VALUE(MID(C23,1,2)),MONTH(DATE(L23,VALUE(MID(C23,3,2)),VALUE(MID(C23,1,2))))=VALUE(MID(C23,3,2))),DATE(L23,VALUE(MID(C23,3,2)),VALUE(MID(C23,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1344,27 +1436,31 @@
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="2" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="2" t="n"/>
+      <c r="E24" s="4">
+        <f>IF(A24="","",5)</f>
+        <v/>
+      </c>
+      <c r="F24" s="4" t="n"/>
       <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2">
-        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(J24="","JMBG sadrži nešto što nije cifra",IF(L24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;J24,"Pogrešna kontrolna cifra — treba "&amp;J24,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I24">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2">
+        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(K24="","JMBG sadrži nešto što nije cifra",IF(M24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;K24,"Pogrešna kontrolna cifra — treba "&amp;K24,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J24">
         <f>IFERROR(IF(LEN(C24)&lt;&gt;13,"",7*(VALUE(MID(C24,1,1))+VALUE(MID(C24,7,1)))+6*(VALUE(MID(C24,2,1))+VALUE(MID(C24,8,1)))+5*(VALUE(MID(C24,3,1))+VALUE(MID(C24,9,1)))+4*(VALUE(MID(C24,4,1))+VALUE(MID(C24,10,1)))+3*(VALUE(MID(C24,5,1))+VALUE(MID(C24,11,1)))+2*(VALUE(MID(C24,6,1))+VALUE(MID(C24,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J24">
-        <f>IF(I24="","",IF(11-MOD(I24,11)&gt;9,0,11-MOD(I24,11)))</f>
-        <v/>
-      </c>
       <c r="K24">
+        <f>IF(J24="","",IF(11-MOD(J24,11)&gt;9,0,11-MOD(J24,11)))</f>
+        <v/>
+      </c>
+      <c r="L24">
         <f>IFERROR(IF(LEN(C24)&lt;&gt;13,"",IF(VALUE(MID(C24,5,3))&gt;=800,1000,2000)+VALUE(MID(C24,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L24">
-        <f>IFERROR(IF(K24="","",IF(AND(DAY(DATE(K24,VALUE(MID(C24,3,2)),VALUE(MID(C24,1,2))))=VALUE(MID(C24,1,2)),MONTH(DATE(K24,VALUE(MID(C24,3,2)),VALUE(MID(C24,1,2))))=VALUE(MID(C24,3,2))),DATE(K24,VALUE(MID(C24,3,2)),VALUE(MID(C24,1,2))),"")),"")</f>
+      <c r="M24">
+        <f>IFERROR(IF(L24="","",IF(AND(DAY(DATE(L24,VALUE(MID(C24,3,2)),VALUE(MID(C24,1,2))))=VALUE(MID(C24,1,2)),MONTH(DATE(L24,VALUE(MID(C24,3,2)),VALUE(MID(C24,1,2))))=VALUE(MID(C24,3,2))),DATE(L24,VALUE(MID(C24,3,2)),VALUE(MID(C24,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1373,27 +1469,31 @@
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="2" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="2" t="n"/>
+      <c r="E25" s="4">
+        <f>IF(A25="","",5)</f>
+        <v/>
+      </c>
+      <c r="F25" s="4" t="n"/>
       <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2">
-        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(J25="","JMBG sadrži nešto što nije cifra",IF(L25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;J25,"Pogrešna kontrolna cifra — treba "&amp;J25,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I25">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2">
+        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(K25="","JMBG sadrži nešto što nije cifra",IF(M25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;K25,"Pogrešna kontrolna cifra — treba "&amp;K25,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J25">
         <f>IFERROR(IF(LEN(C25)&lt;&gt;13,"",7*(VALUE(MID(C25,1,1))+VALUE(MID(C25,7,1)))+6*(VALUE(MID(C25,2,1))+VALUE(MID(C25,8,1)))+5*(VALUE(MID(C25,3,1))+VALUE(MID(C25,9,1)))+4*(VALUE(MID(C25,4,1))+VALUE(MID(C25,10,1)))+3*(VALUE(MID(C25,5,1))+VALUE(MID(C25,11,1)))+2*(VALUE(MID(C25,6,1))+VALUE(MID(C25,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J25">
-        <f>IF(I25="","",IF(11-MOD(I25,11)&gt;9,0,11-MOD(I25,11)))</f>
-        <v/>
-      </c>
       <c r="K25">
+        <f>IF(J25="","",IF(11-MOD(J25,11)&gt;9,0,11-MOD(J25,11)))</f>
+        <v/>
+      </c>
+      <c r="L25">
         <f>IFERROR(IF(LEN(C25)&lt;&gt;13,"",IF(VALUE(MID(C25,5,3))&gt;=800,1000,2000)+VALUE(MID(C25,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L25">
-        <f>IFERROR(IF(K25="","",IF(AND(DAY(DATE(K25,VALUE(MID(C25,3,2)),VALUE(MID(C25,1,2))))=VALUE(MID(C25,1,2)),MONTH(DATE(K25,VALUE(MID(C25,3,2)),VALUE(MID(C25,1,2))))=VALUE(MID(C25,3,2))),DATE(K25,VALUE(MID(C25,3,2)),VALUE(MID(C25,1,2))),"")),"")</f>
+      <c r="M25">
+        <f>IFERROR(IF(L25="","",IF(AND(DAY(DATE(L25,VALUE(MID(C25,3,2)),VALUE(MID(C25,1,2))))=VALUE(MID(C25,1,2)),MONTH(DATE(L25,VALUE(MID(C25,3,2)),VALUE(MID(C25,1,2))))=VALUE(MID(C25,3,2))),DATE(L25,VALUE(MID(C25,3,2)),VALUE(MID(C25,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1402,27 +1502,31 @@
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="2" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="E26" s="4">
+        <f>IF(A26="","",5)</f>
+        <v/>
+      </c>
+      <c r="F26" s="4" t="n"/>
       <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2">
-        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(J26="","JMBG sadrži nešto što nije cifra",IF(L26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;J26,"Pogrešna kontrolna cifra — treba "&amp;J26,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I26">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2">
+        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(K26="","JMBG sadrži nešto što nije cifra",IF(M26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;K26,"Pogrešna kontrolna cifra — treba "&amp;K26,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J26">
         <f>IFERROR(IF(LEN(C26)&lt;&gt;13,"",7*(VALUE(MID(C26,1,1))+VALUE(MID(C26,7,1)))+6*(VALUE(MID(C26,2,1))+VALUE(MID(C26,8,1)))+5*(VALUE(MID(C26,3,1))+VALUE(MID(C26,9,1)))+4*(VALUE(MID(C26,4,1))+VALUE(MID(C26,10,1)))+3*(VALUE(MID(C26,5,1))+VALUE(MID(C26,11,1)))+2*(VALUE(MID(C26,6,1))+VALUE(MID(C26,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J26">
-        <f>IF(I26="","",IF(11-MOD(I26,11)&gt;9,0,11-MOD(I26,11)))</f>
-        <v/>
-      </c>
       <c r="K26">
+        <f>IF(J26="","",IF(11-MOD(J26,11)&gt;9,0,11-MOD(J26,11)))</f>
+        <v/>
+      </c>
+      <c r="L26">
         <f>IFERROR(IF(LEN(C26)&lt;&gt;13,"",IF(VALUE(MID(C26,5,3))&gt;=800,1000,2000)+VALUE(MID(C26,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L26">
-        <f>IFERROR(IF(K26="","",IF(AND(DAY(DATE(K26,VALUE(MID(C26,3,2)),VALUE(MID(C26,1,2))))=VALUE(MID(C26,1,2)),MONTH(DATE(K26,VALUE(MID(C26,3,2)),VALUE(MID(C26,1,2))))=VALUE(MID(C26,3,2))),DATE(K26,VALUE(MID(C26,3,2)),VALUE(MID(C26,1,2))),"")),"")</f>
+      <c r="M26">
+        <f>IFERROR(IF(L26="","",IF(AND(DAY(DATE(L26,VALUE(MID(C26,3,2)),VALUE(MID(C26,1,2))))=VALUE(MID(C26,1,2)),MONTH(DATE(L26,VALUE(MID(C26,3,2)),VALUE(MID(C26,1,2))))=VALUE(MID(C26,3,2))),DATE(L26,VALUE(MID(C26,3,2)),VALUE(MID(C26,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1431,27 +1535,31 @@
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="2" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="2" t="n"/>
+      <c r="E27" s="4">
+        <f>IF(A27="","",5)</f>
+        <v/>
+      </c>
+      <c r="F27" s="4" t="n"/>
       <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2">
-        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(J27="","JMBG sadrži nešto što nije cifra",IF(L27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;J27,"Pogrešna kontrolna cifra — treba "&amp;J27,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I27">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2">
+        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(K27="","JMBG sadrži nešto što nije cifra",IF(M27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;K27,"Pogrešna kontrolna cifra — treba "&amp;K27,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J27">
         <f>IFERROR(IF(LEN(C27)&lt;&gt;13,"",7*(VALUE(MID(C27,1,1))+VALUE(MID(C27,7,1)))+6*(VALUE(MID(C27,2,1))+VALUE(MID(C27,8,1)))+5*(VALUE(MID(C27,3,1))+VALUE(MID(C27,9,1)))+4*(VALUE(MID(C27,4,1))+VALUE(MID(C27,10,1)))+3*(VALUE(MID(C27,5,1))+VALUE(MID(C27,11,1)))+2*(VALUE(MID(C27,6,1))+VALUE(MID(C27,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J27">
-        <f>IF(I27="","",IF(11-MOD(I27,11)&gt;9,0,11-MOD(I27,11)))</f>
-        <v/>
-      </c>
       <c r="K27">
+        <f>IF(J27="","",IF(11-MOD(J27,11)&gt;9,0,11-MOD(J27,11)))</f>
+        <v/>
+      </c>
+      <c r="L27">
         <f>IFERROR(IF(LEN(C27)&lt;&gt;13,"",IF(VALUE(MID(C27,5,3))&gt;=800,1000,2000)+VALUE(MID(C27,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L27">
-        <f>IFERROR(IF(K27="","",IF(AND(DAY(DATE(K27,VALUE(MID(C27,3,2)),VALUE(MID(C27,1,2))))=VALUE(MID(C27,1,2)),MONTH(DATE(K27,VALUE(MID(C27,3,2)),VALUE(MID(C27,1,2))))=VALUE(MID(C27,3,2))),DATE(K27,VALUE(MID(C27,3,2)),VALUE(MID(C27,1,2))),"")),"")</f>
+      <c r="M27">
+        <f>IFERROR(IF(L27="","",IF(AND(DAY(DATE(L27,VALUE(MID(C27,3,2)),VALUE(MID(C27,1,2))))=VALUE(MID(C27,1,2)),MONTH(DATE(L27,VALUE(MID(C27,3,2)),VALUE(MID(C27,1,2))))=VALUE(MID(C27,3,2))),DATE(L27,VALUE(MID(C27,3,2)),VALUE(MID(C27,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1460,27 +1568,31 @@
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="2" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="2" t="n"/>
+      <c r="E28" s="4">
+        <f>IF(A28="","",5)</f>
+        <v/>
+      </c>
+      <c r="F28" s="4" t="n"/>
       <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2">
-        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(J28="","JMBG sadrži nešto što nije cifra",IF(L28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;J28,"Pogrešna kontrolna cifra — treba "&amp;J28,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I28">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2">
+        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(K28="","JMBG sadrži nešto što nije cifra",IF(M28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;K28,"Pogrešna kontrolna cifra — treba "&amp;K28,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J28">
         <f>IFERROR(IF(LEN(C28)&lt;&gt;13,"",7*(VALUE(MID(C28,1,1))+VALUE(MID(C28,7,1)))+6*(VALUE(MID(C28,2,1))+VALUE(MID(C28,8,1)))+5*(VALUE(MID(C28,3,1))+VALUE(MID(C28,9,1)))+4*(VALUE(MID(C28,4,1))+VALUE(MID(C28,10,1)))+3*(VALUE(MID(C28,5,1))+VALUE(MID(C28,11,1)))+2*(VALUE(MID(C28,6,1))+VALUE(MID(C28,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J28">
-        <f>IF(I28="","",IF(11-MOD(I28,11)&gt;9,0,11-MOD(I28,11)))</f>
-        <v/>
-      </c>
       <c r="K28">
+        <f>IF(J28="","",IF(11-MOD(J28,11)&gt;9,0,11-MOD(J28,11)))</f>
+        <v/>
+      </c>
+      <c r="L28">
         <f>IFERROR(IF(LEN(C28)&lt;&gt;13,"",IF(VALUE(MID(C28,5,3))&gt;=800,1000,2000)+VALUE(MID(C28,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L28">
-        <f>IFERROR(IF(K28="","",IF(AND(DAY(DATE(K28,VALUE(MID(C28,3,2)),VALUE(MID(C28,1,2))))=VALUE(MID(C28,1,2)),MONTH(DATE(K28,VALUE(MID(C28,3,2)),VALUE(MID(C28,1,2))))=VALUE(MID(C28,3,2))),DATE(K28,VALUE(MID(C28,3,2)),VALUE(MID(C28,1,2))),"")),"")</f>
+      <c r="M28">
+        <f>IFERROR(IF(L28="","",IF(AND(DAY(DATE(L28,VALUE(MID(C28,3,2)),VALUE(MID(C28,1,2))))=VALUE(MID(C28,1,2)),MONTH(DATE(L28,VALUE(MID(C28,3,2)),VALUE(MID(C28,1,2))))=VALUE(MID(C28,3,2))),DATE(L28,VALUE(MID(C28,3,2)),VALUE(MID(C28,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1489,27 +1601,31 @@
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="2" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="2" t="n"/>
+      <c r="E29" s="4">
+        <f>IF(A29="","",5)</f>
+        <v/>
+      </c>
+      <c r="F29" s="4" t="n"/>
       <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2">
-        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(J29="","JMBG sadrži nešto što nije cifra",IF(L29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;J29,"Pogrešna kontrolna cifra — treba "&amp;J29,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I29">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2">
+        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(K29="","JMBG sadrži nešto što nije cifra",IF(M29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;K29,"Pogrešna kontrolna cifra — treba "&amp;K29,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J29">
         <f>IFERROR(IF(LEN(C29)&lt;&gt;13,"",7*(VALUE(MID(C29,1,1))+VALUE(MID(C29,7,1)))+6*(VALUE(MID(C29,2,1))+VALUE(MID(C29,8,1)))+5*(VALUE(MID(C29,3,1))+VALUE(MID(C29,9,1)))+4*(VALUE(MID(C29,4,1))+VALUE(MID(C29,10,1)))+3*(VALUE(MID(C29,5,1))+VALUE(MID(C29,11,1)))+2*(VALUE(MID(C29,6,1))+VALUE(MID(C29,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J29">
-        <f>IF(I29="","",IF(11-MOD(I29,11)&gt;9,0,11-MOD(I29,11)))</f>
-        <v/>
-      </c>
       <c r="K29">
+        <f>IF(J29="","",IF(11-MOD(J29,11)&gt;9,0,11-MOD(J29,11)))</f>
+        <v/>
+      </c>
+      <c r="L29">
         <f>IFERROR(IF(LEN(C29)&lt;&gt;13,"",IF(VALUE(MID(C29,5,3))&gt;=800,1000,2000)+VALUE(MID(C29,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L29">
-        <f>IFERROR(IF(K29="","",IF(AND(DAY(DATE(K29,VALUE(MID(C29,3,2)),VALUE(MID(C29,1,2))))=VALUE(MID(C29,1,2)),MONTH(DATE(K29,VALUE(MID(C29,3,2)),VALUE(MID(C29,1,2))))=VALUE(MID(C29,3,2))),DATE(K29,VALUE(MID(C29,3,2)),VALUE(MID(C29,1,2))),"")),"")</f>
+      <c r="M29">
+        <f>IFERROR(IF(L29="","",IF(AND(DAY(DATE(L29,VALUE(MID(C29,3,2)),VALUE(MID(C29,1,2))))=VALUE(MID(C29,1,2)),MONTH(DATE(L29,VALUE(MID(C29,3,2)),VALUE(MID(C29,1,2))))=VALUE(MID(C29,3,2))),DATE(L29,VALUE(MID(C29,3,2)),VALUE(MID(C29,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1518,27 +1634,31 @@
       <c r="B30" s="2" t="n"/>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="2" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="E30" s="4">
+        <f>IF(A30="","",5)</f>
+        <v/>
+      </c>
+      <c r="F30" s="4" t="n"/>
       <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2">
-        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(J30="","JMBG sadrži nešto što nije cifra",IF(L30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;J30,"Pogrešna kontrolna cifra — treba "&amp;J30,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I30">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2">
+        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(K30="","JMBG sadrži nešto što nije cifra",IF(M30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;K30,"Pogrešna kontrolna cifra — treba "&amp;K30,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J30">
         <f>IFERROR(IF(LEN(C30)&lt;&gt;13,"",7*(VALUE(MID(C30,1,1))+VALUE(MID(C30,7,1)))+6*(VALUE(MID(C30,2,1))+VALUE(MID(C30,8,1)))+5*(VALUE(MID(C30,3,1))+VALUE(MID(C30,9,1)))+4*(VALUE(MID(C30,4,1))+VALUE(MID(C30,10,1)))+3*(VALUE(MID(C30,5,1))+VALUE(MID(C30,11,1)))+2*(VALUE(MID(C30,6,1))+VALUE(MID(C30,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J30">
-        <f>IF(I30="","",IF(11-MOD(I30,11)&gt;9,0,11-MOD(I30,11)))</f>
-        <v/>
-      </c>
       <c r="K30">
+        <f>IF(J30="","",IF(11-MOD(J30,11)&gt;9,0,11-MOD(J30,11)))</f>
+        <v/>
+      </c>
+      <c r="L30">
         <f>IFERROR(IF(LEN(C30)&lt;&gt;13,"",IF(VALUE(MID(C30,5,3))&gt;=800,1000,2000)+VALUE(MID(C30,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L30">
-        <f>IFERROR(IF(K30="","",IF(AND(DAY(DATE(K30,VALUE(MID(C30,3,2)),VALUE(MID(C30,1,2))))=VALUE(MID(C30,1,2)),MONTH(DATE(K30,VALUE(MID(C30,3,2)),VALUE(MID(C30,1,2))))=VALUE(MID(C30,3,2))),DATE(K30,VALUE(MID(C30,3,2)),VALUE(MID(C30,1,2))),"")),"")</f>
+      <c r="M30">
+        <f>IFERROR(IF(L30="","",IF(AND(DAY(DATE(L30,VALUE(MID(C30,3,2)),VALUE(MID(C30,1,2))))=VALUE(MID(C30,1,2)),MONTH(DATE(L30,VALUE(MID(C30,3,2)),VALUE(MID(C30,1,2))))=VALUE(MID(C30,3,2))),DATE(L30,VALUE(MID(C30,3,2)),VALUE(MID(C30,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1547,27 +1667,31 @@
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="2" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="2" t="n"/>
+      <c r="E31" s="4">
+        <f>IF(A31="","",5)</f>
+        <v/>
+      </c>
+      <c r="F31" s="4" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2">
-        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(J31="","JMBG sadrži nešto što nije cifra",IF(L31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;J31,"Pogrešna kontrolna cifra — treba "&amp;J31,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I31">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2">
+        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(K31="","JMBG sadrži nešto što nije cifra",IF(M31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;K31,"Pogrešna kontrolna cifra — treba "&amp;K31,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J31">
         <f>IFERROR(IF(LEN(C31)&lt;&gt;13,"",7*(VALUE(MID(C31,1,1))+VALUE(MID(C31,7,1)))+6*(VALUE(MID(C31,2,1))+VALUE(MID(C31,8,1)))+5*(VALUE(MID(C31,3,1))+VALUE(MID(C31,9,1)))+4*(VALUE(MID(C31,4,1))+VALUE(MID(C31,10,1)))+3*(VALUE(MID(C31,5,1))+VALUE(MID(C31,11,1)))+2*(VALUE(MID(C31,6,1))+VALUE(MID(C31,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J31">
-        <f>IF(I31="","",IF(11-MOD(I31,11)&gt;9,0,11-MOD(I31,11)))</f>
-        <v/>
-      </c>
       <c r="K31">
+        <f>IF(J31="","",IF(11-MOD(J31,11)&gt;9,0,11-MOD(J31,11)))</f>
+        <v/>
+      </c>
+      <c r="L31">
         <f>IFERROR(IF(LEN(C31)&lt;&gt;13,"",IF(VALUE(MID(C31,5,3))&gt;=800,1000,2000)+VALUE(MID(C31,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L31">
-        <f>IFERROR(IF(K31="","",IF(AND(DAY(DATE(K31,VALUE(MID(C31,3,2)),VALUE(MID(C31,1,2))))=VALUE(MID(C31,1,2)),MONTH(DATE(K31,VALUE(MID(C31,3,2)),VALUE(MID(C31,1,2))))=VALUE(MID(C31,3,2))),DATE(K31,VALUE(MID(C31,3,2)),VALUE(MID(C31,1,2))),"")),"")</f>
+      <c r="M31">
+        <f>IFERROR(IF(L31="","",IF(AND(DAY(DATE(L31,VALUE(MID(C31,3,2)),VALUE(MID(C31,1,2))))=VALUE(MID(C31,1,2)),MONTH(DATE(L31,VALUE(MID(C31,3,2)),VALUE(MID(C31,1,2))))=VALUE(MID(C31,3,2))),DATE(L31,VALUE(MID(C31,3,2)),VALUE(MID(C31,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1576,27 +1700,31 @@
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="2" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="2" t="n"/>
+      <c r="E32" s="4">
+        <f>IF(A32="","",5)</f>
+        <v/>
+      </c>
+      <c r="F32" s="4" t="n"/>
       <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2">
-        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(J32="","JMBG sadrži nešto što nije cifra",IF(L32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;J32,"Pogrešna kontrolna cifra — treba "&amp;J32,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I32">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2">
+        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(K32="","JMBG sadrži nešto što nije cifra",IF(M32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;K32,"Pogrešna kontrolna cifra — treba "&amp;K32,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J32">
         <f>IFERROR(IF(LEN(C32)&lt;&gt;13,"",7*(VALUE(MID(C32,1,1))+VALUE(MID(C32,7,1)))+6*(VALUE(MID(C32,2,1))+VALUE(MID(C32,8,1)))+5*(VALUE(MID(C32,3,1))+VALUE(MID(C32,9,1)))+4*(VALUE(MID(C32,4,1))+VALUE(MID(C32,10,1)))+3*(VALUE(MID(C32,5,1))+VALUE(MID(C32,11,1)))+2*(VALUE(MID(C32,6,1))+VALUE(MID(C32,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J32">
-        <f>IF(I32="","",IF(11-MOD(I32,11)&gt;9,0,11-MOD(I32,11)))</f>
-        <v/>
-      </c>
       <c r="K32">
+        <f>IF(J32="","",IF(11-MOD(J32,11)&gt;9,0,11-MOD(J32,11)))</f>
+        <v/>
+      </c>
+      <c r="L32">
         <f>IFERROR(IF(LEN(C32)&lt;&gt;13,"",IF(VALUE(MID(C32,5,3))&gt;=800,1000,2000)+VALUE(MID(C32,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L32">
-        <f>IFERROR(IF(K32="","",IF(AND(DAY(DATE(K32,VALUE(MID(C32,3,2)),VALUE(MID(C32,1,2))))=VALUE(MID(C32,1,2)),MONTH(DATE(K32,VALUE(MID(C32,3,2)),VALUE(MID(C32,1,2))))=VALUE(MID(C32,3,2))),DATE(K32,VALUE(MID(C32,3,2)),VALUE(MID(C32,1,2))),"")),"")</f>
+      <c r="M32">
+        <f>IFERROR(IF(L32="","",IF(AND(DAY(DATE(L32,VALUE(MID(C32,3,2)),VALUE(MID(C32,1,2))))=VALUE(MID(C32,1,2)),MONTH(DATE(L32,VALUE(MID(C32,3,2)),VALUE(MID(C32,1,2))))=VALUE(MID(C32,3,2))),DATE(L32,VALUE(MID(C32,3,2)),VALUE(MID(C32,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1605,27 +1733,31 @@
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="2" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="2" t="n"/>
+      <c r="E33" s="4">
+        <f>IF(A33="","",5)</f>
+        <v/>
+      </c>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2">
-        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(J33="","JMBG sadrži nešto što nije cifra",IF(L33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;J33,"Pogrešna kontrolna cifra — treba "&amp;J33,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I33">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2">
+        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(K33="","JMBG sadrži nešto što nije cifra",IF(M33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;K33,"Pogrešna kontrolna cifra — treba "&amp;K33,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J33">
         <f>IFERROR(IF(LEN(C33)&lt;&gt;13,"",7*(VALUE(MID(C33,1,1))+VALUE(MID(C33,7,1)))+6*(VALUE(MID(C33,2,1))+VALUE(MID(C33,8,1)))+5*(VALUE(MID(C33,3,1))+VALUE(MID(C33,9,1)))+4*(VALUE(MID(C33,4,1))+VALUE(MID(C33,10,1)))+3*(VALUE(MID(C33,5,1))+VALUE(MID(C33,11,1)))+2*(VALUE(MID(C33,6,1))+VALUE(MID(C33,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J33">
-        <f>IF(I33="","",IF(11-MOD(I33,11)&gt;9,0,11-MOD(I33,11)))</f>
-        <v/>
-      </c>
       <c r="K33">
+        <f>IF(J33="","",IF(11-MOD(J33,11)&gt;9,0,11-MOD(J33,11)))</f>
+        <v/>
+      </c>
+      <c r="L33">
         <f>IFERROR(IF(LEN(C33)&lt;&gt;13,"",IF(VALUE(MID(C33,5,3))&gt;=800,1000,2000)+VALUE(MID(C33,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L33">
-        <f>IFERROR(IF(K33="","",IF(AND(DAY(DATE(K33,VALUE(MID(C33,3,2)),VALUE(MID(C33,1,2))))=VALUE(MID(C33,1,2)),MONTH(DATE(K33,VALUE(MID(C33,3,2)),VALUE(MID(C33,1,2))))=VALUE(MID(C33,3,2))),DATE(K33,VALUE(MID(C33,3,2)),VALUE(MID(C33,1,2))),"")),"")</f>
+      <c r="M33">
+        <f>IFERROR(IF(L33="","",IF(AND(DAY(DATE(L33,VALUE(MID(C33,3,2)),VALUE(MID(C33,1,2))))=VALUE(MID(C33,1,2)),MONTH(DATE(L33,VALUE(MID(C33,3,2)),VALUE(MID(C33,1,2))))=VALUE(MID(C33,3,2))),DATE(L33,VALUE(MID(C33,3,2)),VALUE(MID(C33,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1634,27 +1766,31 @@
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="2" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="2" t="n"/>
+      <c r="E34" s="4">
+        <f>IF(A34="","",5)</f>
+        <v/>
+      </c>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2">
-        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(J34="","JMBG sadrži nešto što nije cifra",IF(L34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;J34,"Pogrešna kontrolna cifra — treba "&amp;J34,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I34">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2">
+        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(K34="","JMBG sadrži nešto što nije cifra",IF(M34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;K34,"Pogrešna kontrolna cifra — treba "&amp;K34,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J34">
         <f>IFERROR(IF(LEN(C34)&lt;&gt;13,"",7*(VALUE(MID(C34,1,1))+VALUE(MID(C34,7,1)))+6*(VALUE(MID(C34,2,1))+VALUE(MID(C34,8,1)))+5*(VALUE(MID(C34,3,1))+VALUE(MID(C34,9,1)))+4*(VALUE(MID(C34,4,1))+VALUE(MID(C34,10,1)))+3*(VALUE(MID(C34,5,1))+VALUE(MID(C34,11,1)))+2*(VALUE(MID(C34,6,1))+VALUE(MID(C34,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J34">
-        <f>IF(I34="","",IF(11-MOD(I34,11)&gt;9,0,11-MOD(I34,11)))</f>
-        <v/>
-      </c>
       <c r="K34">
+        <f>IF(J34="","",IF(11-MOD(J34,11)&gt;9,0,11-MOD(J34,11)))</f>
+        <v/>
+      </c>
+      <c r="L34">
         <f>IFERROR(IF(LEN(C34)&lt;&gt;13,"",IF(VALUE(MID(C34,5,3))&gt;=800,1000,2000)+VALUE(MID(C34,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L34">
-        <f>IFERROR(IF(K34="","",IF(AND(DAY(DATE(K34,VALUE(MID(C34,3,2)),VALUE(MID(C34,1,2))))=VALUE(MID(C34,1,2)),MONTH(DATE(K34,VALUE(MID(C34,3,2)),VALUE(MID(C34,1,2))))=VALUE(MID(C34,3,2))),DATE(K34,VALUE(MID(C34,3,2)),VALUE(MID(C34,1,2))),"")),"")</f>
+      <c r="M34">
+        <f>IFERROR(IF(L34="","",IF(AND(DAY(DATE(L34,VALUE(MID(C34,3,2)),VALUE(MID(C34,1,2))))=VALUE(MID(C34,1,2)),MONTH(DATE(L34,VALUE(MID(C34,3,2)),VALUE(MID(C34,1,2))))=VALUE(MID(C34,3,2))),DATE(L34,VALUE(MID(C34,3,2)),VALUE(MID(C34,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1663,27 +1799,31 @@
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="2" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="2" t="n"/>
+      <c r="E35" s="4">
+        <f>IF(A35="","",5)</f>
+        <v/>
+      </c>
+      <c r="F35" s="4" t="n"/>
       <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2">
-        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(J35="","JMBG sadrži nešto što nije cifra",IF(L35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;J35,"Pogrešna kontrolna cifra — treba "&amp;J35,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I35">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2">
+        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(K35="","JMBG sadrži nešto što nije cifra",IF(M35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;K35,"Pogrešna kontrolna cifra — treba "&amp;K35,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J35">
         <f>IFERROR(IF(LEN(C35)&lt;&gt;13,"",7*(VALUE(MID(C35,1,1))+VALUE(MID(C35,7,1)))+6*(VALUE(MID(C35,2,1))+VALUE(MID(C35,8,1)))+5*(VALUE(MID(C35,3,1))+VALUE(MID(C35,9,1)))+4*(VALUE(MID(C35,4,1))+VALUE(MID(C35,10,1)))+3*(VALUE(MID(C35,5,1))+VALUE(MID(C35,11,1)))+2*(VALUE(MID(C35,6,1))+VALUE(MID(C35,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J35">
-        <f>IF(I35="","",IF(11-MOD(I35,11)&gt;9,0,11-MOD(I35,11)))</f>
-        <v/>
-      </c>
       <c r="K35">
+        <f>IF(J35="","",IF(11-MOD(J35,11)&gt;9,0,11-MOD(J35,11)))</f>
+        <v/>
+      </c>
+      <c r="L35">
         <f>IFERROR(IF(LEN(C35)&lt;&gt;13,"",IF(VALUE(MID(C35,5,3))&gt;=800,1000,2000)+VALUE(MID(C35,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L35">
-        <f>IFERROR(IF(K35="","",IF(AND(DAY(DATE(K35,VALUE(MID(C35,3,2)),VALUE(MID(C35,1,2))))=VALUE(MID(C35,1,2)),MONTH(DATE(K35,VALUE(MID(C35,3,2)),VALUE(MID(C35,1,2))))=VALUE(MID(C35,3,2))),DATE(K35,VALUE(MID(C35,3,2)),VALUE(MID(C35,1,2))),"")),"")</f>
+      <c r="M35">
+        <f>IFERROR(IF(L35="","",IF(AND(DAY(DATE(L35,VALUE(MID(C35,3,2)),VALUE(MID(C35,1,2))))=VALUE(MID(C35,1,2)),MONTH(DATE(L35,VALUE(MID(C35,3,2)),VALUE(MID(C35,1,2))))=VALUE(MID(C35,3,2))),DATE(L35,VALUE(MID(C35,3,2)),VALUE(MID(C35,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1692,27 +1832,31 @@
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="2" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="2" t="n"/>
+      <c r="E36" s="4">
+        <f>IF(A36="","",5)</f>
+        <v/>
+      </c>
+      <c r="F36" s="4" t="n"/>
       <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2">
-        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(J36="","JMBG sadrži nešto što nije cifra",IF(L36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;J36,"Pogrešna kontrolna cifra — treba "&amp;J36,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I36">
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2">
+        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(K36="","JMBG sadrži nešto što nije cifra",IF(M36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;K36,"Pogrešna kontrolna cifra — treba "&amp;K36,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J36">
         <f>IFERROR(IF(LEN(C36)&lt;&gt;13,"",7*(VALUE(MID(C36,1,1))+VALUE(MID(C36,7,1)))+6*(VALUE(MID(C36,2,1))+VALUE(MID(C36,8,1)))+5*(VALUE(MID(C36,3,1))+VALUE(MID(C36,9,1)))+4*(VALUE(MID(C36,4,1))+VALUE(MID(C36,10,1)))+3*(VALUE(MID(C36,5,1))+VALUE(MID(C36,11,1)))+2*(VALUE(MID(C36,6,1))+VALUE(MID(C36,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J36">
-        <f>IF(I36="","",IF(11-MOD(I36,11)&gt;9,0,11-MOD(I36,11)))</f>
-        <v/>
-      </c>
       <c r="K36">
+        <f>IF(J36="","",IF(11-MOD(J36,11)&gt;9,0,11-MOD(J36,11)))</f>
+        <v/>
+      </c>
+      <c r="L36">
         <f>IFERROR(IF(LEN(C36)&lt;&gt;13,"",IF(VALUE(MID(C36,5,3))&gt;=800,1000,2000)+VALUE(MID(C36,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L36">
-        <f>IFERROR(IF(K36="","",IF(AND(DAY(DATE(K36,VALUE(MID(C36,3,2)),VALUE(MID(C36,1,2))))=VALUE(MID(C36,1,2)),MONTH(DATE(K36,VALUE(MID(C36,3,2)),VALUE(MID(C36,1,2))))=VALUE(MID(C36,3,2))),DATE(K36,VALUE(MID(C36,3,2)),VALUE(MID(C36,1,2))),"")),"")</f>
+      <c r="M36">
+        <f>IFERROR(IF(L36="","",IF(AND(DAY(DATE(L36,VALUE(MID(C36,3,2)),VALUE(MID(C36,1,2))))=VALUE(MID(C36,1,2)),MONTH(DATE(L36,VALUE(MID(C36,3,2)),VALUE(MID(C36,1,2))))=VALUE(MID(C36,3,2))),DATE(L36,VALUE(MID(C36,3,2)),VALUE(MID(C36,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1721,27 +1865,31 @@
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="2" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="E37" s="4">
+        <f>IF(A37="","",5)</f>
+        <v/>
+      </c>
+      <c r="F37" s="4" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2">
-        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(J37="","JMBG sadrži nešto što nije cifra",IF(L37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;J37,"Pogrešna kontrolna cifra — treba "&amp;J37,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I37">
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2">
+        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(K37="","JMBG sadrži nešto što nije cifra",IF(M37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;K37,"Pogrešna kontrolna cifra — treba "&amp;K37,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J37">
         <f>IFERROR(IF(LEN(C37)&lt;&gt;13,"",7*(VALUE(MID(C37,1,1))+VALUE(MID(C37,7,1)))+6*(VALUE(MID(C37,2,1))+VALUE(MID(C37,8,1)))+5*(VALUE(MID(C37,3,1))+VALUE(MID(C37,9,1)))+4*(VALUE(MID(C37,4,1))+VALUE(MID(C37,10,1)))+3*(VALUE(MID(C37,5,1))+VALUE(MID(C37,11,1)))+2*(VALUE(MID(C37,6,1))+VALUE(MID(C37,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J37">
-        <f>IF(I37="","",IF(11-MOD(I37,11)&gt;9,0,11-MOD(I37,11)))</f>
-        <v/>
-      </c>
       <c r="K37">
+        <f>IF(J37="","",IF(11-MOD(J37,11)&gt;9,0,11-MOD(J37,11)))</f>
+        <v/>
+      </c>
+      <c r="L37">
         <f>IFERROR(IF(LEN(C37)&lt;&gt;13,"",IF(VALUE(MID(C37,5,3))&gt;=800,1000,2000)+VALUE(MID(C37,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L37">
-        <f>IFERROR(IF(K37="","",IF(AND(DAY(DATE(K37,VALUE(MID(C37,3,2)),VALUE(MID(C37,1,2))))=VALUE(MID(C37,1,2)),MONTH(DATE(K37,VALUE(MID(C37,3,2)),VALUE(MID(C37,1,2))))=VALUE(MID(C37,3,2))),DATE(K37,VALUE(MID(C37,3,2)),VALUE(MID(C37,1,2))),"")),"")</f>
+      <c r="M37">
+        <f>IFERROR(IF(L37="","",IF(AND(DAY(DATE(L37,VALUE(MID(C37,3,2)),VALUE(MID(C37,1,2))))=VALUE(MID(C37,1,2)),MONTH(DATE(L37,VALUE(MID(C37,3,2)),VALUE(MID(C37,1,2))))=VALUE(MID(C37,3,2))),DATE(L37,VALUE(MID(C37,3,2)),VALUE(MID(C37,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1750,27 +1898,31 @@
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="2" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="E38" s="4">
+        <f>IF(A38="","",5)</f>
+        <v/>
+      </c>
+      <c r="F38" s="4" t="n"/>
       <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2">
-        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(J38="","JMBG sadrži nešto što nije cifra",IF(L38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;J38,"Pogrešna kontrolna cifra — treba "&amp;J38,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I38">
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2">
+        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(K38="","JMBG sadrži nešto što nije cifra",IF(M38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;K38,"Pogrešna kontrolna cifra — treba "&amp;K38,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J38">
         <f>IFERROR(IF(LEN(C38)&lt;&gt;13,"",7*(VALUE(MID(C38,1,1))+VALUE(MID(C38,7,1)))+6*(VALUE(MID(C38,2,1))+VALUE(MID(C38,8,1)))+5*(VALUE(MID(C38,3,1))+VALUE(MID(C38,9,1)))+4*(VALUE(MID(C38,4,1))+VALUE(MID(C38,10,1)))+3*(VALUE(MID(C38,5,1))+VALUE(MID(C38,11,1)))+2*(VALUE(MID(C38,6,1))+VALUE(MID(C38,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J38">
-        <f>IF(I38="","",IF(11-MOD(I38,11)&gt;9,0,11-MOD(I38,11)))</f>
-        <v/>
-      </c>
       <c r="K38">
+        <f>IF(J38="","",IF(11-MOD(J38,11)&gt;9,0,11-MOD(J38,11)))</f>
+        <v/>
+      </c>
+      <c r="L38">
         <f>IFERROR(IF(LEN(C38)&lt;&gt;13,"",IF(VALUE(MID(C38,5,3))&gt;=800,1000,2000)+VALUE(MID(C38,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L38">
-        <f>IFERROR(IF(K38="","",IF(AND(DAY(DATE(K38,VALUE(MID(C38,3,2)),VALUE(MID(C38,1,2))))=VALUE(MID(C38,1,2)),MONTH(DATE(K38,VALUE(MID(C38,3,2)),VALUE(MID(C38,1,2))))=VALUE(MID(C38,3,2))),DATE(K38,VALUE(MID(C38,3,2)),VALUE(MID(C38,1,2))),"")),"")</f>
+      <c r="M38">
+        <f>IFERROR(IF(L38="","",IF(AND(DAY(DATE(L38,VALUE(MID(C38,3,2)),VALUE(MID(C38,1,2))))=VALUE(MID(C38,1,2)),MONTH(DATE(L38,VALUE(MID(C38,3,2)),VALUE(MID(C38,1,2))))=VALUE(MID(C38,3,2))),DATE(L38,VALUE(MID(C38,3,2)),VALUE(MID(C38,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1779,27 +1931,31 @@
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="2" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="2" t="n"/>
+      <c r="E39" s="4">
+        <f>IF(A39="","",5)</f>
+        <v/>
+      </c>
+      <c r="F39" s="4" t="n"/>
       <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2">
-        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(J39="","JMBG sadrži nešto što nije cifra",IF(L39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;J39,"Pogrešna kontrolna cifra — treba "&amp;J39,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I39">
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2">
+        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(K39="","JMBG sadrži nešto što nije cifra",IF(M39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;K39,"Pogrešna kontrolna cifra — treba "&amp;K39,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J39">
         <f>IFERROR(IF(LEN(C39)&lt;&gt;13,"",7*(VALUE(MID(C39,1,1))+VALUE(MID(C39,7,1)))+6*(VALUE(MID(C39,2,1))+VALUE(MID(C39,8,1)))+5*(VALUE(MID(C39,3,1))+VALUE(MID(C39,9,1)))+4*(VALUE(MID(C39,4,1))+VALUE(MID(C39,10,1)))+3*(VALUE(MID(C39,5,1))+VALUE(MID(C39,11,1)))+2*(VALUE(MID(C39,6,1))+VALUE(MID(C39,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J39">
-        <f>IF(I39="","",IF(11-MOD(I39,11)&gt;9,0,11-MOD(I39,11)))</f>
-        <v/>
-      </c>
       <c r="K39">
+        <f>IF(J39="","",IF(11-MOD(J39,11)&gt;9,0,11-MOD(J39,11)))</f>
+        <v/>
+      </c>
+      <c r="L39">
         <f>IFERROR(IF(LEN(C39)&lt;&gt;13,"",IF(VALUE(MID(C39,5,3))&gt;=800,1000,2000)+VALUE(MID(C39,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L39">
-        <f>IFERROR(IF(K39="","",IF(AND(DAY(DATE(K39,VALUE(MID(C39,3,2)),VALUE(MID(C39,1,2))))=VALUE(MID(C39,1,2)),MONTH(DATE(K39,VALUE(MID(C39,3,2)),VALUE(MID(C39,1,2))))=VALUE(MID(C39,3,2))),DATE(K39,VALUE(MID(C39,3,2)),VALUE(MID(C39,1,2))),"")),"")</f>
+      <c r="M39">
+        <f>IFERROR(IF(L39="","",IF(AND(DAY(DATE(L39,VALUE(MID(C39,3,2)),VALUE(MID(C39,1,2))))=VALUE(MID(C39,1,2)),MONTH(DATE(L39,VALUE(MID(C39,3,2)),VALUE(MID(C39,1,2))))=VALUE(MID(C39,3,2))),DATE(L39,VALUE(MID(C39,3,2)),VALUE(MID(C39,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1808,27 +1964,31 @@
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="2" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="2" t="n"/>
+      <c r="E40" s="4">
+        <f>IF(A40="","",5)</f>
+        <v/>
+      </c>
+      <c r="F40" s="4" t="n"/>
       <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2">
-        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(J40="","JMBG sadrži nešto što nije cifra",IF(L40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;J40,"Pogrešna kontrolna cifra — treba "&amp;J40,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I40">
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2">
+        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(K40="","JMBG sadrži nešto što nije cifra",IF(M40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;K40,"Pogrešna kontrolna cifra — treba "&amp;K40,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J40">
         <f>IFERROR(IF(LEN(C40)&lt;&gt;13,"",7*(VALUE(MID(C40,1,1))+VALUE(MID(C40,7,1)))+6*(VALUE(MID(C40,2,1))+VALUE(MID(C40,8,1)))+5*(VALUE(MID(C40,3,1))+VALUE(MID(C40,9,1)))+4*(VALUE(MID(C40,4,1))+VALUE(MID(C40,10,1)))+3*(VALUE(MID(C40,5,1))+VALUE(MID(C40,11,1)))+2*(VALUE(MID(C40,6,1))+VALUE(MID(C40,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J40">
-        <f>IF(I40="","",IF(11-MOD(I40,11)&gt;9,0,11-MOD(I40,11)))</f>
-        <v/>
-      </c>
       <c r="K40">
+        <f>IF(J40="","",IF(11-MOD(J40,11)&gt;9,0,11-MOD(J40,11)))</f>
+        <v/>
+      </c>
+      <c r="L40">
         <f>IFERROR(IF(LEN(C40)&lt;&gt;13,"",IF(VALUE(MID(C40,5,3))&gt;=800,1000,2000)+VALUE(MID(C40,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L40">
-        <f>IFERROR(IF(K40="","",IF(AND(DAY(DATE(K40,VALUE(MID(C40,3,2)),VALUE(MID(C40,1,2))))=VALUE(MID(C40,1,2)),MONTH(DATE(K40,VALUE(MID(C40,3,2)),VALUE(MID(C40,1,2))))=VALUE(MID(C40,3,2))),DATE(K40,VALUE(MID(C40,3,2)),VALUE(MID(C40,1,2))),"")),"")</f>
+      <c r="M40">
+        <f>IFERROR(IF(L40="","",IF(AND(DAY(DATE(L40,VALUE(MID(C40,3,2)),VALUE(MID(C40,1,2))))=VALUE(MID(C40,1,2)),MONTH(DATE(L40,VALUE(MID(C40,3,2)),VALUE(MID(C40,1,2))))=VALUE(MID(C40,3,2))),DATE(L40,VALUE(MID(C40,3,2)),VALUE(MID(C40,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1837,27 +1997,31 @@
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="2" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="2" t="n"/>
+      <c r="E41" s="4">
+        <f>IF(A41="","",5)</f>
+        <v/>
+      </c>
+      <c r="F41" s="4" t="n"/>
       <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2">
-        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(J41="","JMBG sadrži nešto što nije cifra",IF(L41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;J41,"Pogrešna kontrolna cifra — treba "&amp;J41,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I41">
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2">
+        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(K41="","JMBG sadrži nešto što nije cifra",IF(M41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;K41,"Pogrešna kontrolna cifra — treba "&amp;K41,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J41">
         <f>IFERROR(IF(LEN(C41)&lt;&gt;13,"",7*(VALUE(MID(C41,1,1))+VALUE(MID(C41,7,1)))+6*(VALUE(MID(C41,2,1))+VALUE(MID(C41,8,1)))+5*(VALUE(MID(C41,3,1))+VALUE(MID(C41,9,1)))+4*(VALUE(MID(C41,4,1))+VALUE(MID(C41,10,1)))+3*(VALUE(MID(C41,5,1))+VALUE(MID(C41,11,1)))+2*(VALUE(MID(C41,6,1))+VALUE(MID(C41,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J41">
-        <f>IF(I41="","",IF(11-MOD(I41,11)&gt;9,0,11-MOD(I41,11)))</f>
-        <v/>
-      </c>
       <c r="K41">
+        <f>IF(J41="","",IF(11-MOD(J41,11)&gt;9,0,11-MOD(J41,11)))</f>
+        <v/>
+      </c>
+      <c r="L41">
         <f>IFERROR(IF(LEN(C41)&lt;&gt;13,"",IF(VALUE(MID(C41,5,3))&gt;=800,1000,2000)+VALUE(MID(C41,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L41">
-        <f>IFERROR(IF(K41="","",IF(AND(DAY(DATE(K41,VALUE(MID(C41,3,2)),VALUE(MID(C41,1,2))))=VALUE(MID(C41,1,2)),MONTH(DATE(K41,VALUE(MID(C41,3,2)),VALUE(MID(C41,1,2))))=VALUE(MID(C41,3,2))),DATE(K41,VALUE(MID(C41,3,2)),VALUE(MID(C41,1,2))),"")),"")</f>
+      <c r="M41">
+        <f>IFERROR(IF(L41="","",IF(AND(DAY(DATE(L41,VALUE(MID(C41,3,2)),VALUE(MID(C41,1,2))))=VALUE(MID(C41,1,2)),MONTH(DATE(L41,VALUE(MID(C41,3,2)),VALUE(MID(C41,1,2))))=VALUE(MID(C41,3,2))),DATE(L41,VALUE(MID(C41,3,2)),VALUE(MID(C41,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1866,27 +2030,31 @@
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="2" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="E42" s="4">
+        <f>IF(A42="","",5)</f>
+        <v/>
+      </c>
+      <c r="F42" s="4" t="n"/>
       <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2">
-        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(J42="","JMBG sadrži nešto što nije cifra",IF(L42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;J42,"Pogrešna kontrolna cifra — treba "&amp;J42,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I42">
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2">
+        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(K42="","JMBG sadrži nešto što nije cifra",IF(M42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;K42,"Pogrešna kontrolna cifra — treba "&amp;K42,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J42">
         <f>IFERROR(IF(LEN(C42)&lt;&gt;13,"",7*(VALUE(MID(C42,1,1))+VALUE(MID(C42,7,1)))+6*(VALUE(MID(C42,2,1))+VALUE(MID(C42,8,1)))+5*(VALUE(MID(C42,3,1))+VALUE(MID(C42,9,1)))+4*(VALUE(MID(C42,4,1))+VALUE(MID(C42,10,1)))+3*(VALUE(MID(C42,5,1))+VALUE(MID(C42,11,1)))+2*(VALUE(MID(C42,6,1))+VALUE(MID(C42,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J42">
-        <f>IF(I42="","",IF(11-MOD(I42,11)&gt;9,0,11-MOD(I42,11)))</f>
-        <v/>
-      </c>
       <c r="K42">
+        <f>IF(J42="","",IF(11-MOD(J42,11)&gt;9,0,11-MOD(J42,11)))</f>
+        <v/>
+      </c>
+      <c r="L42">
         <f>IFERROR(IF(LEN(C42)&lt;&gt;13,"",IF(VALUE(MID(C42,5,3))&gt;=800,1000,2000)+VALUE(MID(C42,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L42">
-        <f>IFERROR(IF(K42="","",IF(AND(DAY(DATE(K42,VALUE(MID(C42,3,2)),VALUE(MID(C42,1,2))))=VALUE(MID(C42,1,2)),MONTH(DATE(K42,VALUE(MID(C42,3,2)),VALUE(MID(C42,1,2))))=VALUE(MID(C42,3,2))),DATE(K42,VALUE(MID(C42,3,2)),VALUE(MID(C42,1,2))),"")),"")</f>
+      <c r="M42">
+        <f>IFERROR(IF(L42="","",IF(AND(DAY(DATE(L42,VALUE(MID(C42,3,2)),VALUE(MID(C42,1,2))))=VALUE(MID(C42,1,2)),MONTH(DATE(L42,VALUE(MID(C42,3,2)),VALUE(MID(C42,1,2))))=VALUE(MID(C42,3,2))),DATE(L42,VALUE(MID(C42,3,2)),VALUE(MID(C42,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1895,27 +2063,31 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="2" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="2" t="n"/>
+      <c r="E43" s="4">
+        <f>IF(A43="","",5)</f>
+        <v/>
+      </c>
+      <c r="F43" s="4" t="n"/>
       <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2">
-        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(J43="","JMBG sadrži nešto što nije cifra",IF(L43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;J43,"Pogrešna kontrolna cifra — treba "&amp;J43,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I43">
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2">
+        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(K43="","JMBG sadrži nešto što nije cifra",IF(M43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;K43,"Pogrešna kontrolna cifra — treba "&amp;K43,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J43">
         <f>IFERROR(IF(LEN(C43)&lt;&gt;13,"",7*(VALUE(MID(C43,1,1))+VALUE(MID(C43,7,1)))+6*(VALUE(MID(C43,2,1))+VALUE(MID(C43,8,1)))+5*(VALUE(MID(C43,3,1))+VALUE(MID(C43,9,1)))+4*(VALUE(MID(C43,4,1))+VALUE(MID(C43,10,1)))+3*(VALUE(MID(C43,5,1))+VALUE(MID(C43,11,1)))+2*(VALUE(MID(C43,6,1))+VALUE(MID(C43,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J43">
-        <f>IF(I43="","",IF(11-MOD(I43,11)&gt;9,0,11-MOD(I43,11)))</f>
-        <v/>
-      </c>
       <c r="K43">
+        <f>IF(J43="","",IF(11-MOD(J43,11)&gt;9,0,11-MOD(J43,11)))</f>
+        <v/>
+      </c>
+      <c r="L43">
         <f>IFERROR(IF(LEN(C43)&lt;&gt;13,"",IF(VALUE(MID(C43,5,3))&gt;=800,1000,2000)+VALUE(MID(C43,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L43">
-        <f>IFERROR(IF(K43="","",IF(AND(DAY(DATE(K43,VALUE(MID(C43,3,2)),VALUE(MID(C43,1,2))))=VALUE(MID(C43,1,2)),MONTH(DATE(K43,VALUE(MID(C43,3,2)),VALUE(MID(C43,1,2))))=VALUE(MID(C43,3,2))),DATE(K43,VALUE(MID(C43,3,2)),VALUE(MID(C43,1,2))),"")),"")</f>
+      <c r="M43">
+        <f>IFERROR(IF(L43="","",IF(AND(DAY(DATE(L43,VALUE(MID(C43,3,2)),VALUE(MID(C43,1,2))))=VALUE(MID(C43,1,2)),MONTH(DATE(L43,VALUE(MID(C43,3,2)),VALUE(MID(C43,1,2))))=VALUE(MID(C43,3,2))),DATE(L43,VALUE(MID(C43,3,2)),VALUE(MID(C43,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1924,27 +2096,31 @@
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="2" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="2" t="n"/>
+      <c r="E44" s="4">
+        <f>IF(A44="","",5)</f>
+        <v/>
+      </c>
+      <c r="F44" s="4" t="n"/>
       <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2">
-        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(J44="","JMBG sadrži nešto što nije cifra",IF(L44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;J44,"Pogrešna kontrolna cifra — treba "&amp;J44,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I44">
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2">
+        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(K44="","JMBG sadrži nešto što nije cifra",IF(M44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;K44,"Pogrešna kontrolna cifra — treba "&amp;K44,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J44">
         <f>IFERROR(IF(LEN(C44)&lt;&gt;13,"",7*(VALUE(MID(C44,1,1))+VALUE(MID(C44,7,1)))+6*(VALUE(MID(C44,2,1))+VALUE(MID(C44,8,1)))+5*(VALUE(MID(C44,3,1))+VALUE(MID(C44,9,1)))+4*(VALUE(MID(C44,4,1))+VALUE(MID(C44,10,1)))+3*(VALUE(MID(C44,5,1))+VALUE(MID(C44,11,1)))+2*(VALUE(MID(C44,6,1))+VALUE(MID(C44,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J44">
-        <f>IF(I44="","",IF(11-MOD(I44,11)&gt;9,0,11-MOD(I44,11)))</f>
-        <v/>
-      </c>
       <c r="K44">
+        <f>IF(J44="","",IF(11-MOD(J44,11)&gt;9,0,11-MOD(J44,11)))</f>
+        <v/>
+      </c>
+      <c r="L44">
         <f>IFERROR(IF(LEN(C44)&lt;&gt;13,"",IF(VALUE(MID(C44,5,3))&gt;=800,1000,2000)+VALUE(MID(C44,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L44">
-        <f>IFERROR(IF(K44="","",IF(AND(DAY(DATE(K44,VALUE(MID(C44,3,2)),VALUE(MID(C44,1,2))))=VALUE(MID(C44,1,2)),MONTH(DATE(K44,VALUE(MID(C44,3,2)),VALUE(MID(C44,1,2))))=VALUE(MID(C44,3,2))),DATE(K44,VALUE(MID(C44,3,2)),VALUE(MID(C44,1,2))),"")),"")</f>
+      <c r="M44">
+        <f>IFERROR(IF(L44="","",IF(AND(DAY(DATE(L44,VALUE(MID(C44,3,2)),VALUE(MID(C44,1,2))))=VALUE(MID(C44,1,2)),MONTH(DATE(L44,VALUE(MID(C44,3,2)),VALUE(MID(C44,1,2))))=VALUE(MID(C44,3,2))),DATE(L44,VALUE(MID(C44,3,2)),VALUE(MID(C44,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1953,27 +2129,31 @@
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="2" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="2" t="n"/>
+      <c r="E45" s="4">
+        <f>IF(A45="","",5)</f>
+        <v/>
+      </c>
+      <c r="F45" s="4" t="n"/>
       <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2">
-        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(J45="","JMBG sadrži nešto što nije cifra",IF(L45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;J45,"Pogrešna kontrolna cifra — treba "&amp;J45,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I45">
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2">
+        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(K45="","JMBG sadrži nešto što nije cifra",IF(M45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;K45,"Pogrešna kontrolna cifra — treba "&amp;K45,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J45">
         <f>IFERROR(IF(LEN(C45)&lt;&gt;13,"",7*(VALUE(MID(C45,1,1))+VALUE(MID(C45,7,1)))+6*(VALUE(MID(C45,2,1))+VALUE(MID(C45,8,1)))+5*(VALUE(MID(C45,3,1))+VALUE(MID(C45,9,1)))+4*(VALUE(MID(C45,4,1))+VALUE(MID(C45,10,1)))+3*(VALUE(MID(C45,5,1))+VALUE(MID(C45,11,1)))+2*(VALUE(MID(C45,6,1))+VALUE(MID(C45,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J45">
-        <f>IF(I45="","",IF(11-MOD(I45,11)&gt;9,0,11-MOD(I45,11)))</f>
-        <v/>
-      </c>
       <c r="K45">
+        <f>IF(J45="","",IF(11-MOD(J45,11)&gt;9,0,11-MOD(J45,11)))</f>
+        <v/>
+      </c>
+      <c r="L45">
         <f>IFERROR(IF(LEN(C45)&lt;&gt;13,"",IF(VALUE(MID(C45,5,3))&gt;=800,1000,2000)+VALUE(MID(C45,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L45">
-        <f>IFERROR(IF(K45="","",IF(AND(DAY(DATE(K45,VALUE(MID(C45,3,2)),VALUE(MID(C45,1,2))))=VALUE(MID(C45,1,2)),MONTH(DATE(K45,VALUE(MID(C45,3,2)),VALUE(MID(C45,1,2))))=VALUE(MID(C45,3,2))),DATE(K45,VALUE(MID(C45,3,2)),VALUE(MID(C45,1,2))),"")),"")</f>
+      <c r="M45">
+        <f>IFERROR(IF(L45="","",IF(AND(DAY(DATE(L45,VALUE(MID(C45,3,2)),VALUE(MID(C45,1,2))))=VALUE(MID(C45,1,2)),MONTH(DATE(L45,VALUE(MID(C45,3,2)),VALUE(MID(C45,1,2))))=VALUE(MID(C45,3,2))),DATE(L45,VALUE(MID(C45,3,2)),VALUE(MID(C45,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -1982,27 +2162,31 @@
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="2" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="2" t="n"/>
+      <c r="E46" s="4">
+        <f>IF(A46="","",5)</f>
+        <v/>
+      </c>
+      <c r="F46" s="4" t="n"/>
       <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2">
-        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(J46="","JMBG sadrži nešto što nije cifra",IF(L46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;J46,"Pogrešna kontrolna cifra — treba "&amp;J46,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I46">
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2">
+        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(K46="","JMBG sadrži nešto što nije cifra",IF(M46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;K46,"Pogrešna kontrolna cifra — treba "&amp;K46,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J46">
         <f>IFERROR(IF(LEN(C46)&lt;&gt;13,"",7*(VALUE(MID(C46,1,1))+VALUE(MID(C46,7,1)))+6*(VALUE(MID(C46,2,1))+VALUE(MID(C46,8,1)))+5*(VALUE(MID(C46,3,1))+VALUE(MID(C46,9,1)))+4*(VALUE(MID(C46,4,1))+VALUE(MID(C46,10,1)))+3*(VALUE(MID(C46,5,1))+VALUE(MID(C46,11,1)))+2*(VALUE(MID(C46,6,1))+VALUE(MID(C46,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J46">
-        <f>IF(I46="","",IF(11-MOD(I46,11)&gt;9,0,11-MOD(I46,11)))</f>
-        <v/>
-      </c>
       <c r="K46">
+        <f>IF(J46="","",IF(11-MOD(J46,11)&gt;9,0,11-MOD(J46,11)))</f>
+        <v/>
+      </c>
+      <c r="L46">
         <f>IFERROR(IF(LEN(C46)&lt;&gt;13,"",IF(VALUE(MID(C46,5,3))&gt;=800,1000,2000)+VALUE(MID(C46,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L46">
-        <f>IFERROR(IF(K46="","",IF(AND(DAY(DATE(K46,VALUE(MID(C46,3,2)),VALUE(MID(C46,1,2))))=VALUE(MID(C46,1,2)),MONTH(DATE(K46,VALUE(MID(C46,3,2)),VALUE(MID(C46,1,2))))=VALUE(MID(C46,3,2))),DATE(K46,VALUE(MID(C46,3,2)),VALUE(MID(C46,1,2))),"")),"")</f>
+      <c r="M46">
+        <f>IFERROR(IF(L46="","",IF(AND(DAY(DATE(L46,VALUE(MID(C46,3,2)),VALUE(MID(C46,1,2))))=VALUE(MID(C46,1,2)),MONTH(DATE(L46,VALUE(MID(C46,3,2)),VALUE(MID(C46,1,2))))=VALUE(MID(C46,3,2))),DATE(L46,VALUE(MID(C46,3,2)),VALUE(MID(C46,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2011,27 +2195,31 @@
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="2" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="2" t="n"/>
+      <c r="E47" s="4">
+        <f>IF(A47="","",5)</f>
+        <v/>
+      </c>
+      <c r="F47" s="4" t="n"/>
       <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2">
-        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(J47="","JMBG sadrži nešto što nije cifra",IF(L47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;J47,"Pogrešna kontrolna cifra — treba "&amp;J47,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I47">
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2">
+        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(K47="","JMBG sadrži nešto što nije cifra",IF(M47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;K47,"Pogrešna kontrolna cifra — treba "&amp;K47,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J47">
         <f>IFERROR(IF(LEN(C47)&lt;&gt;13,"",7*(VALUE(MID(C47,1,1))+VALUE(MID(C47,7,1)))+6*(VALUE(MID(C47,2,1))+VALUE(MID(C47,8,1)))+5*(VALUE(MID(C47,3,1))+VALUE(MID(C47,9,1)))+4*(VALUE(MID(C47,4,1))+VALUE(MID(C47,10,1)))+3*(VALUE(MID(C47,5,1))+VALUE(MID(C47,11,1)))+2*(VALUE(MID(C47,6,1))+VALUE(MID(C47,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J47">
-        <f>IF(I47="","",IF(11-MOD(I47,11)&gt;9,0,11-MOD(I47,11)))</f>
-        <v/>
-      </c>
       <c r="K47">
+        <f>IF(J47="","",IF(11-MOD(J47,11)&gt;9,0,11-MOD(J47,11)))</f>
+        <v/>
+      </c>
+      <c r="L47">
         <f>IFERROR(IF(LEN(C47)&lt;&gt;13,"",IF(VALUE(MID(C47,5,3))&gt;=800,1000,2000)+VALUE(MID(C47,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L47">
-        <f>IFERROR(IF(K47="","",IF(AND(DAY(DATE(K47,VALUE(MID(C47,3,2)),VALUE(MID(C47,1,2))))=VALUE(MID(C47,1,2)),MONTH(DATE(K47,VALUE(MID(C47,3,2)),VALUE(MID(C47,1,2))))=VALUE(MID(C47,3,2))),DATE(K47,VALUE(MID(C47,3,2)),VALUE(MID(C47,1,2))),"")),"")</f>
+      <c r="M47">
+        <f>IFERROR(IF(L47="","",IF(AND(DAY(DATE(L47,VALUE(MID(C47,3,2)),VALUE(MID(C47,1,2))))=VALUE(MID(C47,1,2)),MONTH(DATE(L47,VALUE(MID(C47,3,2)),VALUE(MID(C47,1,2))))=VALUE(MID(C47,3,2))),DATE(L47,VALUE(MID(C47,3,2)),VALUE(MID(C47,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2040,27 +2228,31 @@
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="3" t="n"/>
       <c r="D48" s="2" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="2" t="n"/>
+      <c r="E48" s="4">
+        <f>IF(A48="","",5)</f>
+        <v/>
+      </c>
+      <c r="F48" s="4" t="n"/>
       <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2">
-        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(J48="","JMBG sadrži nešto što nije cifra",IF(L48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;J48,"Pogrešna kontrolna cifra — treba "&amp;J48,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I48">
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2">
+        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(K48="","JMBG sadrži nešto što nije cifra",IF(M48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;K48,"Pogrešna kontrolna cifra — treba "&amp;K48,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J48">
         <f>IFERROR(IF(LEN(C48)&lt;&gt;13,"",7*(VALUE(MID(C48,1,1))+VALUE(MID(C48,7,1)))+6*(VALUE(MID(C48,2,1))+VALUE(MID(C48,8,1)))+5*(VALUE(MID(C48,3,1))+VALUE(MID(C48,9,1)))+4*(VALUE(MID(C48,4,1))+VALUE(MID(C48,10,1)))+3*(VALUE(MID(C48,5,1))+VALUE(MID(C48,11,1)))+2*(VALUE(MID(C48,6,1))+VALUE(MID(C48,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J48">
-        <f>IF(I48="","",IF(11-MOD(I48,11)&gt;9,0,11-MOD(I48,11)))</f>
-        <v/>
-      </c>
       <c r="K48">
+        <f>IF(J48="","",IF(11-MOD(J48,11)&gt;9,0,11-MOD(J48,11)))</f>
+        <v/>
+      </c>
+      <c r="L48">
         <f>IFERROR(IF(LEN(C48)&lt;&gt;13,"",IF(VALUE(MID(C48,5,3))&gt;=800,1000,2000)+VALUE(MID(C48,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L48">
-        <f>IFERROR(IF(K48="","",IF(AND(DAY(DATE(K48,VALUE(MID(C48,3,2)),VALUE(MID(C48,1,2))))=VALUE(MID(C48,1,2)),MONTH(DATE(K48,VALUE(MID(C48,3,2)),VALUE(MID(C48,1,2))))=VALUE(MID(C48,3,2))),DATE(K48,VALUE(MID(C48,3,2)),VALUE(MID(C48,1,2))),"")),"")</f>
+      <c r="M48">
+        <f>IFERROR(IF(L48="","",IF(AND(DAY(DATE(L48,VALUE(MID(C48,3,2)),VALUE(MID(C48,1,2))))=VALUE(MID(C48,1,2)),MONTH(DATE(L48,VALUE(MID(C48,3,2)),VALUE(MID(C48,1,2))))=VALUE(MID(C48,3,2))),DATE(L48,VALUE(MID(C48,3,2)),VALUE(MID(C48,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2069,27 +2261,31 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="3" t="n"/>
       <c r="D49" s="2" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="2" t="n"/>
+      <c r="E49" s="4">
+        <f>IF(A49="","",5)</f>
+        <v/>
+      </c>
+      <c r="F49" s="4" t="n"/>
       <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2">
-        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(J49="","JMBG sadrži nešto što nije cifra",IF(L49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;J49,"Pogrešna kontrolna cifra — treba "&amp;J49,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I49">
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2">
+        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(K49="","JMBG sadrži nešto što nije cifra",IF(M49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;K49,"Pogrešna kontrolna cifra — treba "&amp;K49,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J49">
         <f>IFERROR(IF(LEN(C49)&lt;&gt;13,"",7*(VALUE(MID(C49,1,1))+VALUE(MID(C49,7,1)))+6*(VALUE(MID(C49,2,1))+VALUE(MID(C49,8,1)))+5*(VALUE(MID(C49,3,1))+VALUE(MID(C49,9,1)))+4*(VALUE(MID(C49,4,1))+VALUE(MID(C49,10,1)))+3*(VALUE(MID(C49,5,1))+VALUE(MID(C49,11,1)))+2*(VALUE(MID(C49,6,1))+VALUE(MID(C49,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J49">
-        <f>IF(I49="","",IF(11-MOD(I49,11)&gt;9,0,11-MOD(I49,11)))</f>
-        <v/>
-      </c>
       <c r="K49">
+        <f>IF(J49="","",IF(11-MOD(J49,11)&gt;9,0,11-MOD(J49,11)))</f>
+        <v/>
+      </c>
+      <c r="L49">
         <f>IFERROR(IF(LEN(C49)&lt;&gt;13,"",IF(VALUE(MID(C49,5,3))&gt;=800,1000,2000)+VALUE(MID(C49,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L49">
-        <f>IFERROR(IF(K49="","",IF(AND(DAY(DATE(K49,VALUE(MID(C49,3,2)),VALUE(MID(C49,1,2))))=VALUE(MID(C49,1,2)),MONTH(DATE(K49,VALUE(MID(C49,3,2)),VALUE(MID(C49,1,2))))=VALUE(MID(C49,3,2))),DATE(K49,VALUE(MID(C49,3,2)),VALUE(MID(C49,1,2))),"")),"")</f>
+      <c r="M49">
+        <f>IFERROR(IF(L49="","",IF(AND(DAY(DATE(L49,VALUE(MID(C49,3,2)),VALUE(MID(C49,1,2))))=VALUE(MID(C49,1,2)),MONTH(DATE(L49,VALUE(MID(C49,3,2)),VALUE(MID(C49,1,2))))=VALUE(MID(C49,3,2))),DATE(L49,VALUE(MID(C49,3,2)),VALUE(MID(C49,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2098,27 +2294,31 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="3" t="n"/>
       <c r="D50" s="2" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="2" t="n"/>
+      <c r="E50" s="4">
+        <f>IF(A50="","",5)</f>
+        <v/>
+      </c>
+      <c r="F50" s="4" t="n"/>
       <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2">
-        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(J50="","JMBG sadrži nešto što nije cifra",IF(L50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;J50,"Pogrešna kontrolna cifra — treba "&amp;J50,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I50">
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2">
+        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(K50="","JMBG sadrži nešto što nije cifra",IF(M50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;K50,"Pogrešna kontrolna cifra — treba "&amp;K50,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J50">
         <f>IFERROR(IF(LEN(C50)&lt;&gt;13,"",7*(VALUE(MID(C50,1,1))+VALUE(MID(C50,7,1)))+6*(VALUE(MID(C50,2,1))+VALUE(MID(C50,8,1)))+5*(VALUE(MID(C50,3,1))+VALUE(MID(C50,9,1)))+4*(VALUE(MID(C50,4,1))+VALUE(MID(C50,10,1)))+3*(VALUE(MID(C50,5,1))+VALUE(MID(C50,11,1)))+2*(VALUE(MID(C50,6,1))+VALUE(MID(C50,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J50">
-        <f>IF(I50="","",IF(11-MOD(I50,11)&gt;9,0,11-MOD(I50,11)))</f>
-        <v/>
-      </c>
       <c r="K50">
+        <f>IF(J50="","",IF(11-MOD(J50,11)&gt;9,0,11-MOD(J50,11)))</f>
+        <v/>
+      </c>
+      <c r="L50">
         <f>IFERROR(IF(LEN(C50)&lt;&gt;13,"",IF(VALUE(MID(C50,5,3))&gt;=800,1000,2000)+VALUE(MID(C50,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L50">
-        <f>IFERROR(IF(K50="","",IF(AND(DAY(DATE(K50,VALUE(MID(C50,3,2)),VALUE(MID(C50,1,2))))=VALUE(MID(C50,1,2)),MONTH(DATE(K50,VALUE(MID(C50,3,2)),VALUE(MID(C50,1,2))))=VALUE(MID(C50,3,2))),DATE(K50,VALUE(MID(C50,3,2)),VALUE(MID(C50,1,2))),"")),"")</f>
+      <c r="M50">
+        <f>IFERROR(IF(L50="","",IF(AND(DAY(DATE(L50,VALUE(MID(C50,3,2)),VALUE(MID(C50,1,2))))=VALUE(MID(C50,1,2)),MONTH(DATE(L50,VALUE(MID(C50,3,2)),VALUE(MID(C50,1,2))))=VALUE(MID(C50,3,2))),DATE(L50,VALUE(MID(C50,3,2)),VALUE(MID(C50,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2127,27 +2327,31 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="3" t="n"/>
       <c r="D51" s="2" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="2" t="n"/>
+      <c r="E51" s="4">
+        <f>IF(A51="","",5)</f>
+        <v/>
+      </c>
+      <c r="F51" s="4" t="n"/>
       <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2">
-        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(J51="","JMBG sadrži nešto što nije cifra",IF(L51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;J51,"Pogrešna kontrolna cifra — treba "&amp;J51,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I51">
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2">
+        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(K51="","JMBG sadrži nešto što nije cifra",IF(M51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;K51,"Pogrešna kontrolna cifra — treba "&amp;K51,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J51">
         <f>IFERROR(IF(LEN(C51)&lt;&gt;13,"",7*(VALUE(MID(C51,1,1))+VALUE(MID(C51,7,1)))+6*(VALUE(MID(C51,2,1))+VALUE(MID(C51,8,1)))+5*(VALUE(MID(C51,3,1))+VALUE(MID(C51,9,1)))+4*(VALUE(MID(C51,4,1))+VALUE(MID(C51,10,1)))+3*(VALUE(MID(C51,5,1))+VALUE(MID(C51,11,1)))+2*(VALUE(MID(C51,6,1))+VALUE(MID(C51,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J51">
-        <f>IF(I51="","",IF(11-MOD(I51,11)&gt;9,0,11-MOD(I51,11)))</f>
-        <v/>
-      </c>
       <c r="K51">
+        <f>IF(J51="","",IF(11-MOD(J51,11)&gt;9,0,11-MOD(J51,11)))</f>
+        <v/>
+      </c>
+      <c r="L51">
         <f>IFERROR(IF(LEN(C51)&lt;&gt;13,"",IF(VALUE(MID(C51,5,3))&gt;=800,1000,2000)+VALUE(MID(C51,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L51">
-        <f>IFERROR(IF(K51="","",IF(AND(DAY(DATE(K51,VALUE(MID(C51,3,2)),VALUE(MID(C51,1,2))))=VALUE(MID(C51,1,2)),MONTH(DATE(K51,VALUE(MID(C51,3,2)),VALUE(MID(C51,1,2))))=VALUE(MID(C51,3,2))),DATE(K51,VALUE(MID(C51,3,2)),VALUE(MID(C51,1,2))),"")),"")</f>
+      <c r="M51">
+        <f>IFERROR(IF(L51="","",IF(AND(DAY(DATE(L51,VALUE(MID(C51,3,2)),VALUE(MID(C51,1,2))))=VALUE(MID(C51,1,2)),MONTH(DATE(L51,VALUE(MID(C51,3,2)),VALUE(MID(C51,1,2))))=VALUE(MID(C51,3,2))),DATE(L51,VALUE(MID(C51,3,2)),VALUE(MID(C51,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2156,27 +2360,31 @@
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="3" t="n"/>
       <c r="D52" s="2" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="2" t="n"/>
+      <c r="E52" s="4">
+        <f>IF(A52="","",5)</f>
+        <v/>
+      </c>
+      <c r="F52" s="4" t="n"/>
       <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2">
-        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(J52="","JMBG sadrži nešto što nije cifra",IF(L52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;J52,"Pogrešna kontrolna cifra — treba "&amp;J52,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I52">
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2">
+        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(K52="","JMBG sadrži nešto što nije cifra",IF(M52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;K52,"Pogrešna kontrolna cifra — treba "&amp;K52,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J52">
         <f>IFERROR(IF(LEN(C52)&lt;&gt;13,"",7*(VALUE(MID(C52,1,1))+VALUE(MID(C52,7,1)))+6*(VALUE(MID(C52,2,1))+VALUE(MID(C52,8,1)))+5*(VALUE(MID(C52,3,1))+VALUE(MID(C52,9,1)))+4*(VALUE(MID(C52,4,1))+VALUE(MID(C52,10,1)))+3*(VALUE(MID(C52,5,1))+VALUE(MID(C52,11,1)))+2*(VALUE(MID(C52,6,1))+VALUE(MID(C52,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J52">
-        <f>IF(I52="","",IF(11-MOD(I52,11)&gt;9,0,11-MOD(I52,11)))</f>
-        <v/>
-      </c>
       <c r="K52">
+        <f>IF(J52="","",IF(11-MOD(J52,11)&gt;9,0,11-MOD(J52,11)))</f>
+        <v/>
+      </c>
+      <c r="L52">
         <f>IFERROR(IF(LEN(C52)&lt;&gt;13,"",IF(VALUE(MID(C52,5,3))&gt;=800,1000,2000)+VALUE(MID(C52,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L52">
-        <f>IFERROR(IF(K52="","",IF(AND(DAY(DATE(K52,VALUE(MID(C52,3,2)),VALUE(MID(C52,1,2))))=VALUE(MID(C52,1,2)),MONTH(DATE(K52,VALUE(MID(C52,3,2)),VALUE(MID(C52,1,2))))=VALUE(MID(C52,3,2))),DATE(K52,VALUE(MID(C52,3,2)),VALUE(MID(C52,1,2))),"")),"")</f>
+      <c r="M52">
+        <f>IFERROR(IF(L52="","",IF(AND(DAY(DATE(L52,VALUE(MID(C52,3,2)),VALUE(MID(C52,1,2))))=VALUE(MID(C52,1,2)),MONTH(DATE(L52,VALUE(MID(C52,3,2)),VALUE(MID(C52,1,2))))=VALUE(MID(C52,3,2))),DATE(L52,VALUE(MID(C52,3,2)),VALUE(MID(C52,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2185,27 +2393,31 @@
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="3" t="n"/>
       <c r="D53" s="2" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="2" t="n"/>
+      <c r="E53" s="4">
+        <f>IF(A53="","",5)</f>
+        <v/>
+      </c>
+      <c r="F53" s="4" t="n"/>
       <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2">
-        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(J53="","JMBG sadrži nešto što nije cifra",IF(L53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;J53,"Pogrešna kontrolna cifra — treba "&amp;J53,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I53">
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2">
+        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(K53="","JMBG sadrži nešto što nije cifra",IF(M53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;K53,"Pogrešna kontrolna cifra — treba "&amp;K53,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J53">
         <f>IFERROR(IF(LEN(C53)&lt;&gt;13,"",7*(VALUE(MID(C53,1,1))+VALUE(MID(C53,7,1)))+6*(VALUE(MID(C53,2,1))+VALUE(MID(C53,8,1)))+5*(VALUE(MID(C53,3,1))+VALUE(MID(C53,9,1)))+4*(VALUE(MID(C53,4,1))+VALUE(MID(C53,10,1)))+3*(VALUE(MID(C53,5,1))+VALUE(MID(C53,11,1)))+2*(VALUE(MID(C53,6,1))+VALUE(MID(C53,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J53">
-        <f>IF(I53="","",IF(11-MOD(I53,11)&gt;9,0,11-MOD(I53,11)))</f>
-        <v/>
-      </c>
       <c r="K53">
+        <f>IF(J53="","",IF(11-MOD(J53,11)&gt;9,0,11-MOD(J53,11)))</f>
+        <v/>
+      </c>
+      <c r="L53">
         <f>IFERROR(IF(LEN(C53)&lt;&gt;13,"",IF(VALUE(MID(C53,5,3))&gt;=800,1000,2000)+VALUE(MID(C53,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L53">
-        <f>IFERROR(IF(K53="","",IF(AND(DAY(DATE(K53,VALUE(MID(C53,3,2)),VALUE(MID(C53,1,2))))=VALUE(MID(C53,1,2)),MONTH(DATE(K53,VALUE(MID(C53,3,2)),VALUE(MID(C53,1,2))))=VALUE(MID(C53,3,2))),DATE(K53,VALUE(MID(C53,3,2)),VALUE(MID(C53,1,2))),"")),"")</f>
+      <c r="M53">
+        <f>IFERROR(IF(L53="","",IF(AND(DAY(DATE(L53,VALUE(MID(C53,3,2)),VALUE(MID(C53,1,2))))=VALUE(MID(C53,1,2)),MONTH(DATE(L53,VALUE(MID(C53,3,2)),VALUE(MID(C53,1,2))))=VALUE(MID(C53,3,2))),DATE(L53,VALUE(MID(C53,3,2)),VALUE(MID(C53,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2214,27 +2426,31 @@
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="3" t="n"/>
       <c r="D54" s="2" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="2" t="n"/>
+      <c r="E54" s="4">
+        <f>IF(A54="","",5)</f>
+        <v/>
+      </c>
+      <c r="F54" s="4" t="n"/>
       <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2">
-        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(J54="","JMBG sadrži nešto što nije cifra",IF(L54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;J54,"Pogrešna kontrolna cifra — treba "&amp;J54,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I54">
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2">
+        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(K54="","JMBG sadrži nešto što nije cifra",IF(M54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;K54,"Pogrešna kontrolna cifra — treba "&amp;K54,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J54">
         <f>IFERROR(IF(LEN(C54)&lt;&gt;13,"",7*(VALUE(MID(C54,1,1))+VALUE(MID(C54,7,1)))+6*(VALUE(MID(C54,2,1))+VALUE(MID(C54,8,1)))+5*(VALUE(MID(C54,3,1))+VALUE(MID(C54,9,1)))+4*(VALUE(MID(C54,4,1))+VALUE(MID(C54,10,1)))+3*(VALUE(MID(C54,5,1))+VALUE(MID(C54,11,1)))+2*(VALUE(MID(C54,6,1))+VALUE(MID(C54,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J54">
-        <f>IF(I54="","",IF(11-MOD(I54,11)&gt;9,0,11-MOD(I54,11)))</f>
-        <v/>
-      </c>
       <c r="K54">
+        <f>IF(J54="","",IF(11-MOD(J54,11)&gt;9,0,11-MOD(J54,11)))</f>
+        <v/>
+      </c>
+      <c r="L54">
         <f>IFERROR(IF(LEN(C54)&lt;&gt;13,"",IF(VALUE(MID(C54,5,3))&gt;=800,1000,2000)+VALUE(MID(C54,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L54">
-        <f>IFERROR(IF(K54="","",IF(AND(DAY(DATE(K54,VALUE(MID(C54,3,2)),VALUE(MID(C54,1,2))))=VALUE(MID(C54,1,2)),MONTH(DATE(K54,VALUE(MID(C54,3,2)),VALUE(MID(C54,1,2))))=VALUE(MID(C54,3,2))),DATE(K54,VALUE(MID(C54,3,2)),VALUE(MID(C54,1,2))),"")),"")</f>
+      <c r="M54">
+        <f>IFERROR(IF(L54="","",IF(AND(DAY(DATE(L54,VALUE(MID(C54,3,2)),VALUE(MID(C54,1,2))))=VALUE(MID(C54,1,2)),MONTH(DATE(L54,VALUE(MID(C54,3,2)),VALUE(MID(C54,1,2))))=VALUE(MID(C54,3,2))),DATE(L54,VALUE(MID(C54,3,2)),VALUE(MID(C54,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2243,27 +2459,31 @@
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="3" t="n"/>
       <c r="D55" s="2" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="2" t="n"/>
+      <c r="E55" s="4">
+        <f>IF(A55="","",5)</f>
+        <v/>
+      </c>
+      <c r="F55" s="4" t="n"/>
       <c r="G55" s="2" t="n"/>
-      <c r="H55" s="2">
-        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(J55="","JMBG sadrži nešto što nije cifra",IF(L55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;J55,"Pogrešna kontrolna cifra — treba "&amp;J55,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I55">
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2">
+        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(K55="","JMBG sadrži nešto što nije cifra",IF(M55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;K55,"Pogrešna kontrolna cifra — treba "&amp;K55,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J55">
         <f>IFERROR(IF(LEN(C55)&lt;&gt;13,"",7*(VALUE(MID(C55,1,1))+VALUE(MID(C55,7,1)))+6*(VALUE(MID(C55,2,1))+VALUE(MID(C55,8,1)))+5*(VALUE(MID(C55,3,1))+VALUE(MID(C55,9,1)))+4*(VALUE(MID(C55,4,1))+VALUE(MID(C55,10,1)))+3*(VALUE(MID(C55,5,1))+VALUE(MID(C55,11,1)))+2*(VALUE(MID(C55,6,1))+VALUE(MID(C55,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J55">
-        <f>IF(I55="","",IF(11-MOD(I55,11)&gt;9,0,11-MOD(I55,11)))</f>
-        <v/>
-      </c>
       <c r="K55">
+        <f>IF(J55="","",IF(11-MOD(J55,11)&gt;9,0,11-MOD(J55,11)))</f>
+        <v/>
+      </c>
+      <c r="L55">
         <f>IFERROR(IF(LEN(C55)&lt;&gt;13,"",IF(VALUE(MID(C55,5,3))&gt;=800,1000,2000)+VALUE(MID(C55,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L55">
-        <f>IFERROR(IF(K55="","",IF(AND(DAY(DATE(K55,VALUE(MID(C55,3,2)),VALUE(MID(C55,1,2))))=VALUE(MID(C55,1,2)),MONTH(DATE(K55,VALUE(MID(C55,3,2)),VALUE(MID(C55,1,2))))=VALUE(MID(C55,3,2))),DATE(K55,VALUE(MID(C55,3,2)),VALUE(MID(C55,1,2))),"")),"")</f>
+      <c r="M55">
+        <f>IFERROR(IF(L55="","",IF(AND(DAY(DATE(L55,VALUE(MID(C55,3,2)),VALUE(MID(C55,1,2))))=VALUE(MID(C55,1,2)),MONTH(DATE(L55,VALUE(MID(C55,3,2)),VALUE(MID(C55,1,2))))=VALUE(MID(C55,3,2))),DATE(L55,VALUE(MID(C55,3,2)),VALUE(MID(C55,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2272,27 +2492,31 @@
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="3" t="n"/>
       <c r="D56" s="2" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="2" t="n"/>
+      <c r="E56" s="4">
+        <f>IF(A56="","",5)</f>
+        <v/>
+      </c>
+      <c r="F56" s="4" t="n"/>
       <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2">
-        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(J56="","JMBG sadrži nešto što nije cifra",IF(L56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;J56,"Pogrešna kontrolna cifra — treba "&amp;J56,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I56">
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2">
+        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(K56="","JMBG sadrži nešto što nije cifra",IF(M56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;K56,"Pogrešna kontrolna cifra — treba "&amp;K56,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J56">
         <f>IFERROR(IF(LEN(C56)&lt;&gt;13,"",7*(VALUE(MID(C56,1,1))+VALUE(MID(C56,7,1)))+6*(VALUE(MID(C56,2,1))+VALUE(MID(C56,8,1)))+5*(VALUE(MID(C56,3,1))+VALUE(MID(C56,9,1)))+4*(VALUE(MID(C56,4,1))+VALUE(MID(C56,10,1)))+3*(VALUE(MID(C56,5,1))+VALUE(MID(C56,11,1)))+2*(VALUE(MID(C56,6,1))+VALUE(MID(C56,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J56">
-        <f>IF(I56="","",IF(11-MOD(I56,11)&gt;9,0,11-MOD(I56,11)))</f>
-        <v/>
-      </c>
       <c r="K56">
+        <f>IF(J56="","",IF(11-MOD(J56,11)&gt;9,0,11-MOD(J56,11)))</f>
+        <v/>
+      </c>
+      <c r="L56">
         <f>IFERROR(IF(LEN(C56)&lt;&gt;13,"",IF(VALUE(MID(C56,5,3))&gt;=800,1000,2000)+VALUE(MID(C56,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L56">
-        <f>IFERROR(IF(K56="","",IF(AND(DAY(DATE(K56,VALUE(MID(C56,3,2)),VALUE(MID(C56,1,2))))=VALUE(MID(C56,1,2)),MONTH(DATE(K56,VALUE(MID(C56,3,2)),VALUE(MID(C56,1,2))))=VALUE(MID(C56,3,2))),DATE(K56,VALUE(MID(C56,3,2)),VALUE(MID(C56,1,2))),"")),"")</f>
+      <c r="M56">
+        <f>IFERROR(IF(L56="","",IF(AND(DAY(DATE(L56,VALUE(MID(C56,3,2)),VALUE(MID(C56,1,2))))=VALUE(MID(C56,1,2)),MONTH(DATE(L56,VALUE(MID(C56,3,2)),VALUE(MID(C56,1,2))))=VALUE(MID(C56,3,2))),DATE(L56,VALUE(MID(C56,3,2)),VALUE(MID(C56,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2301,27 +2525,31 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="3" t="n"/>
       <c r="D57" s="2" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="2" t="n"/>
+      <c r="E57" s="4">
+        <f>IF(A57="","",5)</f>
+        <v/>
+      </c>
+      <c r="F57" s="4" t="n"/>
       <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2">
-        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(J57="","JMBG sadrži nešto što nije cifra",IF(L57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;J57,"Pogrešna kontrolna cifra — treba "&amp;J57,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I57">
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2">
+        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(K57="","JMBG sadrži nešto što nije cifra",IF(M57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;K57,"Pogrešna kontrolna cifra — treba "&amp;K57,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J57">
         <f>IFERROR(IF(LEN(C57)&lt;&gt;13,"",7*(VALUE(MID(C57,1,1))+VALUE(MID(C57,7,1)))+6*(VALUE(MID(C57,2,1))+VALUE(MID(C57,8,1)))+5*(VALUE(MID(C57,3,1))+VALUE(MID(C57,9,1)))+4*(VALUE(MID(C57,4,1))+VALUE(MID(C57,10,1)))+3*(VALUE(MID(C57,5,1))+VALUE(MID(C57,11,1)))+2*(VALUE(MID(C57,6,1))+VALUE(MID(C57,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J57">
-        <f>IF(I57="","",IF(11-MOD(I57,11)&gt;9,0,11-MOD(I57,11)))</f>
-        <v/>
-      </c>
       <c r="K57">
+        <f>IF(J57="","",IF(11-MOD(J57,11)&gt;9,0,11-MOD(J57,11)))</f>
+        <v/>
+      </c>
+      <c r="L57">
         <f>IFERROR(IF(LEN(C57)&lt;&gt;13,"",IF(VALUE(MID(C57,5,3))&gt;=800,1000,2000)+VALUE(MID(C57,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L57">
-        <f>IFERROR(IF(K57="","",IF(AND(DAY(DATE(K57,VALUE(MID(C57,3,2)),VALUE(MID(C57,1,2))))=VALUE(MID(C57,1,2)),MONTH(DATE(K57,VALUE(MID(C57,3,2)),VALUE(MID(C57,1,2))))=VALUE(MID(C57,3,2))),DATE(K57,VALUE(MID(C57,3,2)),VALUE(MID(C57,1,2))),"")),"")</f>
+      <c r="M57">
+        <f>IFERROR(IF(L57="","",IF(AND(DAY(DATE(L57,VALUE(MID(C57,3,2)),VALUE(MID(C57,1,2))))=VALUE(MID(C57,1,2)),MONTH(DATE(L57,VALUE(MID(C57,3,2)),VALUE(MID(C57,1,2))))=VALUE(MID(C57,3,2))),DATE(L57,VALUE(MID(C57,3,2)),VALUE(MID(C57,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2330,27 +2558,31 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="3" t="n"/>
       <c r="D58" s="2" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="2" t="n"/>
+      <c r="E58" s="4">
+        <f>IF(A58="","",5)</f>
+        <v/>
+      </c>
+      <c r="F58" s="4" t="n"/>
       <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2">
-        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(J58="","JMBG sadrži nešto što nije cifra",IF(L58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;J58,"Pogrešna kontrolna cifra — treba "&amp;J58,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I58">
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2">
+        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(K58="","JMBG sadrži nešto što nije cifra",IF(M58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;K58,"Pogrešna kontrolna cifra — treba "&amp;K58,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J58">
         <f>IFERROR(IF(LEN(C58)&lt;&gt;13,"",7*(VALUE(MID(C58,1,1))+VALUE(MID(C58,7,1)))+6*(VALUE(MID(C58,2,1))+VALUE(MID(C58,8,1)))+5*(VALUE(MID(C58,3,1))+VALUE(MID(C58,9,1)))+4*(VALUE(MID(C58,4,1))+VALUE(MID(C58,10,1)))+3*(VALUE(MID(C58,5,1))+VALUE(MID(C58,11,1)))+2*(VALUE(MID(C58,6,1))+VALUE(MID(C58,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J58">
-        <f>IF(I58="","",IF(11-MOD(I58,11)&gt;9,0,11-MOD(I58,11)))</f>
-        <v/>
-      </c>
       <c r="K58">
+        <f>IF(J58="","",IF(11-MOD(J58,11)&gt;9,0,11-MOD(J58,11)))</f>
+        <v/>
+      </c>
+      <c r="L58">
         <f>IFERROR(IF(LEN(C58)&lt;&gt;13,"",IF(VALUE(MID(C58,5,3))&gt;=800,1000,2000)+VALUE(MID(C58,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L58">
-        <f>IFERROR(IF(K58="","",IF(AND(DAY(DATE(K58,VALUE(MID(C58,3,2)),VALUE(MID(C58,1,2))))=VALUE(MID(C58,1,2)),MONTH(DATE(K58,VALUE(MID(C58,3,2)),VALUE(MID(C58,1,2))))=VALUE(MID(C58,3,2))),DATE(K58,VALUE(MID(C58,3,2)),VALUE(MID(C58,1,2))),"")),"")</f>
+      <c r="M58">
+        <f>IFERROR(IF(L58="","",IF(AND(DAY(DATE(L58,VALUE(MID(C58,3,2)),VALUE(MID(C58,1,2))))=VALUE(MID(C58,1,2)),MONTH(DATE(L58,VALUE(MID(C58,3,2)),VALUE(MID(C58,1,2))))=VALUE(MID(C58,3,2))),DATE(L58,VALUE(MID(C58,3,2)),VALUE(MID(C58,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2359,27 +2591,31 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="3" t="n"/>
       <c r="D59" s="2" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="2" t="n"/>
+      <c r="E59" s="4">
+        <f>IF(A59="","",5)</f>
+        <v/>
+      </c>
+      <c r="F59" s="4" t="n"/>
       <c r="G59" s="2" t="n"/>
-      <c r="H59" s="2">
-        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(J59="","JMBG sadrži nešto što nije cifra",IF(L59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;J59,"Pogrešna kontrolna cifra — treba "&amp;J59,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I59">
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2">
+        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(K59="","JMBG sadrži nešto što nije cifra",IF(M59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;K59,"Pogrešna kontrolna cifra — treba "&amp;K59,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J59">
         <f>IFERROR(IF(LEN(C59)&lt;&gt;13,"",7*(VALUE(MID(C59,1,1))+VALUE(MID(C59,7,1)))+6*(VALUE(MID(C59,2,1))+VALUE(MID(C59,8,1)))+5*(VALUE(MID(C59,3,1))+VALUE(MID(C59,9,1)))+4*(VALUE(MID(C59,4,1))+VALUE(MID(C59,10,1)))+3*(VALUE(MID(C59,5,1))+VALUE(MID(C59,11,1)))+2*(VALUE(MID(C59,6,1))+VALUE(MID(C59,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J59">
-        <f>IF(I59="","",IF(11-MOD(I59,11)&gt;9,0,11-MOD(I59,11)))</f>
-        <v/>
-      </c>
       <c r="K59">
+        <f>IF(J59="","",IF(11-MOD(J59,11)&gt;9,0,11-MOD(J59,11)))</f>
+        <v/>
+      </c>
+      <c r="L59">
         <f>IFERROR(IF(LEN(C59)&lt;&gt;13,"",IF(VALUE(MID(C59,5,3))&gt;=800,1000,2000)+VALUE(MID(C59,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L59">
-        <f>IFERROR(IF(K59="","",IF(AND(DAY(DATE(K59,VALUE(MID(C59,3,2)),VALUE(MID(C59,1,2))))=VALUE(MID(C59,1,2)),MONTH(DATE(K59,VALUE(MID(C59,3,2)),VALUE(MID(C59,1,2))))=VALUE(MID(C59,3,2))),DATE(K59,VALUE(MID(C59,3,2)),VALUE(MID(C59,1,2))),"")),"")</f>
+      <c r="M59">
+        <f>IFERROR(IF(L59="","",IF(AND(DAY(DATE(L59,VALUE(MID(C59,3,2)),VALUE(MID(C59,1,2))))=VALUE(MID(C59,1,2)),MONTH(DATE(L59,VALUE(MID(C59,3,2)),VALUE(MID(C59,1,2))))=VALUE(MID(C59,3,2))),DATE(L59,VALUE(MID(C59,3,2)),VALUE(MID(C59,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2388,27 +2624,31 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="3" t="n"/>
       <c r="D60" s="2" t="n"/>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="2" t="n"/>
+      <c r="E60" s="4">
+        <f>IF(A60="","",5)</f>
+        <v/>
+      </c>
+      <c r="F60" s="4" t="n"/>
       <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2">
-        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(J60="","JMBG sadrži nešto što nije cifra",IF(L60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;J60,"Pogrešna kontrolna cifra — treba "&amp;J60,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I60">
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2">
+        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(K60="","JMBG sadrži nešto što nije cifra",IF(M60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;K60,"Pogrešna kontrolna cifra — treba "&amp;K60,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J60">
         <f>IFERROR(IF(LEN(C60)&lt;&gt;13,"",7*(VALUE(MID(C60,1,1))+VALUE(MID(C60,7,1)))+6*(VALUE(MID(C60,2,1))+VALUE(MID(C60,8,1)))+5*(VALUE(MID(C60,3,1))+VALUE(MID(C60,9,1)))+4*(VALUE(MID(C60,4,1))+VALUE(MID(C60,10,1)))+3*(VALUE(MID(C60,5,1))+VALUE(MID(C60,11,1)))+2*(VALUE(MID(C60,6,1))+VALUE(MID(C60,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J60">
-        <f>IF(I60="","",IF(11-MOD(I60,11)&gt;9,0,11-MOD(I60,11)))</f>
-        <v/>
-      </c>
       <c r="K60">
+        <f>IF(J60="","",IF(11-MOD(J60,11)&gt;9,0,11-MOD(J60,11)))</f>
+        <v/>
+      </c>
+      <c r="L60">
         <f>IFERROR(IF(LEN(C60)&lt;&gt;13,"",IF(VALUE(MID(C60,5,3))&gt;=800,1000,2000)+VALUE(MID(C60,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L60">
-        <f>IFERROR(IF(K60="","",IF(AND(DAY(DATE(K60,VALUE(MID(C60,3,2)),VALUE(MID(C60,1,2))))=VALUE(MID(C60,1,2)),MONTH(DATE(K60,VALUE(MID(C60,3,2)),VALUE(MID(C60,1,2))))=VALUE(MID(C60,3,2))),DATE(K60,VALUE(MID(C60,3,2)),VALUE(MID(C60,1,2))),"")),"")</f>
+      <c r="M60">
+        <f>IFERROR(IF(L60="","",IF(AND(DAY(DATE(L60,VALUE(MID(C60,3,2)),VALUE(MID(C60,1,2))))=VALUE(MID(C60,1,2)),MONTH(DATE(L60,VALUE(MID(C60,3,2)),VALUE(MID(C60,1,2))))=VALUE(MID(C60,3,2))),DATE(L60,VALUE(MID(C60,3,2)),VALUE(MID(C60,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2417,27 +2657,31 @@
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="3" t="n"/>
       <c r="D61" s="2" t="n"/>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="2" t="n"/>
+      <c r="E61" s="4">
+        <f>IF(A61="","",5)</f>
+        <v/>
+      </c>
+      <c r="F61" s="4" t="n"/>
       <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2">
-        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(J61="","JMBG sadrži nešto što nije cifra",IF(L61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;J61,"Pogrešna kontrolna cifra — treba "&amp;J61,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I61">
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2">
+        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(K61="","JMBG sadrži nešto što nije cifra",IF(M61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;K61,"Pogrešna kontrolna cifra — treba "&amp;K61,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J61">
         <f>IFERROR(IF(LEN(C61)&lt;&gt;13,"",7*(VALUE(MID(C61,1,1))+VALUE(MID(C61,7,1)))+6*(VALUE(MID(C61,2,1))+VALUE(MID(C61,8,1)))+5*(VALUE(MID(C61,3,1))+VALUE(MID(C61,9,1)))+4*(VALUE(MID(C61,4,1))+VALUE(MID(C61,10,1)))+3*(VALUE(MID(C61,5,1))+VALUE(MID(C61,11,1)))+2*(VALUE(MID(C61,6,1))+VALUE(MID(C61,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J61">
-        <f>IF(I61="","",IF(11-MOD(I61,11)&gt;9,0,11-MOD(I61,11)))</f>
-        <v/>
-      </c>
       <c r="K61">
+        <f>IF(J61="","",IF(11-MOD(J61,11)&gt;9,0,11-MOD(J61,11)))</f>
+        <v/>
+      </c>
+      <c r="L61">
         <f>IFERROR(IF(LEN(C61)&lt;&gt;13,"",IF(VALUE(MID(C61,5,3))&gt;=800,1000,2000)+VALUE(MID(C61,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L61">
-        <f>IFERROR(IF(K61="","",IF(AND(DAY(DATE(K61,VALUE(MID(C61,3,2)),VALUE(MID(C61,1,2))))=VALUE(MID(C61,1,2)),MONTH(DATE(K61,VALUE(MID(C61,3,2)),VALUE(MID(C61,1,2))))=VALUE(MID(C61,3,2))),DATE(K61,VALUE(MID(C61,3,2)),VALUE(MID(C61,1,2))),"")),"")</f>
+      <c r="M61">
+        <f>IFERROR(IF(L61="","",IF(AND(DAY(DATE(L61,VALUE(MID(C61,3,2)),VALUE(MID(C61,1,2))))=VALUE(MID(C61,1,2)),MONTH(DATE(L61,VALUE(MID(C61,3,2)),VALUE(MID(C61,1,2))))=VALUE(MID(C61,3,2))),DATE(L61,VALUE(MID(C61,3,2)),VALUE(MID(C61,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2446,27 +2690,31 @@
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="3" t="n"/>
       <c r="D62" s="2" t="n"/>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="2" t="n"/>
+      <c r="E62" s="4">
+        <f>IF(A62="","",5)</f>
+        <v/>
+      </c>
+      <c r="F62" s="4" t="n"/>
       <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2">
-        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(J62="","JMBG sadrži nešto što nije cifra",IF(L62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;J62,"Pogrešna kontrolna cifra — treba "&amp;J62,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I62">
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2">
+        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(K62="","JMBG sadrži nešto što nije cifra",IF(M62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;K62,"Pogrešna kontrolna cifra — treba "&amp;K62,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J62">
         <f>IFERROR(IF(LEN(C62)&lt;&gt;13,"",7*(VALUE(MID(C62,1,1))+VALUE(MID(C62,7,1)))+6*(VALUE(MID(C62,2,1))+VALUE(MID(C62,8,1)))+5*(VALUE(MID(C62,3,1))+VALUE(MID(C62,9,1)))+4*(VALUE(MID(C62,4,1))+VALUE(MID(C62,10,1)))+3*(VALUE(MID(C62,5,1))+VALUE(MID(C62,11,1)))+2*(VALUE(MID(C62,6,1))+VALUE(MID(C62,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J62">
-        <f>IF(I62="","",IF(11-MOD(I62,11)&gt;9,0,11-MOD(I62,11)))</f>
-        <v/>
-      </c>
       <c r="K62">
+        <f>IF(J62="","",IF(11-MOD(J62,11)&gt;9,0,11-MOD(J62,11)))</f>
+        <v/>
+      </c>
+      <c r="L62">
         <f>IFERROR(IF(LEN(C62)&lt;&gt;13,"",IF(VALUE(MID(C62,5,3))&gt;=800,1000,2000)+VALUE(MID(C62,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L62">
-        <f>IFERROR(IF(K62="","",IF(AND(DAY(DATE(K62,VALUE(MID(C62,3,2)),VALUE(MID(C62,1,2))))=VALUE(MID(C62,1,2)),MONTH(DATE(K62,VALUE(MID(C62,3,2)),VALUE(MID(C62,1,2))))=VALUE(MID(C62,3,2))),DATE(K62,VALUE(MID(C62,3,2)),VALUE(MID(C62,1,2))),"")),"")</f>
+      <c r="M62">
+        <f>IFERROR(IF(L62="","",IF(AND(DAY(DATE(L62,VALUE(MID(C62,3,2)),VALUE(MID(C62,1,2))))=VALUE(MID(C62,1,2)),MONTH(DATE(L62,VALUE(MID(C62,3,2)),VALUE(MID(C62,1,2))))=VALUE(MID(C62,3,2))),DATE(L62,VALUE(MID(C62,3,2)),VALUE(MID(C62,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2475,27 +2723,31 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="3" t="n"/>
       <c r="D63" s="2" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="2" t="n"/>
+      <c r="E63" s="4">
+        <f>IF(A63="","",5)</f>
+        <v/>
+      </c>
+      <c r="F63" s="4" t="n"/>
       <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2">
-        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(J63="","JMBG sadrži nešto što nije cifra",IF(L63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;J63,"Pogrešna kontrolna cifra — treba "&amp;J63,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I63">
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2">
+        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(K63="","JMBG sadrži nešto što nije cifra",IF(M63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;K63,"Pogrešna kontrolna cifra — treba "&amp;K63,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J63">
         <f>IFERROR(IF(LEN(C63)&lt;&gt;13,"",7*(VALUE(MID(C63,1,1))+VALUE(MID(C63,7,1)))+6*(VALUE(MID(C63,2,1))+VALUE(MID(C63,8,1)))+5*(VALUE(MID(C63,3,1))+VALUE(MID(C63,9,1)))+4*(VALUE(MID(C63,4,1))+VALUE(MID(C63,10,1)))+3*(VALUE(MID(C63,5,1))+VALUE(MID(C63,11,1)))+2*(VALUE(MID(C63,6,1))+VALUE(MID(C63,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J63">
-        <f>IF(I63="","",IF(11-MOD(I63,11)&gt;9,0,11-MOD(I63,11)))</f>
-        <v/>
-      </c>
       <c r="K63">
+        <f>IF(J63="","",IF(11-MOD(J63,11)&gt;9,0,11-MOD(J63,11)))</f>
+        <v/>
+      </c>
+      <c r="L63">
         <f>IFERROR(IF(LEN(C63)&lt;&gt;13,"",IF(VALUE(MID(C63,5,3))&gt;=800,1000,2000)+VALUE(MID(C63,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L63">
-        <f>IFERROR(IF(K63="","",IF(AND(DAY(DATE(K63,VALUE(MID(C63,3,2)),VALUE(MID(C63,1,2))))=VALUE(MID(C63,1,2)),MONTH(DATE(K63,VALUE(MID(C63,3,2)),VALUE(MID(C63,1,2))))=VALUE(MID(C63,3,2))),DATE(K63,VALUE(MID(C63,3,2)),VALUE(MID(C63,1,2))),"")),"")</f>
+      <c r="M63">
+        <f>IFERROR(IF(L63="","",IF(AND(DAY(DATE(L63,VALUE(MID(C63,3,2)),VALUE(MID(C63,1,2))))=VALUE(MID(C63,1,2)),MONTH(DATE(L63,VALUE(MID(C63,3,2)),VALUE(MID(C63,1,2))))=VALUE(MID(C63,3,2))),DATE(L63,VALUE(MID(C63,3,2)),VALUE(MID(C63,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2504,27 +2756,31 @@
       <c r="B64" s="2" t="n"/>
       <c r="C64" s="3" t="n"/>
       <c r="D64" s="2" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="2" t="n"/>
+      <c r="E64" s="4">
+        <f>IF(A64="","",5)</f>
+        <v/>
+      </c>
+      <c r="F64" s="4" t="n"/>
       <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2">
-        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(J64="","JMBG sadrži nešto što nije cifra",IF(L64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;J64,"Pogrešna kontrolna cifra — treba "&amp;J64,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I64">
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2">
+        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(K64="","JMBG sadrži nešto što nije cifra",IF(M64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;K64,"Pogrešna kontrolna cifra — treba "&amp;K64,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J64">
         <f>IFERROR(IF(LEN(C64)&lt;&gt;13,"",7*(VALUE(MID(C64,1,1))+VALUE(MID(C64,7,1)))+6*(VALUE(MID(C64,2,1))+VALUE(MID(C64,8,1)))+5*(VALUE(MID(C64,3,1))+VALUE(MID(C64,9,1)))+4*(VALUE(MID(C64,4,1))+VALUE(MID(C64,10,1)))+3*(VALUE(MID(C64,5,1))+VALUE(MID(C64,11,1)))+2*(VALUE(MID(C64,6,1))+VALUE(MID(C64,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J64">
-        <f>IF(I64="","",IF(11-MOD(I64,11)&gt;9,0,11-MOD(I64,11)))</f>
-        <v/>
-      </c>
       <c r="K64">
+        <f>IF(J64="","",IF(11-MOD(J64,11)&gt;9,0,11-MOD(J64,11)))</f>
+        <v/>
+      </c>
+      <c r="L64">
         <f>IFERROR(IF(LEN(C64)&lt;&gt;13,"",IF(VALUE(MID(C64,5,3))&gt;=800,1000,2000)+VALUE(MID(C64,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L64">
-        <f>IFERROR(IF(K64="","",IF(AND(DAY(DATE(K64,VALUE(MID(C64,3,2)),VALUE(MID(C64,1,2))))=VALUE(MID(C64,1,2)),MONTH(DATE(K64,VALUE(MID(C64,3,2)),VALUE(MID(C64,1,2))))=VALUE(MID(C64,3,2))),DATE(K64,VALUE(MID(C64,3,2)),VALUE(MID(C64,1,2))),"")),"")</f>
+      <c r="M64">
+        <f>IFERROR(IF(L64="","",IF(AND(DAY(DATE(L64,VALUE(MID(C64,3,2)),VALUE(MID(C64,1,2))))=VALUE(MID(C64,1,2)),MONTH(DATE(L64,VALUE(MID(C64,3,2)),VALUE(MID(C64,1,2))))=VALUE(MID(C64,3,2))),DATE(L64,VALUE(MID(C64,3,2)),VALUE(MID(C64,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2533,27 +2789,31 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="3" t="n"/>
       <c r="D65" s="2" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="2" t="n"/>
+      <c r="E65" s="4">
+        <f>IF(A65="","",5)</f>
+        <v/>
+      </c>
+      <c r="F65" s="4" t="n"/>
       <c r="G65" s="2" t="n"/>
-      <c r="H65" s="2">
-        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(J65="","JMBG sadrži nešto što nije cifra",IF(L65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;J65,"Pogrešna kontrolna cifra — treba "&amp;J65,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I65">
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2">
+        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(K65="","JMBG sadrži nešto što nije cifra",IF(M65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;K65,"Pogrešna kontrolna cifra — treba "&amp;K65,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J65">
         <f>IFERROR(IF(LEN(C65)&lt;&gt;13,"",7*(VALUE(MID(C65,1,1))+VALUE(MID(C65,7,1)))+6*(VALUE(MID(C65,2,1))+VALUE(MID(C65,8,1)))+5*(VALUE(MID(C65,3,1))+VALUE(MID(C65,9,1)))+4*(VALUE(MID(C65,4,1))+VALUE(MID(C65,10,1)))+3*(VALUE(MID(C65,5,1))+VALUE(MID(C65,11,1)))+2*(VALUE(MID(C65,6,1))+VALUE(MID(C65,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J65">
-        <f>IF(I65="","",IF(11-MOD(I65,11)&gt;9,0,11-MOD(I65,11)))</f>
-        <v/>
-      </c>
       <c r="K65">
+        <f>IF(J65="","",IF(11-MOD(J65,11)&gt;9,0,11-MOD(J65,11)))</f>
+        <v/>
+      </c>
+      <c r="L65">
         <f>IFERROR(IF(LEN(C65)&lt;&gt;13,"",IF(VALUE(MID(C65,5,3))&gt;=800,1000,2000)+VALUE(MID(C65,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L65">
-        <f>IFERROR(IF(K65="","",IF(AND(DAY(DATE(K65,VALUE(MID(C65,3,2)),VALUE(MID(C65,1,2))))=VALUE(MID(C65,1,2)),MONTH(DATE(K65,VALUE(MID(C65,3,2)),VALUE(MID(C65,1,2))))=VALUE(MID(C65,3,2))),DATE(K65,VALUE(MID(C65,3,2)),VALUE(MID(C65,1,2))),"")),"")</f>
+      <c r="M65">
+        <f>IFERROR(IF(L65="","",IF(AND(DAY(DATE(L65,VALUE(MID(C65,3,2)),VALUE(MID(C65,1,2))))=VALUE(MID(C65,1,2)),MONTH(DATE(L65,VALUE(MID(C65,3,2)),VALUE(MID(C65,1,2))))=VALUE(MID(C65,3,2))),DATE(L65,VALUE(MID(C65,3,2)),VALUE(MID(C65,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2562,27 +2822,31 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="3" t="n"/>
       <c r="D66" s="2" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="2" t="n"/>
+      <c r="E66" s="4">
+        <f>IF(A66="","",5)</f>
+        <v/>
+      </c>
+      <c r="F66" s="4" t="n"/>
       <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2">
-        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(J66="","JMBG sadrži nešto što nije cifra",IF(L66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;J66,"Pogrešna kontrolna cifra — treba "&amp;J66,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I66">
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2">
+        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(K66="","JMBG sadrži nešto što nije cifra",IF(M66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;K66,"Pogrešna kontrolna cifra — treba "&amp;K66,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J66">
         <f>IFERROR(IF(LEN(C66)&lt;&gt;13,"",7*(VALUE(MID(C66,1,1))+VALUE(MID(C66,7,1)))+6*(VALUE(MID(C66,2,1))+VALUE(MID(C66,8,1)))+5*(VALUE(MID(C66,3,1))+VALUE(MID(C66,9,1)))+4*(VALUE(MID(C66,4,1))+VALUE(MID(C66,10,1)))+3*(VALUE(MID(C66,5,1))+VALUE(MID(C66,11,1)))+2*(VALUE(MID(C66,6,1))+VALUE(MID(C66,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J66">
-        <f>IF(I66="","",IF(11-MOD(I66,11)&gt;9,0,11-MOD(I66,11)))</f>
-        <v/>
-      </c>
       <c r="K66">
+        <f>IF(J66="","",IF(11-MOD(J66,11)&gt;9,0,11-MOD(J66,11)))</f>
+        <v/>
+      </c>
+      <c r="L66">
         <f>IFERROR(IF(LEN(C66)&lt;&gt;13,"",IF(VALUE(MID(C66,5,3))&gt;=800,1000,2000)+VALUE(MID(C66,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L66">
-        <f>IFERROR(IF(K66="","",IF(AND(DAY(DATE(K66,VALUE(MID(C66,3,2)),VALUE(MID(C66,1,2))))=VALUE(MID(C66,1,2)),MONTH(DATE(K66,VALUE(MID(C66,3,2)),VALUE(MID(C66,1,2))))=VALUE(MID(C66,3,2))),DATE(K66,VALUE(MID(C66,3,2)),VALUE(MID(C66,1,2))),"")),"")</f>
+      <c r="M66">
+        <f>IFERROR(IF(L66="","",IF(AND(DAY(DATE(L66,VALUE(MID(C66,3,2)),VALUE(MID(C66,1,2))))=VALUE(MID(C66,1,2)),MONTH(DATE(L66,VALUE(MID(C66,3,2)),VALUE(MID(C66,1,2))))=VALUE(MID(C66,3,2))),DATE(L66,VALUE(MID(C66,3,2)),VALUE(MID(C66,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2591,27 +2855,31 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="3" t="n"/>
       <c r="D67" s="2" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="2" t="n"/>
+      <c r="E67" s="4">
+        <f>IF(A67="","",5)</f>
+        <v/>
+      </c>
+      <c r="F67" s="4" t="n"/>
       <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2">
-        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(J67="","JMBG sadrži nešto što nije cifra",IF(L67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;J67,"Pogrešna kontrolna cifra — treba "&amp;J67,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I67">
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2">
+        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(K67="","JMBG sadrži nešto što nije cifra",IF(M67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;K67,"Pogrešna kontrolna cifra — treba "&amp;K67,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J67">
         <f>IFERROR(IF(LEN(C67)&lt;&gt;13,"",7*(VALUE(MID(C67,1,1))+VALUE(MID(C67,7,1)))+6*(VALUE(MID(C67,2,1))+VALUE(MID(C67,8,1)))+5*(VALUE(MID(C67,3,1))+VALUE(MID(C67,9,1)))+4*(VALUE(MID(C67,4,1))+VALUE(MID(C67,10,1)))+3*(VALUE(MID(C67,5,1))+VALUE(MID(C67,11,1)))+2*(VALUE(MID(C67,6,1))+VALUE(MID(C67,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J67">
-        <f>IF(I67="","",IF(11-MOD(I67,11)&gt;9,0,11-MOD(I67,11)))</f>
-        <v/>
-      </c>
       <c r="K67">
+        <f>IF(J67="","",IF(11-MOD(J67,11)&gt;9,0,11-MOD(J67,11)))</f>
+        <v/>
+      </c>
+      <c r="L67">
         <f>IFERROR(IF(LEN(C67)&lt;&gt;13,"",IF(VALUE(MID(C67,5,3))&gt;=800,1000,2000)+VALUE(MID(C67,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L67">
-        <f>IFERROR(IF(K67="","",IF(AND(DAY(DATE(K67,VALUE(MID(C67,3,2)),VALUE(MID(C67,1,2))))=VALUE(MID(C67,1,2)),MONTH(DATE(K67,VALUE(MID(C67,3,2)),VALUE(MID(C67,1,2))))=VALUE(MID(C67,3,2))),DATE(K67,VALUE(MID(C67,3,2)),VALUE(MID(C67,1,2))),"")),"")</f>
+      <c r="M67">
+        <f>IFERROR(IF(L67="","",IF(AND(DAY(DATE(L67,VALUE(MID(C67,3,2)),VALUE(MID(C67,1,2))))=VALUE(MID(C67,1,2)),MONTH(DATE(L67,VALUE(MID(C67,3,2)),VALUE(MID(C67,1,2))))=VALUE(MID(C67,3,2))),DATE(L67,VALUE(MID(C67,3,2)),VALUE(MID(C67,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2620,27 +2888,31 @@
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="3" t="n"/>
       <c r="D68" s="2" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="2" t="n"/>
+      <c r="E68" s="4">
+        <f>IF(A68="","",5)</f>
+        <v/>
+      </c>
+      <c r="F68" s="4" t="n"/>
       <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2">
-        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(J68="","JMBG sadrži nešto što nije cifra",IF(L68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;J68,"Pogrešna kontrolna cifra — treba "&amp;J68,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I68">
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2">
+        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(K68="","JMBG sadrži nešto što nije cifra",IF(M68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;K68,"Pogrešna kontrolna cifra — treba "&amp;K68,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J68">
         <f>IFERROR(IF(LEN(C68)&lt;&gt;13,"",7*(VALUE(MID(C68,1,1))+VALUE(MID(C68,7,1)))+6*(VALUE(MID(C68,2,1))+VALUE(MID(C68,8,1)))+5*(VALUE(MID(C68,3,1))+VALUE(MID(C68,9,1)))+4*(VALUE(MID(C68,4,1))+VALUE(MID(C68,10,1)))+3*(VALUE(MID(C68,5,1))+VALUE(MID(C68,11,1)))+2*(VALUE(MID(C68,6,1))+VALUE(MID(C68,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J68">
-        <f>IF(I68="","",IF(11-MOD(I68,11)&gt;9,0,11-MOD(I68,11)))</f>
-        <v/>
-      </c>
       <c r="K68">
+        <f>IF(J68="","",IF(11-MOD(J68,11)&gt;9,0,11-MOD(J68,11)))</f>
+        <v/>
+      </c>
+      <c r="L68">
         <f>IFERROR(IF(LEN(C68)&lt;&gt;13,"",IF(VALUE(MID(C68,5,3))&gt;=800,1000,2000)+VALUE(MID(C68,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L68">
-        <f>IFERROR(IF(K68="","",IF(AND(DAY(DATE(K68,VALUE(MID(C68,3,2)),VALUE(MID(C68,1,2))))=VALUE(MID(C68,1,2)),MONTH(DATE(K68,VALUE(MID(C68,3,2)),VALUE(MID(C68,1,2))))=VALUE(MID(C68,3,2))),DATE(K68,VALUE(MID(C68,3,2)),VALUE(MID(C68,1,2))),"")),"")</f>
+      <c r="M68">
+        <f>IFERROR(IF(L68="","",IF(AND(DAY(DATE(L68,VALUE(MID(C68,3,2)),VALUE(MID(C68,1,2))))=VALUE(MID(C68,1,2)),MONTH(DATE(L68,VALUE(MID(C68,3,2)),VALUE(MID(C68,1,2))))=VALUE(MID(C68,3,2))),DATE(L68,VALUE(MID(C68,3,2)),VALUE(MID(C68,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2649,27 +2921,31 @@
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="3" t="n"/>
       <c r="D69" s="2" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="2" t="n"/>
+      <c r="E69" s="4">
+        <f>IF(A69="","",5)</f>
+        <v/>
+      </c>
+      <c r="F69" s="4" t="n"/>
       <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2">
-        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(J69="","JMBG sadrži nešto što nije cifra",IF(L69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;J69,"Pogrešna kontrolna cifra — treba "&amp;J69,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I69">
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2">
+        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(K69="","JMBG sadrži nešto što nije cifra",IF(M69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;K69,"Pogrešna kontrolna cifra — treba "&amp;K69,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J69">
         <f>IFERROR(IF(LEN(C69)&lt;&gt;13,"",7*(VALUE(MID(C69,1,1))+VALUE(MID(C69,7,1)))+6*(VALUE(MID(C69,2,1))+VALUE(MID(C69,8,1)))+5*(VALUE(MID(C69,3,1))+VALUE(MID(C69,9,1)))+4*(VALUE(MID(C69,4,1))+VALUE(MID(C69,10,1)))+3*(VALUE(MID(C69,5,1))+VALUE(MID(C69,11,1)))+2*(VALUE(MID(C69,6,1))+VALUE(MID(C69,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J69">
-        <f>IF(I69="","",IF(11-MOD(I69,11)&gt;9,0,11-MOD(I69,11)))</f>
-        <v/>
-      </c>
       <c r="K69">
+        <f>IF(J69="","",IF(11-MOD(J69,11)&gt;9,0,11-MOD(J69,11)))</f>
+        <v/>
+      </c>
+      <c r="L69">
         <f>IFERROR(IF(LEN(C69)&lt;&gt;13,"",IF(VALUE(MID(C69,5,3))&gt;=800,1000,2000)+VALUE(MID(C69,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L69">
-        <f>IFERROR(IF(K69="","",IF(AND(DAY(DATE(K69,VALUE(MID(C69,3,2)),VALUE(MID(C69,1,2))))=VALUE(MID(C69,1,2)),MONTH(DATE(K69,VALUE(MID(C69,3,2)),VALUE(MID(C69,1,2))))=VALUE(MID(C69,3,2))),DATE(K69,VALUE(MID(C69,3,2)),VALUE(MID(C69,1,2))),"")),"")</f>
+      <c r="M69">
+        <f>IFERROR(IF(L69="","",IF(AND(DAY(DATE(L69,VALUE(MID(C69,3,2)),VALUE(MID(C69,1,2))))=VALUE(MID(C69,1,2)),MONTH(DATE(L69,VALUE(MID(C69,3,2)),VALUE(MID(C69,1,2))))=VALUE(MID(C69,3,2))),DATE(L69,VALUE(MID(C69,3,2)),VALUE(MID(C69,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2678,27 +2954,31 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="3" t="n"/>
       <c r="D70" s="2" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="2" t="n"/>
+      <c r="E70" s="4">
+        <f>IF(A70="","",5)</f>
+        <v/>
+      </c>
+      <c r="F70" s="4" t="n"/>
       <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2">
-        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(J70="","JMBG sadrži nešto što nije cifra",IF(L70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;J70,"Pogrešna kontrolna cifra — treba "&amp;J70,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I70">
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2">
+        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(K70="","JMBG sadrži nešto što nije cifra",IF(M70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;K70,"Pogrešna kontrolna cifra — treba "&amp;K70,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J70">
         <f>IFERROR(IF(LEN(C70)&lt;&gt;13,"",7*(VALUE(MID(C70,1,1))+VALUE(MID(C70,7,1)))+6*(VALUE(MID(C70,2,1))+VALUE(MID(C70,8,1)))+5*(VALUE(MID(C70,3,1))+VALUE(MID(C70,9,1)))+4*(VALUE(MID(C70,4,1))+VALUE(MID(C70,10,1)))+3*(VALUE(MID(C70,5,1))+VALUE(MID(C70,11,1)))+2*(VALUE(MID(C70,6,1))+VALUE(MID(C70,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J70">
-        <f>IF(I70="","",IF(11-MOD(I70,11)&gt;9,0,11-MOD(I70,11)))</f>
-        <v/>
-      </c>
       <c r="K70">
+        <f>IF(J70="","",IF(11-MOD(J70,11)&gt;9,0,11-MOD(J70,11)))</f>
+        <v/>
+      </c>
+      <c r="L70">
         <f>IFERROR(IF(LEN(C70)&lt;&gt;13,"",IF(VALUE(MID(C70,5,3))&gt;=800,1000,2000)+VALUE(MID(C70,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L70">
-        <f>IFERROR(IF(K70="","",IF(AND(DAY(DATE(K70,VALUE(MID(C70,3,2)),VALUE(MID(C70,1,2))))=VALUE(MID(C70,1,2)),MONTH(DATE(K70,VALUE(MID(C70,3,2)),VALUE(MID(C70,1,2))))=VALUE(MID(C70,3,2))),DATE(K70,VALUE(MID(C70,3,2)),VALUE(MID(C70,1,2))),"")),"")</f>
+      <c r="M70">
+        <f>IFERROR(IF(L70="","",IF(AND(DAY(DATE(L70,VALUE(MID(C70,3,2)),VALUE(MID(C70,1,2))))=VALUE(MID(C70,1,2)),MONTH(DATE(L70,VALUE(MID(C70,3,2)),VALUE(MID(C70,1,2))))=VALUE(MID(C70,3,2))),DATE(L70,VALUE(MID(C70,3,2)),VALUE(MID(C70,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2707,27 +2987,31 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="3" t="n"/>
       <c r="D71" s="2" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="2" t="n"/>
+      <c r="E71" s="4">
+        <f>IF(A71="","",5)</f>
+        <v/>
+      </c>
+      <c r="F71" s="4" t="n"/>
       <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2">
-        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(J71="","JMBG sadrži nešto što nije cifra",IF(L71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;J71,"Pogrešna kontrolna cifra — treba "&amp;J71,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I71">
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2">
+        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(K71="","JMBG sadrži nešto što nije cifra",IF(M71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;K71,"Pogrešna kontrolna cifra — treba "&amp;K71,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J71">
         <f>IFERROR(IF(LEN(C71)&lt;&gt;13,"",7*(VALUE(MID(C71,1,1))+VALUE(MID(C71,7,1)))+6*(VALUE(MID(C71,2,1))+VALUE(MID(C71,8,1)))+5*(VALUE(MID(C71,3,1))+VALUE(MID(C71,9,1)))+4*(VALUE(MID(C71,4,1))+VALUE(MID(C71,10,1)))+3*(VALUE(MID(C71,5,1))+VALUE(MID(C71,11,1)))+2*(VALUE(MID(C71,6,1))+VALUE(MID(C71,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J71">
-        <f>IF(I71="","",IF(11-MOD(I71,11)&gt;9,0,11-MOD(I71,11)))</f>
-        <v/>
-      </c>
       <c r="K71">
+        <f>IF(J71="","",IF(11-MOD(J71,11)&gt;9,0,11-MOD(J71,11)))</f>
+        <v/>
+      </c>
+      <c r="L71">
         <f>IFERROR(IF(LEN(C71)&lt;&gt;13,"",IF(VALUE(MID(C71,5,3))&gt;=800,1000,2000)+VALUE(MID(C71,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L71">
-        <f>IFERROR(IF(K71="","",IF(AND(DAY(DATE(K71,VALUE(MID(C71,3,2)),VALUE(MID(C71,1,2))))=VALUE(MID(C71,1,2)),MONTH(DATE(K71,VALUE(MID(C71,3,2)),VALUE(MID(C71,1,2))))=VALUE(MID(C71,3,2))),DATE(K71,VALUE(MID(C71,3,2)),VALUE(MID(C71,1,2))),"")),"")</f>
+      <c r="M71">
+        <f>IFERROR(IF(L71="","",IF(AND(DAY(DATE(L71,VALUE(MID(C71,3,2)),VALUE(MID(C71,1,2))))=VALUE(MID(C71,1,2)),MONTH(DATE(L71,VALUE(MID(C71,3,2)),VALUE(MID(C71,1,2))))=VALUE(MID(C71,3,2))),DATE(L71,VALUE(MID(C71,3,2)),VALUE(MID(C71,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2736,27 +3020,31 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="3" t="n"/>
       <c r="D72" s="2" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="2" t="n"/>
+      <c r="E72" s="4">
+        <f>IF(A72="","",5)</f>
+        <v/>
+      </c>
+      <c r="F72" s="4" t="n"/>
       <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2">
-        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(J72="","JMBG sadrži nešto što nije cifra",IF(L72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;J72,"Pogrešna kontrolna cifra — treba "&amp;J72,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I72">
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2">
+        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(K72="","JMBG sadrži nešto što nije cifra",IF(M72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;K72,"Pogrešna kontrolna cifra — treba "&amp;K72,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J72">
         <f>IFERROR(IF(LEN(C72)&lt;&gt;13,"",7*(VALUE(MID(C72,1,1))+VALUE(MID(C72,7,1)))+6*(VALUE(MID(C72,2,1))+VALUE(MID(C72,8,1)))+5*(VALUE(MID(C72,3,1))+VALUE(MID(C72,9,1)))+4*(VALUE(MID(C72,4,1))+VALUE(MID(C72,10,1)))+3*(VALUE(MID(C72,5,1))+VALUE(MID(C72,11,1)))+2*(VALUE(MID(C72,6,1))+VALUE(MID(C72,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J72">
-        <f>IF(I72="","",IF(11-MOD(I72,11)&gt;9,0,11-MOD(I72,11)))</f>
-        <v/>
-      </c>
       <c r="K72">
+        <f>IF(J72="","",IF(11-MOD(J72,11)&gt;9,0,11-MOD(J72,11)))</f>
+        <v/>
+      </c>
+      <c r="L72">
         <f>IFERROR(IF(LEN(C72)&lt;&gt;13,"",IF(VALUE(MID(C72,5,3))&gt;=800,1000,2000)+VALUE(MID(C72,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L72">
-        <f>IFERROR(IF(K72="","",IF(AND(DAY(DATE(K72,VALUE(MID(C72,3,2)),VALUE(MID(C72,1,2))))=VALUE(MID(C72,1,2)),MONTH(DATE(K72,VALUE(MID(C72,3,2)),VALUE(MID(C72,1,2))))=VALUE(MID(C72,3,2))),DATE(K72,VALUE(MID(C72,3,2)),VALUE(MID(C72,1,2))),"")),"")</f>
+      <c r="M72">
+        <f>IFERROR(IF(L72="","",IF(AND(DAY(DATE(L72,VALUE(MID(C72,3,2)),VALUE(MID(C72,1,2))))=VALUE(MID(C72,1,2)),MONTH(DATE(L72,VALUE(MID(C72,3,2)),VALUE(MID(C72,1,2))))=VALUE(MID(C72,3,2))),DATE(L72,VALUE(MID(C72,3,2)),VALUE(MID(C72,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2765,27 +3053,31 @@
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="3" t="n"/>
       <c r="D73" s="2" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="2" t="n"/>
+      <c r="E73" s="4">
+        <f>IF(A73="","",5)</f>
+        <v/>
+      </c>
+      <c r="F73" s="4" t="n"/>
       <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2">
-        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(J73="","JMBG sadrži nešto što nije cifra",IF(L73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;J73,"Pogrešna kontrolna cifra — treba "&amp;J73,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I73">
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2">
+        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(K73="","JMBG sadrži nešto što nije cifra",IF(M73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;K73,"Pogrešna kontrolna cifra — treba "&amp;K73,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J73">
         <f>IFERROR(IF(LEN(C73)&lt;&gt;13,"",7*(VALUE(MID(C73,1,1))+VALUE(MID(C73,7,1)))+6*(VALUE(MID(C73,2,1))+VALUE(MID(C73,8,1)))+5*(VALUE(MID(C73,3,1))+VALUE(MID(C73,9,1)))+4*(VALUE(MID(C73,4,1))+VALUE(MID(C73,10,1)))+3*(VALUE(MID(C73,5,1))+VALUE(MID(C73,11,1)))+2*(VALUE(MID(C73,6,1))+VALUE(MID(C73,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J73">
-        <f>IF(I73="","",IF(11-MOD(I73,11)&gt;9,0,11-MOD(I73,11)))</f>
-        <v/>
-      </c>
       <c r="K73">
+        <f>IF(J73="","",IF(11-MOD(J73,11)&gt;9,0,11-MOD(J73,11)))</f>
+        <v/>
+      </c>
+      <c r="L73">
         <f>IFERROR(IF(LEN(C73)&lt;&gt;13,"",IF(VALUE(MID(C73,5,3))&gt;=800,1000,2000)+VALUE(MID(C73,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L73">
-        <f>IFERROR(IF(K73="","",IF(AND(DAY(DATE(K73,VALUE(MID(C73,3,2)),VALUE(MID(C73,1,2))))=VALUE(MID(C73,1,2)),MONTH(DATE(K73,VALUE(MID(C73,3,2)),VALUE(MID(C73,1,2))))=VALUE(MID(C73,3,2))),DATE(K73,VALUE(MID(C73,3,2)),VALUE(MID(C73,1,2))),"")),"")</f>
+      <c r="M73">
+        <f>IFERROR(IF(L73="","",IF(AND(DAY(DATE(L73,VALUE(MID(C73,3,2)),VALUE(MID(C73,1,2))))=VALUE(MID(C73,1,2)),MONTH(DATE(L73,VALUE(MID(C73,3,2)),VALUE(MID(C73,1,2))))=VALUE(MID(C73,3,2))),DATE(L73,VALUE(MID(C73,3,2)),VALUE(MID(C73,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2794,27 +3086,31 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="3" t="n"/>
       <c r="D74" s="2" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="2" t="n"/>
+      <c r="E74" s="4">
+        <f>IF(A74="","",5)</f>
+        <v/>
+      </c>
+      <c r="F74" s="4" t="n"/>
       <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2">
-        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(J74="","JMBG sadrži nešto što nije cifra",IF(L74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;J74,"Pogrešna kontrolna cifra — treba "&amp;J74,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I74">
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2">
+        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(K74="","JMBG sadrži nešto što nije cifra",IF(M74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;K74,"Pogrešna kontrolna cifra — treba "&amp;K74,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J74">
         <f>IFERROR(IF(LEN(C74)&lt;&gt;13,"",7*(VALUE(MID(C74,1,1))+VALUE(MID(C74,7,1)))+6*(VALUE(MID(C74,2,1))+VALUE(MID(C74,8,1)))+5*(VALUE(MID(C74,3,1))+VALUE(MID(C74,9,1)))+4*(VALUE(MID(C74,4,1))+VALUE(MID(C74,10,1)))+3*(VALUE(MID(C74,5,1))+VALUE(MID(C74,11,1)))+2*(VALUE(MID(C74,6,1))+VALUE(MID(C74,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J74">
-        <f>IF(I74="","",IF(11-MOD(I74,11)&gt;9,0,11-MOD(I74,11)))</f>
-        <v/>
-      </c>
       <c r="K74">
+        <f>IF(J74="","",IF(11-MOD(J74,11)&gt;9,0,11-MOD(J74,11)))</f>
+        <v/>
+      </c>
+      <c r="L74">
         <f>IFERROR(IF(LEN(C74)&lt;&gt;13,"",IF(VALUE(MID(C74,5,3))&gt;=800,1000,2000)+VALUE(MID(C74,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L74">
-        <f>IFERROR(IF(K74="","",IF(AND(DAY(DATE(K74,VALUE(MID(C74,3,2)),VALUE(MID(C74,1,2))))=VALUE(MID(C74,1,2)),MONTH(DATE(K74,VALUE(MID(C74,3,2)),VALUE(MID(C74,1,2))))=VALUE(MID(C74,3,2))),DATE(K74,VALUE(MID(C74,3,2)),VALUE(MID(C74,1,2))),"")),"")</f>
+      <c r="M74">
+        <f>IFERROR(IF(L74="","",IF(AND(DAY(DATE(L74,VALUE(MID(C74,3,2)),VALUE(MID(C74,1,2))))=VALUE(MID(C74,1,2)),MONTH(DATE(L74,VALUE(MID(C74,3,2)),VALUE(MID(C74,1,2))))=VALUE(MID(C74,3,2))),DATE(L74,VALUE(MID(C74,3,2)),VALUE(MID(C74,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2823,27 +3119,31 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="3" t="n"/>
       <c r="D75" s="2" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="2" t="n"/>
+      <c r="E75" s="4">
+        <f>IF(A75="","",5)</f>
+        <v/>
+      </c>
+      <c r="F75" s="4" t="n"/>
       <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2">
-        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(J75="","JMBG sadrži nešto što nije cifra",IF(L75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;J75,"Pogrešna kontrolna cifra — treba "&amp;J75,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I75">
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2">
+        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(K75="","JMBG sadrži nešto što nije cifra",IF(M75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;K75,"Pogrešna kontrolna cifra — treba "&amp;K75,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J75">
         <f>IFERROR(IF(LEN(C75)&lt;&gt;13,"",7*(VALUE(MID(C75,1,1))+VALUE(MID(C75,7,1)))+6*(VALUE(MID(C75,2,1))+VALUE(MID(C75,8,1)))+5*(VALUE(MID(C75,3,1))+VALUE(MID(C75,9,1)))+4*(VALUE(MID(C75,4,1))+VALUE(MID(C75,10,1)))+3*(VALUE(MID(C75,5,1))+VALUE(MID(C75,11,1)))+2*(VALUE(MID(C75,6,1))+VALUE(MID(C75,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J75">
-        <f>IF(I75="","",IF(11-MOD(I75,11)&gt;9,0,11-MOD(I75,11)))</f>
-        <v/>
-      </c>
       <c r="K75">
+        <f>IF(J75="","",IF(11-MOD(J75,11)&gt;9,0,11-MOD(J75,11)))</f>
+        <v/>
+      </c>
+      <c r="L75">
         <f>IFERROR(IF(LEN(C75)&lt;&gt;13,"",IF(VALUE(MID(C75,5,3))&gt;=800,1000,2000)+VALUE(MID(C75,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L75">
-        <f>IFERROR(IF(K75="","",IF(AND(DAY(DATE(K75,VALUE(MID(C75,3,2)),VALUE(MID(C75,1,2))))=VALUE(MID(C75,1,2)),MONTH(DATE(K75,VALUE(MID(C75,3,2)),VALUE(MID(C75,1,2))))=VALUE(MID(C75,3,2))),DATE(K75,VALUE(MID(C75,3,2)),VALUE(MID(C75,1,2))),"")),"")</f>
+      <c r="M75">
+        <f>IFERROR(IF(L75="","",IF(AND(DAY(DATE(L75,VALUE(MID(C75,3,2)),VALUE(MID(C75,1,2))))=VALUE(MID(C75,1,2)),MONTH(DATE(L75,VALUE(MID(C75,3,2)),VALUE(MID(C75,1,2))))=VALUE(MID(C75,3,2))),DATE(L75,VALUE(MID(C75,3,2)),VALUE(MID(C75,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2852,27 +3152,31 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="3" t="n"/>
       <c r="D76" s="2" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="2" t="n"/>
+      <c r="E76" s="4">
+        <f>IF(A76="","",5)</f>
+        <v/>
+      </c>
+      <c r="F76" s="4" t="n"/>
       <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2">
-        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(J76="","JMBG sadrži nešto što nije cifra",IF(L76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;J76,"Pogrešna kontrolna cifra — treba "&amp;J76,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I76">
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2">
+        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(K76="","JMBG sadrži nešto što nije cifra",IF(M76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;K76,"Pogrešna kontrolna cifra — treba "&amp;K76,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J76">
         <f>IFERROR(IF(LEN(C76)&lt;&gt;13,"",7*(VALUE(MID(C76,1,1))+VALUE(MID(C76,7,1)))+6*(VALUE(MID(C76,2,1))+VALUE(MID(C76,8,1)))+5*(VALUE(MID(C76,3,1))+VALUE(MID(C76,9,1)))+4*(VALUE(MID(C76,4,1))+VALUE(MID(C76,10,1)))+3*(VALUE(MID(C76,5,1))+VALUE(MID(C76,11,1)))+2*(VALUE(MID(C76,6,1))+VALUE(MID(C76,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J76">
-        <f>IF(I76="","",IF(11-MOD(I76,11)&gt;9,0,11-MOD(I76,11)))</f>
-        <v/>
-      </c>
       <c r="K76">
+        <f>IF(J76="","",IF(11-MOD(J76,11)&gt;9,0,11-MOD(J76,11)))</f>
+        <v/>
+      </c>
+      <c r="L76">
         <f>IFERROR(IF(LEN(C76)&lt;&gt;13,"",IF(VALUE(MID(C76,5,3))&gt;=800,1000,2000)+VALUE(MID(C76,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L76">
-        <f>IFERROR(IF(K76="","",IF(AND(DAY(DATE(K76,VALUE(MID(C76,3,2)),VALUE(MID(C76,1,2))))=VALUE(MID(C76,1,2)),MONTH(DATE(K76,VALUE(MID(C76,3,2)),VALUE(MID(C76,1,2))))=VALUE(MID(C76,3,2))),DATE(K76,VALUE(MID(C76,3,2)),VALUE(MID(C76,1,2))),"")),"")</f>
+      <c r="M76">
+        <f>IFERROR(IF(L76="","",IF(AND(DAY(DATE(L76,VALUE(MID(C76,3,2)),VALUE(MID(C76,1,2))))=VALUE(MID(C76,1,2)),MONTH(DATE(L76,VALUE(MID(C76,3,2)),VALUE(MID(C76,1,2))))=VALUE(MID(C76,3,2))),DATE(L76,VALUE(MID(C76,3,2)),VALUE(MID(C76,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2881,27 +3185,31 @@
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="3" t="n"/>
       <c r="D77" s="2" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="2" t="n"/>
+      <c r="E77" s="4">
+        <f>IF(A77="","",5)</f>
+        <v/>
+      </c>
+      <c r="F77" s="4" t="n"/>
       <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2">
-        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(J77="","JMBG sadrži nešto što nije cifra",IF(L77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;J77,"Pogrešna kontrolna cifra — treba "&amp;J77,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I77">
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2">
+        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(K77="","JMBG sadrži nešto što nije cifra",IF(M77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;K77,"Pogrešna kontrolna cifra — treba "&amp;K77,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J77">
         <f>IFERROR(IF(LEN(C77)&lt;&gt;13,"",7*(VALUE(MID(C77,1,1))+VALUE(MID(C77,7,1)))+6*(VALUE(MID(C77,2,1))+VALUE(MID(C77,8,1)))+5*(VALUE(MID(C77,3,1))+VALUE(MID(C77,9,1)))+4*(VALUE(MID(C77,4,1))+VALUE(MID(C77,10,1)))+3*(VALUE(MID(C77,5,1))+VALUE(MID(C77,11,1)))+2*(VALUE(MID(C77,6,1))+VALUE(MID(C77,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J77">
-        <f>IF(I77="","",IF(11-MOD(I77,11)&gt;9,0,11-MOD(I77,11)))</f>
-        <v/>
-      </c>
       <c r="K77">
+        <f>IF(J77="","",IF(11-MOD(J77,11)&gt;9,0,11-MOD(J77,11)))</f>
+        <v/>
+      </c>
+      <c r="L77">
         <f>IFERROR(IF(LEN(C77)&lt;&gt;13,"",IF(VALUE(MID(C77,5,3))&gt;=800,1000,2000)+VALUE(MID(C77,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L77">
-        <f>IFERROR(IF(K77="","",IF(AND(DAY(DATE(K77,VALUE(MID(C77,3,2)),VALUE(MID(C77,1,2))))=VALUE(MID(C77,1,2)),MONTH(DATE(K77,VALUE(MID(C77,3,2)),VALUE(MID(C77,1,2))))=VALUE(MID(C77,3,2))),DATE(K77,VALUE(MID(C77,3,2)),VALUE(MID(C77,1,2))),"")),"")</f>
+      <c r="M77">
+        <f>IFERROR(IF(L77="","",IF(AND(DAY(DATE(L77,VALUE(MID(C77,3,2)),VALUE(MID(C77,1,2))))=VALUE(MID(C77,1,2)),MONTH(DATE(L77,VALUE(MID(C77,3,2)),VALUE(MID(C77,1,2))))=VALUE(MID(C77,3,2))),DATE(L77,VALUE(MID(C77,3,2)),VALUE(MID(C77,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2910,27 +3218,31 @@
       <c r="B78" s="2" t="n"/>
       <c r="C78" s="3" t="n"/>
       <c r="D78" s="2" t="n"/>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="2" t="n"/>
+      <c r="E78" s="4">
+        <f>IF(A78="","",5)</f>
+        <v/>
+      </c>
+      <c r="F78" s="4" t="n"/>
       <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2">
-        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(J78="","JMBG sadrži nešto što nije cifra",IF(L78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;J78,"Pogrešna kontrolna cifra — treba "&amp;J78,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I78">
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2">
+        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(K78="","JMBG sadrži nešto što nije cifra",IF(M78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;K78,"Pogrešna kontrolna cifra — treba "&amp;K78,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J78">
         <f>IFERROR(IF(LEN(C78)&lt;&gt;13,"",7*(VALUE(MID(C78,1,1))+VALUE(MID(C78,7,1)))+6*(VALUE(MID(C78,2,1))+VALUE(MID(C78,8,1)))+5*(VALUE(MID(C78,3,1))+VALUE(MID(C78,9,1)))+4*(VALUE(MID(C78,4,1))+VALUE(MID(C78,10,1)))+3*(VALUE(MID(C78,5,1))+VALUE(MID(C78,11,1)))+2*(VALUE(MID(C78,6,1))+VALUE(MID(C78,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J78">
-        <f>IF(I78="","",IF(11-MOD(I78,11)&gt;9,0,11-MOD(I78,11)))</f>
-        <v/>
-      </c>
       <c r="K78">
+        <f>IF(J78="","",IF(11-MOD(J78,11)&gt;9,0,11-MOD(J78,11)))</f>
+        <v/>
+      </c>
+      <c r="L78">
         <f>IFERROR(IF(LEN(C78)&lt;&gt;13,"",IF(VALUE(MID(C78,5,3))&gt;=800,1000,2000)+VALUE(MID(C78,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L78">
-        <f>IFERROR(IF(K78="","",IF(AND(DAY(DATE(K78,VALUE(MID(C78,3,2)),VALUE(MID(C78,1,2))))=VALUE(MID(C78,1,2)),MONTH(DATE(K78,VALUE(MID(C78,3,2)),VALUE(MID(C78,1,2))))=VALUE(MID(C78,3,2))),DATE(K78,VALUE(MID(C78,3,2)),VALUE(MID(C78,1,2))),"")),"")</f>
+      <c r="M78">
+        <f>IFERROR(IF(L78="","",IF(AND(DAY(DATE(L78,VALUE(MID(C78,3,2)),VALUE(MID(C78,1,2))))=VALUE(MID(C78,1,2)),MONTH(DATE(L78,VALUE(MID(C78,3,2)),VALUE(MID(C78,1,2))))=VALUE(MID(C78,3,2))),DATE(L78,VALUE(MID(C78,3,2)),VALUE(MID(C78,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2939,27 +3251,31 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="3" t="n"/>
       <c r="D79" s="2" t="n"/>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="2" t="n"/>
+      <c r="E79" s="4">
+        <f>IF(A79="","",5)</f>
+        <v/>
+      </c>
+      <c r="F79" s="4" t="n"/>
       <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2">
-        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(J79="","JMBG sadrži nešto što nije cifra",IF(L79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;J79,"Pogrešna kontrolna cifra — treba "&amp;J79,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I79">
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2">
+        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(K79="","JMBG sadrži nešto što nije cifra",IF(M79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;K79,"Pogrešna kontrolna cifra — treba "&amp;K79,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J79">
         <f>IFERROR(IF(LEN(C79)&lt;&gt;13,"",7*(VALUE(MID(C79,1,1))+VALUE(MID(C79,7,1)))+6*(VALUE(MID(C79,2,1))+VALUE(MID(C79,8,1)))+5*(VALUE(MID(C79,3,1))+VALUE(MID(C79,9,1)))+4*(VALUE(MID(C79,4,1))+VALUE(MID(C79,10,1)))+3*(VALUE(MID(C79,5,1))+VALUE(MID(C79,11,1)))+2*(VALUE(MID(C79,6,1))+VALUE(MID(C79,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J79">
-        <f>IF(I79="","",IF(11-MOD(I79,11)&gt;9,0,11-MOD(I79,11)))</f>
-        <v/>
-      </c>
       <c r="K79">
+        <f>IF(J79="","",IF(11-MOD(J79,11)&gt;9,0,11-MOD(J79,11)))</f>
+        <v/>
+      </c>
+      <c r="L79">
         <f>IFERROR(IF(LEN(C79)&lt;&gt;13,"",IF(VALUE(MID(C79,5,3))&gt;=800,1000,2000)+VALUE(MID(C79,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L79">
-        <f>IFERROR(IF(K79="","",IF(AND(DAY(DATE(K79,VALUE(MID(C79,3,2)),VALUE(MID(C79,1,2))))=VALUE(MID(C79,1,2)),MONTH(DATE(K79,VALUE(MID(C79,3,2)),VALUE(MID(C79,1,2))))=VALUE(MID(C79,3,2))),DATE(K79,VALUE(MID(C79,3,2)),VALUE(MID(C79,1,2))),"")),"")</f>
+      <c r="M79">
+        <f>IFERROR(IF(L79="","",IF(AND(DAY(DATE(L79,VALUE(MID(C79,3,2)),VALUE(MID(C79,1,2))))=VALUE(MID(C79,1,2)),MONTH(DATE(L79,VALUE(MID(C79,3,2)),VALUE(MID(C79,1,2))))=VALUE(MID(C79,3,2))),DATE(L79,VALUE(MID(C79,3,2)),VALUE(MID(C79,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2968,27 +3284,31 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="3" t="n"/>
       <c r="D80" s="2" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="2" t="n"/>
+      <c r="E80" s="4">
+        <f>IF(A80="","",5)</f>
+        <v/>
+      </c>
+      <c r="F80" s="4" t="n"/>
       <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2">
-        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(J80="","JMBG sadrži nešto što nije cifra",IF(L80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;J80,"Pogrešna kontrolna cifra — treba "&amp;J80,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I80">
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2">
+        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(K80="","JMBG sadrži nešto što nije cifra",IF(M80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;K80,"Pogrešna kontrolna cifra — treba "&amp;K80,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J80">
         <f>IFERROR(IF(LEN(C80)&lt;&gt;13,"",7*(VALUE(MID(C80,1,1))+VALUE(MID(C80,7,1)))+6*(VALUE(MID(C80,2,1))+VALUE(MID(C80,8,1)))+5*(VALUE(MID(C80,3,1))+VALUE(MID(C80,9,1)))+4*(VALUE(MID(C80,4,1))+VALUE(MID(C80,10,1)))+3*(VALUE(MID(C80,5,1))+VALUE(MID(C80,11,1)))+2*(VALUE(MID(C80,6,1))+VALUE(MID(C80,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J80">
-        <f>IF(I80="","",IF(11-MOD(I80,11)&gt;9,0,11-MOD(I80,11)))</f>
-        <v/>
-      </c>
       <c r="K80">
+        <f>IF(J80="","",IF(11-MOD(J80,11)&gt;9,0,11-MOD(J80,11)))</f>
+        <v/>
+      </c>
+      <c r="L80">
         <f>IFERROR(IF(LEN(C80)&lt;&gt;13,"",IF(VALUE(MID(C80,5,3))&gt;=800,1000,2000)+VALUE(MID(C80,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L80">
-        <f>IFERROR(IF(K80="","",IF(AND(DAY(DATE(K80,VALUE(MID(C80,3,2)),VALUE(MID(C80,1,2))))=VALUE(MID(C80,1,2)),MONTH(DATE(K80,VALUE(MID(C80,3,2)),VALUE(MID(C80,1,2))))=VALUE(MID(C80,3,2))),DATE(K80,VALUE(MID(C80,3,2)),VALUE(MID(C80,1,2))),"")),"")</f>
+      <c r="M80">
+        <f>IFERROR(IF(L80="","",IF(AND(DAY(DATE(L80,VALUE(MID(C80,3,2)),VALUE(MID(C80,1,2))))=VALUE(MID(C80,1,2)),MONTH(DATE(L80,VALUE(MID(C80,3,2)),VALUE(MID(C80,1,2))))=VALUE(MID(C80,3,2))),DATE(L80,VALUE(MID(C80,3,2)),VALUE(MID(C80,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -2997,27 +3317,31 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="3" t="n"/>
       <c r="D81" s="2" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="2" t="n"/>
+      <c r="E81" s="4">
+        <f>IF(A81="","",5)</f>
+        <v/>
+      </c>
+      <c r="F81" s="4" t="n"/>
       <c r="G81" s="2" t="n"/>
-      <c r="H81" s="2">
-        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(J81="","JMBG sadrži nešto što nije cifra",IF(L81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;J81,"Pogrešna kontrolna cifra — treba "&amp;J81,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I81">
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2">
+        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(K81="","JMBG sadrži nešto što nije cifra",IF(M81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;K81,"Pogrešna kontrolna cifra — treba "&amp;K81,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J81">
         <f>IFERROR(IF(LEN(C81)&lt;&gt;13,"",7*(VALUE(MID(C81,1,1))+VALUE(MID(C81,7,1)))+6*(VALUE(MID(C81,2,1))+VALUE(MID(C81,8,1)))+5*(VALUE(MID(C81,3,1))+VALUE(MID(C81,9,1)))+4*(VALUE(MID(C81,4,1))+VALUE(MID(C81,10,1)))+3*(VALUE(MID(C81,5,1))+VALUE(MID(C81,11,1)))+2*(VALUE(MID(C81,6,1))+VALUE(MID(C81,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J81">
-        <f>IF(I81="","",IF(11-MOD(I81,11)&gt;9,0,11-MOD(I81,11)))</f>
-        <v/>
-      </c>
       <c r="K81">
+        <f>IF(J81="","",IF(11-MOD(J81,11)&gt;9,0,11-MOD(J81,11)))</f>
+        <v/>
+      </c>
+      <c r="L81">
         <f>IFERROR(IF(LEN(C81)&lt;&gt;13,"",IF(VALUE(MID(C81,5,3))&gt;=800,1000,2000)+VALUE(MID(C81,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L81">
-        <f>IFERROR(IF(K81="","",IF(AND(DAY(DATE(K81,VALUE(MID(C81,3,2)),VALUE(MID(C81,1,2))))=VALUE(MID(C81,1,2)),MONTH(DATE(K81,VALUE(MID(C81,3,2)),VALUE(MID(C81,1,2))))=VALUE(MID(C81,3,2))),DATE(K81,VALUE(MID(C81,3,2)),VALUE(MID(C81,1,2))),"")),"")</f>
+      <c r="M81">
+        <f>IFERROR(IF(L81="","",IF(AND(DAY(DATE(L81,VALUE(MID(C81,3,2)),VALUE(MID(C81,1,2))))=VALUE(MID(C81,1,2)),MONTH(DATE(L81,VALUE(MID(C81,3,2)),VALUE(MID(C81,1,2))))=VALUE(MID(C81,3,2))),DATE(L81,VALUE(MID(C81,3,2)),VALUE(MID(C81,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3026,27 +3350,31 @@
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="3" t="n"/>
       <c r="D82" s="2" t="n"/>
-      <c r="E82" s="4" t="n"/>
-      <c r="F82" s="2" t="n"/>
+      <c r="E82" s="4">
+        <f>IF(A82="","",5)</f>
+        <v/>
+      </c>
+      <c r="F82" s="4" t="n"/>
       <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2">
-        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(J82="","JMBG sadrži nešto što nije cifra",IF(L82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;J82,"Pogrešna kontrolna cifra — treba "&amp;J82,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I82">
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2">
+        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(K82="","JMBG sadrži nešto što nije cifra",IF(M82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;K82,"Pogrešna kontrolna cifra — treba "&amp;K82,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J82">
         <f>IFERROR(IF(LEN(C82)&lt;&gt;13,"",7*(VALUE(MID(C82,1,1))+VALUE(MID(C82,7,1)))+6*(VALUE(MID(C82,2,1))+VALUE(MID(C82,8,1)))+5*(VALUE(MID(C82,3,1))+VALUE(MID(C82,9,1)))+4*(VALUE(MID(C82,4,1))+VALUE(MID(C82,10,1)))+3*(VALUE(MID(C82,5,1))+VALUE(MID(C82,11,1)))+2*(VALUE(MID(C82,6,1))+VALUE(MID(C82,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J82">
-        <f>IF(I82="","",IF(11-MOD(I82,11)&gt;9,0,11-MOD(I82,11)))</f>
-        <v/>
-      </c>
       <c r="K82">
+        <f>IF(J82="","",IF(11-MOD(J82,11)&gt;9,0,11-MOD(J82,11)))</f>
+        <v/>
+      </c>
+      <c r="L82">
         <f>IFERROR(IF(LEN(C82)&lt;&gt;13,"",IF(VALUE(MID(C82,5,3))&gt;=800,1000,2000)+VALUE(MID(C82,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L82">
-        <f>IFERROR(IF(K82="","",IF(AND(DAY(DATE(K82,VALUE(MID(C82,3,2)),VALUE(MID(C82,1,2))))=VALUE(MID(C82,1,2)),MONTH(DATE(K82,VALUE(MID(C82,3,2)),VALUE(MID(C82,1,2))))=VALUE(MID(C82,3,2))),DATE(K82,VALUE(MID(C82,3,2)),VALUE(MID(C82,1,2))),"")),"")</f>
+      <c r="M82">
+        <f>IFERROR(IF(L82="","",IF(AND(DAY(DATE(L82,VALUE(MID(C82,3,2)),VALUE(MID(C82,1,2))))=VALUE(MID(C82,1,2)),MONTH(DATE(L82,VALUE(MID(C82,3,2)),VALUE(MID(C82,1,2))))=VALUE(MID(C82,3,2))),DATE(L82,VALUE(MID(C82,3,2)),VALUE(MID(C82,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3055,27 +3383,31 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="3" t="n"/>
       <c r="D83" s="2" t="n"/>
-      <c r="E83" s="4" t="n"/>
-      <c r="F83" s="2" t="n"/>
+      <c r="E83" s="4">
+        <f>IF(A83="","",5)</f>
+        <v/>
+      </c>
+      <c r="F83" s="4" t="n"/>
       <c r="G83" s="2" t="n"/>
-      <c r="H83" s="2">
-        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(J83="","JMBG sadrži nešto što nije cifra",IF(L83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;J83,"Pogrešna kontrolna cifra — treba "&amp;J83,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I83">
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2">
+        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(K83="","JMBG sadrži nešto što nije cifra",IF(M83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;K83,"Pogrešna kontrolna cifra — treba "&amp;K83,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J83">
         <f>IFERROR(IF(LEN(C83)&lt;&gt;13,"",7*(VALUE(MID(C83,1,1))+VALUE(MID(C83,7,1)))+6*(VALUE(MID(C83,2,1))+VALUE(MID(C83,8,1)))+5*(VALUE(MID(C83,3,1))+VALUE(MID(C83,9,1)))+4*(VALUE(MID(C83,4,1))+VALUE(MID(C83,10,1)))+3*(VALUE(MID(C83,5,1))+VALUE(MID(C83,11,1)))+2*(VALUE(MID(C83,6,1))+VALUE(MID(C83,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J83">
-        <f>IF(I83="","",IF(11-MOD(I83,11)&gt;9,0,11-MOD(I83,11)))</f>
-        <v/>
-      </c>
       <c r="K83">
+        <f>IF(J83="","",IF(11-MOD(J83,11)&gt;9,0,11-MOD(J83,11)))</f>
+        <v/>
+      </c>
+      <c r="L83">
         <f>IFERROR(IF(LEN(C83)&lt;&gt;13,"",IF(VALUE(MID(C83,5,3))&gt;=800,1000,2000)+VALUE(MID(C83,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L83">
-        <f>IFERROR(IF(K83="","",IF(AND(DAY(DATE(K83,VALUE(MID(C83,3,2)),VALUE(MID(C83,1,2))))=VALUE(MID(C83,1,2)),MONTH(DATE(K83,VALUE(MID(C83,3,2)),VALUE(MID(C83,1,2))))=VALUE(MID(C83,3,2))),DATE(K83,VALUE(MID(C83,3,2)),VALUE(MID(C83,1,2))),"")),"")</f>
+      <c r="M83">
+        <f>IFERROR(IF(L83="","",IF(AND(DAY(DATE(L83,VALUE(MID(C83,3,2)),VALUE(MID(C83,1,2))))=VALUE(MID(C83,1,2)),MONTH(DATE(L83,VALUE(MID(C83,3,2)),VALUE(MID(C83,1,2))))=VALUE(MID(C83,3,2))),DATE(L83,VALUE(MID(C83,3,2)),VALUE(MID(C83,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3084,27 +3416,31 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="3" t="n"/>
       <c r="D84" s="2" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="2" t="n"/>
+      <c r="E84" s="4">
+        <f>IF(A84="","",5)</f>
+        <v/>
+      </c>
+      <c r="F84" s="4" t="n"/>
       <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2">
-        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(J84="","JMBG sadrži nešto što nije cifra",IF(L84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;J84,"Pogrešna kontrolna cifra — treba "&amp;J84,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I84">
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2">
+        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(K84="","JMBG sadrži nešto što nije cifra",IF(M84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;K84,"Pogrešna kontrolna cifra — treba "&amp;K84,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J84">
         <f>IFERROR(IF(LEN(C84)&lt;&gt;13,"",7*(VALUE(MID(C84,1,1))+VALUE(MID(C84,7,1)))+6*(VALUE(MID(C84,2,1))+VALUE(MID(C84,8,1)))+5*(VALUE(MID(C84,3,1))+VALUE(MID(C84,9,1)))+4*(VALUE(MID(C84,4,1))+VALUE(MID(C84,10,1)))+3*(VALUE(MID(C84,5,1))+VALUE(MID(C84,11,1)))+2*(VALUE(MID(C84,6,1))+VALUE(MID(C84,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J84">
-        <f>IF(I84="","",IF(11-MOD(I84,11)&gt;9,0,11-MOD(I84,11)))</f>
-        <v/>
-      </c>
       <c r="K84">
+        <f>IF(J84="","",IF(11-MOD(J84,11)&gt;9,0,11-MOD(J84,11)))</f>
+        <v/>
+      </c>
+      <c r="L84">
         <f>IFERROR(IF(LEN(C84)&lt;&gt;13,"",IF(VALUE(MID(C84,5,3))&gt;=800,1000,2000)+VALUE(MID(C84,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L84">
-        <f>IFERROR(IF(K84="","",IF(AND(DAY(DATE(K84,VALUE(MID(C84,3,2)),VALUE(MID(C84,1,2))))=VALUE(MID(C84,1,2)),MONTH(DATE(K84,VALUE(MID(C84,3,2)),VALUE(MID(C84,1,2))))=VALUE(MID(C84,3,2))),DATE(K84,VALUE(MID(C84,3,2)),VALUE(MID(C84,1,2))),"")),"")</f>
+      <c r="M84">
+        <f>IFERROR(IF(L84="","",IF(AND(DAY(DATE(L84,VALUE(MID(C84,3,2)),VALUE(MID(C84,1,2))))=VALUE(MID(C84,1,2)),MONTH(DATE(L84,VALUE(MID(C84,3,2)),VALUE(MID(C84,1,2))))=VALUE(MID(C84,3,2))),DATE(L84,VALUE(MID(C84,3,2)),VALUE(MID(C84,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3113,27 +3449,31 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="3" t="n"/>
       <c r="D85" s="2" t="n"/>
-      <c r="E85" s="4" t="n"/>
-      <c r="F85" s="2" t="n"/>
+      <c r="E85" s="4">
+        <f>IF(A85="","",5)</f>
+        <v/>
+      </c>
+      <c r="F85" s="4" t="n"/>
       <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2">
-        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(J85="","JMBG sadrži nešto što nije cifra",IF(L85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;J85,"Pogrešna kontrolna cifra — treba "&amp;J85,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I85">
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2">
+        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(K85="","JMBG sadrži nešto što nije cifra",IF(M85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;K85,"Pogrešna kontrolna cifra — treba "&amp;K85,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J85">
         <f>IFERROR(IF(LEN(C85)&lt;&gt;13,"",7*(VALUE(MID(C85,1,1))+VALUE(MID(C85,7,1)))+6*(VALUE(MID(C85,2,1))+VALUE(MID(C85,8,1)))+5*(VALUE(MID(C85,3,1))+VALUE(MID(C85,9,1)))+4*(VALUE(MID(C85,4,1))+VALUE(MID(C85,10,1)))+3*(VALUE(MID(C85,5,1))+VALUE(MID(C85,11,1)))+2*(VALUE(MID(C85,6,1))+VALUE(MID(C85,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J85">
-        <f>IF(I85="","",IF(11-MOD(I85,11)&gt;9,0,11-MOD(I85,11)))</f>
-        <v/>
-      </c>
       <c r="K85">
+        <f>IF(J85="","",IF(11-MOD(J85,11)&gt;9,0,11-MOD(J85,11)))</f>
+        <v/>
+      </c>
+      <c r="L85">
         <f>IFERROR(IF(LEN(C85)&lt;&gt;13,"",IF(VALUE(MID(C85,5,3))&gt;=800,1000,2000)+VALUE(MID(C85,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L85">
-        <f>IFERROR(IF(K85="","",IF(AND(DAY(DATE(K85,VALUE(MID(C85,3,2)),VALUE(MID(C85,1,2))))=VALUE(MID(C85,1,2)),MONTH(DATE(K85,VALUE(MID(C85,3,2)),VALUE(MID(C85,1,2))))=VALUE(MID(C85,3,2))),DATE(K85,VALUE(MID(C85,3,2)),VALUE(MID(C85,1,2))),"")),"")</f>
+      <c r="M85">
+        <f>IFERROR(IF(L85="","",IF(AND(DAY(DATE(L85,VALUE(MID(C85,3,2)),VALUE(MID(C85,1,2))))=VALUE(MID(C85,1,2)),MONTH(DATE(L85,VALUE(MID(C85,3,2)),VALUE(MID(C85,1,2))))=VALUE(MID(C85,3,2))),DATE(L85,VALUE(MID(C85,3,2)),VALUE(MID(C85,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3142,27 +3482,31 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="3" t="n"/>
       <c r="D86" s="2" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="2" t="n"/>
+      <c r="E86" s="4">
+        <f>IF(A86="","",5)</f>
+        <v/>
+      </c>
+      <c r="F86" s="4" t="n"/>
       <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2">
-        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(J86="","JMBG sadrži nešto što nije cifra",IF(L86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;J86,"Pogrešna kontrolna cifra — treba "&amp;J86,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I86">
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2">
+        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(K86="","JMBG sadrži nešto što nije cifra",IF(M86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;K86,"Pogrešna kontrolna cifra — treba "&amp;K86,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J86">
         <f>IFERROR(IF(LEN(C86)&lt;&gt;13,"",7*(VALUE(MID(C86,1,1))+VALUE(MID(C86,7,1)))+6*(VALUE(MID(C86,2,1))+VALUE(MID(C86,8,1)))+5*(VALUE(MID(C86,3,1))+VALUE(MID(C86,9,1)))+4*(VALUE(MID(C86,4,1))+VALUE(MID(C86,10,1)))+3*(VALUE(MID(C86,5,1))+VALUE(MID(C86,11,1)))+2*(VALUE(MID(C86,6,1))+VALUE(MID(C86,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J86">
-        <f>IF(I86="","",IF(11-MOD(I86,11)&gt;9,0,11-MOD(I86,11)))</f>
-        <v/>
-      </c>
       <c r="K86">
+        <f>IF(J86="","",IF(11-MOD(J86,11)&gt;9,0,11-MOD(J86,11)))</f>
+        <v/>
+      </c>
+      <c r="L86">
         <f>IFERROR(IF(LEN(C86)&lt;&gt;13,"",IF(VALUE(MID(C86,5,3))&gt;=800,1000,2000)+VALUE(MID(C86,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L86">
-        <f>IFERROR(IF(K86="","",IF(AND(DAY(DATE(K86,VALUE(MID(C86,3,2)),VALUE(MID(C86,1,2))))=VALUE(MID(C86,1,2)),MONTH(DATE(K86,VALUE(MID(C86,3,2)),VALUE(MID(C86,1,2))))=VALUE(MID(C86,3,2))),DATE(K86,VALUE(MID(C86,3,2)),VALUE(MID(C86,1,2))),"")),"")</f>
+      <c r="M86">
+        <f>IFERROR(IF(L86="","",IF(AND(DAY(DATE(L86,VALUE(MID(C86,3,2)),VALUE(MID(C86,1,2))))=VALUE(MID(C86,1,2)),MONTH(DATE(L86,VALUE(MID(C86,3,2)),VALUE(MID(C86,1,2))))=VALUE(MID(C86,3,2))),DATE(L86,VALUE(MID(C86,3,2)),VALUE(MID(C86,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3171,27 +3515,31 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="3" t="n"/>
       <c r="D87" s="2" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="2" t="n"/>
+      <c r="E87" s="4">
+        <f>IF(A87="","",5)</f>
+        <v/>
+      </c>
+      <c r="F87" s="4" t="n"/>
       <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2">
-        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(J87="","JMBG sadrži nešto što nije cifra",IF(L87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;J87,"Pogrešna kontrolna cifra — treba "&amp;J87,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I87">
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2">
+        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(K87="","JMBG sadrži nešto što nije cifra",IF(M87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;K87,"Pogrešna kontrolna cifra — treba "&amp;K87,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J87">
         <f>IFERROR(IF(LEN(C87)&lt;&gt;13,"",7*(VALUE(MID(C87,1,1))+VALUE(MID(C87,7,1)))+6*(VALUE(MID(C87,2,1))+VALUE(MID(C87,8,1)))+5*(VALUE(MID(C87,3,1))+VALUE(MID(C87,9,1)))+4*(VALUE(MID(C87,4,1))+VALUE(MID(C87,10,1)))+3*(VALUE(MID(C87,5,1))+VALUE(MID(C87,11,1)))+2*(VALUE(MID(C87,6,1))+VALUE(MID(C87,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J87">
-        <f>IF(I87="","",IF(11-MOD(I87,11)&gt;9,0,11-MOD(I87,11)))</f>
-        <v/>
-      </c>
       <c r="K87">
+        <f>IF(J87="","",IF(11-MOD(J87,11)&gt;9,0,11-MOD(J87,11)))</f>
+        <v/>
+      </c>
+      <c r="L87">
         <f>IFERROR(IF(LEN(C87)&lt;&gt;13,"",IF(VALUE(MID(C87,5,3))&gt;=800,1000,2000)+VALUE(MID(C87,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L87">
-        <f>IFERROR(IF(K87="","",IF(AND(DAY(DATE(K87,VALUE(MID(C87,3,2)),VALUE(MID(C87,1,2))))=VALUE(MID(C87,1,2)),MONTH(DATE(K87,VALUE(MID(C87,3,2)),VALUE(MID(C87,1,2))))=VALUE(MID(C87,3,2))),DATE(K87,VALUE(MID(C87,3,2)),VALUE(MID(C87,1,2))),"")),"")</f>
+      <c r="M87">
+        <f>IFERROR(IF(L87="","",IF(AND(DAY(DATE(L87,VALUE(MID(C87,3,2)),VALUE(MID(C87,1,2))))=VALUE(MID(C87,1,2)),MONTH(DATE(L87,VALUE(MID(C87,3,2)),VALUE(MID(C87,1,2))))=VALUE(MID(C87,3,2))),DATE(L87,VALUE(MID(C87,3,2)),VALUE(MID(C87,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3200,27 +3548,31 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" s="3" t="n"/>
       <c r="D88" s="2" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="2" t="n"/>
+      <c r="E88" s="4">
+        <f>IF(A88="","",5)</f>
+        <v/>
+      </c>
+      <c r="F88" s="4" t="n"/>
       <c r="G88" s="2" t="n"/>
-      <c r="H88" s="2">
-        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(J88="","JMBG sadrži nešto što nije cifra",IF(L88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;J88,"Pogrešna kontrolna cifra — treba "&amp;J88,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I88">
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2">
+        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(K88="","JMBG sadrži nešto što nije cifra",IF(M88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;K88,"Pogrešna kontrolna cifra — treba "&amp;K88,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J88">
         <f>IFERROR(IF(LEN(C88)&lt;&gt;13,"",7*(VALUE(MID(C88,1,1))+VALUE(MID(C88,7,1)))+6*(VALUE(MID(C88,2,1))+VALUE(MID(C88,8,1)))+5*(VALUE(MID(C88,3,1))+VALUE(MID(C88,9,1)))+4*(VALUE(MID(C88,4,1))+VALUE(MID(C88,10,1)))+3*(VALUE(MID(C88,5,1))+VALUE(MID(C88,11,1)))+2*(VALUE(MID(C88,6,1))+VALUE(MID(C88,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J88">
-        <f>IF(I88="","",IF(11-MOD(I88,11)&gt;9,0,11-MOD(I88,11)))</f>
-        <v/>
-      </c>
       <c r="K88">
+        <f>IF(J88="","",IF(11-MOD(J88,11)&gt;9,0,11-MOD(J88,11)))</f>
+        <v/>
+      </c>
+      <c r="L88">
         <f>IFERROR(IF(LEN(C88)&lt;&gt;13,"",IF(VALUE(MID(C88,5,3))&gt;=800,1000,2000)+VALUE(MID(C88,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L88">
-        <f>IFERROR(IF(K88="","",IF(AND(DAY(DATE(K88,VALUE(MID(C88,3,2)),VALUE(MID(C88,1,2))))=VALUE(MID(C88,1,2)),MONTH(DATE(K88,VALUE(MID(C88,3,2)),VALUE(MID(C88,1,2))))=VALUE(MID(C88,3,2))),DATE(K88,VALUE(MID(C88,3,2)),VALUE(MID(C88,1,2))),"")),"")</f>
+      <c r="M88">
+        <f>IFERROR(IF(L88="","",IF(AND(DAY(DATE(L88,VALUE(MID(C88,3,2)),VALUE(MID(C88,1,2))))=VALUE(MID(C88,1,2)),MONTH(DATE(L88,VALUE(MID(C88,3,2)),VALUE(MID(C88,1,2))))=VALUE(MID(C88,3,2))),DATE(L88,VALUE(MID(C88,3,2)),VALUE(MID(C88,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3229,27 +3581,31 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" s="3" t="n"/>
       <c r="D89" s="2" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="2" t="n"/>
+      <c r="E89" s="4">
+        <f>IF(A89="","",5)</f>
+        <v/>
+      </c>
+      <c r="F89" s="4" t="n"/>
       <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2">
-        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(J89="","JMBG sadrži nešto što nije cifra",IF(L89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;J89,"Pogrešna kontrolna cifra — treba "&amp;J89,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I89">
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2">
+        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(K89="","JMBG sadrži nešto što nije cifra",IF(M89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;K89,"Pogrešna kontrolna cifra — treba "&amp;K89,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J89">
         <f>IFERROR(IF(LEN(C89)&lt;&gt;13,"",7*(VALUE(MID(C89,1,1))+VALUE(MID(C89,7,1)))+6*(VALUE(MID(C89,2,1))+VALUE(MID(C89,8,1)))+5*(VALUE(MID(C89,3,1))+VALUE(MID(C89,9,1)))+4*(VALUE(MID(C89,4,1))+VALUE(MID(C89,10,1)))+3*(VALUE(MID(C89,5,1))+VALUE(MID(C89,11,1)))+2*(VALUE(MID(C89,6,1))+VALUE(MID(C89,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J89">
-        <f>IF(I89="","",IF(11-MOD(I89,11)&gt;9,0,11-MOD(I89,11)))</f>
-        <v/>
-      </c>
       <c r="K89">
+        <f>IF(J89="","",IF(11-MOD(J89,11)&gt;9,0,11-MOD(J89,11)))</f>
+        <v/>
+      </c>
+      <c r="L89">
         <f>IFERROR(IF(LEN(C89)&lt;&gt;13,"",IF(VALUE(MID(C89,5,3))&gt;=800,1000,2000)+VALUE(MID(C89,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L89">
-        <f>IFERROR(IF(K89="","",IF(AND(DAY(DATE(K89,VALUE(MID(C89,3,2)),VALUE(MID(C89,1,2))))=VALUE(MID(C89,1,2)),MONTH(DATE(K89,VALUE(MID(C89,3,2)),VALUE(MID(C89,1,2))))=VALUE(MID(C89,3,2))),DATE(K89,VALUE(MID(C89,3,2)),VALUE(MID(C89,1,2))),"")),"")</f>
+      <c r="M89">
+        <f>IFERROR(IF(L89="","",IF(AND(DAY(DATE(L89,VALUE(MID(C89,3,2)),VALUE(MID(C89,1,2))))=VALUE(MID(C89,1,2)),MONTH(DATE(L89,VALUE(MID(C89,3,2)),VALUE(MID(C89,1,2))))=VALUE(MID(C89,3,2))),DATE(L89,VALUE(MID(C89,3,2)),VALUE(MID(C89,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3258,27 +3614,31 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" s="3" t="n"/>
       <c r="D90" s="2" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="2" t="n"/>
+      <c r="E90" s="4">
+        <f>IF(A90="","",5)</f>
+        <v/>
+      </c>
+      <c r="F90" s="4" t="n"/>
       <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2">
-        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(J90="","JMBG sadrži nešto što nije cifra",IF(L90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;J90,"Pogrešna kontrolna cifra — treba "&amp;J90,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I90">
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2">
+        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(K90="","JMBG sadrži nešto što nije cifra",IF(M90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;K90,"Pogrešna kontrolna cifra — treba "&amp;K90,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J90">
         <f>IFERROR(IF(LEN(C90)&lt;&gt;13,"",7*(VALUE(MID(C90,1,1))+VALUE(MID(C90,7,1)))+6*(VALUE(MID(C90,2,1))+VALUE(MID(C90,8,1)))+5*(VALUE(MID(C90,3,1))+VALUE(MID(C90,9,1)))+4*(VALUE(MID(C90,4,1))+VALUE(MID(C90,10,1)))+3*(VALUE(MID(C90,5,1))+VALUE(MID(C90,11,1)))+2*(VALUE(MID(C90,6,1))+VALUE(MID(C90,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J90">
-        <f>IF(I90="","",IF(11-MOD(I90,11)&gt;9,0,11-MOD(I90,11)))</f>
-        <v/>
-      </c>
       <c r="K90">
+        <f>IF(J90="","",IF(11-MOD(J90,11)&gt;9,0,11-MOD(J90,11)))</f>
+        <v/>
+      </c>
+      <c r="L90">
         <f>IFERROR(IF(LEN(C90)&lt;&gt;13,"",IF(VALUE(MID(C90,5,3))&gt;=800,1000,2000)+VALUE(MID(C90,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L90">
-        <f>IFERROR(IF(K90="","",IF(AND(DAY(DATE(K90,VALUE(MID(C90,3,2)),VALUE(MID(C90,1,2))))=VALUE(MID(C90,1,2)),MONTH(DATE(K90,VALUE(MID(C90,3,2)),VALUE(MID(C90,1,2))))=VALUE(MID(C90,3,2))),DATE(K90,VALUE(MID(C90,3,2)),VALUE(MID(C90,1,2))),"")),"")</f>
+      <c r="M90">
+        <f>IFERROR(IF(L90="","",IF(AND(DAY(DATE(L90,VALUE(MID(C90,3,2)),VALUE(MID(C90,1,2))))=VALUE(MID(C90,1,2)),MONTH(DATE(L90,VALUE(MID(C90,3,2)),VALUE(MID(C90,1,2))))=VALUE(MID(C90,3,2))),DATE(L90,VALUE(MID(C90,3,2)),VALUE(MID(C90,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3287,27 +3647,31 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" s="3" t="n"/>
       <c r="D91" s="2" t="n"/>
-      <c r="E91" s="4" t="n"/>
-      <c r="F91" s="2" t="n"/>
+      <c r="E91" s="4">
+        <f>IF(A91="","",5)</f>
+        <v/>
+      </c>
+      <c r="F91" s="4" t="n"/>
       <c r="G91" s="2" t="n"/>
-      <c r="H91" s="2">
-        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(J91="","JMBG sadrži nešto što nije cifra",IF(L91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;J91,"Pogrešna kontrolna cifra — treba "&amp;J91,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I91">
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2">
+        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(K91="","JMBG sadrži nešto što nije cifra",IF(M91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;K91,"Pogrešna kontrolna cifra — treba "&amp;K91,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J91">
         <f>IFERROR(IF(LEN(C91)&lt;&gt;13,"",7*(VALUE(MID(C91,1,1))+VALUE(MID(C91,7,1)))+6*(VALUE(MID(C91,2,1))+VALUE(MID(C91,8,1)))+5*(VALUE(MID(C91,3,1))+VALUE(MID(C91,9,1)))+4*(VALUE(MID(C91,4,1))+VALUE(MID(C91,10,1)))+3*(VALUE(MID(C91,5,1))+VALUE(MID(C91,11,1)))+2*(VALUE(MID(C91,6,1))+VALUE(MID(C91,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J91">
-        <f>IF(I91="","",IF(11-MOD(I91,11)&gt;9,0,11-MOD(I91,11)))</f>
-        <v/>
-      </c>
       <c r="K91">
+        <f>IF(J91="","",IF(11-MOD(J91,11)&gt;9,0,11-MOD(J91,11)))</f>
+        <v/>
+      </c>
+      <c r="L91">
         <f>IFERROR(IF(LEN(C91)&lt;&gt;13,"",IF(VALUE(MID(C91,5,3))&gt;=800,1000,2000)+VALUE(MID(C91,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L91">
-        <f>IFERROR(IF(K91="","",IF(AND(DAY(DATE(K91,VALUE(MID(C91,3,2)),VALUE(MID(C91,1,2))))=VALUE(MID(C91,1,2)),MONTH(DATE(K91,VALUE(MID(C91,3,2)),VALUE(MID(C91,1,2))))=VALUE(MID(C91,3,2))),DATE(K91,VALUE(MID(C91,3,2)),VALUE(MID(C91,1,2))),"")),"")</f>
+      <c r="M91">
+        <f>IFERROR(IF(L91="","",IF(AND(DAY(DATE(L91,VALUE(MID(C91,3,2)),VALUE(MID(C91,1,2))))=VALUE(MID(C91,1,2)),MONTH(DATE(L91,VALUE(MID(C91,3,2)),VALUE(MID(C91,1,2))))=VALUE(MID(C91,3,2))),DATE(L91,VALUE(MID(C91,3,2)),VALUE(MID(C91,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3316,27 +3680,31 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="3" t="n"/>
       <c r="D92" s="2" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="2" t="n"/>
+      <c r="E92" s="4">
+        <f>IF(A92="","",5)</f>
+        <v/>
+      </c>
+      <c r="F92" s="4" t="n"/>
       <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2">
-        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(J92="","JMBG sadrži nešto što nije cifra",IF(L92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;J92,"Pogrešna kontrolna cifra — treba "&amp;J92,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I92">
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2">
+        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(K92="","JMBG sadrži nešto što nije cifra",IF(M92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;K92,"Pogrešna kontrolna cifra — treba "&amp;K92,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J92">
         <f>IFERROR(IF(LEN(C92)&lt;&gt;13,"",7*(VALUE(MID(C92,1,1))+VALUE(MID(C92,7,1)))+6*(VALUE(MID(C92,2,1))+VALUE(MID(C92,8,1)))+5*(VALUE(MID(C92,3,1))+VALUE(MID(C92,9,1)))+4*(VALUE(MID(C92,4,1))+VALUE(MID(C92,10,1)))+3*(VALUE(MID(C92,5,1))+VALUE(MID(C92,11,1)))+2*(VALUE(MID(C92,6,1))+VALUE(MID(C92,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J92">
-        <f>IF(I92="","",IF(11-MOD(I92,11)&gt;9,0,11-MOD(I92,11)))</f>
-        <v/>
-      </c>
       <c r="K92">
+        <f>IF(J92="","",IF(11-MOD(J92,11)&gt;9,0,11-MOD(J92,11)))</f>
+        <v/>
+      </c>
+      <c r="L92">
         <f>IFERROR(IF(LEN(C92)&lt;&gt;13,"",IF(VALUE(MID(C92,5,3))&gt;=800,1000,2000)+VALUE(MID(C92,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L92">
-        <f>IFERROR(IF(K92="","",IF(AND(DAY(DATE(K92,VALUE(MID(C92,3,2)),VALUE(MID(C92,1,2))))=VALUE(MID(C92,1,2)),MONTH(DATE(K92,VALUE(MID(C92,3,2)),VALUE(MID(C92,1,2))))=VALUE(MID(C92,3,2))),DATE(K92,VALUE(MID(C92,3,2)),VALUE(MID(C92,1,2))),"")),"")</f>
+      <c r="M92">
+        <f>IFERROR(IF(L92="","",IF(AND(DAY(DATE(L92,VALUE(MID(C92,3,2)),VALUE(MID(C92,1,2))))=VALUE(MID(C92,1,2)),MONTH(DATE(L92,VALUE(MID(C92,3,2)),VALUE(MID(C92,1,2))))=VALUE(MID(C92,3,2))),DATE(L92,VALUE(MID(C92,3,2)),VALUE(MID(C92,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3345,27 +3713,31 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" s="3" t="n"/>
       <c r="D93" s="2" t="n"/>
-      <c r="E93" s="4" t="n"/>
-      <c r="F93" s="2" t="n"/>
+      <c r="E93" s="4">
+        <f>IF(A93="","",5)</f>
+        <v/>
+      </c>
+      <c r="F93" s="4" t="n"/>
       <c r="G93" s="2" t="n"/>
-      <c r="H93" s="2">
-        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(J93="","JMBG sadrži nešto što nije cifra",IF(L93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;J93,"Pogrešna kontrolna cifra — treba "&amp;J93,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I93">
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2">
+        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(K93="","JMBG sadrži nešto što nije cifra",IF(M93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;K93,"Pogrešna kontrolna cifra — treba "&amp;K93,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J93">
         <f>IFERROR(IF(LEN(C93)&lt;&gt;13,"",7*(VALUE(MID(C93,1,1))+VALUE(MID(C93,7,1)))+6*(VALUE(MID(C93,2,1))+VALUE(MID(C93,8,1)))+5*(VALUE(MID(C93,3,1))+VALUE(MID(C93,9,1)))+4*(VALUE(MID(C93,4,1))+VALUE(MID(C93,10,1)))+3*(VALUE(MID(C93,5,1))+VALUE(MID(C93,11,1)))+2*(VALUE(MID(C93,6,1))+VALUE(MID(C93,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J93">
-        <f>IF(I93="","",IF(11-MOD(I93,11)&gt;9,0,11-MOD(I93,11)))</f>
-        <v/>
-      </c>
       <c r="K93">
+        <f>IF(J93="","",IF(11-MOD(J93,11)&gt;9,0,11-MOD(J93,11)))</f>
+        <v/>
+      </c>
+      <c r="L93">
         <f>IFERROR(IF(LEN(C93)&lt;&gt;13,"",IF(VALUE(MID(C93,5,3))&gt;=800,1000,2000)+VALUE(MID(C93,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L93">
-        <f>IFERROR(IF(K93="","",IF(AND(DAY(DATE(K93,VALUE(MID(C93,3,2)),VALUE(MID(C93,1,2))))=VALUE(MID(C93,1,2)),MONTH(DATE(K93,VALUE(MID(C93,3,2)),VALUE(MID(C93,1,2))))=VALUE(MID(C93,3,2))),DATE(K93,VALUE(MID(C93,3,2)),VALUE(MID(C93,1,2))),"")),"")</f>
+      <c r="M93">
+        <f>IFERROR(IF(L93="","",IF(AND(DAY(DATE(L93,VALUE(MID(C93,3,2)),VALUE(MID(C93,1,2))))=VALUE(MID(C93,1,2)),MONTH(DATE(L93,VALUE(MID(C93,3,2)),VALUE(MID(C93,1,2))))=VALUE(MID(C93,3,2))),DATE(L93,VALUE(MID(C93,3,2)),VALUE(MID(C93,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3374,27 +3746,31 @@
       <c r="B94" s="2" t="n"/>
       <c r="C94" s="3" t="n"/>
       <c r="D94" s="2" t="n"/>
-      <c r="E94" s="4" t="n"/>
-      <c r="F94" s="2" t="n"/>
+      <c r="E94" s="4">
+        <f>IF(A94="","",5)</f>
+        <v/>
+      </c>
+      <c r="F94" s="4" t="n"/>
       <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2">
-        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(J94="","JMBG sadrži nešto što nije cifra",IF(L94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;J94,"Pogrešna kontrolna cifra — treba "&amp;J94,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I94">
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2">
+        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(K94="","JMBG sadrži nešto što nije cifra",IF(M94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;K94,"Pogrešna kontrolna cifra — treba "&amp;K94,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J94">
         <f>IFERROR(IF(LEN(C94)&lt;&gt;13,"",7*(VALUE(MID(C94,1,1))+VALUE(MID(C94,7,1)))+6*(VALUE(MID(C94,2,1))+VALUE(MID(C94,8,1)))+5*(VALUE(MID(C94,3,1))+VALUE(MID(C94,9,1)))+4*(VALUE(MID(C94,4,1))+VALUE(MID(C94,10,1)))+3*(VALUE(MID(C94,5,1))+VALUE(MID(C94,11,1)))+2*(VALUE(MID(C94,6,1))+VALUE(MID(C94,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J94">
-        <f>IF(I94="","",IF(11-MOD(I94,11)&gt;9,0,11-MOD(I94,11)))</f>
-        <v/>
-      </c>
       <c r="K94">
+        <f>IF(J94="","",IF(11-MOD(J94,11)&gt;9,0,11-MOD(J94,11)))</f>
+        <v/>
+      </c>
+      <c r="L94">
         <f>IFERROR(IF(LEN(C94)&lt;&gt;13,"",IF(VALUE(MID(C94,5,3))&gt;=800,1000,2000)+VALUE(MID(C94,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L94">
-        <f>IFERROR(IF(K94="","",IF(AND(DAY(DATE(K94,VALUE(MID(C94,3,2)),VALUE(MID(C94,1,2))))=VALUE(MID(C94,1,2)),MONTH(DATE(K94,VALUE(MID(C94,3,2)),VALUE(MID(C94,1,2))))=VALUE(MID(C94,3,2))),DATE(K94,VALUE(MID(C94,3,2)),VALUE(MID(C94,1,2))),"")),"")</f>
+      <c r="M94">
+        <f>IFERROR(IF(L94="","",IF(AND(DAY(DATE(L94,VALUE(MID(C94,3,2)),VALUE(MID(C94,1,2))))=VALUE(MID(C94,1,2)),MONTH(DATE(L94,VALUE(MID(C94,3,2)),VALUE(MID(C94,1,2))))=VALUE(MID(C94,3,2))),DATE(L94,VALUE(MID(C94,3,2)),VALUE(MID(C94,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3403,27 +3779,31 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" s="3" t="n"/>
       <c r="D95" s="2" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="2" t="n"/>
+      <c r="E95" s="4">
+        <f>IF(A95="","",5)</f>
+        <v/>
+      </c>
+      <c r="F95" s="4" t="n"/>
       <c r="G95" s="2" t="n"/>
-      <c r="H95" s="2">
-        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(J95="","JMBG sadrži nešto što nije cifra",IF(L95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;J95,"Pogrešna kontrolna cifra — treba "&amp;J95,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I95">
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2">
+        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(K95="","JMBG sadrži nešto što nije cifra",IF(M95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;K95,"Pogrešna kontrolna cifra — treba "&amp;K95,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J95">
         <f>IFERROR(IF(LEN(C95)&lt;&gt;13,"",7*(VALUE(MID(C95,1,1))+VALUE(MID(C95,7,1)))+6*(VALUE(MID(C95,2,1))+VALUE(MID(C95,8,1)))+5*(VALUE(MID(C95,3,1))+VALUE(MID(C95,9,1)))+4*(VALUE(MID(C95,4,1))+VALUE(MID(C95,10,1)))+3*(VALUE(MID(C95,5,1))+VALUE(MID(C95,11,1)))+2*(VALUE(MID(C95,6,1))+VALUE(MID(C95,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J95">
-        <f>IF(I95="","",IF(11-MOD(I95,11)&gt;9,0,11-MOD(I95,11)))</f>
-        <v/>
-      </c>
       <c r="K95">
+        <f>IF(J95="","",IF(11-MOD(J95,11)&gt;9,0,11-MOD(J95,11)))</f>
+        <v/>
+      </c>
+      <c r="L95">
         <f>IFERROR(IF(LEN(C95)&lt;&gt;13,"",IF(VALUE(MID(C95,5,3))&gt;=800,1000,2000)+VALUE(MID(C95,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L95">
-        <f>IFERROR(IF(K95="","",IF(AND(DAY(DATE(K95,VALUE(MID(C95,3,2)),VALUE(MID(C95,1,2))))=VALUE(MID(C95,1,2)),MONTH(DATE(K95,VALUE(MID(C95,3,2)),VALUE(MID(C95,1,2))))=VALUE(MID(C95,3,2))),DATE(K95,VALUE(MID(C95,3,2)),VALUE(MID(C95,1,2))),"")),"")</f>
+      <c r="M95">
+        <f>IFERROR(IF(L95="","",IF(AND(DAY(DATE(L95,VALUE(MID(C95,3,2)),VALUE(MID(C95,1,2))))=VALUE(MID(C95,1,2)),MONTH(DATE(L95,VALUE(MID(C95,3,2)),VALUE(MID(C95,1,2))))=VALUE(MID(C95,3,2))),DATE(L95,VALUE(MID(C95,3,2)),VALUE(MID(C95,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3432,27 +3812,31 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" s="3" t="n"/>
       <c r="D96" s="2" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="2" t="n"/>
+      <c r="E96" s="4">
+        <f>IF(A96="","",5)</f>
+        <v/>
+      </c>
+      <c r="F96" s="4" t="n"/>
       <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2">
-        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(J96="","JMBG sadrži nešto što nije cifra",IF(L96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;J96,"Pogrešna kontrolna cifra — treba "&amp;J96,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I96">
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2">
+        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(K96="","JMBG sadrži nešto što nije cifra",IF(M96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;K96,"Pogrešna kontrolna cifra — treba "&amp;K96,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J96">
         <f>IFERROR(IF(LEN(C96)&lt;&gt;13,"",7*(VALUE(MID(C96,1,1))+VALUE(MID(C96,7,1)))+6*(VALUE(MID(C96,2,1))+VALUE(MID(C96,8,1)))+5*(VALUE(MID(C96,3,1))+VALUE(MID(C96,9,1)))+4*(VALUE(MID(C96,4,1))+VALUE(MID(C96,10,1)))+3*(VALUE(MID(C96,5,1))+VALUE(MID(C96,11,1)))+2*(VALUE(MID(C96,6,1))+VALUE(MID(C96,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J96">
-        <f>IF(I96="","",IF(11-MOD(I96,11)&gt;9,0,11-MOD(I96,11)))</f>
-        <v/>
-      </c>
       <c r="K96">
+        <f>IF(J96="","",IF(11-MOD(J96,11)&gt;9,0,11-MOD(J96,11)))</f>
+        <v/>
+      </c>
+      <c r="L96">
         <f>IFERROR(IF(LEN(C96)&lt;&gt;13,"",IF(VALUE(MID(C96,5,3))&gt;=800,1000,2000)+VALUE(MID(C96,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L96">
-        <f>IFERROR(IF(K96="","",IF(AND(DAY(DATE(K96,VALUE(MID(C96,3,2)),VALUE(MID(C96,1,2))))=VALUE(MID(C96,1,2)),MONTH(DATE(K96,VALUE(MID(C96,3,2)),VALUE(MID(C96,1,2))))=VALUE(MID(C96,3,2))),DATE(K96,VALUE(MID(C96,3,2)),VALUE(MID(C96,1,2))),"")),"")</f>
+      <c r="M96">
+        <f>IFERROR(IF(L96="","",IF(AND(DAY(DATE(L96,VALUE(MID(C96,3,2)),VALUE(MID(C96,1,2))))=VALUE(MID(C96,1,2)),MONTH(DATE(L96,VALUE(MID(C96,3,2)),VALUE(MID(C96,1,2))))=VALUE(MID(C96,3,2))),DATE(L96,VALUE(MID(C96,3,2)),VALUE(MID(C96,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3461,27 +3845,31 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" s="3" t="n"/>
       <c r="D97" s="2" t="n"/>
-      <c r="E97" s="4" t="n"/>
-      <c r="F97" s="2" t="n"/>
+      <c r="E97" s="4">
+        <f>IF(A97="","",5)</f>
+        <v/>
+      </c>
+      <c r="F97" s="4" t="n"/>
       <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2">
-        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(J97="","JMBG sadrži nešto što nije cifra",IF(L97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;J97,"Pogrešna kontrolna cifra — treba "&amp;J97,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I97">
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2">
+        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(K97="","JMBG sadrži nešto što nije cifra",IF(M97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;K97,"Pogrešna kontrolna cifra — treba "&amp;K97,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J97">
         <f>IFERROR(IF(LEN(C97)&lt;&gt;13,"",7*(VALUE(MID(C97,1,1))+VALUE(MID(C97,7,1)))+6*(VALUE(MID(C97,2,1))+VALUE(MID(C97,8,1)))+5*(VALUE(MID(C97,3,1))+VALUE(MID(C97,9,1)))+4*(VALUE(MID(C97,4,1))+VALUE(MID(C97,10,1)))+3*(VALUE(MID(C97,5,1))+VALUE(MID(C97,11,1)))+2*(VALUE(MID(C97,6,1))+VALUE(MID(C97,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J97">
-        <f>IF(I97="","",IF(11-MOD(I97,11)&gt;9,0,11-MOD(I97,11)))</f>
-        <v/>
-      </c>
       <c r="K97">
+        <f>IF(J97="","",IF(11-MOD(J97,11)&gt;9,0,11-MOD(J97,11)))</f>
+        <v/>
+      </c>
+      <c r="L97">
         <f>IFERROR(IF(LEN(C97)&lt;&gt;13,"",IF(VALUE(MID(C97,5,3))&gt;=800,1000,2000)+VALUE(MID(C97,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L97">
-        <f>IFERROR(IF(K97="","",IF(AND(DAY(DATE(K97,VALUE(MID(C97,3,2)),VALUE(MID(C97,1,2))))=VALUE(MID(C97,1,2)),MONTH(DATE(K97,VALUE(MID(C97,3,2)),VALUE(MID(C97,1,2))))=VALUE(MID(C97,3,2))),DATE(K97,VALUE(MID(C97,3,2)),VALUE(MID(C97,1,2))),"")),"")</f>
+      <c r="M97">
+        <f>IFERROR(IF(L97="","",IF(AND(DAY(DATE(L97,VALUE(MID(C97,3,2)),VALUE(MID(C97,1,2))))=VALUE(MID(C97,1,2)),MONTH(DATE(L97,VALUE(MID(C97,3,2)),VALUE(MID(C97,1,2))))=VALUE(MID(C97,3,2))),DATE(L97,VALUE(MID(C97,3,2)),VALUE(MID(C97,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3490,27 +3878,31 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" s="3" t="n"/>
       <c r="D98" s="2" t="n"/>
-      <c r="E98" s="4" t="n"/>
-      <c r="F98" s="2" t="n"/>
+      <c r="E98" s="4">
+        <f>IF(A98="","",5)</f>
+        <v/>
+      </c>
+      <c r="F98" s="4" t="n"/>
       <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2">
-        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(J98="","JMBG sadrži nešto što nije cifra",IF(L98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;J98,"Pogrešna kontrolna cifra — treba "&amp;J98,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I98">
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2">
+        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(K98="","JMBG sadrži nešto što nije cifra",IF(M98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;K98,"Pogrešna kontrolna cifra — treba "&amp;K98,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J98">
         <f>IFERROR(IF(LEN(C98)&lt;&gt;13,"",7*(VALUE(MID(C98,1,1))+VALUE(MID(C98,7,1)))+6*(VALUE(MID(C98,2,1))+VALUE(MID(C98,8,1)))+5*(VALUE(MID(C98,3,1))+VALUE(MID(C98,9,1)))+4*(VALUE(MID(C98,4,1))+VALUE(MID(C98,10,1)))+3*(VALUE(MID(C98,5,1))+VALUE(MID(C98,11,1)))+2*(VALUE(MID(C98,6,1))+VALUE(MID(C98,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J98">
-        <f>IF(I98="","",IF(11-MOD(I98,11)&gt;9,0,11-MOD(I98,11)))</f>
-        <v/>
-      </c>
       <c r="K98">
+        <f>IF(J98="","",IF(11-MOD(J98,11)&gt;9,0,11-MOD(J98,11)))</f>
+        <v/>
+      </c>
+      <c r="L98">
         <f>IFERROR(IF(LEN(C98)&lt;&gt;13,"",IF(VALUE(MID(C98,5,3))&gt;=800,1000,2000)+VALUE(MID(C98,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L98">
-        <f>IFERROR(IF(K98="","",IF(AND(DAY(DATE(K98,VALUE(MID(C98,3,2)),VALUE(MID(C98,1,2))))=VALUE(MID(C98,1,2)),MONTH(DATE(K98,VALUE(MID(C98,3,2)),VALUE(MID(C98,1,2))))=VALUE(MID(C98,3,2))),DATE(K98,VALUE(MID(C98,3,2)),VALUE(MID(C98,1,2))),"")),"")</f>
+      <c r="M98">
+        <f>IFERROR(IF(L98="","",IF(AND(DAY(DATE(L98,VALUE(MID(C98,3,2)),VALUE(MID(C98,1,2))))=VALUE(MID(C98,1,2)),MONTH(DATE(L98,VALUE(MID(C98,3,2)),VALUE(MID(C98,1,2))))=VALUE(MID(C98,3,2))),DATE(L98,VALUE(MID(C98,3,2)),VALUE(MID(C98,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3519,27 +3911,31 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" s="3" t="n"/>
       <c r="D99" s="2" t="n"/>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="2" t="n"/>
+      <c r="E99" s="4">
+        <f>IF(A99="","",5)</f>
+        <v/>
+      </c>
+      <c r="F99" s="4" t="n"/>
       <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2">
-        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(J99="","JMBG sadrži nešto što nije cifra",IF(L99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;J99,"Pogrešna kontrolna cifra — treba "&amp;J99,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I99">
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2">
+        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(K99="","JMBG sadrži nešto što nije cifra",IF(M99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;K99,"Pogrešna kontrolna cifra — treba "&amp;K99,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J99">
         <f>IFERROR(IF(LEN(C99)&lt;&gt;13,"",7*(VALUE(MID(C99,1,1))+VALUE(MID(C99,7,1)))+6*(VALUE(MID(C99,2,1))+VALUE(MID(C99,8,1)))+5*(VALUE(MID(C99,3,1))+VALUE(MID(C99,9,1)))+4*(VALUE(MID(C99,4,1))+VALUE(MID(C99,10,1)))+3*(VALUE(MID(C99,5,1))+VALUE(MID(C99,11,1)))+2*(VALUE(MID(C99,6,1))+VALUE(MID(C99,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J99">
-        <f>IF(I99="","",IF(11-MOD(I99,11)&gt;9,0,11-MOD(I99,11)))</f>
-        <v/>
-      </c>
       <c r="K99">
+        <f>IF(J99="","",IF(11-MOD(J99,11)&gt;9,0,11-MOD(J99,11)))</f>
+        <v/>
+      </c>
+      <c r="L99">
         <f>IFERROR(IF(LEN(C99)&lt;&gt;13,"",IF(VALUE(MID(C99,5,3))&gt;=800,1000,2000)+VALUE(MID(C99,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L99">
-        <f>IFERROR(IF(K99="","",IF(AND(DAY(DATE(K99,VALUE(MID(C99,3,2)),VALUE(MID(C99,1,2))))=VALUE(MID(C99,1,2)),MONTH(DATE(K99,VALUE(MID(C99,3,2)),VALUE(MID(C99,1,2))))=VALUE(MID(C99,3,2))),DATE(K99,VALUE(MID(C99,3,2)),VALUE(MID(C99,1,2))),"")),"")</f>
+      <c r="M99">
+        <f>IFERROR(IF(L99="","",IF(AND(DAY(DATE(L99,VALUE(MID(C99,3,2)),VALUE(MID(C99,1,2))))=VALUE(MID(C99,1,2)),MONTH(DATE(L99,VALUE(MID(C99,3,2)),VALUE(MID(C99,1,2))))=VALUE(MID(C99,3,2))),DATE(L99,VALUE(MID(C99,3,2)),VALUE(MID(C99,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3548,27 +3944,31 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" s="3" t="n"/>
       <c r="D100" s="2" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="2" t="n"/>
+      <c r="E100" s="4">
+        <f>IF(A100="","",5)</f>
+        <v/>
+      </c>
+      <c r="F100" s="4" t="n"/>
       <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2">
-        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(J100="","JMBG sadrži nešto što nije cifra",IF(L100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;J100,"Pogrešna kontrolna cifra — treba "&amp;J100,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I100">
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2">
+        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(K100="","JMBG sadrži nešto što nije cifra",IF(M100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;K100,"Pogrešna kontrolna cifra — treba "&amp;K100,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J100">
         <f>IFERROR(IF(LEN(C100)&lt;&gt;13,"",7*(VALUE(MID(C100,1,1))+VALUE(MID(C100,7,1)))+6*(VALUE(MID(C100,2,1))+VALUE(MID(C100,8,1)))+5*(VALUE(MID(C100,3,1))+VALUE(MID(C100,9,1)))+4*(VALUE(MID(C100,4,1))+VALUE(MID(C100,10,1)))+3*(VALUE(MID(C100,5,1))+VALUE(MID(C100,11,1)))+2*(VALUE(MID(C100,6,1))+VALUE(MID(C100,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J100">
-        <f>IF(I100="","",IF(11-MOD(I100,11)&gt;9,0,11-MOD(I100,11)))</f>
-        <v/>
-      </c>
       <c r="K100">
+        <f>IF(J100="","",IF(11-MOD(J100,11)&gt;9,0,11-MOD(J100,11)))</f>
+        <v/>
+      </c>
+      <c r="L100">
         <f>IFERROR(IF(LEN(C100)&lt;&gt;13,"",IF(VALUE(MID(C100,5,3))&gt;=800,1000,2000)+VALUE(MID(C100,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L100">
-        <f>IFERROR(IF(K100="","",IF(AND(DAY(DATE(K100,VALUE(MID(C100,3,2)),VALUE(MID(C100,1,2))))=VALUE(MID(C100,1,2)),MONTH(DATE(K100,VALUE(MID(C100,3,2)),VALUE(MID(C100,1,2))))=VALUE(MID(C100,3,2))),DATE(K100,VALUE(MID(C100,3,2)),VALUE(MID(C100,1,2))),"")),"")</f>
+      <c r="M100">
+        <f>IFERROR(IF(L100="","",IF(AND(DAY(DATE(L100,VALUE(MID(C100,3,2)),VALUE(MID(C100,1,2))))=VALUE(MID(C100,1,2)),MONTH(DATE(L100,VALUE(MID(C100,3,2)),VALUE(MID(C100,1,2))))=VALUE(MID(C100,3,2))),DATE(L100,VALUE(MID(C100,3,2)),VALUE(MID(C100,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3577,27 +3977,31 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" s="3" t="n"/>
       <c r="D101" s="2" t="n"/>
-      <c r="E101" s="4" t="n"/>
-      <c r="F101" s="2" t="n"/>
+      <c r="E101" s="4">
+        <f>IF(A101="","",5)</f>
+        <v/>
+      </c>
+      <c r="F101" s="4" t="n"/>
       <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2">
-        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(J101="","JMBG sadrži nešto što nije cifra",IF(L101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;J101,"Pogrešna kontrolna cifra — treba "&amp;J101,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I101">
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2">
+        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(K101="","JMBG sadrži nešto što nije cifra",IF(M101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;K101,"Pogrešna kontrolna cifra — treba "&amp;K101,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J101">
         <f>IFERROR(IF(LEN(C101)&lt;&gt;13,"",7*(VALUE(MID(C101,1,1))+VALUE(MID(C101,7,1)))+6*(VALUE(MID(C101,2,1))+VALUE(MID(C101,8,1)))+5*(VALUE(MID(C101,3,1))+VALUE(MID(C101,9,1)))+4*(VALUE(MID(C101,4,1))+VALUE(MID(C101,10,1)))+3*(VALUE(MID(C101,5,1))+VALUE(MID(C101,11,1)))+2*(VALUE(MID(C101,6,1))+VALUE(MID(C101,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J101">
-        <f>IF(I101="","",IF(11-MOD(I101,11)&gt;9,0,11-MOD(I101,11)))</f>
-        <v/>
-      </c>
       <c r="K101">
+        <f>IF(J101="","",IF(11-MOD(J101,11)&gt;9,0,11-MOD(J101,11)))</f>
+        <v/>
+      </c>
+      <c r="L101">
         <f>IFERROR(IF(LEN(C101)&lt;&gt;13,"",IF(VALUE(MID(C101,5,3))&gt;=800,1000,2000)+VALUE(MID(C101,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L101">
-        <f>IFERROR(IF(K101="","",IF(AND(DAY(DATE(K101,VALUE(MID(C101,3,2)),VALUE(MID(C101,1,2))))=VALUE(MID(C101,1,2)),MONTH(DATE(K101,VALUE(MID(C101,3,2)),VALUE(MID(C101,1,2))))=VALUE(MID(C101,3,2))),DATE(K101,VALUE(MID(C101,3,2)),VALUE(MID(C101,1,2))),"")),"")</f>
+      <c r="M101">
+        <f>IFERROR(IF(L101="","",IF(AND(DAY(DATE(L101,VALUE(MID(C101,3,2)),VALUE(MID(C101,1,2))))=VALUE(MID(C101,1,2)),MONTH(DATE(L101,VALUE(MID(C101,3,2)),VALUE(MID(C101,1,2))))=VALUE(MID(C101,3,2))),DATE(L101,VALUE(MID(C101,3,2)),VALUE(MID(C101,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3606,27 +4010,31 @@
       <c r="B102" s="2" t="n"/>
       <c r="C102" s="3" t="n"/>
       <c r="D102" s="2" t="n"/>
-      <c r="E102" s="4" t="n"/>
-      <c r="F102" s="2" t="n"/>
+      <c r="E102" s="4">
+        <f>IF(A102="","",5)</f>
+        <v/>
+      </c>
+      <c r="F102" s="4" t="n"/>
       <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2">
-        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(J102="","JMBG sadrži nešto što nije cifra",IF(L102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;J102,"Pogrešna kontrolna cifra — treba "&amp;J102,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I102">
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2">
+        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(K102="","JMBG sadrži nešto što nije cifra",IF(M102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;K102,"Pogrešna kontrolna cifra — treba "&amp;K102,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J102">
         <f>IFERROR(IF(LEN(C102)&lt;&gt;13,"",7*(VALUE(MID(C102,1,1))+VALUE(MID(C102,7,1)))+6*(VALUE(MID(C102,2,1))+VALUE(MID(C102,8,1)))+5*(VALUE(MID(C102,3,1))+VALUE(MID(C102,9,1)))+4*(VALUE(MID(C102,4,1))+VALUE(MID(C102,10,1)))+3*(VALUE(MID(C102,5,1))+VALUE(MID(C102,11,1)))+2*(VALUE(MID(C102,6,1))+VALUE(MID(C102,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J102">
-        <f>IF(I102="","",IF(11-MOD(I102,11)&gt;9,0,11-MOD(I102,11)))</f>
-        <v/>
-      </c>
       <c r="K102">
+        <f>IF(J102="","",IF(11-MOD(J102,11)&gt;9,0,11-MOD(J102,11)))</f>
+        <v/>
+      </c>
+      <c r="L102">
         <f>IFERROR(IF(LEN(C102)&lt;&gt;13,"",IF(VALUE(MID(C102,5,3))&gt;=800,1000,2000)+VALUE(MID(C102,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L102">
-        <f>IFERROR(IF(K102="","",IF(AND(DAY(DATE(K102,VALUE(MID(C102,3,2)),VALUE(MID(C102,1,2))))=VALUE(MID(C102,1,2)),MONTH(DATE(K102,VALUE(MID(C102,3,2)),VALUE(MID(C102,1,2))))=VALUE(MID(C102,3,2))),DATE(K102,VALUE(MID(C102,3,2)),VALUE(MID(C102,1,2))),"")),"")</f>
+      <c r="M102">
+        <f>IFERROR(IF(L102="","",IF(AND(DAY(DATE(L102,VALUE(MID(C102,3,2)),VALUE(MID(C102,1,2))))=VALUE(MID(C102,1,2)),MONTH(DATE(L102,VALUE(MID(C102,3,2)),VALUE(MID(C102,1,2))))=VALUE(MID(C102,3,2))),DATE(L102,VALUE(MID(C102,3,2)),VALUE(MID(C102,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3635,27 +4043,31 @@
       <c r="B103" s="2" t="n"/>
       <c r="C103" s="3" t="n"/>
       <c r="D103" s="2" t="n"/>
-      <c r="E103" s="4" t="n"/>
-      <c r="F103" s="2" t="n"/>
+      <c r="E103" s="4">
+        <f>IF(A103="","",5)</f>
+        <v/>
+      </c>
+      <c r="F103" s="4" t="n"/>
       <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2">
-        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(J103="","JMBG sadrži nešto što nije cifra",IF(L103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;J103,"Pogrešna kontrolna cifra — treba "&amp;J103,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I103">
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2">
+        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(K103="","JMBG sadrži nešto što nije cifra",IF(M103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;K103,"Pogrešna kontrolna cifra — treba "&amp;K103,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J103">
         <f>IFERROR(IF(LEN(C103)&lt;&gt;13,"",7*(VALUE(MID(C103,1,1))+VALUE(MID(C103,7,1)))+6*(VALUE(MID(C103,2,1))+VALUE(MID(C103,8,1)))+5*(VALUE(MID(C103,3,1))+VALUE(MID(C103,9,1)))+4*(VALUE(MID(C103,4,1))+VALUE(MID(C103,10,1)))+3*(VALUE(MID(C103,5,1))+VALUE(MID(C103,11,1)))+2*(VALUE(MID(C103,6,1))+VALUE(MID(C103,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J103">
-        <f>IF(I103="","",IF(11-MOD(I103,11)&gt;9,0,11-MOD(I103,11)))</f>
-        <v/>
-      </c>
       <c r="K103">
+        <f>IF(J103="","",IF(11-MOD(J103,11)&gt;9,0,11-MOD(J103,11)))</f>
+        <v/>
+      </c>
+      <c r="L103">
         <f>IFERROR(IF(LEN(C103)&lt;&gt;13,"",IF(VALUE(MID(C103,5,3))&gt;=800,1000,2000)+VALUE(MID(C103,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L103">
-        <f>IFERROR(IF(K103="","",IF(AND(DAY(DATE(K103,VALUE(MID(C103,3,2)),VALUE(MID(C103,1,2))))=VALUE(MID(C103,1,2)),MONTH(DATE(K103,VALUE(MID(C103,3,2)),VALUE(MID(C103,1,2))))=VALUE(MID(C103,3,2))),DATE(K103,VALUE(MID(C103,3,2)),VALUE(MID(C103,1,2))),"")),"")</f>
+      <c r="M103">
+        <f>IFERROR(IF(L103="","",IF(AND(DAY(DATE(L103,VALUE(MID(C103,3,2)),VALUE(MID(C103,1,2))))=VALUE(MID(C103,1,2)),MONTH(DATE(L103,VALUE(MID(C103,3,2)),VALUE(MID(C103,1,2))))=VALUE(MID(C103,3,2))),DATE(L103,VALUE(MID(C103,3,2)),VALUE(MID(C103,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3664,27 +4076,31 @@
       <c r="B104" s="2" t="n"/>
       <c r="C104" s="3" t="n"/>
       <c r="D104" s="2" t="n"/>
-      <c r="E104" s="4" t="n"/>
-      <c r="F104" s="2" t="n"/>
+      <c r="E104" s="4">
+        <f>IF(A104="","",5)</f>
+        <v/>
+      </c>
+      <c r="F104" s="4" t="n"/>
       <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2">
-        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(J104="","JMBG sadrži nešto što nije cifra",IF(L104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;J104,"Pogrešna kontrolna cifra — treba "&amp;J104,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I104">
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2">
+        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(K104="","JMBG sadrži nešto što nije cifra",IF(M104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;K104,"Pogrešna kontrolna cifra — treba "&amp;K104,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J104">
         <f>IFERROR(IF(LEN(C104)&lt;&gt;13,"",7*(VALUE(MID(C104,1,1))+VALUE(MID(C104,7,1)))+6*(VALUE(MID(C104,2,1))+VALUE(MID(C104,8,1)))+5*(VALUE(MID(C104,3,1))+VALUE(MID(C104,9,1)))+4*(VALUE(MID(C104,4,1))+VALUE(MID(C104,10,1)))+3*(VALUE(MID(C104,5,1))+VALUE(MID(C104,11,1)))+2*(VALUE(MID(C104,6,1))+VALUE(MID(C104,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J104">
-        <f>IF(I104="","",IF(11-MOD(I104,11)&gt;9,0,11-MOD(I104,11)))</f>
-        <v/>
-      </c>
       <c r="K104">
+        <f>IF(J104="","",IF(11-MOD(J104,11)&gt;9,0,11-MOD(J104,11)))</f>
+        <v/>
+      </c>
+      <c r="L104">
         <f>IFERROR(IF(LEN(C104)&lt;&gt;13,"",IF(VALUE(MID(C104,5,3))&gt;=800,1000,2000)+VALUE(MID(C104,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L104">
-        <f>IFERROR(IF(K104="","",IF(AND(DAY(DATE(K104,VALUE(MID(C104,3,2)),VALUE(MID(C104,1,2))))=VALUE(MID(C104,1,2)),MONTH(DATE(K104,VALUE(MID(C104,3,2)),VALUE(MID(C104,1,2))))=VALUE(MID(C104,3,2))),DATE(K104,VALUE(MID(C104,3,2)),VALUE(MID(C104,1,2))),"")),"")</f>
+      <c r="M104">
+        <f>IFERROR(IF(L104="","",IF(AND(DAY(DATE(L104,VALUE(MID(C104,3,2)),VALUE(MID(C104,1,2))))=VALUE(MID(C104,1,2)),MONTH(DATE(L104,VALUE(MID(C104,3,2)),VALUE(MID(C104,1,2))))=VALUE(MID(C104,3,2))),DATE(L104,VALUE(MID(C104,3,2)),VALUE(MID(C104,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3693,27 +4109,31 @@
       <c r="B105" s="2" t="n"/>
       <c r="C105" s="3" t="n"/>
       <c r="D105" s="2" t="n"/>
-      <c r="E105" s="4" t="n"/>
-      <c r="F105" s="2" t="n"/>
+      <c r="E105" s="4">
+        <f>IF(A105="","",5)</f>
+        <v/>
+      </c>
+      <c r="F105" s="4" t="n"/>
       <c r="G105" s="2" t="n"/>
-      <c r="H105" s="2">
-        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(J105="","JMBG sadrži nešto što nije cifra",IF(L105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;J105,"Pogrešna kontrolna cifra — treba "&amp;J105,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I105">
+      <c r="H105" s="2" t="n"/>
+      <c r="I105" s="2">
+        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(K105="","JMBG sadrži nešto što nije cifra",IF(M105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;K105,"Pogrešna kontrolna cifra — treba "&amp;K105,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J105">
         <f>IFERROR(IF(LEN(C105)&lt;&gt;13,"",7*(VALUE(MID(C105,1,1))+VALUE(MID(C105,7,1)))+6*(VALUE(MID(C105,2,1))+VALUE(MID(C105,8,1)))+5*(VALUE(MID(C105,3,1))+VALUE(MID(C105,9,1)))+4*(VALUE(MID(C105,4,1))+VALUE(MID(C105,10,1)))+3*(VALUE(MID(C105,5,1))+VALUE(MID(C105,11,1)))+2*(VALUE(MID(C105,6,1))+VALUE(MID(C105,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J105">
-        <f>IF(I105="","",IF(11-MOD(I105,11)&gt;9,0,11-MOD(I105,11)))</f>
-        <v/>
-      </c>
       <c r="K105">
+        <f>IF(J105="","",IF(11-MOD(J105,11)&gt;9,0,11-MOD(J105,11)))</f>
+        <v/>
+      </c>
+      <c r="L105">
         <f>IFERROR(IF(LEN(C105)&lt;&gt;13,"",IF(VALUE(MID(C105,5,3))&gt;=800,1000,2000)+VALUE(MID(C105,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L105">
-        <f>IFERROR(IF(K105="","",IF(AND(DAY(DATE(K105,VALUE(MID(C105,3,2)),VALUE(MID(C105,1,2))))=VALUE(MID(C105,1,2)),MONTH(DATE(K105,VALUE(MID(C105,3,2)),VALUE(MID(C105,1,2))))=VALUE(MID(C105,3,2))),DATE(K105,VALUE(MID(C105,3,2)),VALUE(MID(C105,1,2))),"")),"")</f>
+      <c r="M105">
+        <f>IFERROR(IF(L105="","",IF(AND(DAY(DATE(L105,VALUE(MID(C105,3,2)),VALUE(MID(C105,1,2))))=VALUE(MID(C105,1,2)),MONTH(DATE(L105,VALUE(MID(C105,3,2)),VALUE(MID(C105,1,2))))=VALUE(MID(C105,3,2))),DATE(L105,VALUE(MID(C105,3,2)),VALUE(MID(C105,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3722,27 +4142,31 @@
       <c r="B106" s="2" t="n"/>
       <c r="C106" s="3" t="n"/>
       <c r="D106" s="2" t="n"/>
-      <c r="E106" s="4" t="n"/>
-      <c r="F106" s="2" t="n"/>
+      <c r="E106" s="4">
+        <f>IF(A106="","",5)</f>
+        <v/>
+      </c>
+      <c r="F106" s="4" t="n"/>
       <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2">
-        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(J106="","JMBG sadrži nešto što nije cifra",IF(L106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;J106,"Pogrešna kontrolna cifra — treba "&amp;J106,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I106">
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2">
+        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(K106="","JMBG sadrži nešto što nije cifra",IF(M106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;K106,"Pogrešna kontrolna cifra — treba "&amp;K106,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J106">
         <f>IFERROR(IF(LEN(C106)&lt;&gt;13,"",7*(VALUE(MID(C106,1,1))+VALUE(MID(C106,7,1)))+6*(VALUE(MID(C106,2,1))+VALUE(MID(C106,8,1)))+5*(VALUE(MID(C106,3,1))+VALUE(MID(C106,9,1)))+4*(VALUE(MID(C106,4,1))+VALUE(MID(C106,10,1)))+3*(VALUE(MID(C106,5,1))+VALUE(MID(C106,11,1)))+2*(VALUE(MID(C106,6,1))+VALUE(MID(C106,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J106">
-        <f>IF(I106="","",IF(11-MOD(I106,11)&gt;9,0,11-MOD(I106,11)))</f>
-        <v/>
-      </c>
       <c r="K106">
+        <f>IF(J106="","",IF(11-MOD(J106,11)&gt;9,0,11-MOD(J106,11)))</f>
+        <v/>
+      </c>
+      <c r="L106">
         <f>IFERROR(IF(LEN(C106)&lt;&gt;13,"",IF(VALUE(MID(C106,5,3))&gt;=800,1000,2000)+VALUE(MID(C106,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L106">
-        <f>IFERROR(IF(K106="","",IF(AND(DAY(DATE(K106,VALUE(MID(C106,3,2)),VALUE(MID(C106,1,2))))=VALUE(MID(C106,1,2)),MONTH(DATE(K106,VALUE(MID(C106,3,2)),VALUE(MID(C106,1,2))))=VALUE(MID(C106,3,2))),DATE(K106,VALUE(MID(C106,3,2)),VALUE(MID(C106,1,2))),"")),"")</f>
+      <c r="M106">
+        <f>IFERROR(IF(L106="","",IF(AND(DAY(DATE(L106,VALUE(MID(C106,3,2)),VALUE(MID(C106,1,2))))=VALUE(MID(C106,1,2)),MONTH(DATE(L106,VALUE(MID(C106,3,2)),VALUE(MID(C106,1,2))))=VALUE(MID(C106,3,2))),DATE(L106,VALUE(MID(C106,3,2)),VALUE(MID(C106,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3751,27 +4175,31 @@
       <c r="B107" s="2" t="n"/>
       <c r="C107" s="3" t="n"/>
       <c r="D107" s="2" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="2" t="n"/>
+      <c r="E107" s="4">
+        <f>IF(A107="","",5)</f>
+        <v/>
+      </c>
+      <c r="F107" s="4" t="n"/>
       <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2">
-        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(J107="","JMBG sadrži nešto što nije cifra",IF(L107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;J107,"Pogrešna kontrolna cifra — treba "&amp;J107,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I107">
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2">
+        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(K107="","JMBG sadrži nešto što nije cifra",IF(M107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;K107,"Pogrešna kontrolna cifra — treba "&amp;K107,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J107">
         <f>IFERROR(IF(LEN(C107)&lt;&gt;13,"",7*(VALUE(MID(C107,1,1))+VALUE(MID(C107,7,1)))+6*(VALUE(MID(C107,2,1))+VALUE(MID(C107,8,1)))+5*(VALUE(MID(C107,3,1))+VALUE(MID(C107,9,1)))+4*(VALUE(MID(C107,4,1))+VALUE(MID(C107,10,1)))+3*(VALUE(MID(C107,5,1))+VALUE(MID(C107,11,1)))+2*(VALUE(MID(C107,6,1))+VALUE(MID(C107,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J107">
-        <f>IF(I107="","",IF(11-MOD(I107,11)&gt;9,0,11-MOD(I107,11)))</f>
-        <v/>
-      </c>
       <c r="K107">
+        <f>IF(J107="","",IF(11-MOD(J107,11)&gt;9,0,11-MOD(J107,11)))</f>
+        <v/>
+      </c>
+      <c r="L107">
         <f>IFERROR(IF(LEN(C107)&lt;&gt;13,"",IF(VALUE(MID(C107,5,3))&gt;=800,1000,2000)+VALUE(MID(C107,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L107">
-        <f>IFERROR(IF(K107="","",IF(AND(DAY(DATE(K107,VALUE(MID(C107,3,2)),VALUE(MID(C107,1,2))))=VALUE(MID(C107,1,2)),MONTH(DATE(K107,VALUE(MID(C107,3,2)),VALUE(MID(C107,1,2))))=VALUE(MID(C107,3,2))),DATE(K107,VALUE(MID(C107,3,2)),VALUE(MID(C107,1,2))),"")),"")</f>
+      <c r="M107">
+        <f>IFERROR(IF(L107="","",IF(AND(DAY(DATE(L107,VALUE(MID(C107,3,2)),VALUE(MID(C107,1,2))))=VALUE(MID(C107,1,2)),MONTH(DATE(L107,VALUE(MID(C107,3,2)),VALUE(MID(C107,1,2))))=VALUE(MID(C107,3,2))),DATE(L107,VALUE(MID(C107,3,2)),VALUE(MID(C107,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3780,27 +4208,31 @@
       <c r="B108" s="2" t="n"/>
       <c r="C108" s="3" t="n"/>
       <c r="D108" s="2" t="n"/>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="2" t="n"/>
+      <c r="E108" s="4">
+        <f>IF(A108="","",5)</f>
+        <v/>
+      </c>
+      <c r="F108" s="4" t="n"/>
       <c r="G108" s="2" t="n"/>
-      <c r="H108" s="2">
-        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(J108="","JMBG sadrži nešto što nije cifra",IF(L108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;J108,"Pogrešna kontrolna cifra — treba "&amp;J108,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I108">
+      <c r="H108" s="2" t="n"/>
+      <c r="I108" s="2">
+        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(K108="","JMBG sadrži nešto što nije cifra",IF(M108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;K108,"Pogrešna kontrolna cifra — treba "&amp;K108,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J108">
         <f>IFERROR(IF(LEN(C108)&lt;&gt;13,"",7*(VALUE(MID(C108,1,1))+VALUE(MID(C108,7,1)))+6*(VALUE(MID(C108,2,1))+VALUE(MID(C108,8,1)))+5*(VALUE(MID(C108,3,1))+VALUE(MID(C108,9,1)))+4*(VALUE(MID(C108,4,1))+VALUE(MID(C108,10,1)))+3*(VALUE(MID(C108,5,1))+VALUE(MID(C108,11,1)))+2*(VALUE(MID(C108,6,1))+VALUE(MID(C108,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J108">
-        <f>IF(I108="","",IF(11-MOD(I108,11)&gt;9,0,11-MOD(I108,11)))</f>
-        <v/>
-      </c>
       <c r="K108">
+        <f>IF(J108="","",IF(11-MOD(J108,11)&gt;9,0,11-MOD(J108,11)))</f>
+        <v/>
+      </c>
+      <c r="L108">
         <f>IFERROR(IF(LEN(C108)&lt;&gt;13,"",IF(VALUE(MID(C108,5,3))&gt;=800,1000,2000)+VALUE(MID(C108,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L108">
-        <f>IFERROR(IF(K108="","",IF(AND(DAY(DATE(K108,VALUE(MID(C108,3,2)),VALUE(MID(C108,1,2))))=VALUE(MID(C108,1,2)),MONTH(DATE(K108,VALUE(MID(C108,3,2)),VALUE(MID(C108,1,2))))=VALUE(MID(C108,3,2))),DATE(K108,VALUE(MID(C108,3,2)),VALUE(MID(C108,1,2))),"")),"")</f>
+      <c r="M108">
+        <f>IFERROR(IF(L108="","",IF(AND(DAY(DATE(L108,VALUE(MID(C108,3,2)),VALUE(MID(C108,1,2))))=VALUE(MID(C108,1,2)),MONTH(DATE(L108,VALUE(MID(C108,3,2)),VALUE(MID(C108,1,2))))=VALUE(MID(C108,3,2))),DATE(L108,VALUE(MID(C108,3,2)),VALUE(MID(C108,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3809,27 +4241,31 @@
       <c r="B109" s="2" t="n"/>
       <c r="C109" s="3" t="n"/>
       <c r="D109" s="2" t="n"/>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="2" t="n"/>
+      <c r="E109" s="4">
+        <f>IF(A109="","",5)</f>
+        <v/>
+      </c>
+      <c r="F109" s="4" t="n"/>
       <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2">
-        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(J109="","JMBG sadrži nešto što nije cifra",IF(L109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;J109,"Pogrešna kontrolna cifra — treba "&amp;J109,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I109">
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2">
+        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(K109="","JMBG sadrži nešto što nije cifra",IF(M109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;K109,"Pogrešna kontrolna cifra — treba "&amp;K109,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J109">
         <f>IFERROR(IF(LEN(C109)&lt;&gt;13,"",7*(VALUE(MID(C109,1,1))+VALUE(MID(C109,7,1)))+6*(VALUE(MID(C109,2,1))+VALUE(MID(C109,8,1)))+5*(VALUE(MID(C109,3,1))+VALUE(MID(C109,9,1)))+4*(VALUE(MID(C109,4,1))+VALUE(MID(C109,10,1)))+3*(VALUE(MID(C109,5,1))+VALUE(MID(C109,11,1)))+2*(VALUE(MID(C109,6,1))+VALUE(MID(C109,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J109">
-        <f>IF(I109="","",IF(11-MOD(I109,11)&gt;9,0,11-MOD(I109,11)))</f>
-        <v/>
-      </c>
       <c r="K109">
+        <f>IF(J109="","",IF(11-MOD(J109,11)&gt;9,0,11-MOD(J109,11)))</f>
+        <v/>
+      </c>
+      <c r="L109">
         <f>IFERROR(IF(LEN(C109)&lt;&gt;13,"",IF(VALUE(MID(C109,5,3))&gt;=800,1000,2000)+VALUE(MID(C109,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L109">
-        <f>IFERROR(IF(K109="","",IF(AND(DAY(DATE(K109,VALUE(MID(C109,3,2)),VALUE(MID(C109,1,2))))=VALUE(MID(C109,1,2)),MONTH(DATE(K109,VALUE(MID(C109,3,2)),VALUE(MID(C109,1,2))))=VALUE(MID(C109,3,2))),DATE(K109,VALUE(MID(C109,3,2)),VALUE(MID(C109,1,2))),"")),"")</f>
+      <c r="M109">
+        <f>IFERROR(IF(L109="","",IF(AND(DAY(DATE(L109,VALUE(MID(C109,3,2)),VALUE(MID(C109,1,2))))=VALUE(MID(C109,1,2)),MONTH(DATE(L109,VALUE(MID(C109,3,2)),VALUE(MID(C109,1,2))))=VALUE(MID(C109,3,2))),DATE(L109,VALUE(MID(C109,3,2)),VALUE(MID(C109,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3838,27 +4274,31 @@
       <c r="B110" s="2" t="n"/>
       <c r="C110" s="3" t="n"/>
       <c r="D110" s="2" t="n"/>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="2" t="n"/>
+      <c r="E110" s="4">
+        <f>IF(A110="","",5)</f>
+        <v/>
+      </c>
+      <c r="F110" s="4" t="n"/>
       <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2">
-        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(J110="","JMBG sadrži nešto što nije cifra",IF(L110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;J110,"Pogrešna kontrolna cifra — treba "&amp;J110,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I110">
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2">
+        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(K110="","JMBG sadrži nešto što nije cifra",IF(M110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;K110,"Pogrešna kontrolna cifra — treba "&amp;K110,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J110">
         <f>IFERROR(IF(LEN(C110)&lt;&gt;13,"",7*(VALUE(MID(C110,1,1))+VALUE(MID(C110,7,1)))+6*(VALUE(MID(C110,2,1))+VALUE(MID(C110,8,1)))+5*(VALUE(MID(C110,3,1))+VALUE(MID(C110,9,1)))+4*(VALUE(MID(C110,4,1))+VALUE(MID(C110,10,1)))+3*(VALUE(MID(C110,5,1))+VALUE(MID(C110,11,1)))+2*(VALUE(MID(C110,6,1))+VALUE(MID(C110,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J110">
-        <f>IF(I110="","",IF(11-MOD(I110,11)&gt;9,0,11-MOD(I110,11)))</f>
-        <v/>
-      </c>
       <c r="K110">
+        <f>IF(J110="","",IF(11-MOD(J110,11)&gt;9,0,11-MOD(J110,11)))</f>
+        <v/>
+      </c>
+      <c r="L110">
         <f>IFERROR(IF(LEN(C110)&lt;&gt;13,"",IF(VALUE(MID(C110,5,3))&gt;=800,1000,2000)+VALUE(MID(C110,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L110">
-        <f>IFERROR(IF(K110="","",IF(AND(DAY(DATE(K110,VALUE(MID(C110,3,2)),VALUE(MID(C110,1,2))))=VALUE(MID(C110,1,2)),MONTH(DATE(K110,VALUE(MID(C110,3,2)),VALUE(MID(C110,1,2))))=VALUE(MID(C110,3,2))),DATE(K110,VALUE(MID(C110,3,2)),VALUE(MID(C110,1,2))),"")),"")</f>
+      <c r="M110">
+        <f>IFERROR(IF(L110="","",IF(AND(DAY(DATE(L110,VALUE(MID(C110,3,2)),VALUE(MID(C110,1,2))))=VALUE(MID(C110,1,2)),MONTH(DATE(L110,VALUE(MID(C110,3,2)),VALUE(MID(C110,1,2))))=VALUE(MID(C110,3,2))),DATE(L110,VALUE(MID(C110,3,2)),VALUE(MID(C110,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3867,27 +4307,31 @@
       <c r="B111" s="2" t="n"/>
       <c r="C111" s="3" t="n"/>
       <c r="D111" s="2" t="n"/>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="2" t="n"/>
+      <c r="E111" s="4">
+        <f>IF(A111="","",5)</f>
+        <v/>
+      </c>
+      <c r="F111" s="4" t="n"/>
       <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2">
-        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(J111="","JMBG sadrži nešto što nije cifra",IF(L111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;J111,"Pogrešna kontrolna cifra — treba "&amp;J111,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I111">
+      <c r="H111" s="2" t="n"/>
+      <c r="I111" s="2">
+        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(K111="","JMBG sadrži nešto što nije cifra",IF(M111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;K111,"Pogrešna kontrolna cifra — treba "&amp;K111,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J111">
         <f>IFERROR(IF(LEN(C111)&lt;&gt;13,"",7*(VALUE(MID(C111,1,1))+VALUE(MID(C111,7,1)))+6*(VALUE(MID(C111,2,1))+VALUE(MID(C111,8,1)))+5*(VALUE(MID(C111,3,1))+VALUE(MID(C111,9,1)))+4*(VALUE(MID(C111,4,1))+VALUE(MID(C111,10,1)))+3*(VALUE(MID(C111,5,1))+VALUE(MID(C111,11,1)))+2*(VALUE(MID(C111,6,1))+VALUE(MID(C111,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J111">
-        <f>IF(I111="","",IF(11-MOD(I111,11)&gt;9,0,11-MOD(I111,11)))</f>
-        <v/>
-      </c>
       <c r="K111">
+        <f>IF(J111="","",IF(11-MOD(J111,11)&gt;9,0,11-MOD(J111,11)))</f>
+        <v/>
+      </c>
+      <c r="L111">
         <f>IFERROR(IF(LEN(C111)&lt;&gt;13,"",IF(VALUE(MID(C111,5,3))&gt;=800,1000,2000)+VALUE(MID(C111,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L111">
-        <f>IFERROR(IF(K111="","",IF(AND(DAY(DATE(K111,VALUE(MID(C111,3,2)),VALUE(MID(C111,1,2))))=VALUE(MID(C111,1,2)),MONTH(DATE(K111,VALUE(MID(C111,3,2)),VALUE(MID(C111,1,2))))=VALUE(MID(C111,3,2))),DATE(K111,VALUE(MID(C111,3,2)),VALUE(MID(C111,1,2))),"")),"")</f>
+      <c r="M111">
+        <f>IFERROR(IF(L111="","",IF(AND(DAY(DATE(L111,VALUE(MID(C111,3,2)),VALUE(MID(C111,1,2))))=VALUE(MID(C111,1,2)),MONTH(DATE(L111,VALUE(MID(C111,3,2)),VALUE(MID(C111,1,2))))=VALUE(MID(C111,3,2))),DATE(L111,VALUE(MID(C111,3,2)),VALUE(MID(C111,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3896,27 +4340,31 @@
       <c r="B112" s="2" t="n"/>
       <c r="C112" s="3" t="n"/>
       <c r="D112" s="2" t="n"/>
-      <c r="E112" s="4" t="n"/>
-      <c r="F112" s="2" t="n"/>
+      <c r="E112" s="4">
+        <f>IF(A112="","",5)</f>
+        <v/>
+      </c>
+      <c r="F112" s="4" t="n"/>
       <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2">
-        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(J112="","JMBG sadrži nešto što nije cifra",IF(L112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;J112,"Pogrešna kontrolna cifra — treba "&amp;J112,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I112">
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2">
+        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(K112="","JMBG sadrži nešto što nije cifra",IF(M112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;K112,"Pogrešna kontrolna cifra — treba "&amp;K112,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J112">
         <f>IFERROR(IF(LEN(C112)&lt;&gt;13,"",7*(VALUE(MID(C112,1,1))+VALUE(MID(C112,7,1)))+6*(VALUE(MID(C112,2,1))+VALUE(MID(C112,8,1)))+5*(VALUE(MID(C112,3,1))+VALUE(MID(C112,9,1)))+4*(VALUE(MID(C112,4,1))+VALUE(MID(C112,10,1)))+3*(VALUE(MID(C112,5,1))+VALUE(MID(C112,11,1)))+2*(VALUE(MID(C112,6,1))+VALUE(MID(C112,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J112">
-        <f>IF(I112="","",IF(11-MOD(I112,11)&gt;9,0,11-MOD(I112,11)))</f>
-        <v/>
-      </c>
       <c r="K112">
+        <f>IF(J112="","",IF(11-MOD(J112,11)&gt;9,0,11-MOD(J112,11)))</f>
+        <v/>
+      </c>
+      <c r="L112">
         <f>IFERROR(IF(LEN(C112)&lt;&gt;13,"",IF(VALUE(MID(C112,5,3))&gt;=800,1000,2000)+VALUE(MID(C112,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L112">
-        <f>IFERROR(IF(K112="","",IF(AND(DAY(DATE(K112,VALUE(MID(C112,3,2)),VALUE(MID(C112,1,2))))=VALUE(MID(C112,1,2)),MONTH(DATE(K112,VALUE(MID(C112,3,2)),VALUE(MID(C112,1,2))))=VALUE(MID(C112,3,2))),DATE(K112,VALUE(MID(C112,3,2)),VALUE(MID(C112,1,2))),"")),"")</f>
+      <c r="M112">
+        <f>IFERROR(IF(L112="","",IF(AND(DAY(DATE(L112,VALUE(MID(C112,3,2)),VALUE(MID(C112,1,2))))=VALUE(MID(C112,1,2)),MONTH(DATE(L112,VALUE(MID(C112,3,2)),VALUE(MID(C112,1,2))))=VALUE(MID(C112,3,2))),DATE(L112,VALUE(MID(C112,3,2)),VALUE(MID(C112,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3925,27 +4373,31 @@
       <c r="B113" s="2" t="n"/>
       <c r="C113" s="3" t="n"/>
       <c r="D113" s="2" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="2" t="n"/>
+      <c r="E113" s="4">
+        <f>IF(A113="","",5)</f>
+        <v/>
+      </c>
+      <c r="F113" s="4" t="n"/>
       <c r="G113" s="2" t="n"/>
-      <c r="H113" s="2">
-        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(J113="","JMBG sadrži nešto što nije cifra",IF(L113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;J113,"Pogrešna kontrolna cifra — treba "&amp;J113,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I113">
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2">
+        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(K113="","JMBG sadrži nešto što nije cifra",IF(M113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;K113,"Pogrešna kontrolna cifra — treba "&amp;K113,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J113">
         <f>IFERROR(IF(LEN(C113)&lt;&gt;13,"",7*(VALUE(MID(C113,1,1))+VALUE(MID(C113,7,1)))+6*(VALUE(MID(C113,2,1))+VALUE(MID(C113,8,1)))+5*(VALUE(MID(C113,3,1))+VALUE(MID(C113,9,1)))+4*(VALUE(MID(C113,4,1))+VALUE(MID(C113,10,1)))+3*(VALUE(MID(C113,5,1))+VALUE(MID(C113,11,1)))+2*(VALUE(MID(C113,6,1))+VALUE(MID(C113,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J113">
-        <f>IF(I113="","",IF(11-MOD(I113,11)&gt;9,0,11-MOD(I113,11)))</f>
-        <v/>
-      </c>
       <c r="K113">
+        <f>IF(J113="","",IF(11-MOD(J113,11)&gt;9,0,11-MOD(J113,11)))</f>
+        <v/>
+      </c>
+      <c r="L113">
         <f>IFERROR(IF(LEN(C113)&lt;&gt;13,"",IF(VALUE(MID(C113,5,3))&gt;=800,1000,2000)+VALUE(MID(C113,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L113">
-        <f>IFERROR(IF(K113="","",IF(AND(DAY(DATE(K113,VALUE(MID(C113,3,2)),VALUE(MID(C113,1,2))))=VALUE(MID(C113,1,2)),MONTH(DATE(K113,VALUE(MID(C113,3,2)),VALUE(MID(C113,1,2))))=VALUE(MID(C113,3,2))),DATE(K113,VALUE(MID(C113,3,2)),VALUE(MID(C113,1,2))),"")),"")</f>
+      <c r="M113">
+        <f>IFERROR(IF(L113="","",IF(AND(DAY(DATE(L113,VALUE(MID(C113,3,2)),VALUE(MID(C113,1,2))))=VALUE(MID(C113,1,2)),MONTH(DATE(L113,VALUE(MID(C113,3,2)),VALUE(MID(C113,1,2))))=VALUE(MID(C113,3,2))),DATE(L113,VALUE(MID(C113,3,2)),VALUE(MID(C113,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3954,27 +4406,31 @@
       <c r="B114" s="2" t="n"/>
       <c r="C114" s="3" t="n"/>
       <c r="D114" s="2" t="n"/>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="2" t="n"/>
+      <c r="E114" s="4">
+        <f>IF(A114="","",5)</f>
+        <v/>
+      </c>
+      <c r="F114" s="4" t="n"/>
       <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2">
-        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(J114="","JMBG sadrži nešto što nije cifra",IF(L114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;J114,"Pogrešna kontrolna cifra — treba "&amp;J114,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I114">
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2">
+        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(K114="","JMBG sadrži nešto što nije cifra",IF(M114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;K114,"Pogrešna kontrolna cifra — treba "&amp;K114,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J114">
         <f>IFERROR(IF(LEN(C114)&lt;&gt;13,"",7*(VALUE(MID(C114,1,1))+VALUE(MID(C114,7,1)))+6*(VALUE(MID(C114,2,1))+VALUE(MID(C114,8,1)))+5*(VALUE(MID(C114,3,1))+VALUE(MID(C114,9,1)))+4*(VALUE(MID(C114,4,1))+VALUE(MID(C114,10,1)))+3*(VALUE(MID(C114,5,1))+VALUE(MID(C114,11,1)))+2*(VALUE(MID(C114,6,1))+VALUE(MID(C114,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J114">
-        <f>IF(I114="","",IF(11-MOD(I114,11)&gt;9,0,11-MOD(I114,11)))</f>
-        <v/>
-      </c>
       <c r="K114">
+        <f>IF(J114="","",IF(11-MOD(J114,11)&gt;9,0,11-MOD(J114,11)))</f>
+        <v/>
+      </c>
+      <c r="L114">
         <f>IFERROR(IF(LEN(C114)&lt;&gt;13,"",IF(VALUE(MID(C114,5,3))&gt;=800,1000,2000)+VALUE(MID(C114,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L114">
-        <f>IFERROR(IF(K114="","",IF(AND(DAY(DATE(K114,VALUE(MID(C114,3,2)),VALUE(MID(C114,1,2))))=VALUE(MID(C114,1,2)),MONTH(DATE(K114,VALUE(MID(C114,3,2)),VALUE(MID(C114,1,2))))=VALUE(MID(C114,3,2))),DATE(K114,VALUE(MID(C114,3,2)),VALUE(MID(C114,1,2))),"")),"")</f>
+      <c r="M114">
+        <f>IFERROR(IF(L114="","",IF(AND(DAY(DATE(L114,VALUE(MID(C114,3,2)),VALUE(MID(C114,1,2))))=VALUE(MID(C114,1,2)),MONTH(DATE(L114,VALUE(MID(C114,3,2)),VALUE(MID(C114,1,2))))=VALUE(MID(C114,3,2))),DATE(L114,VALUE(MID(C114,3,2)),VALUE(MID(C114,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -3983,27 +4439,31 @@
       <c r="B115" s="2" t="n"/>
       <c r="C115" s="3" t="n"/>
       <c r="D115" s="2" t="n"/>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="2" t="n"/>
+      <c r="E115" s="4">
+        <f>IF(A115="","",5)</f>
+        <v/>
+      </c>
+      <c r="F115" s="4" t="n"/>
       <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2">
-        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(J115="","JMBG sadrži nešto što nije cifra",IF(L115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;J115,"Pogrešna kontrolna cifra — treba "&amp;J115,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I115">
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2">
+        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(K115="","JMBG sadrži nešto što nije cifra",IF(M115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;K115,"Pogrešna kontrolna cifra — treba "&amp;K115,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J115">
         <f>IFERROR(IF(LEN(C115)&lt;&gt;13,"",7*(VALUE(MID(C115,1,1))+VALUE(MID(C115,7,1)))+6*(VALUE(MID(C115,2,1))+VALUE(MID(C115,8,1)))+5*(VALUE(MID(C115,3,1))+VALUE(MID(C115,9,1)))+4*(VALUE(MID(C115,4,1))+VALUE(MID(C115,10,1)))+3*(VALUE(MID(C115,5,1))+VALUE(MID(C115,11,1)))+2*(VALUE(MID(C115,6,1))+VALUE(MID(C115,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J115">
-        <f>IF(I115="","",IF(11-MOD(I115,11)&gt;9,0,11-MOD(I115,11)))</f>
-        <v/>
-      </c>
       <c r="K115">
+        <f>IF(J115="","",IF(11-MOD(J115,11)&gt;9,0,11-MOD(J115,11)))</f>
+        <v/>
+      </c>
+      <c r="L115">
         <f>IFERROR(IF(LEN(C115)&lt;&gt;13,"",IF(VALUE(MID(C115,5,3))&gt;=800,1000,2000)+VALUE(MID(C115,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L115">
-        <f>IFERROR(IF(K115="","",IF(AND(DAY(DATE(K115,VALUE(MID(C115,3,2)),VALUE(MID(C115,1,2))))=VALUE(MID(C115,1,2)),MONTH(DATE(K115,VALUE(MID(C115,3,2)),VALUE(MID(C115,1,2))))=VALUE(MID(C115,3,2))),DATE(K115,VALUE(MID(C115,3,2)),VALUE(MID(C115,1,2))),"")),"")</f>
+      <c r="M115">
+        <f>IFERROR(IF(L115="","",IF(AND(DAY(DATE(L115,VALUE(MID(C115,3,2)),VALUE(MID(C115,1,2))))=VALUE(MID(C115,1,2)),MONTH(DATE(L115,VALUE(MID(C115,3,2)),VALUE(MID(C115,1,2))))=VALUE(MID(C115,3,2))),DATE(L115,VALUE(MID(C115,3,2)),VALUE(MID(C115,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4012,27 +4472,31 @@
       <c r="B116" s="2" t="n"/>
       <c r="C116" s="3" t="n"/>
       <c r="D116" s="2" t="n"/>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="2" t="n"/>
+      <c r="E116" s="4">
+        <f>IF(A116="","",5)</f>
+        <v/>
+      </c>
+      <c r="F116" s="4" t="n"/>
       <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2">
-        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(J116="","JMBG sadrži nešto što nije cifra",IF(L116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;J116,"Pogrešna kontrolna cifra — treba "&amp;J116,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I116">
+      <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2">
+        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(K116="","JMBG sadrži nešto što nije cifra",IF(M116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;K116,"Pogrešna kontrolna cifra — treba "&amp;K116,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J116">
         <f>IFERROR(IF(LEN(C116)&lt;&gt;13,"",7*(VALUE(MID(C116,1,1))+VALUE(MID(C116,7,1)))+6*(VALUE(MID(C116,2,1))+VALUE(MID(C116,8,1)))+5*(VALUE(MID(C116,3,1))+VALUE(MID(C116,9,1)))+4*(VALUE(MID(C116,4,1))+VALUE(MID(C116,10,1)))+3*(VALUE(MID(C116,5,1))+VALUE(MID(C116,11,1)))+2*(VALUE(MID(C116,6,1))+VALUE(MID(C116,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J116">
-        <f>IF(I116="","",IF(11-MOD(I116,11)&gt;9,0,11-MOD(I116,11)))</f>
-        <v/>
-      </c>
       <c r="K116">
+        <f>IF(J116="","",IF(11-MOD(J116,11)&gt;9,0,11-MOD(J116,11)))</f>
+        <v/>
+      </c>
+      <c r="L116">
         <f>IFERROR(IF(LEN(C116)&lt;&gt;13,"",IF(VALUE(MID(C116,5,3))&gt;=800,1000,2000)+VALUE(MID(C116,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L116">
-        <f>IFERROR(IF(K116="","",IF(AND(DAY(DATE(K116,VALUE(MID(C116,3,2)),VALUE(MID(C116,1,2))))=VALUE(MID(C116,1,2)),MONTH(DATE(K116,VALUE(MID(C116,3,2)),VALUE(MID(C116,1,2))))=VALUE(MID(C116,3,2))),DATE(K116,VALUE(MID(C116,3,2)),VALUE(MID(C116,1,2))),"")),"")</f>
+      <c r="M116">
+        <f>IFERROR(IF(L116="","",IF(AND(DAY(DATE(L116,VALUE(MID(C116,3,2)),VALUE(MID(C116,1,2))))=VALUE(MID(C116,1,2)),MONTH(DATE(L116,VALUE(MID(C116,3,2)),VALUE(MID(C116,1,2))))=VALUE(MID(C116,3,2))),DATE(L116,VALUE(MID(C116,3,2)),VALUE(MID(C116,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4041,27 +4505,31 @@
       <c r="B117" s="2" t="n"/>
       <c r="C117" s="3" t="n"/>
       <c r="D117" s="2" t="n"/>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="2" t="n"/>
+      <c r="E117" s="4">
+        <f>IF(A117="","",5)</f>
+        <v/>
+      </c>
+      <c r="F117" s="4" t="n"/>
       <c r="G117" s="2" t="n"/>
-      <c r="H117" s="2">
-        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(J117="","JMBG sadrži nešto što nije cifra",IF(L117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;J117,"Pogrešna kontrolna cifra — treba "&amp;J117,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I117">
+      <c r="H117" s="2" t="n"/>
+      <c r="I117" s="2">
+        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(K117="","JMBG sadrži nešto što nije cifra",IF(M117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;K117,"Pogrešna kontrolna cifra — treba "&amp;K117,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J117">
         <f>IFERROR(IF(LEN(C117)&lt;&gt;13,"",7*(VALUE(MID(C117,1,1))+VALUE(MID(C117,7,1)))+6*(VALUE(MID(C117,2,1))+VALUE(MID(C117,8,1)))+5*(VALUE(MID(C117,3,1))+VALUE(MID(C117,9,1)))+4*(VALUE(MID(C117,4,1))+VALUE(MID(C117,10,1)))+3*(VALUE(MID(C117,5,1))+VALUE(MID(C117,11,1)))+2*(VALUE(MID(C117,6,1))+VALUE(MID(C117,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J117">
-        <f>IF(I117="","",IF(11-MOD(I117,11)&gt;9,0,11-MOD(I117,11)))</f>
-        <v/>
-      </c>
       <c r="K117">
+        <f>IF(J117="","",IF(11-MOD(J117,11)&gt;9,0,11-MOD(J117,11)))</f>
+        <v/>
+      </c>
+      <c r="L117">
         <f>IFERROR(IF(LEN(C117)&lt;&gt;13,"",IF(VALUE(MID(C117,5,3))&gt;=800,1000,2000)+VALUE(MID(C117,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L117">
-        <f>IFERROR(IF(K117="","",IF(AND(DAY(DATE(K117,VALUE(MID(C117,3,2)),VALUE(MID(C117,1,2))))=VALUE(MID(C117,1,2)),MONTH(DATE(K117,VALUE(MID(C117,3,2)),VALUE(MID(C117,1,2))))=VALUE(MID(C117,3,2))),DATE(K117,VALUE(MID(C117,3,2)),VALUE(MID(C117,1,2))),"")),"")</f>
+      <c r="M117">
+        <f>IFERROR(IF(L117="","",IF(AND(DAY(DATE(L117,VALUE(MID(C117,3,2)),VALUE(MID(C117,1,2))))=VALUE(MID(C117,1,2)),MONTH(DATE(L117,VALUE(MID(C117,3,2)),VALUE(MID(C117,1,2))))=VALUE(MID(C117,3,2))),DATE(L117,VALUE(MID(C117,3,2)),VALUE(MID(C117,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4070,27 +4538,31 @@
       <c r="B118" s="2" t="n"/>
       <c r="C118" s="3" t="n"/>
       <c r="D118" s="2" t="n"/>
-      <c r="E118" s="4" t="n"/>
-      <c r="F118" s="2" t="n"/>
+      <c r="E118" s="4">
+        <f>IF(A118="","",5)</f>
+        <v/>
+      </c>
+      <c r="F118" s="4" t="n"/>
       <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2">
-        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(J118="","JMBG sadrži nešto što nije cifra",IF(L118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;J118,"Pogrešna kontrolna cifra — treba "&amp;J118,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I118">
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2">
+        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(K118="","JMBG sadrži nešto što nije cifra",IF(M118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;K118,"Pogrešna kontrolna cifra — treba "&amp;K118,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J118">
         <f>IFERROR(IF(LEN(C118)&lt;&gt;13,"",7*(VALUE(MID(C118,1,1))+VALUE(MID(C118,7,1)))+6*(VALUE(MID(C118,2,1))+VALUE(MID(C118,8,1)))+5*(VALUE(MID(C118,3,1))+VALUE(MID(C118,9,1)))+4*(VALUE(MID(C118,4,1))+VALUE(MID(C118,10,1)))+3*(VALUE(MID(C118,5,1))+VALUE(MID(C118,11,1)))+2*(VALUE(MID(C118,6,1))+VALUE(MID(C118,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J118">
-        <f>IF(I118="","",IF(11-MOD(I118,11)&gt;9,0,11-MOD(I118,11)))</f>
-        <v/>
-      </c>
       <c r="K118">
+        <f>IF(J118="","",IF(11-MOD(J118,11)&gt;9,0,11-MOD(J118,11)))</f>
+        <v/>
+      </c>
+      <c r="L118">
         <f>IFERROR(IF(LEN(C118)&lt;&gt;13,"",IF(VALUE(MID(C118,5,3))&gt;=800,1000,2000)+VALUE(MID(C118,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L118">
-        <f>IFERROR(IF(K118="","",IF(AND(DAY(DATE(K118,VALUE(MID(C118,3,2)),VALUE(MID(C118,1,2))))=VALUE(MID(C118,1,2)),MONTH(DATE(K118,VALUE(MID(C118,3,2)),VALUE(MID(C118,1,2))))=VALUE(MID(C118,3,2))),DATE(K118,VALUE(MID(C118,3,2)),VALUE(MID(C118,1,2))),"")),"")</f>
+      <c r="M118">
+        <f>IFERROR(IF(L118="","",IF(AND(DAY(DATE(L118,VALUE(MID(C118,3,2)),VALUE(MID(C118,1,2))))=VALUE(MID(C118,1,2)),MONTH(DATE(L118,VALUE(MID(C118,3,2)),VALUE(MID(C118,1,2))))=VALUE(MID(C118,3,2))),DATE(L118,VALUE(MID(C118,3,2)),VALUE(MID(C118,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4099,27 +4571,31 @@
       <c r="B119" s="2" t="n"/>
       <c r="C119" s="3" t="n"/>
       <c r="D119" s="2" t="n"/>
-      <c r="E119" s="4" t="n"/>
-      <c r="F119" s="2" t="n"/>
+      <c r="E119" s="4">
+        <f>IF(A119="","",5)</f>
+        <v/>
+      </c>
+      <c r="F119" s="4" t="n"/>
       <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2">
-        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(J119="","JMBG sadrži nešto što nije cifra",IF(L119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;J119,"Pogrešna kontrolna cifra — treba "&amp;J119,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I119">
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2">
+        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(K119="","JMBG sadrži nešto što nije cifra",IF(M119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;K119,"Pogrešna kontrolna cifra — treba "&amp;K119,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J119">
         <f>IFERROR(IF(LEN(C119)&lt;&gt;13,"",7*(VALUE(MID(C119,1,1))+VALUE(MID(C119,7,1)))+6*(VALUE(MID(C119,2,1))+VALUE(MID(C119,8,1)))+5*(VALUE(MID(C119,3,1))+VALUE(MID(C119,9,1)))+4*(VALUE(MID(C119,4,1))+VALUE(MID(C119,10,1)))+3*(VALUE(MID(C119,5,1))+VALUE(MID(C119,11,1)))+2*(VALUE(MID(C119,6,1))+VALUE(MID(C119,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J119">
-        <f>IF(I119="","",IF(11-MOD(I119,11)&gt;9,0,11-MOD(I119,11)))</f>
-        <v/>
-      </c>
       <c r="K119">
+        <f>IF(J119="","",IF(11-MOD(J119,11)&gt;9,0,11-MOD(J119,11)))</f>
+        <v/>
+      </c>
+      <c r="L119">
         <f>IFERROR(IF(LEN(C119)&lt;&gt;13,"",IF(VALUE(MID(C119,5,3))&gt;=800,1000,2000)+VALUE(MID(C119,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L119">
-        <f>IFERROR(IF(K119="","",IF(AND(DAY(DATE(K119,VALUE(MID(C119,3,2)),VALUE(MID(C119,1,2))))=VALUE(MID(C119,1,2)),MONTH(DATE(K119,VALUE(MID(C119,3,2)),VALUE(MID(C119,1,2))))=VALUE(MID(C119,3,2))),DATE(K119,VALUE(MID(C119,3,2)),VALUE(MID(C119,1,2))),"")),"")</f>
+      <c r="M119">
+        <f>IFERROR(IF(L119="","",IF(AND(DAY(DATE(L119,VALUE(MID(C119,3,2)),VALUE(MID(C119,1,2))))=VALUE(MID(C119,1,2)),MONTH(DATE(L119,VALUE(MID(C119,3,2)),VALUE(MID(C119,1,2))))=VALUE(MID(C119,3,2))),DATE(L119,VALUE(MID(C119,3,2)),VALUE(MID(C119,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4128,27 +4604,31 @@
       <c r="B120" s="2" t="n"/>
       <c r="C120" s="3" t="n"/>
       <c r="D120" s="2" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="2" t="n"/>
+      <c r="E120" s="4">
+        <f>IF(A120="","",5)</f>
+        <v/>
+      </c>
+      <c r="F120" s="4" t="n"/>
       <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2">
-        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(J120="","JMBG sadrži nešto što nije cifra",IF(L120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;J120,"Pogrešna kontrolna cifra — treba "&amp;J120,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I120">
+      <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2">
+        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(K120="","JMBG sadrži nešto što nije cifra",IF(M120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;K120,"Pogrešna kontrolna cifra — treba "&amp;K120,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J120">
         <f>IFERROR(IF(LEN(C120)&lt;&gt;13,"",7*(VALUE(MID(C120,1,1))+VALUE(MID(C120,7,1)))+6*(VALUE(MID(C120,2,1))+VALUE(MID(C120,8,1)))+5*(VALUE(MID(C120,3,1))+VALUE(MID(C120,9,1)))+4*(VALUE(MID(C120,4,1))+VALUE(MID(C120,10,1)))+3*(VALUE(MID(C120,5,1))+VALUE(MID(C120,11,1)))+2*(VALUE(MID(C120,6,1))+VALUE(MID(C120,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J120">
-        <f>IF(I120="","",IF(11-MOD(I120,11)&gt;9,0,11-MOD(I120,11)))</f>
-        <v/>
-      </c>
       <c r="K120">
+        <f>IF(J120="","",IF(11-MOD(J120,11)&gt;9,0,11-MOD(J120,11)))</f>
+        <v/>
+      </c>
+      <c r="L120">
         <f>IFERROR(IF(LEN(C120)&lt;&gt;13,"",IF(VALUE(MID(C120,5,3))&gt;=800,1000,2000)+VALUE(MID(C120,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L120">
-        <f>IFERROR(IF(K120="","",IF(AND(DAY(DATE(K120,VALUE(MID(C120,3,2)),VALUE(MID(C120,1,2))))=VALUE(MID(C120,1,2)),MONTH(DATE(K120,VALUE(MID(C120,3,2)),VALUE(MID(C120,1,2))))=VALUE(MID(C120,3,2))),DATE(K120,VALUE(MID(C120,3,2)),VALUE(MID(C120,1,2))),"")),"")</f>
+      <c r="M120">
+        <f>IFERROR(IF(L120="","",IF(AND(DAY(DATE(L120,VALUE(MID(C120,3,2)),VALUE(MID(C120,1,2))))=VALUE(MID(C120,1,2)),MONTH(DATE(L120,VALUE(MID(C120,3,2)),VALUE(MID(C120,1,2))))=VALUE(MID(C120,3,2))),DATE(L120,VALUE(MID(C120,3,2)),VALUE(MID(C120,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4157,27 +4637,31 @@
       <c r="B121" s="2" t="n"/>
       <c r="C121" s="3" t="n"/>
       <c r="D121" s="2" t="n"/>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="2" t="n"/>
+      <c r="E121" s="4">
+        <f>IF(A121="","",5)</f>
+        <v/>
+      </c>
+      <c r="F121" s="4" t="n"/>
       <c r="G121" s="2" t="n"/>
-      <c r="H121" s="2">
-        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(J121="","JMBG sadrži nešto što nije cifra",IF(L121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;J121,"Pogrešna kontrolna cifra — treba "&amp;J121,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I121">
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2">
+        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(K121="","JMBG sadrži nešto što nije cifra",IF(M121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;K121,"Pogrešna kontrolna cifra — treba "&amp;K121,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J121">
         <f>IFERROR(IF(LEN(C121)&lt;&gt;13,"",7*(VALUE(MID(C121,1,1))+VALUE(MID(C121,7,1)))+6*(VALUE(MID(C121,2,1))+VALUE(MID(C121,8,1)))+5*(VALUE(MID(C121,3,1))+VALUE(MID(C121,9,1)))+4*(VALUE(MID(C121,4,1))+VALUE(MID(C121,10,1)))+3*(VALUE(MID(C121,5,1))+VALUE(MID(C121,11,1)))+2*(VALUE(MID(C121,6,1))+VALUE(MID(C121,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J121">
-        <f>IF(I121="","",IF(11-MOD(I121,11)&gt;9,0,11-MOD(I121,11)))</f>
-        <v/>
-      </c>
       <c r="K121">
+        <f>IF(J121="","",IF(11-MOD(J121,11)&gt;9,0,11-MOD(J121,11)))</f>
+        <v/>
+      </c>
+      <c r="L121">
         <f>IFERROR(IF(LEN(C121)&lt;&gt;13,"",IF(VALUE(MID(C121,5,3))&gt;=800,1000,2000)+VALUE(MID(C121,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L121">
-        <f>IFERROR(IF(K121="","",IF(AND(DAY(DATE(K121,VALUE(MID(C121,3,2)),VALUE(MID(C121,1,2))))=VALUE(MID(C121,1,2)),MONTH(DATE(K121,VALUE(MID(C121,3,2)),VALUE(MID(C121,1,2))))=VALUE(MID(C121,3,2))),DATE(K121,VALUE(MID(C121,3,2)),VALUE(MID(C121,1,2))),"")),"")</f>
+      <c r="M121">
+        <f>IFERROR(IF(L121="","",IF(AND(DAY(DATE(L121,VALUE(MID(C121,3,2)),VALUE(MID(C121,1,2))))=VALUE(MID(C121,1,2)),MONTH(DATE(L121,VALUE(MID(C121,3,2)),VALUE(MID(C121,1,2))))=VALUE(MID(C121,3,2))),DATE(L121,VALUE(MID(C121,3,2)),VALUE(MID(C121,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4186,27 +4670,31 @@
       <c r="B122" s="2" t="n"/>
       <c r="C122" s="3" t="n"/>
       <c r="D122" s="2" t="n"/>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="2" t="n"/>
+      <c r="E122" s="4">
+        <f>IF(A122="","",5)</f>
+        <v/>
+      </c>
+      <c r="F122" s="4" t="n"/>
       <c r="G122" s="2" t="n"/>
-      <c r="H122" s="2">
-        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(J122="","JMBG sadrži nešto što nije cifra",IF(L122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;J122,"Pogrešna kontrolna cifra — treba "&amp;J122,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I122">
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2">
+        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(K122="","JMBG sadrži nešto što nije cifra",IF(M122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;K122,"Pogrešna kontrolna cifra — treba "&amp;K122,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J122">
         <f>IFERROR(IF(LEN(C122)&lt;&gt;13,"",7*(VALUE(MID(C122,1,1))+VALUE(MID(C122,7,1)))+6*(VALUE(MID(C122,2,1))+VALUE(MID(C122,8,1)))+5*(VALUE(MID(C122,3,1))+VALUE(MID(C122,9,1)))+4*(VALUE(MID(C122,4,1))+VALUE(MID(C122,10,1)))+3*(VALUE(MID(C122,5,1))+VALUE(MID(C122,11,1)))+2*(VALUE(MID(C122,6,1))+VALUE(MID(C122,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J122">
-        <f>IF(I122="","",IF(11-MOD(I122,11)&gt;9,0,11-MOD(I122,11)))</f>
-        <v/>
-      </c>
       <c r="K122">
+        <f>IF(J122="","",IF(11-MOD(J122,11)&gt;9,0,11-MOD(J122,11)))</f>
+        <v/>
+      </c>
+      <c r="L122">
         <f>IFERROR(IF(LEN(C122)&lt;&gt;13,"",IF(VALUE(MID(C122,5,3))&gt;=800,1000,2000)+VALUE(MID(C122,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L122">
-        <f>IFERROR(IF(K122="","",IF(AND(DAY(DATE(K122,VALUE(MID(C122,3,2)),VALUE(MID(C122,1,2))))=VALUE(MID(C122,1,2)),MONTH(DATE(K122,VALUE(MID(C122,3,2)),VALUE(MID(C122,1,2))))=VALUE(MID(C122,3,2))),DATE(K122,VALUE(MID(C122,3,2)),VALUE(MID(C122,1,2))),"")),"")</f>
+      <c r="M122">
+        <f>IFERROR(IF(L122="","",IF(AND(DAY(DATE(L122,VALUE(MID(C122,3,2)),VALUE(MID(C122,1,2))))=VALUE(MID(C122,1,2)),MONTH(DATE(L122,VALUE(MID(C122,3,2)),VALUE(MID(C122,1,2))))=VALUE(MID(C122,3,2))),DATE(L122,VALUE(MID(C122,3,2)),VALUE(MID(C122,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4215,27 +4703,31 @@
       <c r="B123" s="2" t="n"/>
       <c r="C123" s="3" t="n"/>
       <c r="D123" s="2" t="n"/>
-      <c r="E123" s="4" t="n"/>
-      <c r="F123" s="2" t="n"/>
+      <c r="E123" s="4">
+        <f>IF(A123="","",5)</f>
+        <v/>
+      </c>
+      <c r="F123" s="4" t="n"/>
       <c r="G123" s="2" t="n"/>
-      <c r="H123" s="2">
-        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(J123="","JMBG sadrži nešto što nije cifra",IF(L123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;J123,"Pogrešna kontrolna cifra — treba "&amp;J123,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I123">
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2">
+        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(K123="","JMBG sadrži nešto što nije cifra",IF(M123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;K123,"Pogrešna kontrolna cifra — treba "&amp;K123,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J123">
         <f>IFERROR(IF(LEN(C123)&lt;&gt;13,"",7*(VALUE(MID(C123,1,1))+VALUE(MID(C123,7,1)))+6*(VALUE(MID(C123,2,1))+VALUE(MID(C123,8,1)))+5*(VALUE(MID(C123,3,1))+VALUE(MID(C123,9,1)))+4*(VALUE(MID(C123,4,1))+VALUE(MID(C123,10,1)))+3*(VALUE(MID(C123,5,1))+VALUE(MID(C123,11,1)))+2*(VALUE(MID(C123,6,1))+VALUE(MID(C123,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J123">
-        <f>IF(I123="","",IF(11-MOD(I123,11)&gt;9,0,11-MOD(I123,11)))</f>
-        <v/>
-      </c>
       <c r="K123">
+        <f>IF(J123="","",IF(11-MOD(J123,11)&gt;9,0,11-MOD(J123,11)))</f>
+        <v/>
+      </c>
+      <c r="L123">
         <f>IFERROR(IF(LEN(C123)&lt;&gt;13,"",IF(VALUE(MID(C123,5,3))&gt;=800,1000,2000)+VALUE(MID(C123,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L123">
-        <f>IFERROR(IF(K123="","",IF(AND(DAY(DATE(K123,VALUE(MID(C123,3,2)),VALUE(MID(C123,1,2))))=VALUE(MID(C123,1,2)),MONTH(DATE(K123,VALUE(MID(C123,3,2)),VALUE(MID(C123,1,2))))=VALUE(MID(C123,3,2))),DATE(K123,VALUE(MID(C123,3,2)),VALUE(MID(C123,1,2))),"")),"")</f>
+      <c r="M123">
+        <f>IFERROR(IF(L123="","",IF(AND(DAY(DATE(L123,VALUE(MID(C123,3,2)),VALUE(MID(C123,1,2))))=VALUE(MID(C123,1,2)),MONTH(DATE(L123,VALUE(MID(C123,3,2)),VALUE(MID(C123,1,2))))=VALUE(MID(C123,3,2))),DATE(L123,VALUE(MID(C123,3,2)),VALUE(MID(C123,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4244,27 +4736,31 @@
       <c r="B124" s="2" t="n"/>
       <c r="C124" s="3" t="n"/>
       <c r="D124" s="2" t="n"/>
-      <c r="E124" s="4" t="n"/>
-      <c r="F124" s="2" t="n"/>
+      <c r="E124" s="4">
+        <f>IF(A124="","",5)</f>
+        <v/>
+      </c>
+      <c r="F124" s="4" t="n"/>
       <c r="G124" s="2" t="n"/>
-      <c r="H124" s="2">
-        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(J124="","JMBG sadrži nešto što nije cifra",IF(L124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;J124,"Pogrešna kontrolna cifra — treba "&amp;J124,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I124">
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2">
+        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(K124="","JMBG sadrži nešto što nije cifra",IF(M124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;K124,"Pogrešna kontrolna cifra — treba "&amp;K124,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J124">
         <f>IFERROR(IF(LEN(C124)&lt;&gt;13,"",7*(VALUE(MID(C124,1,1))+VALUE(MID(C124,7,1)))+6*(VALUE(MID(C124,2,1))+VALUE(MID(C124,8,1)))+5*(VALUE(MID(C124,3,1))+VALUE(MID(C124,9,1)))+4*(VALUE(MID(C124,4,1))+VALUE(MID(C124,10,1)))+3*(VALUE(MID(C124,5,1))+VALUE(MID(C124,11,1)))+2*(VALUE(MID(C124,6,1))+VALUE(MID(C124,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J124">
-        <f>IF(I124="","",IF(11-MOD(I124,11)&gt;9,0,11-MOD(I124,11)))</f>
-        <v/>
-      </c>
       <c r="K124">
+        <f>IF(J124="","",IF(11-MOD(J124,11)&gt;9,0,11-MOD(J124,11)))</f>
+        <v/>
+      </c>
+      <c r="L124">
         <f>IFERROR(IF(LEN(C124)&lt;&gt;13,"",IF(VALUE(MID(C124,5,3))&gt;=800,1000,2000)+VALUE(MID(C124,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L124">
-        <f>IFERROR(IF(K124="","",IF(AND(DAY(DATE(K124,VALUE(MID(C124,3,2)),VALUE(MID(C124,1,2))))=VALUE(MID(C124,1,2)),MONTH(DATE(K124,VALUE(MID(C124,3,2)),VALUE(MID(C124,1,2))))=VALUE(MID(C124,3,2))),DATE(K124,VALUE(MID(C124,3,2)),VALUE(MID(C124,1,2))),"")),"")</f>
+      <c r="M124">
+        <f>IFERROR(IF(L124="","",IF(AND(DAY(DATE(L124,VALUE(MID(C124,3,2)),VALUE(MID(C124,1,2))))=VALUE(MID(C124,1,2)),MONTH(DATE(L124,VALUE(MID(C124,3,2)),VALUE(MID(C124,1,2))))=VALUE(MID(C124,3,2))),DATE(L124,VALUE(MID(C124,3,2)),VALUE(MID(C124,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4273,27 +4769,31 @@
       <c r="B125" s="2" t="n"/>
       <c r="C125" s="3" t="n"/>
       <c r="D125" s="2" t="n"/>
-      <c r="E125" s="4" t="n"/>
-      <c r="F125" s="2" t="n"/>
+      <c r="E125" s="4">
+        <f>IF(A125="","",5)</f>
+        <v/>
+      </c>
+      <c r="F125" s="4" t="n"/>
       <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2">
-        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(J125="","JMBG sadrži nešto što nije cifra",IF(L125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;J125,"Pogrešna kontrolna cifra — treba "&amp;J125,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I125">
+      <c r="H125" s="2" t="n"/>
+      <c r="I125" s="2">
+        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(K125="","JMBG sadrži nešto što nije cifra",IF(M125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;K125,"Pogrešna kontrolna cifra — treba "&amp;K125,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J125">
         <f>IFERROR(IF(LEN(C125)&lt;&gt;13,"",7*(VALUE(MID(C125,1,1))+VALUE(MID(C125,7,1)))+6*(VALUE(MID(C125,2,1))+VALUE(MID(C125,8,1)))+5*(VALUE(MID(C125,3,1))+VALUE(MID(C125,9,1)))+4*(VALUE(MID(C125,4,1))+VALUE(MID(C125,10,1)))+3*(VALUE(MID(C125,5,1))+VALUE(MID(C125,11,1)))+2*(VALUE(MID(C125,6,1))+VALUE(MID(C125,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J125">
-        <f>IF(I125="","",IF(11-MOD(I125,11)&gt;9,0,11-MOD(I125,11)))</f>
-        <v/>
-      </c>
       <c r="K125">
+        <f>IF(J125="","",IF(11-MOD(J125,11)&gt;9,0,11-MOD(J125,11)))</f>
+        <v/>
+      </c>
+      <c r="L125">
         <f>IFERROR(IF(LEN(C125)&lt;&gt;13,"",IF(VALUE(MID(C125,5,3))&gt;=800,1000,2000)+VALUE(MID(C125,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L125">
-        <f>IFERROR(IF(K125="","",IF(AND(DAY(DATE(K125,VALUE(MID(C125,3,2)),VALUE(MID(C125,1,2))))=VALUE(MID(C125,1,2)),MONTH(DATE(K125,VALUE(MID(C125,3,2)),VALUE(MID(C125,1,2))))=VALUE(MID(C125,3,2))),DATE(K125,VALUE(MID(C125,3,2)),VALUE(MID(C125,1,2))),"")),"")</f>
+      <c r="M125">
+        <f>IFERROR(IF(L125="","",IF(AND(DAY(DATE(L125,VALUE(MID(C125,3,2)),VALUE(MID(C125,1,2))))=VALUE(MID(C125,1,2)),MONTH(DATE(L125,VALUE(MID(C125,3,2)),VALUE(MID(C125,1,2))))=VALUE(MID(C125,3,2))),DATE(L125,VALUE(MID(C125,3,2)),VALUE(MID(C125,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4302,27 +4802,31 @@
       <c r="B126" s="2" t="n"/>
       <c r="C126" s="3" t="n"/>
       <c r="D126" s="2" t="n"/>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="2" t="n"/>
+      <c r="E126" s="4">
+        <f>IF(A126="","",5)</f>
+        <v/>
+      </c>
+      <c r="F126" s="4" t="n"/>
       <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2">
-        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(J126="","JMBG sadrži nešto što nije cifra",IF(L126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;J126,"Pogrešna kontrolna cifra — treba "&amp;J126,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I126">
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2">
+        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(K126="","JMBG sadrži nešto što nije cifra",IF(M126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;K126,"Pogrešna kontrolna cifra — treba "&amp;K126,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J126">
         <f>IFERROR(IF(LEN(C126)&lt;&gt;13,"",7*(VALUE(MID(C126,1,1))+VALUE(MID(C126,7,1)))+6*(VALUE(MID(C126,2,1))+VALUE(MID(C126,8,1)))+5*(VALUE(MID(C126,3,1))+VALUE(MID(C126,9,1)))+4*(VALUE(MID(C126,4,1))+VALUE(MID(C126,10,1)))+3*(VALUE(MID(C126,5,1))+VALUE(MID(C126,11,1)))+2*(VALUE(MID(C126,6,1))+VALUE(MID(C126,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J126">
-        <f>IF(I126="","",IF(11-MOD(I126,11)&gt;9,0,11-MOD(I126,11)))</f>
-        <v/>
-      </c>
       <c r="K126">
+        <f>IF(J126="","",IF(11-MOD(J126,11)&gt;9,0,11-MOD(J126,11)))</f>
+        <v/>
+      </c>
+      <c r="L126">
         <f>IFERROR(IF(LEN(C126)&lt;&gt;13,"",IF(VALUE(MID(C126,5,3))&gt;=800,1000,2000)+VALUE(MID(C126,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L126">
-        <f>IFERROR(IF(K126="","",IF(AND(DAY(DATE(K126,VALUE(MID(C126,3,2)),VALUE(MID(C126,1,2))))=VALUE(MID(C126,1,2)),MONTH(DATE(K126,VALUE(MID(C126,3,2)),VALUE(MID(C126,1,2))))=VALUE(MID(C126,3,2))),DATE(K126,VALUE(MID(C126,3,2)),VALUE(MID(C126,1,2))),"")),"")</f>
+      <c r="M126">
+        <f>IFERROR(IF(L126="","",IF(AND(DAY(DATE(L126,VALUE(MID(C126,3,2)),VALUE(MID(C126,1,2))))=VALUE(MID(C126,1,2)),MONTH(DATE(L126,VALUE(MID(C126,3,2)),VALUE(MID(C126,1,2))))=VALUE(MID(C126,3,2))),DATE(L126,VALUE(MID(C126,3,2)),VALUE(MID(C126,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4331,27 +4835,31 @@
       <c r="B127" s="2" t="n"/>
       <c r="C127" s="3" t="n"/>
       <c r="D127" s="2" t="n"/>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="2" t="n"/>
+      <c r="E127" s="4">
+        <f>IF(A127="","",5)</f>
+        <v/>
+      </c>
+      <c r="F127" s="4" t="n"/>
       <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2">
-        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(J127="","JMBG sadrži nešto što nije cifra",IF(L127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;J127,"Pogrešna kontrolna cifra — treba "&amp;J127,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I127">
+      <c r="H127" s="2" t="n"/>
+      <c r="I127" s="2">
+        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(K127="","JMBG sadrži nešto što nije cifra",IF(M127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;K127,"Pogrešna kontrolna cifra — treba "&amp;K127,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J127">
         <f>IFERROR(IF(LEN(C127)&lt;&gt;13,"",7*(VALUE(MID(C127,1,1))+VALUE(MID(C127,7,1)))+6*(VALUE(MID(C127,2,1))+VALUE(MID(C127,8,1)))+5*(VALUE(MID(C127,3,1))+VALUE(MID(C127,9,1)))+4*(VALUE(MID(C127,4,1))+VALUE(MID(C127,10,1)))+3*(VALUE(MID(C127,5,1))+VALUE(MID(C127,11,1)))+2*(VALUE(MID(C127,6,1))+VALUE(MID(C127,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J127">
-        <f>IF(I127="","",IF(11-MOD(I127,11)&gt;9,0,11-MOD(I127,11)))</f>
-        <v/>
-      </c>
       <c r="K127">
+        <f>IF(J127="","",IF(11-MOD(J127,11)&gt;9,0,11-MOD(J127,11)))</f>
+        <v/>
+      </c>
+      <c r="L127">
         <f>IFERROR(IF(LEN(C127)&lt;&gt;13,"",IF(VALUE(MID(C127,5,3))&gt;=800,1000,2000)+VALUE(MID(C127,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L127">
-        <f>IFERROR(IF(K127="","",IF(AND(DAY(DATE(K127,VALUE(MID(C127,3,2)),VALUE(MID(C127,1,2))))=VALUE(MID(C127,1,2)),MONTH(DATE(K127,VALUE(MID(C127,3,2)),VALUE(MID(C127,1,2))))=VALUE(MID(C127,3,2))),DATE(K127,VALUE(MID(C127,3,2)),VALUE(MID(C127,1,2))),"")),"")</f>
+      <c r="M127">
+        <f>IFERROR(IF(L127="","",IF(AND(DAY(DATE(L127,VALUE(MID(C127,3,2)),VALUE(MID(C127,1,2))))=VALUE(MID(C127,1,2)),MONTH(DATE(L127,VALUE(MID(C127,3,2)),VALUE(MID(C127,1,2))))=VALUE(MID(C127,3,2))),DATE(L127,VALUE(MID(C127,3,2)),VALUE(MID(C127,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4360,27 +4868,31 @@
       <c r="B128" s="2" t="n"/>
       <c r="C128" s="3" t="n"/>
       <c r="D128" s="2" t="n"/>
-      <c r="E128" s="4" t="n"/>
-      <c r="F128" s="2" t="n"/>
+      <c r="E128" s="4">
+        <f>IF(A128="","",5)</f>
+        <v/>
+      </c>
+      <c r="F128" s="4" t="n"/>
       <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2">
-        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(J128="","JMBG sadrži nešto što nije cifra",IF(L128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;J128,"Pogrešna kontrolna cifra — treba "&amp;J128,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I128">
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2">
+        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(K128="","JMBG sadrži nešto što nije cifra",IF(M128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;K128,"Pogrešna kontrolna cifra — treba "&amp;K128,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J128">
         <f>IFERROR(IF(LEN(C128)&lt;&gt;13,"",7*(VALUE(MID(C128,1,1))+VALUE(MID(C128,7,1)))+6*(VALUE(MID(C128,2,1))+VALUE(MID(C128,8,1)))+5*(VALUE(MID(C128,3,1))+VALUE(MID(C128,9,1)))+4*(VALUE(MID(C128,4,1))+VALUE(MID(C128,10,1)))+3*(VALUE(MID(C128,5,1))+VALUE(MID(C128,11,1)))+2*(VALUE(MID(C128,6,1))+VALUE(MID(C128,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J128">
-        <f>IF(I128="","",IF(11-MOD(I128,11)&gt;9,0,11-MOD(I128,11)))</f>
-        <v/>
-      </c>
       <c r="K128">
+        <f>IF(J128="","",IF(11-MOD(J128,11)&gt;9,0,11-MOD(J128,11)))</f>
+        <v/>
+      </c>
+      <c r="L128">
         <f>IFERROR(IF(LEN(C128)&lt;&gt;13,"",IF(VALUE(MID(C128,5,3))&gt;=800,1000,2000)+VALUE(MID(C128,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L128">
-        <f>IFERROR(IF(K128="","",IF(AND(DAY(DATE(K128,VALUE(MID(C128,3,2)),VALUE(MID(C128,1,2))))=VALUE(MID(C128,1,2)),MONTH(DATE(K128,VALUE(MID(C128,3,2)),VALUE(MID(C128,1,2))))=VALUE(MID(C128,3,2))),DATE(K128,VALUE(MID(C128,3,2)),VALUE(MID(C128,1,2))),"")),"")</f>
+      <c r="M128">
+        <f>IFERROR(IF(L128="","",IF(AND(DAY(DATE(L128,VALUE(MID(C128,3,2)),VALUE(MID(C128,1,2))))=VALUE(MID(C128,1,2)),MONTH(DATE(L128,VALUE(MID(C128,3,2)),VALUE(MID(C128,1,2))))=VALUE(MID(C128,3,2))),DATE(L128,VALUE(MID(C128,3,2)),VALUE(MID(C128,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4389,27 +4901,31 @@
       <c r="B129" s="2" t="n"/>
       <c r="C129" s="3" t="n"/>
       <c r="D129" s="2" t="n"/>
-      <c r="E129" s="4" t="n"/>
-      <c r="F129" s="2" t="n"/>
+      <c r="E129" s="4">
+        <f>IF(A129="","",5)</f>
+        <v/>
+      </c>
+      <c r="F129" s="4" t="n"/>
       <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2">
-        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(J129="","JMBG sadrži nešto što nije cifra",IF(L129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;J129,"Pogrešna kontrolna cifra — treba "&amp;J129,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I129">
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2">
+        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(K129="","JMBG sadrži nešto što nije cifra",IF(M129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;K129,"Pogrešna kontrolna cifra — treba "&amp;K129,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J129">
         <f>IFERROR(IF(LEN(C129)&lt;&gt;13,"",7*(VALUE(MID(C129,1,1))+VALUE(MID(C129,7,1)))+6*(VALUE(MID(C129,2,1))+VALUE(MID(C129,8,1)))+5*(VALUE(MID(C129,3,1))+VALUE(MID(C129,9,1)))+4*(VALUE(MID(C129,4,1))+VALUE(MID(C129,10,1)))+3*(VALUE(MID(C129,5,1))+VALUE(MID(C129,11,1)))+2*(VALUE(MID(C129,6,1))+VALUE(MID(C129,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J129">
-        <f>IF(I129="","",IF(11-MOD(I129,11)&gt;9,0,11-MOD(I129,11)))</f>
-        <v/>
-      </c>
       <c r="K129">
+        <f>IF(J129="","",IF(11-MOD(J129,11)&gt;9,0,11-MOD(J129,11)))</f>
+        <v/>
+      </c>
+      <c r="L129">
         <f>IFERROR(IF(LEN(C129)&lt;&gt;13,"",IF(VALUE(MID(C129,5,3))&gt;=800,1000,2000)+VALUE(MID(C129,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L129">
-        <f>IFERROR(IF(K129="","",IF(AND(DAY(DATE(K129,VALUE(MID(C129,3,2)),VALUE(MID(C129,1,2))))=VALUE(MID(C129,1,2)),MONTH(DATE(K129,VALUE(MID(C129,3,2)),VALUE(MID(C129,1,2))))=VALUE(MID(C129,3,2))),DATE(K129,VALUE(MID(C129,3,2)),VALUE(MID(C129,1,2))),"")),"")</f>
+      <c r="M129">
+        <f>IFERROR(IF(L129="","",IF(AND(DAY(DATE(L129,VALUE(MID(C129,3,2)),VALUE(MID(C129,1,2))))=VALUE(MID(C129,1,2)),MONTH(DATE(L129,VALUE(MID(C129,3,2)),VALUE(MID(C129,1,2))))=VALUE(MID(C129,3,2))),DATE(L129,VALUE(MID(C129,3,2)),VALUE(MID(C129,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4418,27 +4934,31 @@
       <c r="B130" s="2" t="n"/>
       <c r="C130" s="3" t="n"/>
       <c r="D130" s="2" t="n"/>
-      <c r="E130" s="4" t="n"/>
-      <c r="F130" s="2" t="n"/>
+      <c r="E130" s="4">
+        <f>IF(A130="","",5)</f>
+        <v/>
+      </c>
+      <c r="F130" s="4" t="n"/>
       <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2">
-        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(J130="","JMBG sadrži nešto što nije cifra",IF(L130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;J130,"Pogrešna kontrolna cifra — treba "&amp;J130,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I130">
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2">
+        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(K130="","JMBG sadrži nešto što nije cifra",IF(M130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;K130,"Pogrešna kontrolna cifra — treba "&amp;K130,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J130">
         <f>IFERROR(IF(LEN(C130)&lt;&gt;13,"",7*(VALUE(MID(C130,1,1))+VALUE(MID(C130,7,1)))+6*(VALUE(MID(C130,2,1))+VALUE(MID(C130,8,1)))+5*(VALUE(MID(C130,3,1))+VALUE(MID(C130,9,1)))+4*(VALUE(MID(C130,4,1))+VALUE(MID(C130,10,1)))+3*(VALUE(MID(C130,5,1))+VALUE(MID(C130,11,1)))+2*(VALUE(MID(C130,6,1))+VALUE(MID(C130,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J130">
-        <f>IF(I130="","",IF(11-MOD(I130,11)&gt;9,0,11-MOD(I130,11)))</f>
-        <v/>
-      </c>
       <c r="K130">
+        <f>IF(J130="","",IF(11-MOD(J130,11)&gt;9,0,11-MOD(J130,11)))</f>
+        <v/>
+      </c>
+      <c r="L130">
         <f>IFERROR(IF(LEN(C130)&lt;&gt;13,"",IF(VALUE(MID(C130,5,3))&gt;=800,1000,2000)+VALUE(MID(C130,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L130">
-        <f>IFERROR(IF(K130="","",IF(AND(DAY(DATE(K130,VALUE(MID(C130,3,2)),VALUE(MID(C130,1,2))))=VALUE(MID(C130,1,2)),MONTH(DATE(K130,VALUE(MID(C130,3,2)),VALUE(MID(C130,1,2))))=VALUE(MID(C130,3,2))),DATE(K130,VALUE(MID(C130,3,2)),VALUE(MID(C130,1,2))),"")),"")</f>
+      <c r="M130">
+        <f>IFERROR(IF(L130="","",IF(AND(DAY(DATE(L130,VALUE(MID(C130,3,2)),VALUE(MID(C130,1,2))))=VALUE(MID(C130,1,2)),MONTH(DATE(L130,VALUE(MID(C130,3,2)),VALUE(MID(C130,1,2))))=VALUE(MID(C130,3,2))),DATE(L130,VALUE(MID(C130,3,2)),VALUE(MID(C130,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4447,27 +4967,31 @@
       <c r="B131" s="2" t="n"/>
       <c r="C131" s="3" t="n"/>
       <c r="D131" s="2" t="n"/>
-      <c r="E131" s="4" t="n"/>
-      <c r="F131" s="2" t="n"/>
+      <c r="E131" s="4">
+        <f>IF(A131="","",5)</f>
+        <v/>
+      </c>
+      <c r="F131" s="4" t="n"/>
       <c r="G131" s="2" t="n"/>
-      <c r="H131" s="2">
-        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(J131="","JMBG sadrži nešto što nije cifra",IF(L131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;J131,"Pogrešna kontrolna cifra — treba "&amp;J131,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I131">
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2">
+        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(K131="","JMBG sadrži nešto što nije cifra",IF(M131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;K131,"Pogrešna kontrolna cifra — treba "&amp;K131,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J131">
         <f>IFERROR(IF(LEN(C131)&lt;&gt;13,"",7*(VALUE(MID(C131,1,1))+VALUE(MID(C131,7,1)))+6*(VALUE(MID(C131,2,1))+VALUE(MID(C131,8,1)))+5*(VALUE(MID(C131,3,1))+VALUE(MID(C131,9,1)))+4*(VALUE(MID(C131,4,1))+VALUE(MID(C131,10,1)))+3*(VALUE(MID(C131,5,1))+VALUE(MID(C131,11,1)))+2*(VALUE(MID(C131,6,1))+VALUE(MID(C131,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J131">
-        <f>IF(I131="","",IF(11-MOD(I131,11)&gt;9,0,11-MOD(I131,11)))</f>
-        <v/>
-      </c>
       <c r="K131">
+        <f>IF(J131="","",IF(11-MOD(J131,11)&gt;9,0,11-MOD(J131,11)))</f>
+        <v/>
+      </c>
+      <c r="L131">
         <f>IFERROR(IF(LEN(C131)&lt;&gt;13,"",IF(VALUE(MID(C131,5,3))&gt;=800,1000,2000)+VALUE(MID(C131,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L131">
-        <f>IFERROR(IF(K131="","",IF(AND(DAY(DATE(K131,VALUE(MID(C131,3,2)),VALUE(MID(C131,1,2))))=VALUE(MID(C131,1,2)),MONTH(DATE(K131,VALUE(MID(C131,3,2)),VALUE(MID(C131,1,2))))=VALUE(MID(C131,3,2))),DATE(K131,VALUE(MID(C131,3,2)),VALUE(MID(C131,1,2))),"")),"")</f>
+      <c r="M131">
+        <f>IFERROR(IF(L131="","",IF(AND(DAY(DATE(L131,VALUE(MID(C131,3,2)),VALUE(MID(C131,1,2))))=VALUE(MID(C131,1,2)),MONTH(DATE(L131,VALUE(MID(C131,3,2)),VALUE(MID(C131,1,2))))=VALUE(MID(C131,3,2))),DATE(L131,VALUE(MID(C131,3,2)),VALUE(MID(C131,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4476,27 +5000,31 @@
       <c r="B132" s="2" t="n"/>
       <c r="C132" s="3" t="n"/>
       <c r="D132" s="2" t="n"/>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="2" t="n"/>
+      <c r="E132" s="4">
+        <f>IF(A132="","",5)</f>
+        <v/>
+      </c>
+      <c r="F132" s="4" t="n"/>
       <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2">
-        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(J132="","JMBG sadrži nešto što nije cifra",IF(L132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;J132,"Pogrešna kontrolna cifra — treba "&amp;J132,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I132">
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2">
+        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(K132="","JMBG sadrži nešto što nije cifra",IF(M132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;K132,"Pogrešna kontrolna cifra — treba "&amp;K132,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J132">
         <f>IFERROR(IF(LEN(C132)&lt;&gt;13,"",7*(VALUE(MID(C132,1,1))+VALUE(MID(C132,7,1)))+6*(VALUE(MID(C132,2,1))+VALUE(MID(C132,8,1)))+5*(VALUE(MID(C132,3,1))+VALUE(MID(C132,9,1)))+4*(VALUE(MID(C132,4,1))+VALUE(MID(C132,10,1)))+3*(VALUE(MID(C132,5,1))+VALUE(MID(C132,11,1)))+2*(VALUE(MID(C132,6,1))+VALUE(MID(C132,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J132">
-        <f>IF(I132="","",IF(11-MOD(I132,11)&gt;9,0,11-MOD(I132,11)))</f>
-        <v/>
-      </c>
       <c r="K132">
+        <f>IF(J132="","",IF(11-MOD(J132,11)&gt;9,0,11-MOD(J132,11)))</f>
+        <v/>
+      </c>
+      <c r="L132">
         <f>IFERROR(IF(LEN(C132)&lt;&gt;13,"",IF(VALUE(MID(C132,5,3))&gt;=800,1000,2000)+VALUE(MID(C132,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L132">
-        <f>IFERROR(IF(K132="","",IF(AND(DAY(DATE(K132,VALUE(MID(C132,3,2)),VALUE(MID(C132,1,2))))=VALUE(MID(C132,1,2)),MONTH(DATE(K132,VALUE(MID(C132,3,2)),VALUE(MID(C132,1,2))))=VALUE(MID(C132,3,2))),DATE(K132,VALUE(MID(C132,3,2)),VALUE(MID(C132,1,2))),"")),"")</f>
+      <c r="M132">
+        <f>IFERROR(IF(L132="","",IF(AND(DAY(DATE(L132,VALUE(MID(C132,3,2)),VALUE(MID(C132,1,2))))=VALUE(MID(C132,1,2)),MONTH(DATE(L132,VALUE(MID(C132,3,2)),VALUE(MID(C132,1,2))))=VALUE(MID(C132,3,2))),DATE(L132,VALUE(MID(C132,3,2)),VALUE(MID(C132,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4505,27 +5033,31 @@
       <c r="B133" s="2" t="n"/>
       <c r="C133" s="3" t="n"/>
       <c r="D133" s="2" t="n"/>
-      <c r="E133" s="4" t="n"/>
-      <c r="F133" s="2" t="n"/>
+      <c r="E133" s="4">
+        <f>IF(A133="","",5)</f>
+        <v/>
+      </c>
+      <c r="F133" s="4" t="n"/>
       <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2">
-        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(J133="","JMBG sadrži nešto što nije cifra",IF(L133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;J133,"Pogrešna kontrolna cifra — treba "&amp;J133,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I133">
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2">
+        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(K133="","JMBG sadrži nešto što nije cifra",IF(M133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;K133,"Pogrešna kontrolna cifra — treba "&amp;K133,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J133">
         <f>IFERROR(IF(LEN(C133)&lt;&gt;13,"",7*(VALUE(MID(C133,1,1))+VALUE(MID(C133,7,1)))+6*(VALUE(MID(C133,2,1))+VALUE(MID(C133,8,1)))+5*(VALUE(MID(C133,3,1))+VALUE(MID(C133,9,1)))+4*(VALUE(MID(C133,4,1))+VALUE(MID(C133,10,1)))+3*(VALUE(MID(C133,5,1))+VALUE(MID(C133,11,1)))+2*(VALUE(MID(C133,6,1))+VALUE(MID(C133,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J133">
-        <f>IF(I133="","",IF(11-MOD(I133,11)&gt;9,0,11-MOD(I133,11)))</f>
-        <v/>
-      </c>
       <c r="K133">
+        <f>IF(J133="","",IF(11-MOD(J133,11)&gt;9,0,11-MOD(J133,11)))</f>
+        <v/>
+      </c>
+      <c r="L133">
         <f>IFERROR(IF(LEN(C133)&lt;&gt;13,"",IF(VALUE(MID(C133,5,3))&gt;=800,1000,2000)+VALUE(MID(C133,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L133">
-        <f>IFERROR(IF(K133="","",IF(AND(DAY(DATE(K133,VALUE(MID(C133,3,2)),VALUE(MID(C133,1,2))))=VALUE(MID(C133,1,2)),MONTH(DATE(K133,VALUE(MID(C133,3,2)),VALUE(MID(C133,1,2))))=VALUE(MID(C133,3,2))),DATE(K133,VALUE(MID(C133,3,2)),VALUE(MID(C133,1,2))),"")),"")</f>
+      <c r="M133">
+        <f>IFERROR(IF(L133="","",IF(AND(DAY(DATE(L133,VALUE(MID(C133,3,2)),VALUE(MID(C133,1,2))))=VALUE(MID(C133,1,2)),MONTH(DATE(L133,VALUE(MID(C133,3,2)),VALUE(MID(C133,1,2))))=VALUE(MID(C133,3,2))),DATE(L133,VALUE(MID(C133,3,2)),VALUE(MID(C133,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4534,27 +5066,31 @@
       <c r="B134" s="2" t="n"/>
       <c r="C134" s="3" t="n"/>
       <c r="D134" s="2" t="n"/>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="2" t="n"/>
+      <c r="E134" s="4">
+        <f>IF(A134="","",5)</f>
+        <v/>
+      </c>
+      <c r="F134" s="4" t="n"/>
       <c r="G134" s="2" t="n"/>
-      <c r="H134" s="2">
-        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(J134="","JMBG sadrži nešto što nije cifra",IF(L134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;J134,"Pogrešna kontrolna cifra — treba "&amp;J134,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I134">
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2">
+        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(K134="","JMBG sadrži nešto što nije cifra",IF(M134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;K134,"Pogrešna kontrolna cifra — treba "&amp;K134,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J134">
         <f>IFERROR(IF(LEN(C134)&lt;&gt;13,"",7*(VALUE(MID(C134,1,1))+VALUE(MID(C134,7,1)))+6*(VALUE(MID(C134,2,1))+VALUE(MID(C134,8,1)))+5*(VALUE(MID(C134,3,1))+VALUE(MID(C134,9,1)))+4*(VALUE(MID(C134,4,1))+VALUE(MID(C134,10,1)))+3*(VALUE(MID(C134,5,1))+VALUE(MID(C134,11,1)))+2*(VALUE(MID(C134,6,1))+VALUE(MID(C134,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J134">
-        <f>IF(I134="","",IF(11-MOD(I134,11)&gt;9,0,11-MOD(I134,11)))</f>
-        <v/>
-      </c>
       <c r="K134">
+        <f>IF(J134="","",IF(11-MOD(J134,11)&gt;9,0,11-MOD(J134,11)))</f>
+        <v/>
+      </c>
+      <c r="L134">
         <f>IFERROR(IF(LEN(C134)&lt;&gt;13,"",IF(VALUE(MID(C134,5,3))&gt;=800,1000,2000)+VALUE(MID(C134,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L134">
-        <f>IFERROR(IF(K134="","",IF(AND(DAY(DATE(K134,VALUE(MID(C134,3,2)),VALUE(MID(C134,1,2))))=VALUE(MID(C134,1,2)),MONTH(DATE(K134,VALUE(MID(C134,3,2)),VALUE(MID(C134,1,2))))=VALUE(MID(C134,3,2))),DATE(K134,VALUE(MID(C134,3,2)),VALUE(MID(C134,1,2))),"")),"")</f>
+      <c r="M134">
+        <f>IFERROR(IF(L134="","",IF(AND(DAY(DATE(L134,VALUE(MID(C134,3,2)),VALUE(MID(C134,1,2))))=VALUE(MID(C134,1,2)),MONTH(DATE(L134,VALUE(MID(C134,3,2)),VALUE(MID(C134,1,2))))=VALUE(MID(C134,3,2))),DATE(L134,VALUE(MID(C134,3,2)),VALUE(MID(C134,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4563,27 +5099,31 @@
       <c r="B135" s="2" t="n"/>
       <c r="C135" s="3" t="n"/>
       <c r="D135" s="2" t="n"/>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="2" t="n"/>
+      <c r="E135" s="4">
+        <f>IF(A135="","",5)</f>
+        <v/>
+      </c>
+      <c r="F135" s="4" t="n"/>
       <c r="G135" s="2" t="n"/>
-      <c r="H135" s="2">
-        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(J135="","JMBG sadrži nešto što nije cifra",IF(L135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;J135,"Pogrešna kontrolna cifra — treba "&amp;J135,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I135">
+      <c r="H135" s="2" t="n"/>
+      <c r="I135" s="2">
+        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(K135="","JMBG sadrži nešto što nije cifra",IF(M135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;K135,"Pogrešna kontrolna cifra — treba "&amp;K135,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J135">
         <f>IFERROR(IF(LEN(C135)&lt;&gt;13,"",7*(VALUE(MID(C135,1,1))+VALUE(MID(C135,7,1)))+6*(VALUE(MID(C135,2,1))+VALUE(MID(C135,8,1)))+5*(VALUE(MID(C135,3,1))+VALUE(MID(C135,9,1)))+4*(VALUE(MID(C135,4,1))+VALUE(MID(C135,10,1)))+3*(VALUE(MID(C135,5,1))+VALUE(MID(C135,11,1)))+2*(VALUE(MID(C135,6,1))+VALUE(MID(C135,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J135">
-        <f>IF(I135="","",IF(11-MOD(I135,11)&gt;9,0,11-MOD(I135,11)))</f>
-        <v/>
-      </c>
       <c r="K135">
+        <f>IF(J135="","",IF(11-MOD(J135,11)&gt;9,0,11-MOD(J135,11)))</f>
+        <v/>
+      </c>
+      <c r="L135">
         <f>IFERROR(IF(LEN(C135)&lt;&gt;13,"",IF(VALUE(MID(C135,5,3))&gt;=800,1000,2000)+VALUE(MID(C135,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L135">
-        <f>IFERROR(IF(K135="","",IF(AND(DAY(DATE(K135,VALUE(MID(C135,3,2)),VALUE(MID(C135,1,2))))=VALUE(MID(C135,1,2)),MONTH(DATE(K135,VALUE(MID(C135,3,2)),VALUE(MID(C135,1,2))))=VALUE(MID(C135,3,2))),DATE(K135,VALUE(MID(C135,3,2)),VALUE(MID(C135,1,2))),"")),"")</f>
+      <c r="M135">
+        <f>IFERROR(IF(L135="","",IF(AND(DAY(DATE(L135,VALUE(MID(C135,3,2)),VALUE(MID(C135,1,2))))=VALUE(MID(C135,1,2)),MONTH(DATE(L135,VALUE(MID(C135,3,2)),VALUE(MID(C135,1,2))))=VALUE(MID(C135,3,2))),DATE(L135,VALUE(MID(C135,3,2)),VALUE(MID(C135,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4592,27 +5132,31 @@
       <c r="B136" s="2" t="n"/>
       <c r="C136" s="3" t="n"/>
       <c r="D136" s="2" t="n"/>
-      <c r="E136" s="4" t="n"/>
-      <c r="F136" s="2" t="n"/>
+      <c r="E136" s="4">
+        <f>IF(A136="","",5)</f>
+        <v/>
+      </c>
+      <c r="F136" s="4" t="n"/>
       <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2">
-        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(J136="","JMBG sadrži nešto što nije cifra",IF(L136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;J136,"Pogrešna kontrolna cifra — treba "&amp;J136,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I136">
+      <c r="H136" s="2" t="n"/>
+      <c r="I136" s="2">
+        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(K136="","JMBG sadrži nešto što nije cifra",IF(M136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;K136,"Pogrešna kontrolna cifra — treba "&amp;K136,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J136">
         <f>IFERROR(IF(LEN(C136)&lt;&gt;13,"",7*(VALUE(MID(C136,1,1))+VALUE(MID(C136,7,1)))+6*(VALUE(MID(C136,2,1))+VALUE(MID(C136,8,1)))+5*(VALUE(MID(C136,3,1))+VALUE(MID(C136,9,1)))+4*(VALUE(MID(C136,4,1))+VALUE(MID(C136,10,1)))+3*(VALUE(MID(C136,5,1))+VALUE(MID(C136,11,1)))+2*(VALUE(MID(C136,6,1))+VALUE(MID(C136,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J136">
-        <f>IF(I136="","",IF(11-MOD(I136,11)&gt;9,0,11-MOD(I136,11)))</f>
-        <v/>
-      </c>
       <c r="K136">
+        <f>IF(J136="","",IF(11-MOD(J136,11)&gt;9,0,11-MOD(J136,11)))</f>
+        <v/>
+      </c>
+      <c r="L136">
         <f>IFERROR(IF(LEN(C136)&lt;&gt;13,"",IF(VALUE(MID(C136,5,3))&gt;=800,1000,2000)+VALUE(MID(C136,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L136">
-        <f>IFERROR(IF(K136="","",IF(AND(DAY(DATE(K136,VALUE(MID(C136,3,2)),VALUE(MID(C136,1,2))))=VALUE(MID(C136,1,2)),MONTH(DATE(K136,VALUE(MID(C136,3,2)),VALUE(MID(C136,1,2))))=VALUE(MID(C136,3,2))),DATE(K136,VALUE(MID(C136,3,2)),VALUE(MID(C136,1,2))),"")),"")</f>
+      <c r="M136">
+        <f>IFERROR(IF(L136="","",IF(AND(DAY(DATE(L136,VALUE(MID(C136,3,2)),VALUE(MID(C136,1,2))))=VALUE(MID(C136,1,2)),MONTH(DATE(L136,VALUE(MID(C136,3,2)),VALUE(MID(C136,1,2))))=VALUE(MID(C136,3,2))),DATE(L136,VALUE(MID(C136,3,2)),VALUE(MID(C136,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4621,27 +5165,31 @@
       <c r="B137" s="2" t="n"/>
       <c r="C137" s="3" t="n"/>
       <c r="D137" s="2" t="n"/>
-      <c r="E137" s="4" t="n"/>
-      <c r="F137" s="2" t="n"/>
+      <c r="E137" s="4">
+        <f>IF(A137="","",5)</f>
+        <v/>
+      </c>
+      <c r="F137" s="4" t="n"/>
       <c r="G137" s="2" t="n"/>
-      <c r="H137" s="2">
-        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(J137="","JMBG sadrži nešto što nije cifra",IF(L137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;J137,"Pogrešna kontrolna cifra — treba "&amp;J137,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I137">
+      <c r="H137" s="2" t="n"/>
+      <c r="I137" s="2">
+        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(K137="","JMBG sadrži nešto što nije cifra",IF(M137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;K137,"Pogrešna kontrolna cifra — treba "&amp;K137,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J137">
         <f>IFERROR(IF(LEN(C137)&lt;&gt;13,"",7*(VALUE(MID(C137,1,1))+VALUE(MID(C137,7,1)))+6*(VALUE(MID(C137,2,1))+VALUE(MID(C137,8,1)))+5*(VALUE(MID(C137,3,1))+VALUE(MID(C137,9,1)))+4*(VALUE(MID(C137,4,1))+VALUE(MID(C137,10,1)))+3*(VALUE(MID(C137,5,1))+VALUE(MID(C137,11,1)))+2*(VALUE(MID(C137,6,1))+VALUE(MID(C137,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J137">
-        <f>IF(I137="","",IF(11-MOD(I137,11)&gt;9,0,11-MOD(I137,11)))</f>
-        <v/>
-      </c>
       <c r="K137">
+        <f>IF(J137="","",IF(11-MOD(J137,11)&gt;9,0,11-MOD(J137,11)))</f>
+        <v/>
+      </c>
+      <c r="L137">
         <f>IFERROR(IF(LEN(C137)&lt;&gt;13,"",IF(VALUE(MID(C137,5,3))&gt;=800,1000,2000)+VALUE(MID(C137,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L137">
-        <f>IFERROR(IF(K137="","",IF(AND(DAY(DATE(K137,VALUE(MID(C137,3,2)),VALUE(MID(C137,1,2))))=VALUE(MID(C137,1,2)),MONTH(DATE(K137,VALUE(MID(C137,3,2)),VALUE(MID(C137,1,2))))=VALUE(MID(C137,3,2))),DATE(K137,VALUE(MID(C137,3,2)),VALUE(MID(C137,1,2))),"")),"")</f>
+      <c r="M137">
+        <f>IFERROR(IF(L137="","",IF(AND(DAY(DATE(L137,VALUE(MID(C137,3,2)),VALUE(MID(C137,1,2))))=VALUE(MID(C137,1,2)),MONTH(DATE(L137,VALUE(MID(C137,3,2)),VALUE(MID(C137,1,2))))=VALUE(MID(C137,3,2))),DATE(L137,VALUE(MID(C137,3,2)),VALUE(MID(C137,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4650,27 +5198,31 @@
       <c r="B138" s="2" t="n"/>
       <c r="C138" s="3" t="n"/>
       <c r="D138" s="2" t="n"/>
-      <c r="E138" s="4" t="n"/>
-      <c r="F138" s="2" t="n"/>
+      <c r="E138" s="4">
+        <f>IF(A138="","",5)</f>
+        <v/>
+      </c>
+      <c r="F138" s="4" t="n"/>
       <c r="G138" s="2" t="n"/>
-      <c r="H138" s="2">
-        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(J138="","JMBG sadrži nešto što nije cifra",IF(L138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;J138,"Pogrešna kontrolna cifra — treba "&amp;J138,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I138">
+      <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2">
+        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(K138="","JMBG sadrži nešto što nije cifra",IF(M138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;K138,"Pogrešna kontrolna cifra — treba "&amp;K138,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J138">
         <f>IFERROR(IF(LEN(C138)&lt;&gt;13,"",7*(VALUE(MID(C138,1,1))+VALUE(MID(C138,7,1)))+6*(VALUE(MID(C138,2,1))+VALUE(MID(C138,8,1)))+5*(VALUE(MID(C138,3,1))+VALUE(MID(C138,9,1)))+4*(VALUE(MID(C138,4,1))+VALUE(MID(C138,10,1)))+3*(VALUE(MID(C138,5,1))+VALUE(MID(C138,11,1)))+2*(VALUE(MID(C138,6,1))+VALUE(MID(C138,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J138">
-        <f>IF(I138="","",IF(11-MOD(I138,11)&gt;9,0,11-MOD(I138,11)))</f>
-        <v/>
-      </c>
       <c r="K138">
+        <f>IF(J138="","",IF(11-MOD(J138,11)&gt;9,0,11-MOD(J138,11)))</f>
+        <v/>
+      </c>
+      <c r="L138">
         <f>IFERROR(IF(LEN(C138)&lt;&gt;13,"",IF(VALUE(MID(C138,5,3))&gt;=800,1000,2000)+VALUE(MID(C138,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L138">
-        <f>IFERROR(IF(K138="","",IF(AND(DAY(DATE(K138,VALUE(MID(C138,3,2)),VALUE(MID(C138,1,2))))=VALUE(MID(C138,1,2)),MONTH(DATE(K138,VALUE(MID(C138,3,2)),VALUE(MID(C138,1,2))))=VALUE(MID(C138,3,2))),DATE(K138,VALUE(MID(C138,3,2)),VALUE(MID(C138,1,2))),"")),"")</f>
+      <c r="M138">
+        <f>IFERROR(IF(L138="","",IF(AND(DAY(DATE(L138,VALUE(MID(C138,3,2)),VALUE(MID(C138,1,2))))=VALUE(MID(C138,1,2)),MONTH(DATE(L138,VALUE(MID(C138,3,2)),VALUE(MID(C138,1,2))))=VALUE(MID(C138,3,2))),DATE(L138,VALUE(MID(C138,3,2)),VALUE(MID(C138,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4679,27 +5231,31 @@
       <c r="B139" s="2" t="n"/>
       <c r="C139" s="3" t="n"/>
       <c r="D139" s="2" t="n"/>
-      <c r="E139" s="4" t="n"/>
-      <c r="F139" s="2" t="n"/>
+      <c r="E139" s="4">
+        <f>IF(A139="","",5)</f>
+        <v/>
+      </c>
+      <c r="F139" s="4" t="n"/>
       <c r="G139" s="2" t="n"/>
-      <c r="H139" s="2">
-        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(J139="","JMBG sadrži nešto što nije cifra",IF(L139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;J139,"Pogrešna kontrolna cifra — treba "&amp;J139,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I139">
+      <c r="H139" s="2" t="n"/>
+      <c r="I139" s="2">
+        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(K139="","JMBG sadrži nešto što nije cifra",IF(M139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;K139,"Pogrešna kontrolna cifra — treba "&amp;K139,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J139">
         <f>IFERROR(IF(LEN(C139)&lt;&gt;13,"",7*(VALUE(MID(C139,1,1))+VALUE(MID(C139,7,1)))+6*(VALUE(MID(C139,2,1))+VALUE(MID(C139,8,1)))+5*(VALUE(MID(C139,3,1))+VALUE(MID(C139,9,1)))+4*(VALUE(MID(C139,4,1))+VALUE(MID(C139,10,1)))+3*(VALUE(MID(C139,5,1))+VALUE(MID(C139,11,1)))+2*(VALUE(MID(C139,6,1))+VALUE(MID(C139,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J139">
-        <f>IF(I139="","",IF(11-MOD(I139,11)&gt;9,0,11-MOD(I139,11)))</f>
-        <v/>
-      </c>
       <c r="K139">
+        <f>IF(J139="","",IF(11-MOD(J139,11)&gt;9,0,11-MOD(J139,11)))</f>
+        <v/>
+      </c>
+      <c r="L139">
         <f>IFERROR(IF(LEN(C139)&lt;&gt;13,"",IF(VALUE(MID(C139,5,3))&gt;=800,1000,2000)+VALUE(MID(C139,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L139">
-        <f>IFERROR(IF(K139="","",IF(AND(DAY(DATE(K139,VALUE(MID(C139,3,2)),VALUE(MID(C139,1,2))))=VALUE(MID(C139,1,2)),MONTH(DATE(K139,VALUE(MID(C139,3,2)),VALUE(MID(C139,1,2))))=VALUE(MID(C139,3,2))),DATE(K139,VALUE(MID(C139,3,2)),VALUE(MID(C139,1,2))),"")),"")</f>
+      <c r="M139">
+        <f>IFERROR(IF(L139="","",IF(AND(DAY(DATE(L139,VALUE(MID(C139,3,2)),VALUE(MID(C139,1,2))))=VALUE(MID(C139,1,2)),MONTH(DATE(L139,VALUE(MID(C139,3,2)),VALUE(MID(C139,1,2))))=VALUE(MID(C139,3,2))),DATE(L139,VALUE(MID(C139,3,2)),VALUE(MID(C139,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4708,27 +5264,31 @@
       <c r="B140" s="2" t="n"/>
       <c r="C140" s="3" t="n"/>
       <c r="D140" s="2" t="n"/>
-      <c r="E140" s="4" t="n"/>
-      <c r="F140" s="2" t="n"/>
+      <c r="E140" s="4">
+        <f>IF(A140="","",5)</f>
+        <v/>
+      </c>
+      <c r="F140" s="4" t="n"/>
       <c r="G140" s="2" t="n"/>
-      <c r="H140" s="2">
-        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(J140="","JMBG sadrži nešto što nije cifra",IF(L140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;J140,"Pogrešna kontrolna cifra — treba "&amp;J140,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I140">
+      <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2">
+        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(K140="","JMBG sadrži nešto što nije cifra",IF(M140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;K140,"Pogrešna kontrolna cifra — treba "&amp;K140,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J140">
         <f>IFERROR(IF(LEN(C140)&lt;&gt;13,"",7*(VALUE(MID(C140,1,1))+VALUE(MID(C140,7,1)))+6*(VALUE(MID(C140,2,1))+VALUE(MID(C140,8,1)))+5*(VALUE(MID(C140,3,1))+VALUE(MID(C140,9,1)))+4*(VALUE(MID(C140,4,1))+VALUE(MID(C140,10,1)))+3*(VALUE(MID(C140,5,1))+VALUE(MID(C140,11,1)))+2*(VALUE(MID(C140,6,1))+VALUE(MID(C140,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J140">
-        <f>IF(I140="","",IF(11-MOD(I140,11)&gt;9,0,11-MOD(I140,11)))</f>
-        <v/>
-      </c>
       <c r="K140">
+        <f>IF(J140="","",IF(11-MOD(J140,11)&gt;9,0,11-MOD(J140,11)))</f>
+        <v/>
+      </c>
+      <c r="L140">
         <f>IFERROR(IF(LEN(C140)&lt;&gt;13,"",IF(VALUE(MID(C140,5,3))&gt;=800,1000,2000)+VALUE(MID(C140,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L140">
-        <f>IFERROR(IF(K140="","",IF(AND(DAY(DATE(K140,VALUE(MID(C140,3,2)),VALUE(MID(C140,1,2))))=VALUE(MID(C140,1,2)),MONTH(DATE(K140,VALUE(MID(C140,3,2)),VALUE(MID(C140,1,2))))=VALUE(MID(C140,3,2))),DATE(K140,VALUE(MID(C140,3,2)),VALUE(MID(C140,1,2))),"")),"")</f>
+      <c r="M140">
+        <f>IFERROR(IF(L140="","",IF(AND(DAY(DATE(L140,VALUE(MID(C140,3,2)),VALUE(MID(C140,1,2))))=VALUE(MID(C140,1,2)),MONTH(DATE(L140,VALUE(MID(C140,3,2)),VALUE(MID(C140,1,2))))=VALUE(MID(C140,3,2))),DATE(L140,VALUE(MID(C140,3,2)),VALUE(MID(C140,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4737,27 +5297,31 @@
       <c r="B141" s="2" t="n"/>
       <c r="C141" s="3" t="n"/>
       <c r="D141" s="2" t="n"/>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="2" t="n"/>
+      <c r="E141" s="4">
+        <f>IF(A141="","",5)</f>
+        <v/>
+      </c>
+      <c r="F141" s="4" t="n"/>
       <c r="G141" s="2" t="n"/>
-      <c r="H141" s="2">
-        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(J141="","JMBG sadrži nešto što nije cifra",IF(L141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;J141,"Pogrešna kontrolna cifra — treba "&amp;J141,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I141">
+      <c r="H141" s="2" t="n"/>
+      <c r="I141" s="2">
+        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(K141="","JMBG sadrži nešto što nije cifra",IF(M141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;K141,"Pogrešna kontrolna cifra — treba "&amp;K141,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J141">
         <f>IFERROR(IF(LEN(C141)&lt;&gt;13,"",7*(VALUE(MID(C141,1,1))+VALUE(MID(C141,7,1)))+6*(VALUE(MID(C141,2,1))+VALUE(MID(C141,8,1)))+5*(VALUE(MID(C141,3,1))+VALUE(MID(C141,9,1)))+4*(VALUE(MID(C141,4,1))+VALUE(MID(C141,10,1)))+3*(VALUE(MID(C141,5,1))+VALUE(MID(C141,11,1)))+2*(VALUE(MID(C141,6,1))+VALUE(MID(C141,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J141">
-        <f>IF(I141="","",IF(11-MOD(I141,11)&gt;9,0,11-MOD(I141,11)))</f>
-        <v/>
-      </c>
       <c r="K141">
+        <f>IF(J141="","",IF(11-MOD(J141,11)&gt;9,0,11-MOD(J141,11)))</f>
+        <v/>
+      </c>
+      <c r="L141">
         <f>IFERROR(IF(LEN(C141)&lt;&gt;13,"",IF(VALUE(MID(C141,5,3))&gt;=800,1000,2000)+VALUE(MID(C141,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L141">
-        <f>IFERROR(IF(K141="","",IF(AND(DAY(DATE(K141,VALUE(MID(C141,3,2)),VALUE(MID(C141,1,2))))=VALUE(MID(C141,1,2)),MONTH(DATE(K141,VALUE(MID(C141,3,2)),VALUE(MID(C141,1,2))))=VALUE(MID(C141,3,2))),DATE(K141,VALUE(MID(C141,3,2)),VALUE(MID(C141,1,2))),"")),"")</f>
+      <c r="M141">
+        <f>IFERROR(IF(L141="","",IF(AND(DAY(DATE(L141,VALUE(MID(C141,3,2)),VALUE(MID(C141,1,2))))=VALUE(MID(C141,1,2)),MONTH(DATE(L141,VALUE(MID(C141,3,2)),VALUE(MID(C141,1,2))))=VALUE(MID(C141,3,2))),DATE(L141,VALUE(MID(C141,3,2)),VALUE(MID(C141,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4766,27 +5330,31 @@
       <c r="B142" s="2" t="n"/>
       <c r="C142" s="3" t="n"/>
       <c r="D142" s="2" t="n"/>
-      <c r="E142" s="4" t="n"/>
-      <c r="F142" s="2" t="n"/>
+      <c r="E142" s="4">
+        <f>IF(A142="","",5)</f>
+        <v/>
+      </c>
+      <c r="F142" s="4" t="n"/>
       <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2">
-        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(J142="","JMBG sadrži nešto što nije cifra",IF(L142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;J142,"Pogrešna kontrolna cifra — treba "&amp;J142,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I142">
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2">
+        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(K142="","JMBG sadrži nešto što nije cifra",IF(M142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;K142,"Pogrešna kontrolna cifra — treba "&amp;K142,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J142">
         <f>IFERROR(IF(LEN(C142)&lt;&gt;13,"",7*(VALUE(MID(C142,1,1))+VALUE(MID(C142,7,1)))+6*(VALUE(MID(C142,2,1))+VALUE(MID(C142,8,1)))+5*(VALUE(MID(C142,3,1))+VALUE(MID(C142,9,1)))+4*(VALUE(MID(C142,4,1))+VALUE(MID(C142,10,1)))+3*(VALUE(MID(C142,5,1))+VALUE(MID(C142,11,1)))+2*(VALUE(MID(C142,6,1))+VALUE(MID(C142,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J142">
-        <f>IF(I142="","",IF(11-MOD(I142,11)&gt;9,0,11-MOD(I142,11)))</f>
-        <v/>
-      </c>
       <c r="K142">
+        <f>IF(J142="","",IF(11-MOD(J142,11)&gt;9,0,11-MOD(J142,11)))</f>
+        <v/>
+      </c>
+      <c r="L142">
         <f>IFERROR(IF(LEN(C142)&lt;&gt;13,"",IF(VALUE(MID(C142,5,3))&gt;=800,1000,2000)+VALUE(MID(C142,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L142">
-        <f>IFERROR(IF(K142="","",IF(AND(DAY(DATE(K142,VALUE(MID(C142,3,2)),VALUE(MID(C142,1,2))))=VALUE(MID(C142,1,2)),MONTH(DATE(K142,VALUE(MID(C142,3,2)),VALUE(MID(C142,1,2))))=VALUE(MID(C142,3,2))),DATE(K142,VALUE(MID(C142,3,2)),VALUE(MID(C142,1,2))),"")),"")</f>
+      <c r="M142">
+        <f>IFERROR(IF(L142="","",IF(AND(DAY(DATE(L142,VALUE(MID(C142,3,2)),VALUE(MID(C142,1,2))))=VALUE(MID(C142,1,2)),MONTH(DATE(L142,VALUE(MID(C142,3,2)),VALUE(MID(C142,1,2))))=VALUE(MID(C142,3,2))),DATE(L142,VALUE(MID(C142,3,2)),VALUE(MID(C142,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4795,27 +5363,31 @@
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="3" t="n"/>
       <c r="D143" s="2" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="2" t="n"/>
+      <c r="E143" s="4">
+        <f>IF(A143="","",5)</f>
+        <v/>
+      </c>
+      <c r="F143" s="4" t="n"/>
       <c r="G143" s="2" t="n"/>
-      <c r="H143" s="2">
-        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(J143="","JMBG sadrži nešto što nije cifra",IF(L143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;J143,"Pogrešna kontrolna cifra — treba "&amp;J143,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I143">
+      <c r="H143" s="2" t="n"/>
+      <c r="I143" s="2">
+        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(K143="","JMBG sadrži nešto što nije cifra",IF(M143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;K143,"Pogrešna kontrolna cifra — treba "&amp;K143,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J143">
         <f>IFERROR(IF(LEN(C143)&lt;&gt;13,"",7*(VALUE(MID(C143,1,1))+VALUE(MID(C143,7,1)))+6*(VALUE(MID(C143,2,1))+VALUE(MID(C143,8,1)))+5*(VALUE(MID(C143,3,1))+VALUE(MID(C143,9,1)))+4*(VALUE(MID(C143,4,1))+VALUE(MID(C143,10,1)))+3*(VALUE(MID(C143,5,1))+VALUE(MID(C143,11,1)))+2*(VALUE(MID(C143,6,1))+VALUE(MID(C143,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J143">
-        <f>IF(I143="","",IF(11-MOD(I143,11)&gt;9,0,11-MOD(I143,11)))</f>
-        <v/>
-      </c>
       <c r="K143">
+        <f>IF(J143="","",IF(11-MOD(J143,11)&gt;9,0,11-MOD(J143,11)))</f>
+        <v/>
+      </c>
+      <c r="L143">
         <f>IFERROR(IF(LEN(C143)&lt;&gt;13,"",IF(VALUE(MID(C143,5,3))&gt;=800,1000,2000)+VALUE(MID(C143,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L143">
-        <f>IFERROR(IF(K143="","",IF(AND(DAY(DATE(K143,VALUE(MID(C143,3,2)),VALUE(MID(C143,1,2))))=VALUE(MID(C143,1,2)),MONTH(DATE(K143,VALUE(MID(C143,3,2)),VALUE(MID(C143,1,2))))=VALUE(MID(C143,3,2))),DATE(K143,VALUE(MID(C143,3,2)),VALUE(MID(C143,1,2))),"")),"")</f>
+      <c r="M143">
+        <f>IFERROR(IF(L143="","",IF(AND(DAY(DATE(L143,VALUE(MID(C143,3,2)),VALUE(MID(C143,1,2))))=VALUE(MID(C143,1,2)),MONTH(DATE(L143,VALUE(MID(C143,3,2)),VALUE(MID(C143,1,2))))=VALUE(MID(C143,3,2))),DATE(L143,VALUE(MID(C143,3,2)),VALUE(MID(C143,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4824,27 +5396,31 @@
       <c r="B144" s="2" t="n"/>
       <c r="C144" s="3" t="n"/>
       <c r="D144" s="2" t="n"/>
-      <c r="E144" s="4" t="n"/>
-      <c r="F144" s="2" t="n"/>
+      <c r="E144" s="4">
+        <f>IF(A144="","",5)</f>
+        <v/>
+      </c>
+      <c r="F144" s="4" t="n"/>
       <c r="G144" s="2" t="n"/>
-      <c r="H144" s="2">
-        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(J144="","JMBG sadrži nešto što nije cifra",IF(L144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;J144,"Pogrešna kontrolna cifra — treba "&amp;J144,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I144">
+      <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2">
+        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(K144="","JMBG sadrži nešto što nije cifra",IF(M144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;K144,"Pogrešna kontrolna cifra — treba "&amp;K144,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J144">
         <f>IFERROR(IF(LEN(C144)&lt;&gt;13,"",7*(VALUE(MID(C144,1,1))+VALUE(MID(C144,7,1)))+6*(VALUE(MID(C144,2,1))+VALUE(MID(C144,8,1)))+5*(VALUE(MID(C144,3,1))+VALUE(MID(C144,9,1)))+4*(VALUE(MID(C144,4,1))+VALUE(MID(C144,10,1)))+3*(VALUE(MID(C144,5,1))+VALUE(MID(C144,11,1)))+2*(VALUE(MID(C144,6,1))+VALUE(MID(C144,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J144">
-        <f>IF(I144="","",IF(11-MOD(I144,11)&gt;9,0,11-MOD(I144,11)))</f>
-        <v/>
-      </c>
       <c r="K144">
+        <f>IF(J144="","",IF(11-MOD(J144,11)&gt;9,0,11-MOD(J144,11)))</f>
+        <v/>
+      </c>
+      <c r="L144">
         <f>IFERROR(IF(LEN(C144)&lt;&gt;13,"",IF(VALUE(MID(C144,5,3))&gt;=800,1000,2000)+VALUE(MID(C144,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L144">
-        <f>IFERROR(IF(K144="","",IF(AND(DAY(DATE(K144,VALUE(MID(C144,3,2)),VALUE(MID(C144,1,2))))=VALUE(MID(C144,1,2)),MONTH(DATE(K144,VALUE(MID(C144,3,2)),VALUE(MID(C144,1,2))))=VALUE(MID(C144,3,2))),DATE(K144,VALUE(MID(C144,3,2)),VALUE(MID(C144,1,2))),"")),"")</f>
+      <c r="M144">
+        <f>IFERROR(IF(L144="","",IF(AND(DAY(DATE(L144,VALUE(MID(C144,3,2)),VALUE(MID(C144,1,2))))=VALUE(MID(C144,1,2)),MONTH(DATE(L144,VALUE(MID(C144,3,2)),VALUE(MID(C144,1,2))))=VALUE(MID(C144,3,2))),DATE(L144,VALUE(MID(C144,3,2)),VALUE(MID(C144,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4853,27 +5429,31 @@
       <c r="B145" s="2" t="n"/>
       <c r="C145" s="3" t="n"/>
       <c r="D145" s="2" t="n"/>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="2" t="n"/>
+      <c r="E145" s="4">
+        <f>IF(A145="","",5)</f>
+        <v/>
+      </c>
+      <c r="F145" s="4" t="n"/>
       <c r="G145" s="2" t="n"/>
-      <c r="H145" s="2">
-        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(J145="","JMBG sadrži nešto što nije cifra",IF(L145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;J145,"Pogrešna kontrolna cifra — treba "&amp;J145,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I145">
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2">
+        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(K145="","JMBG sadrži nešto što nije cifra",IF(M145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;K145,"Pogrešna kontrolna cifra — treba "&amp;K145,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J145">
         <f>IFERROR(IF(LEN(C145)&lt;&gt;13,"",7*(VALUE(MID(C145,1,1))+VALUE(MID(C145,7,1)))+6*(VALUE(MID(C145,2,1))+VALUE(MID(C145,8,1)))+5*(VALUE(MID(C145,3,1))+VALUE(MID(C145,9,1)))+4*(VALUE(MID(C145,4,1))+VALUE(MID(C145,10,1)))+3*(VALUE(MID(C145,5,1))+VALUE(MID(C145,11,1)))+2*(VALUE(MID(C145,6,1))+VALUE(MID(C145,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J145">
-        <f>IF(I145="","",IF(11-MOD(I145,11)&gt;9,0,11-MOD(I145,11)))</f>
-        <v/>
-      </c>
       <c r="K145">
+        <f>IF(J145="","",IF(11-MOD(J145,11)&gt;9,0,11-MOD(J145,11)))</f>
+        <v/>
+      </c>
+      <c r="L145">
         <f>IFERROR(IF(LEN(C145)&lt;&gt;13,"",IF(VALUE(MID(C145,5,3))&gt;=800,1000,2000)+VALUE(MID(C145,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L145">
-        <f>IFERROR(IF(K145="","",IF(AND(DAY(DATE(K145,VALUE(MID(C145,3,2)),VALUE(MID(C145,1,2))))=VALUE(MID(C145,1,2)),MONTH(DATE(K145,VALUE(MID(C145,3,2)),VALUE(MID(C145,1,2))))=VALUE(MID(C145,3,2))),DATE(K145,VALUE(MID(C145,3,2)),VALUE(MID(C145,1,2))),"")),"")</f>
+      <c r="M145">
+        <f>IFERROR(IF(L145="","",IF(AND(DAY(DATE(L145,VALUE(MID(C145,3,2)),VALUE(MID(C145,1,2))))=VALUE(MID(C145,1,2)),MONTH(DATE(L145,VALUE(MID(C145,3,2)),VALUE(MID(C145,1,2))))=VALUE(MID(C145,3,2))),DATE(L145,VALUE(MID(C145,3,2)),VALUE(MID(C145,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4882,27 +5462,31 @@
       <c r="B146" s="2" t="n"/>
       <c r="C146" s="3" t="n"/>
       <c r="D146" s="2" t="n"/>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="2" t="n"/>
+      <c r="E146" s="4">
+        <f>IF(A146="","",5)</f>
+        <v/>
+      </c>
+      <c r="F146" s="4" t="n"/>
       <c r="G146" s="2" t="n"/>
-      <c r="H146" s="2">
-        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(J146="","JMBG sadrži nešto što nije cifra",IF(L146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;J146,"Pogrešna kontrolna cifra — treba "&amp;J146,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I146">
+      <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2">
+        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(K146="","JMBG sadrži nešto što nije cifra",IF(M146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;K146,"Pogrešna kontrolna cifra — treba "&amp;K146,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J146">
         <f>IFERROR(IF(LEN(C146)&lt;&gt;13,"",7*(VALUE(MID(C146,1,1))+VALUE(MID(C146,7,1)))+6*(VALUE(MID(C146,2,1))+VALUE(MID(C146,8,1)))+5*(VALUE(MID(C146,3,1))+VALUE(MID(C146,9,1)))+4*(VALUE(MID(C146,4,1))+VALUE(MID(C146,10,1)))+3*(VALUE(MID(C146,5,1))+VALUE(MID(C146,11,1)))+2*(VALUE(MID(C146,6,1))+VALUE(MID(C146,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J146">
-        <f>IF(I146="","",IF(11-MOD(I146,11)&gt;9,0,11-MOD(I146,11)))</f>
-        <v/>
-      </c>
       <c r="K146">
+        <f>IF(J146="","",IF(11-MOD(J146,11)&gt;9,0,11-MOD(J146,11)))</f>
+        <v/>
+      </c>
+      <c r="L146">
         <f>IFERROR(IF(LEN(C146)&lt;&gt;13,"",IF(VALUE(MID(C146,5,3))&gt;=800,1000,2000)+VALUE(MID(C146,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L146">
-        <f>IFERROR(IF(K146="","",IF(AND(DAY(DATE(K146,VALUE(MID(C146,3,2)),VALUE(MID(C146,1,2))))=VALUE(MID(C146,1,2)),MONTH(DATE(K146,VALUE(MID(C146,3,2)),VALUE(MID(C146,1,2))))=VALUE(MID(C146,3,2))),DATE(K146,VALUE(MID(C146,3,2)),VALUE(MID(C146,1,2))),"")),"")</f>
+      <c r="M146">
+        <f>IFERROR(IF(L146="","",IF(AND(DAY(DATE(L146,VALUE(MID(C146,3,2)),VALUE(MID(C146,1,2))))=VALUE(MID(C146,1,2)),MONTH(DATE(L146,VALUE(MID(C146,3,2)),VALUE(MID(C146,1,2))))=VALUE(MID(C146,3,2))),DATE(L146,VALUE(MID(C146,3,2)),VALUE(MID(C146,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4911,27 +5495,31 @@
       <c r="B147" s="2" t="n"/>
       <c r="C147" s="3" t="n"/>
       <c r="D147" s="2" t="n"/>
-      <c r="E147" s="4" t="n"/>
-      <c r="F147" s="2" t="n"/>
+      <c r="E147" s="4">
+        <f>IF(A147="","",5)</f>
+        <v/>
+      </c>
+      <c r="F147" s="4" t="n"/>
       <c r="G147" s="2" t="n"/>
-      <c r="H147" s="2">
-        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(J147="","JMBG sadrži nešto što nije cifra",IF(L147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;J147,"Pogrešna kontrolna cifra — treba "&amp;J147,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I147">
+      <c r="H147" s="2" t="n"/>
+      <c r="I147" s="2">
+        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(K147="","JMBG sadrži nešto što nije cifra",IF(M147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;K147,"Pogrešna kontrolna cifra — treba "&amp;K147,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J147">
         <f>IFERROR(IF(LEN(C147)&lt;&gt;13,"",7*(VALUE(MID(C147,1,1))+VALUE(MID(C147,7,1)))+6*(VALUE(MID(C147,2,1))+VALUE(MID(C147,8,1)))+5*(VALUE(MID(C147,3,1))+VALUE(MID(C147,9,1)))+4*(VALUE(MID(C147,4,1))+VALUE(MID(C147,10,1)))+3*(VALUE(MID(C147,5,1))+VALUE(MID(C147,11,1)))+2*(VALUE(MID(C147,6,1))+VALUE(MID(C147,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J147">
-        <f>IF(I147="","",IF(11-MOD(I147,11)&gt;9,0,11-MOD(I147,11)))</f>
-        <v/>
-      </c>
       <c r="K147">
+        <f>IF(J147="","",IF(11-MOD(J147,11)&gt;9,0,11-MOD(J147,11)))</f>
+        <v/>
+      </c>
+      <c r="L147">
         <f>IFERROR(IF(LEN(C147)&lt;&gt;13,"",IF(VALUE(MID(C147,5,3))&gt;=800,1000,2000)+VALUE(MID(C147,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L147">
-        <f>IFERROR(IF(K147="","",IF(AND(DAY(DATE(K147,VALUE(MID(C147,3,2)),VALUE(MID(C147,1,2))))=VALUE(MID(C147,1,2)),MONTH(DATE(K147,VALUE(MID(C147,3,2)),VALUE(MID(C147,1,2))))=VALUE(MID(C147,3,2))),DATE(K147,VALUE(MID(C147,3,2)),VALUE(MID(C147,1,2))),"")),"")</f>
+      <c r="M147">
+        <f>IFERROR(IF(L147="","",IF(AND(DAY(DATE(L147,VALUE(MID(C147,3,2)),VALUE(MID(C147,1,2))))=VALUE(MID(C147,1,2)),MONTH(DATE(L147,VALUE(MID(C147,3,2)),VALUE(MID(C147,1,2))))=VALUE(MID(C147,3,2))),DATE(L147,VALUE(MID(C147,3,2)),VALUE(MID(C147,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4940,27 +5528,31 @@
       <c r="B148" s="2" t="n"/>
       <c r="C148" s="3" t="n"/>
       <c r="D148" s="2" t="n"/>
-      <c r="E148" s="4" t="n"/>
-      <c r="F148" s="2" t="n"/>
+      <c r="E148" s="4">
+        <f>IF(A148="","",5)</f>
+        <v/>
+      </c>
+      <c r="F148" s="4" t="n"/>
       <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2">
-        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(J148="","JMBG sadrži nešto što nije cifra",IF(L148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;J148,"Pogrešna kontrolna cifra — treba "&amp;J148,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I148">
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2">
+        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(K148="","JMBG sadrži nešto što nije cifra",IF(M148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;K148,"Pogrešna kontrolna cifra — treba "&amp;K148,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J148">
         <f>IFERROR(IF(LEN(C148)&lt;&gt;13,"",7*(VALUE(MID(C148,1,1))+VALUE(MID(C148,7,1)))+6*(VALUE(MID(C148,2,1))+VALUE(MID(C148,8,1)))+5*(VALUE(MID(C148,3,1))+VALUE(MID(C148,9,1)))+4*(VALUE(MID(C148,4,1))+VALUE(MID(C148,10,1)))+3*(VALUE(MID(C148,5,1))+VALUE(MID(C148,11,1)))+2*(VALUE(MID(C148,6,1))+VALUE(MID(C148,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J148">
-        <f>IF(I148="","",IF(11-MOD(I148,11)&gt;9,0,11-MOD(I148,11)))</f>
-        <v/>
-      </c>
       <c r="K148">
+        <f>IF(J148="","",IF(11-MOD(J148,11)&gt;9,0,11-MOD(J148,11)))</f>
+        <v/>
+      </c>
+      <c r="L148">
         <f>IFERROR(IF(LEN(C148)&lt;&gt;13,"",IF(VALUE(MID(C148,5,3))&gt;=800,1000,2000)+VALUE(MID(C148,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L148">
-        <f>IFERROR(IF(K148="","",IF(AND(DAY(DATE(K148,VALUE(MID(C148,3,2)),VALUE(MID(C148,1,2))))=VALUE(MID(C148,1,2)),MONTH(DATE(K148,VALUE(MID(C148,3,2)),VALUE(MID(C148,1,2))))=VALUE(MID(C148,3,2))),DATE(K148,VALUE(MID(C148,3,2)),VALUE(MID(C148,1,2))),"")),"")</f>
+      <c r="M148">
+        <f>IFERROR(IF(L148="","",IF(AND(DAY(DATE(L148,VALUE(MID(C148,3,2)),VALUE(MID(C148,1,2))))=VALUE(MID(C148,1,2)),MONTH(DATE(L148,VALUE(MID(C148,3,2)),VALUE(MID(C148,1,2))))=VALUE(MID(C148,3,2))),DATE(L148,VALUE(MID(C148,3,2)),VALUE(MID(C148,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4969,27 +5561,31 @@
       <c r="B149" s="2" t="n"/>
       <c r="C149" s="3" t="n"/>
       <c r="D149" s="2" t="n"/>
-      <c r="E149" s="4" t="n"/>
-      <c r="F149" s="2" t="n"/>
+      <c r="E149" s="4">
+        <f>IF(A149="","",5)</f>
+        <v/>
+      </c>
+      <c r="F149" s="4" t="n"/>
       <c r="G149" s="2" t="n"/>
-      <c r="H149" s="2">
-        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(J149="","JMBG sadrži nešto što nije cifra",IF(L149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;J149,"Pogrešna kontrolna cifra — treba "&amp;J149,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I149">
+      <c r="H149" s="2" t="n"/>
+      <c r="I149" s="2">
+        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(K149="","JMBG sadrži nešto što nije cifra",IF(M149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;K149,"Pogrešna kontrolna cifra — treba "&amp;K149,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J149">
         <f>IFERROR(IF(LEN(C149)&lt;&gt;13,"",7*(VALUE(MID(C149,1,1))+VALUE(MID(C149,7,1)))+6*(VALUE(MID(C149,2,1))+VALUE(MID(C149,8,1)))+5*(VALUE(MID(C149,3,1))+VALUE(MID(C149,9,1)))+4*(VALUE(MID(C149,4,1))+VALUE(MID(C149,10,1)))+3*(VALUE(MID(C149,5,1))+VALUE(MID(C149,11,1)))+2*(VALUE(MID(C149,6,1))+VALUE(MID(C149,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J149">
-        <f>IF(I149="","",IF(11-MOD(I149,11)&gt;9,0,11-MOD(I149,11)))</f>
-        <v/>
-      </c>
       <c r="K149">
+        <f>IF(J149="","",IF(11-MOD(J149,11)&gt;9,0,11-MOD(J149,11)))</f>
+        <v/>
+      </c>
+      <c r="L149">
         <f>IFERROR(IF(LEN(C149)&lt;&gt;13,"",IF(VALUE(MID(C149,5,3))&gt;=800,1000,2000)+VALUE(MID(C149,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L149">
-        <f>IFERROR(IF(K149="","",IF(AND(DAY(DATE(K149,VALUE(MID(C149,3,2)),VALUE(MID(C149,1,2))))=VALUE(MID(C149,1,2)),MONTH(DATE(K149,VALUE(MID(C149,3,2)),VALUE(MID(C149,1,2))))=VALUE(MID(C149,3,2))),DATE(K149,VALUE(MID(C149,3,2)),VALUE(MID(C149,1,2))),"")),"")</f>
+      <c r="M149">
+        <f>IFERROR(IF(L149="","",IF(AND(DAY(DATE(L149,VALUE(MID(C149,3,2)),VALUE(MID(C149,1,2))))=VALUE(MID(C149,1,2)),MONTH(DATE(L149,VALUE(MID(C149,3,2)),VALUE(MID(C149,1,2))))=VALUE(MID(C149,3,2))),DATE(L149,VALUE(MID(C149,3,2)),VALUE(MID(C149,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -4998,27 +5594,31 @@
       <c r="B150" s="2" t="n"/>
       <c r="C150" s="3" t="n"/>
       <c r="D150" s="2" t="n"/>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="2" t="n"/>
+      <c r="E150" s="4">
+        <f>IF(A150="","",5)</f>
+        <v/>
+      </c>
+      <c r="F150" s="4" t="n"/>
       <c r="G150" s="2" t="n"/>
-      <c r="H150" s="2">
-        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(J150="","JMBG sadrži nešto što nije cifra",IF(L150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;J150,"Pogrešna kontrolna cifra — treba "&amp;J150,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I150">
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2">
+        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(K150="","JMBG sadrži nešto što nije cifra",IF(M150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;K150,"Pogrešna kontrolna cifra — treba "&amp;K150,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J150">
         <f>IFERROR(IF(LEN(C150)&lt;&gt;13,"",7*(VALUE(MID(C150,1,1))+VALUE(MID(C150,7,1)))+6*(VALUE(MID(C150,2,1))+VALUE(MID(C150,8,1)))+5*(VALUE(MID(C150,3,1))+VALUE(MID(C150,9,1)))+4*(VALUE(MID(C150,4,1))+VALUE(MID(C150,10,1)))+3*(VALUE(MID(C150,5,1))+VALUE(MID(C150,11,1)))+2*(VALUE(MID(C150,6,1))+VALUE(MID(C150,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J150">
-        <f>IF(I150="","",IF(11-MOD(I150,11)&gt;9,0,11-MOD(I150,11)))</f>
-        <v/>
-      </c>
       <c r="K150">
+        <f>IF(J150="","",IF(11-MOD(J150,11)&gt;9,0,11-MOD(J150,11)))</f>
+        <v/>
+      </c>
+      <c r="L150">
         <f>IFERROR(IF(LEN(C150)&lt;&gt;13,"",IF(VALUE(MID(C150,5,3))&gt;=800,1000,2000)+VALUE(MID(C150,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L150">
-        <f>IFERROR(IF(K150="","",IF(AND(DAY(DATE(K150,VALUE(MID(C150,3,2)),VALUE(MID(C150,1,2))))=VALUE(MID(C150,1,2)),MONTH(DATE(K150,VALUE(MID(C150,3,2)),VALUE(MID(C150,1,2))))=VALUE(MID(C150,3,2))),DATE(K150,VALUE(MID(C150,3,2)),VALUE(MID(C150,1,2))),"")),"")</f>
+      <c r="M150">
+        <f>IFERROR(IF(L150="","",IF(AND(DAY(DATE(L150,VALUE(MID(C150,3,2)),VALUE(MID(C150,1,2))))=VALUE(MID(C150,1,2)),MONTH(DATE(L150,VALUE(MID(C150,3,2)),VALUE(MID(C150,1,2))))=VALUE(MID(C150,3,2))),DATE(L150,VALUE(MID(C150,3,2)),VALUE(MID(C150,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5027,27 +5627,31 @@
       <c r="B151" s="2" t="n"/>
       <c r="C151" s="3" t="n"/>
       <c r="D151" s="2" t="n"/>
-      <c r="E151" s="4" t="n"/>
-      <c r="F151" s="2" t="n"/>
+      <c r="E151" s="4">
+        <f>IF(A151="","",5)</f>
+        <v/>
+      </c>
+      <c r="F151" s="4" t="n"/>
       <c r="G151" s="2" t="n"/>
-      <c r="H151" s="2">
-        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(J151="","JMBG sadrži nešto što nije cifra",IF(L151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;J151,"Pogrešna kontrolna cifra — treba "&amp;J151,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I151">
+      <c r="H151" s="2" t="n"/>
+      <c r="I151" s="2">
+        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(K151="","JMBG sadrži nešto što nije cifra",IF(M151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;K151,"Pogrešna kontrolna cifra — treba "&amp;K151,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J151">
         <f>IFERROR(IF(LEN(C151)&lt;&gt;13,"",7*(VALUE(MID(C151,1,1))+VALUE(MID(C151,7,1)))+6*(VALUE(MID(C151,2,1))+VALUE(MID(C151,8,1)))+5*(VALUE(MID(C151,3,1))+VALUE(MID(C151,9,1)))+4*(VALUE(MID(C151,4,1))+VALUE(MID(C151,10,1)))+3*(VALUE(MID(C151,5,1))+VALUE(MID(C151,11,1)))+2*(VALUE(MID(C151,6,1))+VALUE(MID(C151,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J151">
-        <f>IF(I151="","",IF(11-MOD(I151,11)&gt;9,0,11-MOD(I151,11)))</f>
-        <v/>
-      </c>
       <c r="K151">
+        <f>IF(J151="","",IF(11-MOD(J151,11)&gt;9,0,11-MOD(J151,11)))</f>
+        <v/>
+      </c>
+      <c r="L151">
         <f>IFERROR(IF(LEN(C151)&lt;&gt;13,"",IF(VALUE(MID(C151,5,3))&gt;=800,1000,2000)+VALUE(MID(C151,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L151">
-        <f>IFERROR(IF(K151="","",IF(AND(DAY(DATE(K151,VALUE(MID(C151,3,2)),VALUE(MID(C151,1,2))))=VALUE(MID(C151,1,2)),MONTH(DATE(K151,VALUE(MID(C151,3,2)),VALUE(MID(C151,1,2))))=VALUE(MID(C151,3,2))),DATE(K151,VALUE(MID(C151,3,2)),VALUE(MID(C151,1,2))),"")),"")</f>
+      <c r="M151">
+        <f>IFERROR(IF(L151="","",IF(AND(DAY(DATE(L151,VALUE(MID(C151,3,2)),VALUE(MID(C151,1,2))))=VALUE(MID(C151,1,2)),MONTH(DATE(L151,VALUE(MID(C151,3,2)),VALUE(MID(C151,1,2))))=VALUE(MID(C151,3,2))),DATE(L151,VALUE(MID(C151,3,2)),VALUE(MID(C151,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5056,27 +5660,31 @@
       <c r="B152" s="2" t="n"/>
       <c r="C152" s="3" t="n"/>
       <c r="D152" s="2" t="n"/>
-      <c r="E152" s="4" t="n"/>
-      <c r="F152" s="2" t="n"/>
+      <c r="E152" s="4">
+        <f>IF(A152="","",5)</f>
+        <v/>
+      </c>
+      <c r="F152" s="4" t="n"/>
       <c r="G152" s="2" t="n"/>
-      <c r="H152" s="2">
-        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(J152="","JMBG sadrži nešto što nije cifra",IF(L152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;J152,"Pogrešna kontrolna cifra — treba "&amp;J152,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I152">
+      <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2">
+        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(K152="","JMBG sadrži nešto što nije cifra",IF(M152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;K152,"Pogrešna kontrolna cifra — treba "&amp;K152,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J152">
         <f>IFERROR(IF(LEN(C152)&lt;&gt;13,"",7*(VALUE(MID(C152,1,1))+VALUE(MID(C152,7,1)))+6*(VALUE(MID(C152,2,1))+VALUE(MID(C152,8,1)))+5*(VALUE(MID(C152,3,1))+VALUE(MID(C152,9,1)))+4*(VALUE(MID(C152,4,1))+VALUE(MID(C152,10,1)))+3*(VALUE(MID(C152,5,1))+VALUE(MID(C152,11,1)))+2*(VALUE(MID(C152,6,1))+VALUE(MID(C152,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J152">
-        <f>IF(I152="","",IF(11-MOD(I152,11)&gt;9,0,11-MOD(I152,11)))</f>
-        <v/>
-      </c>
       <c r="K152">
+        <f>IF(J152="","",IF(11-MOD(J152,11)&gt;9,0,11-MOD(J152,11)))</f>
+        <v/>
+      </c>
+      <c r="L152">
         <f>IFERROR(IF(LEN(C152)&lt;&gt;13,"",IF(VALUE(MID(C152,5,3))&gt;=800,1000,2000)+VALUE(MID(C152,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L152">
-        <f>IFERROR(IF(K152="","",IF(AND(DAY(DATE(K152,VALUE(MID(C152,3,2)),VALUE(MID(C152,1,2))))=VALUE(MID(C152,1,2)),MONTH(DATE(K152,VALUE(MID(C152,3,2)),VALUE(MID(C152,1,2))))=VALUE(MID(C152,3,2))),DATE(K152,VALUE(MID(C152,3,2)),VALUE(MID(C152,1,2))),"")),"")</f>
+      <c r="M152">
+        <f>IFERROR(IF(L152="","",IF(AND(DAY(DATE(L152,VALUE(MID(C152,3,2)),VALUE(MID(C152,1,2))))=VALUE(MID(C152,1,2)),MONTH(DATE(L152,VALUE(MID(C152,3,2)),VALUE(MID(C152,1,2))))=VALUE(MID(C152,3,2))),DATE(L152,VALUE(MID(C152,3,2)),VALUE(MID(C152,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5085,27 +5693,31 @@
       <c r="B153" s="2" t="n"/>
       <c r="C153" s="3" t="n"/>
       <c r="D153" s="2" t="n"/>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="2" t="n"/>
+      <c r="E153" s="4">
+        <f>IF(A153="","",5)</f>
+        <v/>
+      </c>
+      <c r="F153" s="4" t="n"/>
       <c r="G153" s="2" t="n"/>
-      <c r="H153" s="2">
-        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(J153="","JMBG sadrži nešto što nije cifra",IF(L153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;J153,"Pogrešna kontrolna cifra — treba "&amp;J153,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I153">
+      <c r="H153" s="2" t="n"/>
+      <c r="I153" s="2">
+        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(K153="","JMBG sadrži nešto što nije cifra",IF(M153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;K153,"Pogrešna kontrolna cifra — treba "&amp;K153,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J153">
         <f>IFERROR(IF(LEN(C153)&lt;&gt;13,"",7*(VALUE(MID(C153,1,1))+VALUE(MID(C153,7,1)))+6*(VALUE(MID(C153,2,1))+VALUE(MID(C153,8,1)))+5*(VALUE(MID(C153,3,1))+VALUE(MID(C153,9,1)))+4*(VALUE(MID(C153,4,1))+VALUE(MID(C153,10,1)))+3*(VALUE(MID(C153,5,1))+VALUE(MID(C153,11,1)))+2*(VALUE(MID(C153,6,1))+VALUE(MID(C153,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J153">
-        <f>IF(I153="","",IF(11-MOD(I153,11)&gt;9,0,11-MOD(I153,11)))</f>
-        <v/>
-      </c>
       <c r="K153">
+        <f>IF(J153="","",IF(11-MOD(J153,11)&gt;9,0,11-MOD(J153,11)))</f>
+        <v/>
+      </c>
+      <c r="L153">
         <f>IFERROR(IF(LEN(C153)&lt;&gt;13,"",IF(VALUE(MID(C153,5,3))&gt;=800,1000,2000)+VALUE(MID(C153,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L153">
-        <f>IFERROR(IF(K153="","",IF(AND(DAY(DATE(K153,VALUE(MID(C153,3,2)),VALUE(MID(C153,1,2))))=VALUE(MID(C153,1,2)),MONTH(DATE(K153,VALUE(MID(C153,3,2)),VALUE(MID(C153,1,2))))=VALUE(MID(C153,3,2))),DATE(K153,VALUE(MID(C153,3,2)),VALUE(MID(C153,1,2))),"")),"")</f>
+      <c r="M153">
+        <f>IFERROR(IF(L153="","",IF(AND(DAY(DATE(L153,VALUE(MID(C153,3,2)),VALUE(MID(C153,1,2))))=VALUE(MID(C153,1,2)),MONTH(DATE(L153,VALUE(MID(C153,3,2)),VALUE(MID(C153,1,2))))=VALUE(MID(C153,3,2))),DATE(L153,VALUE(MID(C153,3,2)),VALUE(MID(C153,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5114,27 +5726,31 @@
       <c r="B154" s="2" t="n"/>
       <c r="C154" s="3" t="n"/>
       <c r="D154" s="2" t="n"/>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="2" t="n"/>
+      <c r="E154" s="4">
+        <f>IF(A154="","",5)</f>
+        <v/>
+      </c>
+      <c r="F154" s="4" t="n"/>
       <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2">
-        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(J154="","JMBG sadrži nešto što nije cifra",IF(L154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;J154,"Pogrešna kontrolna cifra — treba "&amp;J154,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I154">
+      <c r="H154" s="2" t="n"/>
+      <c r="I154" s="2">
+        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(K154="","JMBG sadrži nešto što nije cifra",IF(M154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;K154,"Pogrešna kontrolna cifra — treba "&amp;K154,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J154">
         <f>IFERROR(IF(LEN(C154)&lt;&gt;13,"",7*(VALUE(MID(C154,1,1))+VALUE(MID(C154,7,1)))+6*(VALUE(MID(C154,2,1))+VALUE(MID(C154,8,1)))+5*(VALUE(MID(C154,3,1))+VALUE(MID(C154,9,1)))+4*(VALUE(MID(C154,4,1))+VALUE(MID(C154,10,1)))+3*(VALUE(MID(C154,5,1))+VALUE(MID(C154,11,1)))+2*(VALUE(MID(C154,6,1))+VALUE(MID(C154,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J154">
-        <f>IF(I154="","",IF(11-MOD(I154,11)&gt;9,0,11-MOD(I154,11)))</f>
-        <v/>
-      </c>
       <c r="K154">
+        <f>IF(J154="","",IF(11-MOD(J154,11)&gt;9,0,11-MOD(J154,11)))</f>
+        <v/>
+      </c>
+      <c r="L154">
         <f>IFERROR(IF(LEN(C154)&lt;&gt;13,"",IF(VALUE(MID(C154,5,3))&gt;=800,1000,2000)+VALUE(MID(C154,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L154">
-        <f>IFERROR(IF(K154="","",IF(AND(DAY(DATE(K154,VALUE(MID(C154,3,2)),VALUE(MID(C154,1,2))))=VALUE(MID(C154,1,2)),MONTH(DATE(K154,VALUE(MID(C154,3,2)),VALUE(MID(C154,1,2))))=VALUE(MID(C154,3,2))),DATE(K154,VALUE(MID(C154,3,2)),VALUE(MID(C154,1,2))),"")),"")</f>
+      <c r="M154">
+        <f>IFERROR(IF(L154="","",IF(AND(DAY(DATE(L154,VALUE(MID(C154,3,2)),VALUE(MID(C154,1,2))))=VALUE(MID(C154,1,2)),MONTH(DATE(L154,VALUE(MID(C154,3,2)),VALUE(MID(C154,1,2))))=VALUE(MID(C154,3,2))),DATE(L154,VALUE(MID(C154,3,2)),VALUE(MID(C154,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5143,27 +5759,31 @@
       <c r="B155" s="2" t="n"/>
       <c r="C155" s="3" t="n"/>
       <c r="D155" s="2" t="n"/>
-      <c r="E155" s="4" t="n"/>
-      <c r="F155" s="2" t="n"/>
+      <c r="E155" s="4">
+        <f>IF(A155="","",5)</f>
+        <v/>
+      </c>
+      <c r="F155" s="4" t="n"/>
       <c r="G155" s="2" t="n"/>
-      <c r="H155" s="2">
-        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(J155="","JMBG sadrži nešto što nije cifra",IF(L155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;J155,"Pogrešna kontrolna cifra — treba "&amp;J155,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I155">
+      <c r="H155" s="2" t="n"/>
+      <c r="I155" s="2">
+        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(K155="","JMBG sadrži nešto što nije cifra",IF(M155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;K155,"Pogrešna kontrolna cifra — treba "&amp;K155,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J155">
         <f>IFERROR(IF(LEN(C155)&lt;&gt;13,"",7*(VALUE(MID(C155,1,1))+VALUE(MID(C155,7,1)))+6*(VALUE(MID(C155,2,1))+VALUE(MID(C155,8,1)))+5*(VALUE(MID(C155,3,1))+VALUE(MID(C155,9,1)))+4*(VALUE(MID(C155,4,1))+VALUE(MID(C155,10,1)))+3*(VALUE(MID(C155,5,1))+VALUE(MID(C155,11,1)))+2*(VALUE(MID(C155,6,1))+VALUE(MID(C155,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J155">
-        <f>IF(I155="","",IF(11-MOD(I155,11)&gt;9,0,11-MOD(I155,11)))</f>
-        <v/>
-      </c>
       <c r="K155">
+        <f>IF(J155="","",IF(11-MOD(J155,11)&gt;9,0,11-MOD(J155,11)))</f>
+        <v/>
+      </c>
+      <c r="L155">
         <f>IFERROR(IF(LEN(C155)&lt;&gt;13,"",IF(VALUE(MID(C155,5,3))&gt;=800,1000,2000)+VALUE(MID(C155,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L155">
-        <f>IFERROR(IF(K155="","",IF(AND(DAY(DATE(K155,VALUE(MID(C155,3,2)),VALUE(MID(C155,1,2))))=VALUE(MID(C155,1,2)),MONTH(DATE(K155,VALUE(MID(C155,3,2)),VALUE(MID(C155,1,2))))=VALUE(MID(C155,3,2))),DATE(K155,VALUE(MID(C155,3,2)),VALUE(MID(C155,1,2))),"")),"")</f>
+      <c r="M155">
+        <f>IFERROR(IF(L155="","",IF(AND(DAY(DATE(L155,VALUE(MID(C155,3,2)),VALUE(MID(C155,1,2))))=VALUE(MID(C155,1,2)),MONTH(DATE(L155,VALUE(MID(C155,3,2)),VALUE(MID(C155,1,2))))=VALUE(MID(C155,3,2))),DATE(L155,VALUE(MID(C155,3,2)),VALUE(MID(C155,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5172,27 +5792,31 @@
       <c r="B156" s="2" t="n"/>
       <c r="C156" s="3" t="n"/>
       <c r="D156" s="2" t="n"/>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="2" t="n"/>
+      <c r="E156" s="4">
+        <f>IF(A156="","",5)</f>
+        <v/>
+      </c>
+      <c r="F156" s="4" t="n"/>
       <c r="G156" s="2" t="n"/>
-      <c r="H156" s="2">
-        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(J156="","JMBG sadrži nešto što nije cifra",IF(L156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;J156,"Pogrešna kontrolna cifra — treba "&amp;J156,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I156">
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2">
+        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(K156="","JMBG sadrži nešto što nije cifra",IF(M156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;K156,"Pogrešna kontrolna cifra — treba "&amp;K156,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J156">
         <f>IFERROR(IF(LEN(C156)&lt;&gt;13,"",7*(VALUE(MID(C156,1,1))+VALUE(MID(C156,7,1)))+6*(VALUE(MID(C156,2,1))+VALUE(MID(C156,8,1)))+5*(VALUE(MID(C156,3,1))+VALUE(MID(C156,9,1)))+4*(VALUE(MID(C156,4,1))+VALUE(MID(C156,10,1)))+3*(VALUE(MID(C156,5,1))+VALUE(MID(C156,11,1)))+2*(VALUE(MID(C156,6,1))+VALUE(MID(C156,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J156">
-        <f>IF(I156="","",IF(11-MOD(I156,11)&gt;9,0,11-MOD(I156,11)))</f>
-        <v/>
-      </c>
       <c r="K156">
+        <f>IF(J156="","",IF(11-MOD(J156,11)&gt;9,0,11-MOD(J156,11)))</f>
+        <v/>
+      </c>
+      <c r="L156">
         <f>IFERROR(IF(LEN(C156)&lt;&gt;13,"",IF(VALUE(MID(C156,5,3))&gt;=800,1000,2000)+VALUE(MID(C156,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L156">
-        <f>IFERROR(IF(K156="","",IF(AND(DAY(DATE(K156,VALUE(MID(C156,3,2)),VALUE(MID(C156,1,2))))=VALUE(MID(C156,1,2)),MONTH(DATE(K156,VALUE(MID(C156,3,2)),VALUE(MID(C156,1,2))))=VALUE(MID(C156,3,2))),DATE(K156,VALUE(MID(C156,3,2)),VALUE(MID(C156,1,2))),"")),"")</f>
+      <c r="M156">
+        <f>IFERROR(IF(L156="","",IF(AND(DAY(DATE(L156,VALUE(MID(C156,3,2)),VALUE(MID(C156,1,2))))=VALUE(MID(C156,1,2)),MONTH(DATE(L156,VALUE(MID(C156,3,2)),VALUE(MID(C156,1,2))))=VALUE(MID(C156,3,2))),DATE(L156,VALUE(MID(C156,3,2)),VALUE(MID(C156,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5201,27 +5825,31 @@
       <c r="B157" s="2" t="n"/>
       <c r="C157" s="3" t="n"/>
       <c r="D157" s="2" t="n"/>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="2" t="n"/>
+      <c r="E157" s="4">
+        <f>IF(A157="","",5)</f>
+        <v/>
+      </c>
+      <c r="F157" s="4" t="n"/>
       <c r="G157" s="2" t="n"/>
-      <c r="H157" s="2">
-        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(J157="","JMBG sadrži nešto što nije cifra",IF(L157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;J157,"Pogrešna kontrolna cifra — treba "&amp;J157,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I157">
+      <c r="H157" s="2" t="n"/>
+      <c r="I157" s="2">
+        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(K157="","JMBG sadrži nešto što nije cifra",IF(M157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;K157,"Pogrešna kontrolna cifra — treba "&amp;K157,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J157">
         <f>IFERROR(IF(LEN(C157)&lt;&gt;13,"",7*(VALUE(MID(C157,1,1))+VALUE(MID(C157,7,1)))+6*(VALUE(MID(C157,2,1))+VALUE(MID(C157,8,1)))+5*(VALUE(MID(C157,3,1))+VALUE(MID(C157,9,1)))+4*(VALUE(MID(C157,4,1))+VALUE(MID(C157,10,1)))+3*(VALUE(MID(C157,5,1))+VALUE(MID(C157,11,1)))+2*(VALUE(MID(C157,6,1))+VALUE(MID(C157,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J157">
-        <f>IF(I157="","",IF(11-MOD(I157,11)&gt;9,0,11-MOD(I157,11)))</f>
-        <v/>
-      </c>
       <c r="K157">
+        <f>IF(J157="","",IF(11-MOD(J157,11)&gt;9,0,11-MOD(J157,11)))</f>
+        <v/>
+      </c>
+      <c r="L157">
         <f>IFERROR(IF(LEN(C157)&lt;&gt;13,"",IF(VALUE(MID(C157,5,3))&gt;=800,1000,2000)+VALUE(MID(C157,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L157">
-        <f>IFERROR(IF(K157="","",IF(AND(DAY(DATE(K157,VALUE(MID(C157,3,2)),VALUE(MID(C157,1,2))))=VALUE(MID(C157,1,2)),MONTH(DATE(K157,VALUE(MID(C157,3,2)),VALUE(MID(C157,1,2))))=VALUE(MID(C157,3,2))),DATE(K157,VALUE(MID(C157,3,2)),VALUE(MID(C157,1,2))),"")),"")</f>
+      <c r="M157">
+        <f>IFERROR(IF(L157="","",IF(AND(DAY(DATE(L157,VALUE(MID(C157,3,2)),VALUE(MID(C157,1,2))))=VALUE(MID(C157,1,2)),MONTH(DATE(L157,VALUE(MID(C157,3,2)),VALUE(MID(C157,1,2))))=VALUE(MID(C157,3,2))),DATE(L157,VALUE(MID(C157,3,2)),VALUE(MID(C157,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5230,27 +5858,31 @@
       <c r="B158" s="2" t="n"/>
       <c r="C158" s="3" t="n"/>
       <c r="D158" s="2" t="n"/>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="2" t="n"/>
+      <c r="E158" s="4">
+        <f>IF(A158="","",5)</f>
+        <v/>
+      </c>
+      <c r="F158" s="4" t="n"/>
       <c r="G158" s="2" t="n"/>
-      <c r="H158" s="2">
-        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(J158="","JMBG sadrži nešto što nije cifra",IF(L158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;J158,"Pogrešna kontrolna cifra — treba "&amp;J158,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I158">
+      <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2">
+        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(K158="","JMBG sadrži nešto što nije cifra",IF(M158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;K158,"Pogrešna kontrolna cifra — treba "&amp;K158,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J158">
         <f>IFERROR(IF(LEN(C158)&lt;&gt;13,"",7*(VALUE(MID(C158,1,1))+VALUE(MID(C158,7,1)))+6*(VALUE(MID(C158,2,1))+VALUE(MID(C158,8,1)))+5*(VALUE(MID(C158,3,1))+VALUE(MID(C158,9,1)))+4*(VALUE(MID(C158,4,1))+VALUE(MID(C158,10,1)))+3*(VALUE(MID(C158,5,1))+VALUE(MID(C158,11,1)))+2*(VALUE(MID(C158,6,1))+VALUE(MID(C158,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J158">
-        <f>IF(I158="","",IF(11-MOD(I158,11)&gt;9,0,11-MOD(I158,11)))</f>
-        <v/>
-      </c>
       <c r="K158">
+        <f>IF(J158="","",IF(11-MOD(J158,11)&gt;9,0,11-MOD(J158,11)))</f>
+        <v/>
+      </c>
+      <c r="L158">
         <f>IFERROR(IF(LEN(C158)&lt;&gt;13,"",IF(VALUE(MID(C158,5,3))&gt;=800,1000,2000)+VALUE(MID(C158,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L158">
-        <f>IFERROR(IF(K158="","",IF(AND(DAY(DATE(K158,VALUE(MID(C158,3,2)),VALUE(MID(C158,1,2))))=VALUE(MID(C158,1,2)),MONTH(DATE(K158,VALUE(MID(C158,3,2)),VALUE(MID(C158,1,2))))=VALUE(MID(C158,3,2))),DATE(K158,VALUE(MID(C158,3,2)),VALUE(MID(C158,1,2))),"")),"")</f>
+      <c r="M158">
+        <f>IFERROR(IF(L158="","",IF(AND(DAY(DATE(L158,VALUE(MID(C158,3,2)),VALUE(MID(C158,1,2))))=VALUE(MID(C158,1,2)),MONTH(DATE(L158,VALUE(MID(C158,3,2)),VALUE(MID(C158,1,2))))=VALUE(MID(C158,3,2))),DATE(L158,VALUE(MID(C158,3,2)),VALUE(MID(C158,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5259,27 +5891,31 @@
       <c r="B159" s="2" t="n"/>
       <c r="C159" s="3" t="n"/>
       <c r="D159" s="2" t="n"/>
-      <c r="E159" s="4" t="n"/>
-      <c r="F159" s="2" t="n"/>
+      <c r="E159" s="4">
+        <f>IF(A159="","",5)</f>
+        <v/>
+      </c>
+      <c r="F159" s="4" t="n"/>
       <c r="G159" s="2" t="n"/>
-      <c r="H159" s="2">
-        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(J159="","JMBG sadrži nešto što nije cifra",IF(L159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;J159,"Pogrešna kontrolna cifra — treba "&amp;J159,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I159">
+      <c r="H159" s="2" t="n"/>
+      <c r="I159" s="2">
+        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(K159="","JMBG sadrži nešto što nije cifra",IF(M159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;K159,"Pogrešna kontrolna cifra — treba "&amp;K159,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J159">
         <f>IFERROR(IF(LEN(C159)&lt;&gt;13,"",7*(VALUE(MID(C159,1,1))+VALUE(MID(C159,7,1)))+6*(VALUE(MID(C159,2,1))+VALUE(MID(C159,8,1)))+5*(VALUE(MID(C159,3,1))+VALUE(MID(C159,9,1)))+4*(VALUE(MID(C159,4,1))+VALUE(MID(C159,10,1)))+3*(VALUE(MID(C159,5,1))+VALUE(MID(C159,11,1)))+2*(VALUE(MID(C159,6,1))+VALUE(MID(C159,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J159">
-        <f>IF(I159="","",IF(11-MOD(I159,11)&gt;9,0,11-MOD(I159,11)))</f>
-        <v/>
-      </c>
       <c r="K159">
+        <f>IF(J159="","",IF(11-MOD(J159,11)&gt;9,0,11-MOD(J159,11)))</f>
+        <v/>
+      </c>
+      <c r="L159">
         <f>IFERROR(IF(LEN(C159)&lt;&gt;13,"",IF(VALUE(MID(C159,5,3))&gt;=800,1000,2000)+VALUE(MID(C159,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L159">
-        <f>IFERROR(IF(K159="","",IF(AND(DAY(DATE(K159,VALUE(MID(C159,3,2)),VALUE(MID(C159,1,2))))=VALUE(MID(C159,1,2)),MONTH(DATE(K159,VALUE(MID(C159,3,2)),VALUE(MID(C159,1,2))))=VALUE(MID(C159,3,2))),DATE(K159,VALUE(MID(C159,3,2)),VALUE(MID(C159,1,2))),"")),"")</f>
+      <c r="M159">
+        <f>IFERROR(IF(L159="","",IF(AND(DAY(DATE(L159,VALUE(MID(C159,3,2)),VALUE(MID(C159,1,2))))=VALUE(MID(C159,1,2)),MONTH(DATE(L159,VALUE(MID(C159,3,2)),VALUE(MID(C159,1,2))))=VALUE(MID(C159,3,2))),DATE(L159,VALUE(MID(C159,3,2)),VALUE(MID(C159,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5288,27 +5924,31 @@
       <c r="B160" s="2" t="n"/>
       <c r="C160" s="3" t="n"/>
       <c r="D160" s="2" t="n"/>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="2" t="n"/>
+      <c r="E160" s="4">
+        <f>IF(A160="","",5)</f>
+        <v/>
+      </c>
+      <c r="F160" s="4" t="n"/>
       <c r="G160" s="2" t="n"/>
-      <c r="H160" s="2">
-        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(J160="","JMBG sadrži nešto što nije cifra",IF(L160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;J160,"Pogrešna kontrolna cifra — treba "&amp;J160,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I160">
+      <c r="H160" s="2" t="n"/>
+      <c r="I160" s="2">
+        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(K160="","JMBG sadrži nešto što nije cifra",IF(M160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;K160,"Pogrešna kontrolna cifra — treba "&amp;K160,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J160">
         <f>IFERROR(IF(LEN(C160)&lt;&gt;13,"",7*(VALUE(MID(C160,1,1))+VALUE(MID(C160,7,1)))+6*(VALUE(MID(C160,2,1))+VALUE(MID(C160,8,1)))+5*(VALUE(MID(C160,3,1))+VALUE(MID(C160,9,1)))+4*(VALUE(MID(C160,4,1))+VALUE(MID(C160,10,1)))+3*(VALUE(MID(C160,5,1))+VALUE(MID(C160,11,1)))+2*(VALUE(MID(C160,6,1))+VALUE(MID(C160,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J160">
-        <f>IF(I160="","",IF(11-MOD(I160,11)&gt;9,0,11-MOD(I160,11)))</f>
-        <v/>
-      </c>
       <c r="K160">
+        <f>IF(J160="","",IF(11-MOD(J160,11)&gt;9,0,11-MOD(J160,11)))</f>
+        <v/>
+      </c>
+      <c r="L160">
         <f>IFERROR(IF(LEN(C160)&lt;&gt;13,"",IF(VALUE(MID(C160,5,3))&gt;=800,1000,2000)+VALUE(MID(C160,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L160">
-        <f>IFERROR(IF(K160="","",IF(AND(DAY(DATE(K160,VALUE(MID(C160,3,2)),VALUE(MID(C160,1,2))))=VALUE(MID(C160,1,2)),MONTH(DATE(K160,VALUE(MID(C160,3,2)),VALUE(MID(C160,1,2))))=VALUE(MID(C160,3,2))),DATE(K160,VALUE(MID(C160,3,2)),VALUE(MID(C160,1,2))),"")),"")</f>
+      <c r="M160">
+        <f>IFERROR(IF(L160="","",IF(AND(DAY(DATE(L160,VALUE(MID(C160,3,2)),VALUE(MID(C160,1,2))))=VALUE(MID(C160,1,2)),MONTH(DATE(L160,VALUE(MID(C160,3,2)),VALUE(MID(C160,1,2))))=VALUE(MID(C160,3,2))),DATE(L160,VALUE(MID(C160,3,2)),VALUE(MID(C160,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5317,27 +5957,31 @@
       <c r="B161" s="2" t="n"/>
       <c r="C161" s="3" t="n"/>
       <c r="D161" s="2" t="n"/>
-      <c r="E161" s="4" t="n"/>
-      <c r="F161" s="2" t="n"/>
+      <c r="E161" s="4">
+        <f>IF(A161="","",5)</f>
+        <v/>
+      </c>
+      <c r="F161" s="4" t="n"/>
       <c r="G161" s="2" t="n"/>
-      <c r="H161" s="2">
-        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(J161="","JMBG sadrži nešto što nije cifra",IF(L161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;J161,"Pogrešna kontrolna cifra — treba "&amp;J161,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I161">
+      <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2">
+        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(K161="","JMBG sadrži nešto što nije cifra",IF(M161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;K161,"Pogrešna kontrolna cifra — treba "&amp;K161,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J161">
         <f>IFERROR(IF(LEN(C161)&lt;&gt;13,"",7*(VALUE(MID(C161,1,1))+VALUE(MID(C161,7,1)))+6*(VALUE(MID(C161,2,1))+VALUE(MID(C161,8,1)))+5*(VALUE(MID(C161,3,1))+VALUE(MID(C161,9,1)))+4*(VALUE(MID(C161,4,1))+VALUE(MID(C161,10,1)))+3*(VALUE(MID(C161,5,1))+VALUE(MID(C161,11,1)))+2*(VALUE(MID(C161,6,1))+VALUE(MID(C161,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J161">
-        <f>IF(I161="","",IF(11-MOD(I161,11)&gt;9,0,11-MOD(I161,11)))</f>
-        <v/>
-      </c>
       <c r="K161">
+        <f>IF(J161="","",IF(11-MOD(J161,11)&gt;9,0,11-MOD(J161,11)))</f>
+        <v/>
+      </c>
+      <c r="L161">
         <f>IFERROR(IF(LEN(C161)&lt;&gt;13,"",IF(VALUE(MID(C161,5,3))&gt;=800,1000,2000)+VALUE(MID(C161,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L161">
-        <f>IFERROR(IF(K161="","",IF(AND(DAY(DATE(K161,VALUE(MID(C161,3,2)),VALUE(MID(C161,1,2))))=VALUE(MID(C161,1,2)),MONTH(DATE(K161,VALUE(MID(C161,3,2)),VALUE(MID(C161,1,2))))=VALUE(MID(C161,3,2))),DATE(K161,VALUE(MID(C161,3,2)),VALUE(MID(C161,1,2))),"")),"")</f>
+      <c r="M161">
+        <f>IFERROR(IF(L161="","",IF(AND(DAY(DATE(L161,VALUE(MID(C161,3,2)),VALUE(MID(C161,1,2))))=VALUE(MID(C161,1,2)),MONTH(DATE(L161,VALUE(MID(C161,3,2)),VALUE(MID(C161,1,2))))=VALUE(MID(C161,3,2))),DATE(L161,VALUE(MID(C161,3,2)),VALUE(MID(C161,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5346,27 +5990,31 @@
       <c r="B162" s="2" t="n"/>
       <c r="C162" s="3" t="n"/>
       <c r="D162" s="2" t="n"/>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="2" t="n"/>
+      <c r="E162" s="4">
+        <f>IF(A162="","",5)</f>
+        <v/>
+      </c>
+      <c r="F162" s="4" t="n"/>
       <c r="G162" s="2" t="n"/>
-      <c r="H162" s="2">
-        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(J162="","JMBG sadrži nešto što nije cifra",IF(L162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;J162,"Pogrešna kontrolna cifra — treba "&amp;J162,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I162">
+      <c r="H162" s="2" t="n"/>
+      <c r="I162" s="2">
+        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(K162="","JMBG sadrži nešto što nije cifra",IF(M162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;K162,"Pogrešna kontrolna cifra — treba "&amp;K162,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J162">
         <f>IFERROR(IF(LEN(C162)&lt;&gt;13,"",7*(VALUE(MID(C162,1,1))+VALUE(MID(C162,7,1)))+6*(VALUE(MID(C162,2,1))+VALUE(MID(C162,8,1)))+5*(VALUE(MID(C162,3,1))+VALUE(MID(C162,9,1)))+4*(VALUE(MID(C162,4,1))+VALUE(MID(C162,10,1)))+3*(VALUE(MID(C162,5,1))+VALUE(MID(C162,11,1)))+2*(VALUE(MID(C162,6,1))+VALUE(MID(C162,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J162">
-        <f>IF(I162="","",IF(11-MOD(I162,11)&gt;9,0,11-MOD(I162,11)))</f>
-        <v/>
-      </c>
       <c r="K162">
+        <f>IF(J162="","",IF(11-MOD(J162,11)&gt;9,0,11-MOD(J162,11)))</f>
+        <v/>
+      </c>
+      <c r="L162">
         <f>IFERROR(IF(LEN(C162)&lt;&gt;13,"",IF(VALUE(MID(C162,5,3))&gt;=800,1000,2000)+VALUE(MID(C162,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L162">
-        <f>IFERROR(IF(K162="","",IF(AND(DAY(DATE(K162,VALUE(MID(C162,3,2)),VALUE(MID(C162,1,2))))=VALUE(MID(C162,1,2)),MONTH(DATE(K162,VALUE(MID(C162,3,2)),VALUE(MID(C162,1,2))))=VALUE(MID(C162,3,2))),DATE(K162,VALUE(MID(C162,3,2)),VALUE(MID(C162,1,2))),"")),"")</f>
+      <c r="M162">
+        <f>IFERROR(IF(L162="","",IF(AND(DAY(DATE(L162,VALUE(MID(C162,3,2)),VALUE(MID(C162,1,2))))=VALUE(MID(C162,1,2)),MONTH(DATE(L162,VALUE(MID(C162,3,2)),VALUE(MID(C162,1,2))))=VALUE(MID(C162,3,2))),DATE(L162,VALUE(MID(C162,3,2)),VALUE(MID(C162,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5375,27 +6023,31 @@
       <c r="B163" s="2" t="n"/>
       <c r="C163" s="3" t="n"/>
       <c r="D163" s="2" t="n"/>
-      <c r="E163" s="4" t="n"/>
-      <c r="F163" s="2" t="n"/>
+      <c r="E163" s="4">
+        <f>IF(A163="","",5)</f>
+        <v/>
+      </c>
+      <c r="F163" s="4" t="n"/>
       <c r="G163" s="2" t="n"/>
-      <c r="H163" s="2">
-        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(J163="","JMBG sadrži nešto što nije cifra",IF(L163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;J163,"Pogrešna kontrolna cifra — treba "&amp;J163,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I163">
+      <c r="H163" s="2" t="n"/>
+      <c r="I163" s="2">
+        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(K163="","JMBG sadrži nešto što nije cifra",IF(M163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;K163,"Pogrešna kontrolna cifra — treba "&amp;K163,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J163">
         <f>IFERROR(IF(LEN(C163)&lt;&gt;13,"",7*(VALUE(MID(C163,1,1))+VALUE(MID(C163,7,1)))+6*(VALUE(MID(C163,2,1))+VALUE(MID(C163,8,1)))+5*(VALUE(MID(C163,3,1))+VALUE(MID(C163,9,1)))+4*(VALUE(MID(C163,4,1))+VALUE(MID(C163,10,1)))+3*(VALUE(MID(C163,5,1))+VALUE(MID(C163,11,1)))+2*(VALUE(MID(C163,6,1))+VALUE(MID(C163,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J163">
-        <f>IF(I163="","",IF(11-MOD(I163,11)&gt;9,0,11-MOD(I163,11)))</f>
-        <v/>
-      </c>
       <c r="K163">
+        <f>IF(J163="","",IF(11-MOD(J163,11)&gt;9,0,11-MOD(J163,11)))</f>
+        <v/>
+      </c>
+      <c r="L163">
         <f>IFERROR(IF(LEN(C163)&lt;&gt;13,"",IF(VALUE(MID(C163,5,3))&gt;=800,1000,2000)+VALUE(MID(C163,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L163">
-        <f>IFERROR(IF(K163="","",IF(AND(DAY(DATE(K163,VALUE(MID(C163,3,2)),VALUE(MID(C163,1,2))))=VALUE(MID(C163,1,2)),MONTH(DATE(K163,VALUE(MID(C163,3,2)),VALUE(MID(C163,1,2))))=VALUE(MID(C163,3,2))),DATE(K163,VALUE(MID(C163,3,2)),VALUE(MID(C163,1,2))),"")),"")</f>
+      <c r="M163">
+        <f>IFERROR(IF(L163="","",IF(AND(DAY(DATE(L163,VALUE(MID(C163,3,2)),VALUE(MID(C163,1,2))))=VALUE(MID(C163,1,2)),MONTH(DATE(L163,VALUE(MID(C163,3,2)),VALUE(MID(C163,1,2))))=VALUE(MID(C163,3,2))),DATE(L163,VALUE(MID(C163,3,2)),VALUE(MID(C163,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5404,27 +6056,31 @@
       <c r="B164" s="2" t="n"/>
       <c r="C164" s="3" t="n"/>
       <c r="D164" s="2" t="n"/>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="2" t="n"/>
+      <c r="E164" s="4">
+        <f>IF(A164="","",5)</f>
+        <v/>
+      </c>
+      <c r="F164" s="4" t="n"/>
       <c r="G164" s="2" t="n"/>
-      <c r="H164" s="2">
-        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(J164="","JMBG sadrži nešto što nije cifra",IF(L164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;J164,"Pogrešna kontrolna cifra — treba "&amp;J164,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I164">
+      <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2">
+        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(K164="","JMBG sadrži nešto što nije cifra",IF(M164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;K164,"Pogrešna kontrolna cifra — treba "&amp;K164,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J164">
         <f>IFERROR(IF(LEN(C164)&lt;&gt;13,"",7*(VALUE(MID(C164,1,1))+VALUE(MID(C164,7,1)))+6*(VALUE(MID(C164,2,1))+VALUE(MID(C164,8,1)))+5*(VALUE(MID(C164,3,1))+VALUE(MID(C164,9,1)))+4*(VALUE(MID(C164,4,1))+VALUE(MID(C164,10,1)))+3*(VALUE(MID(C164,5,1))+VALUE(MID(C164,11,1)))+2*(VALUE(MID(C164,6,1))+VALUE(MID(C164,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J164">
-        <f>IF(I164="","",IF(11-MOD(I164,11)&gt;9,0,11-MOD(I164,11)))</f>
-        <v/>
-      </c>
       <c r="K164">
+        <f>IF(J164="","",IF(11-MOD(J164,11)&gt;9,0,11-MOD(J164,11)))</f>
+        <v/>
+      </c>
+      <c r="L164">
         <f>IFERROR(IF(LEN(C164)&lt;&gt;13,"",IF(VALUE(MID(C164,5,3))&gt;=800,1000,2000)+VALUE(MID(C164,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L164">
-        <f>IFERROR(IF(K164="","",IF(AND(DAY(DATE(K164,VALUE(MID(C164,3,2)),VALUE(MID(C164,1,2))))=VALUE(MID(C164,1,2)),MONTH(DATE(K164,VALUE(MID(C164,3,2)),VALUE(MID(C164,1,2))))=VALUE(MID(C164,3,2))),DATE(K164,VALUE(MID(C164,3,2)),VALUE(MID(C164,1,2))),"")),"")</f>
+      <c r="M164">
+        <f>IFERROR(IF(L164="","",IF(AND(DAY(DATE(L164,VALUE(MID(C164,3,2)),VALUE(MID(C164,1,2))))=VALUE(MID(C164,1,2)),MONTH(DATE(L164,VALUE(MID(C164,3,2)),VALUE(MID(C164,1,2))))=VALUE(MID(C164,3,2))),DATE(L164,VALUE(MID(C164,3,2)),VALUE(MID(C164,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5433,27 +6089,31 @@
       <c r="B165" s="2" t="n"/>
       <c r="C165" s="3" t="n"/>
       <c r="D165" s="2" t="n"/>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="2" t="n"/>
+      <c r="E165" s="4">
+        <f>IF(A165="","",5)</f>
+        <v/>
+      </c>
+      <c r="F165" s="4" t="n"/>
       <c r="G165" s="2" t="n"/>
-      <c r="H165" s="2">
-        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(J165="","JMBG sadrži nešto što nije cifra",IF(L165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;J165,"Pogrešna kontrolna cifra — treba "&amp;J165,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I165">
+      <c r="H165" s="2" t="n"/>
+      <c r="I165" s="2">
+        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(K165="","JMBG sadrži nešto što nije cifra",IF(M165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;K165,"Pogrešna kontrolna cifra — treba "&amp;K165,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J165">
         <f>IFERROR(IF(LEN(C165)&lt;&gt;13,"",7*(VALUE(MID(C165,1,1))+VALUE(MID(C165,7,1)))+6*(VALUE(MID(C165,2,1))+VALUE(MID(C165,8,1)))+5*(VALUE(MID(C165,3,1))+VALUE(MID(C165,9,1)))+4*(VALUE(MID(C165,4,1))+VALUE(MID(C165,10,1)))+3*(VALUE(MID(C165,5,1))+VALUE(MID(C165,11,1)))+2*(VALUE(MID(C165,6,1))+VALUE(MID(C165,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J165">
-        <f>IF(I165="","",IF(11-MOD(I165,11)&gt;9,0,11-MOD(I165,11)))</f>
-        <v/>
-      </c>
       <c r="K165">
+        <f>IF(J165="","",IF(11-MOD(J165,11)&gt;9,0,11-MOD(J165,11)))</f>
+        <v/>
+      </c>
+      <c r="L165">
         <f>IFERROR(IF(LEN(C165)&lt;&gt;13,"",IF(VALUE(MID(C165,5,3))&gt;=800,1000,2000)+VALUE(MID(C165,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L165">
-        <f>IFERROR(IF(K165="","",IF(AND(DAY(DATE(K165,VALUE(MID(C165,3,2)),VALUE(MID(C165,1,2))))=VALUE(MID(C165,1,2)),MONTH(DATE(K165,VALUE(MID(C165,3,2)),VALUE(MID(C165,1,2))))=VALUE(MID(C165,3,2))),DATE(K165,VALUE(MID(C165,3,2)),VALUE(MID(C165,1,2))),"")),"")</f>
+      <c r="M165">
+        <f>IFERROR(IF(L165="","",IF(AND(DAY(DATE(L165,VALUE(MID(C165,3,2)),VALUE(MID(C165,1,2))))=VALUE(MID(C165,1,2)),MONTH(DATE(L165,VALUE(MID(C165,3,2)),VALUE(MID(C165,1,2))))=VALUE(MID(C165,3,2))),DATE(L165,VALUE(MID(C165,3,2)),VALUE(MID(C165,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5462,27 +6122,31 @@
       <c r="B166" s="2" t="n"/>
       <c r="C166" s="3" t="n"/>
       <c r="D166" s="2" t="n"/>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="2" t="n"/>
+      <c r="E166" s="4">
+        <f>IF(A166="","",5)</f>
+        <v/>
+      </c>
+      <c r="F166" s="4" t="n"/>
       <c r="G166" s="2" t="n"/>
-      <c r="H166" s="2">
-        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(J166="","JMBG sadrži nešto što nije cifra",IF(L166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;J166,"Pogrešna kontrolna cifra — treba "&amp;J166,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I166">
+      <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2">
+        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(K166="","JMBG sadrži nešto što nije cifra",IF(M166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;K166,"Pogrešna kontrolna cifra — treba "&amp;K166,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J166">
         <f>IFERROR(IF(LEN(C166)&lt;&gt;13,"",7*(VALUE(MID(C166,1,1))+VALUE(MID(C166,7,1)))+6*(VALUE(MID(C166,2,1))+VALUE(MID(C166,8,1)))+5*(VALUE(MID(C166,3,1))+VALUE(MID(C166,9,1)))+4*(VALUE(MID(C166,4,1))+VALUE(MID(C166,10,1)))+3*(VALUE(MID(C166,5,1))+VALUE(MID(C166,11,1)))+2*(VALUE(MID(C166,6,1))+VALUE(MID(C166,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J166">
-        <f>IF(I166="","",IF(11-MOD(I166,11)&gt;9,0,11-MOD(I166,11)))</f>
-        <v/>
-      </c>
       <c r="K166">
+        <f>IF(J166="","",IF(11-MOD(J166,11)&gt;9,0,11-MOD(J166,11)))</f>
+        <v/>
+      </c>
+      <c r="L166">
         <f>IFERROR(IF(LEN(C166)&lt;&gt;13,"",IF(VALUE(MID(C166,5,3))&gt;=800,1000,2000)+VALUE(MID(C166,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L166">
-        <f>IFERROR(IF(K166="","",IF(AND(DAY(DATE(K166,VALUE(MID(C166,3,2)),VALUE(MID(C166,1,2))))=VALUE(MID(C166,1,2)),MONTH(DATE(K166,VALUE(MID(C166,3,2)),VALUE(MID(C166,1,2))))=VALUE(MID(C166,3,2))),DATE(K166,VALUE(MID(C166,3,2)),VALUE(MID(C166,1,2))),"")),"")</f>
+      <c r="M166">
+        <f>IFERROR(IF(L166="","",IF(AND(DAY(DATE(L166,VALUE(MID(C166,3,2)),VALUE(MID(C166,1,2))))=VALUE(MID(C166,1,2)),MONTH(DATE(L166,VALUE(MID(C166,3,2)),VALUE(MID(C166,1,2))))=VALUE(MID(C166,3,2))),DATE(L166,VALUE(MID(C166,3,2)),VALUE(MID(C166,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5491,27 +6155,31 @@
       <c r="B167" s="2" t="n"/>
       <c r="C167" s="3" t="n"/>
       <c r="D167" s="2" t="n"/>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="2" t="n"/>
+      <c r="E167" s="4">
+        <f>IF(A167="","",5)</f>
+        <v/>
+      </c>
+      <c r="F167" s="4" t="n"/>
       <c r="G167" s="2" t="n"/>
-      <c r="H167" s="2">
-        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(J167="","JMBG sadrži nešto što nije cifra",IF(L167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;J167,"Pogrešna kontrolna cifra — treba "&amp;J167,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I167">
+      <c r="H167" s="2" t="n"/>
+      <c r="I167" s="2">
+        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(K167="","JMBG sadrži nešto što nije cifra",IF(M167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;K167,"Pogrešna kontrolna cifra — treba "&amp;K167,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J167">
         <f>IFERROR(IF(LEN(C167)&lt;&gt;13,"",7*(VALUE(MID(C167,1,1))+VALUE(MID(C167,7,1)))+6*(VALUE(MID(C167,2,1))+VALUE(MID(C167,8,1)))+5*(VALUE(MID(C167,3,1))+VALUE(MID(C167,9,1)))+4*(VALUE(MID(C167,4,1))+VALUE(MID(C167,10,1)))+3*(VALUE(MID(C167,5,1))+VALUE(MID(C167,11,1)))+2*(VALUE(MID(C167,6,1))+VALUE(MID(C167,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J167">
-        <f>IF(I167="","",IF(11-MOD(I167,11)&gt;9,0,11-MOD(I167,11)))</f>
-        <v/>
-      </c>
       <c r="K167">
+        <f>IF(J167="","",IF(11-MOD(J167,11)&gt;9,0,11-MOD(J167,11)))</f>
+        <v/>
+      </c>
+      <c r="L167">
         <f>IFERROR(IF(LEN(C167)&lt;&gt;13,"",IF(VALUE(MID(C167,5,3))&gt;=800,1000,2000)+VALUE(MID(C167,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L167">
-        <f>IFERROR(IF(K167="","",IF(AND(DAY(DATE(K167,VALUE(MID(C167,3,2)),VALUE(MID(C167,1,2))))=VALUE(MID(C167,1,2)),MONTH(DATE(K167,VALUE(MID(C167,3,2)),VALUE(MID(C167,1,2))))=VALUE(MID(C167,3,2))),DATE(K167,VALUE(MID(C167,3,2)),VALUE(MID(C167,1,2))),"")),"")</f>
+      <c r="M167">
+        <f>IFERROR(IF(L167="","",IF(AND(DAY(DATE(L167,VALUE(MID(C167,3,2)),VALUE(MID(C167,1,2))))=VALUE(MID(C167,1,2)),MONTH(DATE(L167,VALUE(MID(C167,3,2)),VALUE(MID(C167,1,2))))=VALUE(MID(C167,3,2))),DATE(L167,VALUE(MID(C167,3,2)),VALUE(MID(C167,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5520,27 +6188,31 @@
       <c r="B168" s="2" t="n"/>
       <c r="C168" s="3" t="n"/>
       <c r="D168" s="2" t="n"/>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="2" t="n"/>
+      <c r="E168" s="4">
+        <f>IF(A168="","",5)</f>
+        <v/>
+      </c>
+      <c r="F168" s="4" t="n"/>
       <c r="G168" s="2" t="n"/>
-      <c r="H168" s="2">
-        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(J168="","JMBG sadrži nešto što nije cifra",IF(L168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;J168,"Pogrešna kontrolna cifra — treba "&amp;J168,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I168">
+      <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2">
+        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(K168="","JMBG sadrži nešto što nije cifra",IF(M168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;K168,"Pogrešna kontrolna cifra — treba "&amp;K168,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J168">
         <f>IFERROR(IF(LEN(C168)&lt;&gt;13,"",7*(VALUE(MID(C168,1,1))+VALUE(MID(C168,7,1)))+6*(VALUE(MID(C168,2,1))+VALUE(MID(C168,8,1)))+5*(VALUE(MID(C168,3,1))+VALUE(MID(C168,9,1)))+4*(VALUE(MID(C168,4,1))+VALUE(MID(C168,10,1)))+3*(VALUE(MID(C168,5,1))+VALUE(MID(C168,11,1)))+2*(VALUE(MID(C168,6,1))+VALUE(MID(C168,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J168">
-        <f>IF(I168="","",IF(11-MOD(I168,11)&gt;9,0,11-MOD(I168,11)))</f>
-        <v/>
-      </c>
       <c r="K168">
+        <f>IF(J168="","",IF(11-MOD(J168,11)&gt;9,0,11-MOD(J168,11)))</f>
+        <v/>
+      </c>
+      <c r="L168">
         <f>IFERROR(IF(LEN(C168)&lt;&gt;13,"",IF(VALUE(MID(C168,5,3))&gt;=800,1000,2000)+VALUE(MID(C168,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L168">
-        <f>IFERROR(IF(K168="","",IF(AND(DAY(DATE(K168,VALUE(MID(C168,3,2)),VALUE(MID(C168,1,2))))=VALUE(MID(C168,1,2)),MONTH(DATE(K168,VALUE(MID(C168,3,2)),VALUE(MID(C168,1,2))))=VALUE(MID(C168,3,2))),DATE(K168,VALUE(MID(C168,3,2)),VALUE(MID(C168,1,2))),"")),"")</f>
+      <c r="M168">
+        <f>IFERROR(IF(L168="","",IF(AND(DAY(DATE(L168,VALUE(MID(C168,3,2)),VALUE(MID(C168,1,2))))=VALUE(MID(C168,1,2)),MONTH(DATE(L168,VALUE(MID(C168,3,2)),VALUE(MID(C168,1,2))))=VALUE(MID(C168,3,2))),DATE(L168,VALUE(MID(C168,3,2)),VALUE(MID(C168,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5549,27 +6221,31 @@
       <c r="B169" s="2" t="n"/>
       <c r="C169" s="3" t="n"/>
       <c r="D169" s="2" t="n"/>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="2" t="n"/>
+      <c r="E169" s="4">
+        <f>IF(A169="","",5)</f>
+        <v/>
+      </c>
+      <c r="F169" s="4" t="n"/>
       <c r="G169" s="2" t="n"/>
-      <c r="H169" s="2">
-        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(J169="","JMBG sadrži nešto što nije cifra",IF(L169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;J169,"Pogrešna kontrolna cifra — treba "&amp;J169,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I169">
+      <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2">
+        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(K169="","JMBG sadrži nešto što nije cifra",IF(M169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;K169,"Pogrešna kontrolna cifra — treba "&amp;K169,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J169">
         <f>IFERROR(IF(LEN(C169)&lt;&gt;13,"",7*(VALUE(MID(C169,1,1))+VALUE(MID(C169,7,1)))+6*(VALUE(MID(C169,2,1))+VALUE(MID(C169,8,1)))+5*(VALUE(MID(C169,3,1))+VALUE(MID(C169,9,1)))+4*(VALUE(MID(C169,4,1))+VALUE(MID(C169,10,1)))+3*(VALUE(MID(C169,5,1))+VALUE(MID(C169,11,1)))+2*(VALUE(MID(C169,6,1))+VALUE(MID(C169,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J169">
-        <f>IF(I169="","",IF(11-MOD(I169,11)&gt;9,0,11-MOD(I169,11)))</f>
-        <v/>
-      </c>
       <c r="K169">
+        <f>IF(J169="","",IF(11-MOD(J169,11)&gt;9,0,11-MOD(J169,11)))</f>
+        <v/>
+      </c>
+      <c r="L169">
         <f>IFERROR(IF(LEN(C169)&lt;&gt;13,"",IF(VALUE(MID(C169,5,3))&gt;=800,1000,2000)+VALUE(MID(C169,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L169">
-        <f>IFERROR(IF(K169="","",IF(AND(DAY(DATE(K169,VALUE(MID(C169,3,2)),VALUE(MID(C169,1,2))))=VALUE(MID(C169,1,2)),MONTH(DATE(K169,VALUE(MID(C169,3,2)),VALUE(MID(C169,1,2))))=VALUE(MID(C169,3,2))),DATE(K169,VALUE(MID(C169,3,2)),VALUE(MID(C169,1,2))),"")),"")</f>
+      <c r="M169">
+        <f>IFERROR(IF(L169="","",IF(AND(DAY(DATE(L169,VALUE(MID(C169,3,2)),VALUE(MID(C169,1,2))))=VALUE(MID(C169,1,2)),MONTH(DATE(L169,VALUE(MID(C169,3,2)),VALUE(MID(C169,1,2))))=VALUE(MID(C169,3,2))),DATE(L169,VALUE(MID(C169,3,2)),VALUE(MID(C169,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5578,27 +6254,31 @@
       <c r="B170" s="2" t="n"/>
       <c r="C170" s="3" t="n"/>
       <c r="D170" s="2" t="n"/>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="2" t="n"/>
+      <c r="E170" s="4">
+        <f>IF(A170="","",5)</f>
+        <v/>
+      </c>
+      <c r="F170" s="4" t="n"/>
       <c r="G170" s="2" t="n"/>
-      <c r="H170" s="2">
-        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(J170="","JMBG sadrži nešto što nije cifra",IF(L170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;J170,"Pogrešna kontrolna cifra — treba "&amp;J170,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I170">
+      <c r="H170" s="2" t="n"/>
+      <c r="I170" s="2">
+        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(K170="","JMBG sadrži nešto što nije cifra",IF(M170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;K170,"Pogrešna kontrolna cifra — treba "&amp;K170,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J170">
         <f>IFERROR(IF(LEN(C170)&lt;&gt;13,"",7*(VALUE(MID(C170,1,1))+VALUE(MID(C170,7,1)))+6*(VALUE(MID(C170,2,1))+VALUE(MID(C170,8,1)))+5*(VALUE(MID(C170,3,1))+VALUE(MID(C170,9,1)))+4*(VALUE(MID(C170,4,1))+VALUE(MID(C170,10,1)))+3*(VALUE(MID(C170,5,1))+VALUE(MID(C170,11,1)))+2*(VALUE(MID(C170,6,1))+VALUE(MID(C170,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J170">
-        <f>IF(I170="","",IF(11-MOD(I170,11)&gt;9,0,11-MOD(I170,11)))</f>
-        <v/>
-      </c>
       <c r="K170">
+        <f>IF(J170="","",IF(11-MOD(J170,11)&gt;9,0,11-MOD(J170,11)))</f>
+        <v/>
+      </c>
+      <c r="L170">
         <f>IFERROR(IF(LEN(C170)&lt;&gt;13,"",IF(VALUE(MID(C170,5,3))&gt;=800,1000,2000)+VALUE(MID(C170,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L170">
-        <f>IFERROR(IF(K170="","",IF(AND(DAY(DATE(K170,VALUE(MID(C170,3,2)),VALUE(MID(C170,1,2))))=VALUE(MID(C170,1,2)),MONTH(DATE(K170,VALUE(MID(C170,3,2)),VALUE(MID(C170,1,2))))=VALUE(MID(C170,3,2))),DATE(K170,VALUE(MID(C170,3,2)),VALUE(MID(C170,1,2))),"")),"")</f>
+      <c r="M170">
+        <f>IFERROR(IF(L170="","",IF(AND(DAY(DATE(L170,VALUE(MID(C170,3,2)),VALUE(MID(C170,1,2))))=VALUE(MID(C170,1,2)),MONTH(DATE(L170,VALUE(MID(C170,3,2)),VALUE(MID(C170,1,2))))=VALUE(MID(C170,3,2))),DATE(L170,VALUE(MID(C170,3,2)),VALUE(MID(C170,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5607,27 +6287,31 @@
       <c r="B171" s="2" t="n"/>
       <c r="C171" s="3" t="n"/>
       <c r="D171" s="2" t="n"/>
-      <c r="E171" s="4" t="n"/>
-      <c r="F171" s="2" t="n"/>
+      <c r="E171" s="4">
+        <f>IF(A171="","",5)</f>
+        <v/>
+      </c>
+      <c r="F171" s="4" t="n"/>
       <c r="G171" s="2" t="n"/>
-      <c r="H171" s="2">
-        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(J171="","JMBG sadrži nešto što nije cifra",IF(L171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;J171,"Pogrešna kontrolna cifra — treba "&amp;J171,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I171">
+      <c r="H171" s="2" t="n"/>
+      <c r="I171" s="2">
+        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(K171="","JMBG sadrži nešto što nije cifra",IF(M171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;K171,"Pogrešna kontrolna cifra — treba "&amp;K171,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J171">
         <f>IFERROR(IF(LEN(C171)&lt;&gt;13,"",7*(VALUE(MID(C171,1,1))+VALUE(MID(C171,7,1)))+6*(VALUE(MID(C171,2,1))+VALUE(MID(C171,8,1)))+5*(VALUE(MID(C171,3,1))+VALUE(MID(C171,9,1)))+4*(VALUE(MID(C171,4,1))+VALUE(MID(C171,10,1)))+3*(VALUE(MID(C171,5,1))+VALUE(MID(C171,11,1)))+2*(VALUE(MID(C171,6,1))+VALUE(MID(C171,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J171">
-        <f>IF(I171="","",IF(11-MOD(I171,11)&gt;9,0,11-MOD(I171,11)))</f>
-        <v/>
-      </c>
       <c r="K171">
+        <f>IF(J171="","",IF(11-MOD(J171,11)&gt;9,0,11-MOD(J171,11)))</f>
+        <v/>
+      </c>
+      <c r="L171">
         <f>IFERROR(IF(LEN(C171)&lt;&gt;13,"",IF(VALUE(MID(C171,5,3))&gt;=800,1000,2000)+VALUE(MID(C171,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L171">
-        <f>IFERROR(IF(K171="","",IF(AND(DAY(DATE(K171,VALUE(MID(C171,3,2)),VALUE(MID(C171,1,2))))=VALUE(MID(C171,1,2)),MONTH(DATE(K171,VALUE(MID(C171,3,2)),VALUE(MID(C171,1,2))))=VALUE(MID(C171,3,2))),DATE(K171,VALUE(MID(C171,3,2)),VALUE(MID(C171,1,2))),"")),"")</f>
+      <c r="M171">
+        <f>IFERROR(IF(L171="","",IF(AND(DAY(DATE(L171,VALUE(MID(C171,3,2)),VALUE(MID(C171,1,2))))=VALUE(MID(C171,1,2)),MONTH(DATE(L171,VALUE(MID(C171,3,2)),VALUE(MID(C171,1,2))))=VALUE(MID(C171,3,2))),DATE(L171,VALUE(MID(C171,3,2)),VALUE(MID(C171,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5636,27 +6320,31 @@
       <c r="B172" s="2" t="n"/>
       <c r="C172" s="3" t="n"/>
       <c r="D172" s="2" t="n"/>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="2" t="n"/>
+      <c r="E172" s="4">
+        <f>IF(A172="","",5)</f>
+        <v/>
+      </c>
+      <c r="F172" s="4" t="n"/>
       <c r="G172" s="2" t="n"/>
-      <c r="H172" s="2">
-        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(J172="","JMBG sadrži nešto što nije cifra",IF(L172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;J172,"Pogrešna kontrolna cifra — treba "&amp;J172,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I172">
+      <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2">
+        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(K172="","JMBG sadrži nešto što nije cifra",IF(M172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;K172,"Pogrešna kontrolna cifra — treba "&amp;K172,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J172">
         <f>IFERROR(IF(LEN(C172)&lt;&gt;13,"",7*(VALUE(MID(C172,1,1))+VALUE(MID(C172,7,1)))+6*(VALUE(MID(C172,2,1))+VALUE(MID(C172,8,1)))+5*(VALUE(MID(C172,3,1))+VALUE(MID(C172,9,1)))+4*(VALUE(MID(C172,4,1))+VALUE(MID(C172,10,1)))+3*(VALUE(MID(C172,5,1))+VALUE(MID(C172,11,1)))+2*(VALUE(MID(C172,6,1))+VALUE(MID(C172,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J172">
-        <f>IF(I172="","",IF(11-MOD(I172,11)&gt;9,0,11-MOD(I172,11)))</f>
-        <v/>
-      </c>
       <c r="K172">
+        <f>IF(J172="","",IF(11-MOD(J172,11)&gt;9,0,11-MOD(J172,11)))</f>
+        <v/>
+      </c>
+      <c r="L172">
         <f>IFERROR(IF(LEN(C172)&lt;&gt;13,"",IF(VALUE(MID(C172,5,3))&gt;=800,1000,2000)+VALUE(MID(C172,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L172">
-        <f>IFERROR(IF(K172="","",IF(AND(DAY(DATE(K172,VALUE(MID(C172,3,2)),VALUE(MID(C172,1,2))))=VALUE(MID(C172,1,2)),MONTH(DATE(K172,VALUE(MID(C172,3,2)),VALUE(MID(C172,1,2))))=VALUE(MID(C172,3,2))),DATE(K172,VALUE(MID(C172,3,2)),VALUE(MID(C172,1,2))),"")),"")</f>
+      <c r="M172">
+        <f>IFERROR(IF(L172="","",IF(AND(DAY(DATE(L172,VALUE(MID(C172,3,2)),VALUE(MID(C172,1,2))))=VALUE(MID(C172,1,2)),MONTH(DATE(L172,VALUE(MID(C172,3,2)),VALUE(MID(C172,1,2))))=VALUE(MID(C172,3,2))),DATE(L172,VALUE(MID(C172,3,2)),VALUE(MID(C172,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5665,27 +6353,31 @@
       <c r="B173" s="2" t="n"/>
       <c r="C173" s="3" t="n"/>
       <c r="D173" s="2" t="n"/>
-      <c r="E173" s="4" t="n"/>
-      <c r="F173" s="2" t="n"/>
+      <c r="E173" s="4">
+        <f>IF(A173="","",5)</f>
+        <v/>
+      </c>
+      <c r="F173" s="4" t="n"/>
       <c r="G173" s="2" t="n"/>
-      <c r="H173" s="2">
-        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(J173="","JMBG sadrži nešto što nije cifra",IF(L173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;J173,"Pogrešna kontrolna cifra — treba "&amp;J173,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I173">
+      <c r="H173" s="2" t="n"/>
+      <c r="I173" s="2">
+        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(K173="","JMBG sadrži nešto što nije cifra",IF(M173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;K173,"Pogrešna kontrolna cifra — treba "&amp;K173,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J173">
         <f>IFERROR(IF(LEN(C173)&lt;&gt;13,"",7*(VALUE(MID(C173,1,1))+VALUE(MID(C173,7,1)))+6*(VALUE(MID(C173,2,1))+VALUE(MID(C173,8,1)))+5*(VALUE(MID(C173,3,1))+VALUE(MID(C173,9,1)))+4*(VALUE(MID(C173,4,1))+VALUE(MID(C173,10,1)))+3*(VALUE(MID(C173,5,1))+VALUE(MID(C173,11,1)))+2*(VALUE(MID(C173,6,1))+VALUE(MID(C173,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J173">
-        <f>IF(I173="","",IF(11-MOD(I173,11)&gt;9,0,11-MOD(I173,11)))</f>
-        <v/>
-      </c>
       <c r="K173">
+        <f>IF(J173="","",IF(11-MOD(J173,11)&gt;9,0,11-MOD(J173,11)))</f>
+        <v/>
+      </c>
+      <c r="L173">
         <f>IFERROR(IF(LEN(C173)&lt;&gt;13,"",IF(VALUE(MID(C173,5,3))&gt;=800,1000,2000)+VALUE(MID(C173,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L173">
-        <f>IFERROR(IF(K173="","",IF(AND(DAY(DATE(K173,VALUE(MID(C173,3,2)),VALUE(MID(C173,1,2))))=VALUE(MID(C173,1,2)),MONTH(DATE(K173,VALUE(MID(C173,3,2)),VALUE(MID(C173,1,2))))=VALUE(MID(C173,3,2))),DATE(K173,VALUE(MID(C173,3,2)),VALUE(MID(C173,1,2))),"")),"")</f>
+      <c r="M173">
+        <f>IFERROR(IF(L173="","",IF(AND(DAY(DATE(L173,VALUE(MID(C173,3,2)),VALUE(MID(C173,1,2))))=VALUE(MID(C173,1,2)),MONTH(DATE(L173,VALUE(MID(C173,3,2)),VALUE(MID(C173,1,2))))=VALUE(MID(C173,3,2))),DATE(L173,VALUE(MID(C173,3,2)),VALUE(MID(C173,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5694,27 +6386,31 @@
       <c r="B174" s="2" t="n"/>
       <c r="C174" s="3" t="n"/>
       <c r="D174" s="2" t="n"/>
-      <c r="E174" s="4" t="n"/>
-      <c r="F174" s="2" t="n"/>
+      <c r="E174" s="4">
+        <f>IF(A174="","",5)</f>
+        <v/>
+      </c>
+      <c r="F174" s="4" t="n"/>
       <c r="G174" s="2" t="n"/>
-      <c r="H174" s="2">
-        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(J174="","JMBG sadrži nešto što nije cifra",IF(L174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;J174,"Pogrešna kontrolna cifra — treba "&amp;J174,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I174">
+      <c r="H174" s="2" t="n"/>
+      <c r="I174" s="2">
+        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(K174="","JMBG sadrži nešto što nije cifra",IF(M174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;K174,"Pogrešna kontrolna cifra — treba "&amp;K174,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J174">
         <f>IFERROR(IF(LEN(C174)&lt;&gt;13,"",7*(VALUE(MID(C174,1,1))+VALUE(MID(C174,7,1)))+6*(VALUE(MID(C174,2,1))+VALUE(MID(C174,8,1)))+5*(VALUE(MID(C174,3,1))+VALUE(MID(C174,9,1)))+4*(VALUE(MID(C174,4,1))+VALUE(MID(C174,10,1)))+3*(VALUE(MID(C174,5,1))+VALUE(MID(C174,11,1)))+2*(VALUE(MID(C174,6,1))+VALUE(MID(C174,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J174">
-        <f>IF(I174="","",IF(11-MOD(I174,11)&gt;9,0,11-MOD(I174,11)))</f>
-        <v/>
-      </c>
       <c r="K174">
+        <f>IF(J174="","",IF(11-MOD(J174,11)&gt;9,0,11-MOD(J174,11)))</f>
+        <v/>
+      </c>
+      <c r="L174">
         <f>IFERROR(IF(LEN(C174)&lt;&gt;13,"",IF(VALUE(MID(C174,5,3))&gt;=800,1000,2000)+VALUE(MID(C174,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L174">
-        <f>IFERROR(IF(K174="","",IF(AND(DAY(DATE(K174,VALUE(MID(C174,3,2)),VALUE(MID(C174,1,2))))=VALUE(MID(C174,1,2)),MONTH(DATE(K174,VALUE(MID(C174,3,2)),VALUE(MID(C174,1,2))))=VALUE(MID(C174,3,2))),DATE(K174,VALUE(MID(C174,3,2)),VALUE(MID(C174,1,2))),"")),"")</f>
+      <c r="M174">
+        <f>IFERROR(IF(L174="","",IF(AND(DAY(DATE(L174,VALUE(MID(C174,3,2)),VALUE(MID(C174,1,2))))=VALUE(MID(C174,1,2)),MONTH(DATE(L174,VALUE(MID(C174,3,2)),VALUE(MID(C174,1,2))))=VALUE(MID(C174,3,2))),DATE(L174,VALUE(MID(C174,3,2)),VALUE(MID(C174,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5723,27 +6419,31 @@
       <c r="B175" s="2" t="n"/>
       <c r="C175" s="3" t="n"/>
       <c r="D175" s="2" t="n"/>
-      <c r="E175" s="4" t="n"/>
-      <c r="F175" s="2" t="n"/>
+      <c r="E175" s="4">
+        <f>IF(A175="","",5)</f>
+        <v/>
+      </c>
+      <c r="F175" s="4" t="n"/>
       <c r="G175" s="2" t="n"/>
-      <c r="H175" s="2">
-        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(J175="","JMBG sadrži nešto što nije cifra",IF(L175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;J175,"Pogrešna kontrolna cifra — treba "&amp;J175,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I175">
+      <c r="H175" s="2" t="n"/>
+      <c r="I175" s="2">
+        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(K175="","JMBG sadrži nešto što nije cifra",IF(M175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;K175,"Pogrešna kontrolna cifra — treba "&amp;K175,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J175">
         <f>IFERROR(IF(LEN(C175)&lt;&gt;13,"",7*(VALUE(MID(C175,1,1))+VALUE(MID(C175,7,1)))+6*(VALUE(MID(C175,2,1))+VALUE(MID(C175,8,1)))+5*(VALUE(MID(C175,3,1))+VALUE(MID(C175,9,1)))+4*(VALUE(MID(C175,4,1))+VALUE(MID(C175,10,1)))+3*(VALUE(MID(C175,5,1))+VALUE(MID(C175,11,1)))+2*(VALUE(MID(C175,6,1))+VALUE(MID(C175,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J175">
-        <f>IF(I175="","",IF(11-MOD(I175,11)&gt;9,0,11-MOD(I175,11)))</f>
-        <v/>
-      </c>
       <c r="K175">
+        <f>IF(J175="","",IF(11-MOD(J175,11)&gt;9,0,11-MOD(J175,11)))</f>
+        <v/>
+      </c>
+      <c r="L175">
         <f>IFERROR(IF(LEN(C175)&lt;&gt;13,"",IF(VALUE(MID(C175,5,3))&gt;=800,1000,2000)+VALUE(MID(C175,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L175">
-        <f>IFERROR(IF(K175="","",IF(AND(DAY(DATE(K175,VALUE(MID(C175,3,2)),VALUE(MID(C175,1,2))))=VALUE(MID(C175,1,2)),MONTH(DATE(K175,VALUE(MID(C175,3,2)),VALUE(MID(C175,1,2))))=VALUE(MID(C175,3,2))),DATE(K175,VALUE(MID(C175,3,2)),VALUE(MID(C175,1,2))),"")),"")</f>
+      <c r="M175">
+        <f>IFERROR(IF(L175="","",IF(AND(DAY(DATE(L175,VALUE(MID(C175,3,2)),VALUE(MID(C175,1,2))))=VALUE(MID(C175,1,2)),MONTH(DATE(L175,VALUE(MID(C175,3,2)),VALUE(MID(C175,1,2))))=VALUE(MID(C175,3,2))),DATE(L175,VALUE(MID(C175,3,2)),VALUE(MID(C175,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5752,27 +6452,31 @@
       <c r="B176" s="2" t="n"/>
       <c r="C176" s="3" t="n"/>
       <c r="D176" s="2" t="n"/>
-      <c r="E176" s="4" t="n"/>
-      <c r="F176" s="2" t="n"/>
+      <c r="E176" s="4">
+        <f>IF(A176="","",5)</f>
+        <v/>
+      </c>
+      <c r="F176" s="4" t="n"/>
       <c r="G176" s="2" t="n"/>
-      <c r="H176" s="2">
-        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(J176="","JMBG sadrži nešto što nije cifra",IF(L176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;J176,"Pogrešna kontrolna cifra — treba "&amp;J176,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I176">
+      <c r="H176" s="2" t="n"/>
+      <c r="I176" s="2">
+        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(K176="","JMBG sadrži nešto što nije cifra",IF(M176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;K176,"Pogrešna kontrolna cifra — treba "&amp;K176,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J176">
         <f>IFERROR(IF(LEN(C176)&lt;&gt;13,"",7*(VALUE(MID(C176,1,1))+VALUE(MID(C176,7,1)))+6*(VALUE(MID(C176,2,1))+VALUE(MID(C176,8,1)))+5*(VALUE(MID(C176,3,1))+VALUE(MID(C176,9,1)))+4*(VALUE(MID(C176,4,1))+VALUE(MID(C176,10,1)))+3*(VALUE(MID(C176,5,1))+VALUE(MID(C176,11,1)))+2*(VALUE(MID(C176,6,1))+VALUE(MID(C176,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J176">
-        <f>IF(I176="","",IF(11-MOD(I176,11)&gt;9,0,11-MOD(I176,11)))</f>
-        <v/>
-      </c>
       <c r="K176">
+        <f>IF(J176="","",IF(11-MOD(J176,11)&gt;9,0,11-MOD(J176,11)))</f>
+        <v/>
+      </c>
+      <c r="L176">
         <f>IFERROR(IF(LEN(C176)&lt;&gt;13,"",IF(VALUE(MID(C176,5,3))&gt;=800,1000,2000)+VALUE(MID(C176,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L176">
-        <f>IFERROR(IF(K176="","",IF(AND(DAY(DATE(K176,VALUE(MID(C176,3,2)),VALUE(MID(C176,1,2))))=VALUE(MID(C176,1,2)),MONTH(DATE(K176,VALUE(MID(C176,3,2)),VALUE(MID(C176,1,2))))=VALUE(MID(C176,3,2))),DATE(K176,VALUE(MID(C176,3,2)),VALUE(MID(C176,1,2))),"")),"")</f>
+      <c r="M176">
+        <f>IFERROR(IF(L176="","",IF(AND(DAY(DATE(L176,VALUE(MID(C176,3,2)),VALUE(MID(C176,1,2))))=VALUE(MID(C176,1,2)),MONTH(DATE(L176,VALUE(MID(C176,3,2)),VALUE(MID(C176,1,2))))=VALUE(MID(C176,3,2))),DATE(L176,VALUE(MID(C176,3,2)),VALUE(MID(C176,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5781,27 +6485,31 @@
       <c r="B177" s="2" t="n"/>
       <c r="C177" s="3" t="n"/>
       <c r="D177" s="2" t="n"/>
-      <c r="E177" s="4" t="n"/>
-      <c r="F177" s="2" t="n"/>
+      <c r="E177" s="4">
+        <f>IF(A177="","",5)</f>
+        <v/>
+      </c>
+      <c r="F177" s="4" t="n"/>
       <c r="G177" s="2" t="n"/>
-      <c r="H177" s="2">
-        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(J177="","JMBG sadrži nešto što nije cifra",IF(L177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;J177,"Pogrešna kontrolna cifra — treba "&amp;J177,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I177">
+      <c r="H177" s="2" t="n"/>
+      <c r="I177" s="2">
+        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(K177="","JMBG sadrži nešto što nije cifra",IF(M177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;K177,"Pogrešna kontrolna cifra — treba "&amp;K177,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J177">
         <f>IFERROR(IF(LEN(C177)&lt;&gt;13,"",7*(VALUE(MID(C177,1,1))+VALUE(MID(C177,7,1)))+6*(VALUE(MID(C177,2,1))+VALUE(MID(C177,8,1)))+5*(VALUE(MID(C177,3,1))+VALUE(MID(C177,9,1)))+4*(VALUE(MID(C177,4,1))+VALUE(MID(C177,10,1)))+3*(VALUE(MID(C177,5,1))+VALUE(MID(C177,11,1)))+2*(VALUE(MID(C177,6,1))+VALUE(MID(C177,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J177">
-        <f>IF(I177="","",IF(11-MOD(I177,11)&gt;9,0,11-MOD(I177,11)))</f>
-        <v/>
-      </c>
       <c r="K177">
+        <f>IF(J177="","",IF(11-MOD(J177,11)&gt;9,0,11-MOD(J177,11)))</f>
+        <v/>
+      </c>
+      <c r="L177">
         <f>IFERROR(IF(LEN(C177)&lt;&gt;13,"",IF(VALUE(MID(C177,5,3))&gt;=800,1000,2000)+VALUE(MID(C177,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L177">
-        <f>IFERROR(IF(K177="","",IF(AND(DAY(DATE(K177,VALUE(MID(C177,3,2)),VALUE(MID(C177,1,2))))=VALUE(MID(C177,1,2)),MONTH(DATE(K177,VALUE(MID(C177,3,2)),VALUE(MID(C177,1,2))))=VALUE(MID(C177,3,2))),DATE(K177,VALUE(MID(C177,3,2)),VALUE(MID(C177,1,2))),"")),"")</f>
+      <c r="M177">
+        <f>IFERROR(IF(L177="","",IF(AND(DAY(DATE(L177,VALUE(MID(C177,3,2)),VALUE(MID(C177,1,2))))=VALUE(MID(C177,1,2)),MONTH(DATE(L177,VALUE(MID(C177,3,2)),VALUE(MID(C177,1,2))))=VALUE(MID(C177,3,2))),DATE(L177,VALUE(MID(C177,3,2)),VALUE(MID(C177,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5810,27 +6518,31 @@
       <c r="B178" s="2" t="n"/>
       <c r="C178" s="3" t="n"/>
       <c r="D178" s="2" t="n"/>
-      <c r="E178" s="4" t="n"/>
-      <c r="F178" s="2" t="n"/>
+      <c r="E178" s="4">
+        <f>IF(A178="","",5)</f>
+        <v/>
+      </c>
+      <c r="F178" s="4" t="n"/>
       <c r="G178" s="2" t="n"/>
-      <c r="H178" s="2">
-        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(J178="","JMBG sadrži nešto što nije cifra",IF(L178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;J178,"Pogrešna kontrolna cifra — treba "&amp;J178,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I178">
+      <c r="H178" s="2" t="n"/>
+      <c r="I178" s="2">
+        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(K178="","JMBG sadrži nešto što nije cifra",IF(M178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;K178,"Pogrešna kontrolna cifra — treba "&amp;K178,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J178">
         <f>IFERROR(IF(LEN(C178)&lt;&gt;13,"",7*(VALUE(MID(C178,1,1))+VALUE(MID(C178,7,1)))+6*(VALUE(MID(C178,2,1))+VALUE(MID(C178,8,1)))+5*(VALUE(MID(C178,3,1))+VALUE(MID(C178,9,1)))+4*(VALUE(MID(C178,4,1))+VALUE(MID(C178,10,1)))+3*(VALUE(MID(C178,5,1))+VALUE(MID(C178,11,1)))+2*(VALUE(MID(C178,6,1))+VALUE(MID(C178,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J178">
-        <f>IF(I178="","",IF(11-MOD(I178,11)&gt;9,0,11-MOD(I178,11)))</f>
-        <v/>
-      </c>
       <c r="K178">
+        <f>IF(J178="","",IF(11-MOD(J178,11)&gt;9,0,11-MOD(J178,11)))</f>
+        <v/>
+      </c>
+      <c r="L178">
         <f>IFERROR(IF(LEN(C178)&lt;&gt;13,"",IF(VALUE(MID(C178,5,3))&gt;=800,1000,2000)+VALUE(MID(C178,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L178">
-        <f>IFERROR(IF(K178="","",IF(AND(DAY(DATE(K178,VALUE(MID(C178,3,2)),VALUE(MID(C178,1,2))))=VALUE(MID(C178,1,2)),MONTH(DATE(K178,VALUE(MID(C178,3,2)),VALUE(MID(C178,1,2))))=VALUE(MID(C178,3,2))),DATE(K178,VALUE(MID(C178,3,2)),VALUE(MID(C178,1,2))),"")),"")</f>
+      <c r="M178">
+        <f>IFERROR(IF(L178="","",IF(AND(DAY(DATE(L178,VALUE(MID(C178,3,2)),VALUE(MID(C178,1,2))))=VALUE(MID(C178,1,2)),MONTH(DATE(L178,VALUE(MID(C178,3,2)),VALUE(MID(C178,1,2))))=VALUE(MID(C178,3,2))),DATE(L178,VALUE(MID(C178,3,2)),VALUE(MID(C178,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5839,27 +6551,31 @@
       <c r="B179" s="2" t="n"/>
       <c r="C179" s="3" t="n"/>
       <c r="D179" s="2" t="n"/>
-      <c r="E179" s="4" t="n"/>
-      <c r="F179" s="2" t="n"/>
+      <c r="E179" s="4">
+        <f>IF(A179="","",5)</f>
+        <v/>
+      </c>
+      <c r="F179" s="4" t="n"/>
       <c r="G179" s="2" t="n"/>
-      <c r="H179" s="2">
-        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(J179="","JMBG sadrži nešto što nije cifra",IF(L179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;J179,"Pogrešna kontrolna cifra — treba "&amp;J179,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I179">
+      <c r="H179" s="2" t="n"/>
+      <c r="I179" s="2">
+        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(K179="","JMBG sadrži nešto što nije cifra",IF(M179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;K179,"Pogrešna kontrolna cifra — treba "&amp;K179,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J179">
         <f>IFERROR(IF(LEN(C179)&lt;&gt;13,"",7*(VALUE(MID(C179,1,1))+VALUE(MID(C179,7,1)))+6*(VALUE(MID(C179,2,1))+VALUE(MID(C179,8,1)))+5*(VALUE(MID(C179,3,1))+VALUE(MID(C179,9,1)))+4*(VALUE(MID(C179,4,1))+VALUE(MID(C179,10,1)))+3*(VALUE(MID(C179,5,1))+VALUE(MID(C179,11,1)))+2*(VALUE(MID(C179,6,1))+VALUE(MID(C179,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J179">
-        <f>IF(I179="","",IF(11-MOD(I179,11)&gt;9,0,11-MOD(I179,11)))</f>
-        <v/>
-      </c>
       <c r="K179">
+        <f>IF(J179="","",IF(11-MOD(J179,11)&gt;9,0,11-MOD(J179,11)))</f>
+        <v/>
+      </c>
+      <c r="L179">
         <f>IFERROR(IF(LEN(C179)&lt;&gt;13,"",IF(VALUE(MID(C179,5,3))&gt;=800,1000,2000)+VALUE(MID(C179,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L179">
-        <f>IFERROR(IF(K179="","",IF(AND(DAY(DATE(K179,VALUE(MID(C179,3,2)),VALUE(MID(C179,1,2))))=VALUE(MID(C179,1,2)),MONTH(DATE(K179,VALUE(MID(C179,3,2)),VALUE(MID(C179,1,2))))=VALUE(MID(C179,3,2))),DATE(K179,VALUE(MID(C179,3,2)),VALUE(MID(C179,1,2))),"")),"")</f>
+      <c r="M179">
+        <f>IFERROR(IF(L179="","",IF(AND(DAY(DATE(L179,VALUE(MID(C179,3,2)),VALUE(MID(C179,1,2))))=VALUE(MID(C179,1,2)),MONTH(DATE(L179,VALUE(MID(C179,3,2)),VALUE(MID(C179,1,2))))=VALUE(MID(C179,3,2))),DATE(L179,VALUE(MID(C179,3,2)),VALUE(MID(C179,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5868,27 +6584,31 @@
       <c r="B180" s="2" t="n"/>
       <c r="C180" s="3" t="n"/>
       <c r="D180" s="2" t="n"/>
-      <c r="E180" s="4" t="n"/>
-      <c r="F180" s="2" t="n"/>
+      <c r="E180" s="4">
+        <f>IF(A180="","",5)</f>
+        <v/>
+      </c>
+      <c r="F180" s="4" t="n"/>
       <c r="G180" s="2" t="n"/>
-      <c r="H180" s="2">
-        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(J180="","JMBG sadrži nešto što nije cifra",IF(L180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;J180,"Pogrešna kontrolna cifra — treba "&amp;J180,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I180">
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2">
+        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(K180="","JMBG sadrži nešto što nije cifra",IF(M180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;K180,"Pogrešna kontrolna cifra — treba "&amp;K180,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J180">
         <f>IFERROR(IF(LEN(C180)&lt;&gt;13,"",7*(VALUE(MID(C180,1,1))+VALUE(MID(C180,7,1)))+6*(VALUE(MID(C180,2,1))+VALUE(MID(C180,8,1)))+5*(VALUE(MID(C180,3,1))+VALUE(MID(C180,9,1)))+4*(VALUE(MID(C180,4,1))+VALUE(MID(C180,10,1)))+3*(VALUE(MID(C180,5,1))+VALUE(MID(C180,11,1)))+2*(VALUE(MID(C180,6,1))+VALUE(MID(C180,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J180">
-        <f>IF(I180="","",IF(11-MOD(I180,11)&gt;9,0,11-MOD(I180,11)))</f>
-        <v/>
-      </c>
       <c r="K180">
+        <f>IF(J180="","",IF(11-MOD(J180,11)&gt;9,0,11-MOD(J180,11)))</f>
+        <v/>
+      </c>
+      <c r="L180">
         <f>IFERROR(IF(LEN(C180)&lt;&gt;13,"",IF(VALUE(MID(C180,5,3))&gt;=800,1000,2000)+VALUE(MID(C180,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L180">
-        <f>IFERROR(IF(K180="","",IF(AND(DAY(DATE(K180,VALUE(MID(C180,3,2)),VALUE(MID(C180,1,2))))=VALUE(MID(C180,1,2)),MONTH(DATE(K180,VALUE(MID(C180,3,2)),VALUE(MID(C180,1,2))))=VALUE(MID(C180,3,2))),DATE(K180,VALUE(MID(C180,3,2)),VALUE(MID(C180,1,2))),"")),"")</f>
+      <c r="M180">
+        <f>IFERROR(IF(L180="","",IF(AND(DAY(DATE(L180,VALUE(MID(C180,3,2)),VALUE(MID(C180,1,2))))=VALUE(MID(C180,1,2)),MONTH(DATE(L180,VALUE(MID(C180,3,2)),VALUE(MID(C180,1,2))))=VALUE(MID(C180,3,2))),DATE(L180,VALUE(MID(C180,3,2)),VALUE(MID(C180,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5897,27 +6617,31 @@
       <c r="B181" s="2" t="n"/>
       <c r="C181" s="3" t="n"/>
       <c r="D181" s="2" t="n"/>
-      <c r="E181" s="4" t="n"/>
-      <c r="F181" s="2" t="n"/>
+      <c r="E181" s="4">
+        <f>IF(A181="","",5)</f>
+        <v/>
+      </c>
+      <c r="F181" s="4" t="n"/>
       <c r="G181" s="2" t="n"/>
-      <c r="H181" s="2">
-        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(J181="","JMBG sadrži nešto što nije cifra",IF(L181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;J181,"Pogrešna kontrolna cifra — treba "&amp;J181,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I181">
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2">
+        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(K181="","JMBG sadrži nešto što nije cifra",IF(M181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;K181,"Pogrešna kontrolna cifra — treba "&amp;K181,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J181">
         <f>IFERROR(IF(LEN(C181)&lt;&gt;13,"",7*(VALUE(MID(C181,1,1))+VALUE(MID(C181,7,1)))+6*(VALUE(MID(C181,2,1))+VALUE(MID(C181,8,1)))+5*(VALUE(MID(C181,3,1))+VALUE(MID(C181,9,1)))+4*(VALUE(MID(C181,4,1))+VALUE(MID(C181,10,1)))+3*(VALUE(MID(C181,5,1))+VALUE(MID(C181,11,1)))+2*(VALUE(MID(C181,6,1))+VALUE(MID(C181,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J181">
-        <f>IF(I181="","",IF(11-MOD(I181,11)&gt;9,0,11-MOD(I181,11)))</f>
-        <v/>
-      </c>
       <c r="K181">
+        <f>IF(J181="","",IF(11-MOD(J181,11)&gt;9,0,11-MOD(J181,11)))</f>
+        <v/>
+      </c>
+      <c r="L181">
         <f>IFERROR(IF(LEN(C181)&lt;&gt;13,"",IF(VALUE(MID(C181,5,3))&gt;=800,1000,2000)+VALUE(MID(C181,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L181">
-        <f>IFERROR(IF(K181="","",IF(AND(DAY(DATE(K181,VALUE(MID(C181,3,2)),VALUE(MID(C181,1,2))))=VALUE(MID(C181,1,2)),MONTH(DATE(K181,VALUE(MID(C181,3,2)),VALUE(MID(C181,1,2))))=VALUE(MID(C181,3,2))),DATE(K181,VALUE(MID(C181,3,2)),VALUE(MID(C181,1,2))),"")),"")</f>
+      <c r="M181">
+        <f>IFERROR(IF(L181="","",IF(AND(DAY(DATE(L181,VALUE(MID(C181,3,2)),VALUE(MID(C181,1,2))))=VALUE(MID(C181,1,2)),MONTH(DATE(L181,VALUE(MID(C181,3,2)),VALUE(MID(C181,1,2))))=VALUE(MID(C181,3,2))),DATE(L181,VALUE(MID(C181,3,2)),VALUE(MID(C181,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5926,27 +6650,31 @@
       <c r="B182" s="2" t="n"/>
       <c r="C182" s="3" t="n"/>
       <c r="D182" s="2" t="n"/>
-      <c r="E182" s="4" t="n"/>
-      <c r="F182" s="2" t="n"/>
+      <c r="E182" s="4">
+        <f>IF(A182="","",5)</f>
+        <v/>
+      </c>
+      <c r="F182" s="4" t="n"/>
       <c r="G182" s="2" t="n"/>
-      <c r="H182" s="2">
-        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(J182="","JMBG sadrži nešto što nije cifra",IF(L182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;J182,"Pogrešna kontrolna cifra — treba "&amp;J182,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I182">
+      <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2">
+        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(K182="","JMBG sadrži nešto što nije cifra",IF(M182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;K182,"Pogrešna kontrolna cifra — treba "&amp;K182,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J182">
         <f>IFERROR(IF(LEN(C182)&lt;&gt;13,"",7*(VALUE(MID(C182,1,1))+VALUE(MID(C182,7,1)))+6*(VALUE(MID(C182,2,1))+VALUE(MID(C182,8,1)))+5*(VALUE(MID(C182,3,1))+VALUE(MID(C182,9,1)))+4*(VALUE(MID(C182,4,1))+VALUE(MID(C182,10,1)))+3*(VALUE(MID(C182,5,1))+VALUE(MID(C182,11,1)))+2*(VALUE(MID(C182,6,1))+VALUE(MID(C182,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J182">
-        <f>IF(I182="","",IF(11-MOD(I182,11)&gt;9,0,11-MOD(I182,11)))</f>
-        <v/>
-      </c>
       <c r="K182">
+        <f>IF(J182="","",IF(11-MOD(J182,11)&gt;9,0,11-MOD(J182,11)))</f>
+        <v/>
+      </c>
+      <c r="L182">
         <f>IFERROR(IF(LEN(C182)&lt;&gt;13,"",IF(VALUE(MID(C182,5,3))&gt;=800,1000,2000)+VALUE(MID(C182,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L182">
-        <f>IFERROR(IF(K182="","",IF(AND(DAY(DATE(K182,VALUE(MID(C182,3,2)),VALUE(MID(C182,1,2))))=VALUE(MID(C182,1,2)),MONTH(DATE(K182,VALUE(MID(C182,3,2)),VALUE(MID(C182,1,2))))=VALUE(MID(C182,3,2))),DATE(K182,VALUE(MID(C182,3,2)),VALUE(MID(C182,1,2))),"")),"")</f>
+      <c r="M182">
+        <f>IFERROR(IF(L182="","",IF(AND(DAY(DATE(L182,VALUE(MID(C182,3,2)),VALUE(MID(C182,1,2))))=VALUE(MID(C182,1,2)),MONTH(DATE(L182,VALUE(MID(C182,3,2)),VALUE(MID(C182,1,2))))=VALUE(MID(C182,3,2))),DATE(L182,VALUE(MID(C182,3,2)),VALUE(MID(C182,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5955,27 +6683,31 @@
       <c r="B183" s="2" t="n"/>
       <c r="C183" s="3" t="n"/>
       <c r="D183" s="2" t="n"/>
-      <c r="E183" s="4" t="n"/>
-      <c r="F183" s="2" t="n"/>
+      <c r="E183" s="4">
+        <f>IF(A183="","",5)</f>
+        <v/>
+      </c>
+      <c r="F183" s="4" t="n"/>
       <c r="G183" s="2" t="n"/>
-      <c r="H183" s="2">
-        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(J183="","JMBG sadrži nešto što nije cifra",IF(L183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;J183,"Pogrešna kontrolna cifra — treba "&amp;J183,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I183">
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2">
+        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(K183="","JMBG sadrži nešto što nije cifra",IF(M183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;K183,"Pogrešna kontrolna cifra — treba "&amp;K183,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J183">
         <f>IFERROR(IF(LEN(C183)&lt;&gt;13,"",7*(VALUE(MID(C183,1,1))+VALUE(MID(C183,7,1)))+6*(VALUE(MID(C183,2,1))+VALUE(MID(C183,8,1)))+5*(VALUE(MID(C183,3,1))+VALUE(MID(C183,9,1)))+4*(VALUE(MID(C183,4,1))+VALUE(MID(C183,10,1)))+3*(VALUE(MID(C183,5,1))+VALUE(MID(C183,11,1)))+2*(VALUE(MID(C183,6,1))+VALUE(MID(C183,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J183">
-        <f>IF(I183="","",IF(11-MOD(I183,11)&gt;9,0,11-MOD(I183,11)))</f>
-        <v/>
-      </c>
       <c r="K183">
+        <f>IF(J183="","",IF(11-MOD(J183,11)&gt;9,0,11-MOD(J183,11)))</f>
+        <v/>
+      </c>
+      <c r="L183">
         <f>IFERROR(IF(LEN(C183)&lt;&gt;13,"",IF(VALUE(MID(C183,5,3))&gt;=800,1000,2000)+VALUE(MID(C183,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L183">
-        <f>IFERROR(IF(K183="","",IF(AND(DAY(DATE(K183,VALUE(MID(C183,3,2)),VALUE(MID(C183,1,2))))=VALUE(MID(C183,1,2)),MONTH(DATE(K183,VALUE(MID(C183,3,2)),VALUE(MID(C183,1,2))))=VALUE(MID(C183,3,2))),DATE(K183,VALUE(MID(C183,3,2)),VALUE(MID(C183,1,2))),"")),"")</f>
+      <c r="M183">
+        <f>IFERROR(IF(L183="","",IF(AND(DAY(DATE(L183,VALUE(MID(C183,3,2)),VALUE(MID(C183,1,2))))=VALUE(MID(C183,1,2)),MONTH(DATE(L183,VALUE(MID(C183,3,2)),VALUE(MID(C183,1,2))))=VALUE(MID(C183,3,2))),DATE(L183,VALUE(MID(C183,3,2)),VALUE(MID(C183,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -5984,27 +6716,31 @@
       <c r="B184" s="2" t="n"/>
       <c r="C184" s="3" t="n"/>
       <c r="D184" s="2" t="n"/>
-      <c r="E184" s="4" t="n"/>
-      <c r="F184" s="2" t="n"/>
+      <c r="E184" s="4">
+        <f>IF(A184="","",5)</f>
+        <v/>
+      </c>
+      <c r="F184" s="4" t="n"/>
       <c r="G184" s="2" t="n"/>
-      <c r="H184" s="2">
-        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(J184="","JMBG sadrži nešto što nije cifra",IF(L184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;J184,"Pogrešna kontrolna cifra — treba "&amp;J184,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I184">
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2">
+        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(K184="","JMBG sadrži nešto što nije cifra",IF(M184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;K184,"Pogrešna kontrolna cifra — treba "&amp;K184,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J184">
         <f>IFERROR(IF(LEN(C184)&lt;&gt;13,"",7*(VALUE(MID(C184,1,1))+VALUE(MID(C184,7,1)))+6*(VALUE(MID(C184,2,1))+VALUE(MID(C184,8,1)))+5*(VALUE(MID(C184,3,1))+VALUE(MID(C184,9,1)))+4*(VALUE(MID(C184,4,1))+VALUE(MID(C184,10,1)))+3*(VALUE(MID(C184,5,1))+VALUE(MID(C184,11,1)))+2*(VALUE(MID(C184,6,1))+VALUE(MID(C184,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J184">
-        <f>IF(I184="","",IF(11-MOD(I184,11)&gt;9,0,11-MOD(I184,11)))</f>
-        <v/>
-      </c>
       <c r="K184">
+        <f>IF(J184="","",IF(11-MOD(J184,11)&gt;9,0,11-MOD(J184,11)))</f>
+        <v/>
+      </c>
+      <c r="L184">
         <f>IFERROR(IF(LEN(C184)&lt;&gt;13,"",IF(VALUE(MID(C184,5,3))&gt;=800,1000,2000)+VALUE(MID(C184,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L184">
-        <f>IFERROR(IF(K184="","",IF(AND(DAY(DATE(K184,VALUE(MID(C184,3,2)),VALUE(MID(C184,1,2))))=VALUE(MID(C184,1,2)),MONTH(DATE(K184,VALUE(MID(C184,3,2)),VALUE(MID(C184,1,2))))=VALUE(MID(C184,3,2))),DATE(K184,VALUE(MID(C184,3,2)),VALUE(MID(C184,1,2))),"")),"")</f>
+      <c r="M184">
+        <f>IFERROR(IF(L184="","",IF(AND(DAY(DATE(L184,VALUE(MID(C184,3,2)),VALUE(MID(C184,1,2))))=VALUE(MID(C184,1,2)),MONTH(DATE(L184,VALUE(MID(C184,3,2)),VALUE(MID(C184,1,2))))=VALUE(MID(C184,3,2))),DATE(L184,VALUE(MID(C184,3,2)),VALUE(MID(C184,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6013,27 +6749,31 @@
       <c r="B185" s="2" t="n"/>
       <c r="C185" s="3" t="n"/>
       <c r="D185" s="2" t="n"/>
-      <c r="E185" s="4" t="n"/>
-      <c r="F185" s="2" t="n"/>
+      <c r="E185" s="4">
+        <f>IF(A185="","",5)</f>
+        <v/>
+      </c>
+      <c r="F185" s="4" t="n"/>
       <c r="G185" s="2" t="n"/>
-      <c r="H185" s="2">
-        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(J185="","JMBG sadrži nešto što nije cifra",IF(L185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;J185,"Pogrešna kontrolna cifra — treba "&amp;J185,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I185">
+      <c r="H185" s="2" t="n"/>
+      <c r="I185" s="2">
+        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(K185="","JMBG sadrži nešto što nije cifra",IF(M185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;K185,"Pogrešna kontrolna cifra — treba "&amp;K185,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J185">
         <f>IFERROR(IF(LEN(C185)&lt;&gt;13,"",7*(VALUE(MID(C185,1,1))+VALUE(MID(C185,7,1)))+6*(VALUE(MID(C185,2,1))+VALUE(MID(C185,8,1)))+5*(VALUE(MID(C185,3,1))+VALUE(MID(C185,9,1)))+4*(VALUE(MID(C185,4,1))+VALUE(MID(C185,10,1)))+3*(VALUE(MID(C185,5,1))+VALUE(MID(C185,11,1)))+2*(VALUE(MID(C185,6,1))+VALUE(MID(C185,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J185">
-        <f>IF(I185="","",IF(11-MOD(I185,11)&gt;9,0,11-MOD(I185,11)))</f>
-        <v/>
-      </c>
       <c r="K185">
+        <f>IF(J185="","",IF(11-MOD(J185,11)&gt;9,0,11-MOD(J185,11)))</f>
+        <v/>
+      </c>
+      <c r="L185">
         <f>IFERROR(IF(LEN(C185)&lt;&gt;13,"",IF(VALUE(MID(C185,5,3))&gt;=800,1000,2000)+VALUE(MID(C185,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L185">
-        <f>IFERROR(IF(K185="","",IF(AND(DAY(DATE(K185,VALUE(MID(C185,3,2)),VALUE(MID(C185,1,2))))=VALUE(MID(C185,1,2)),MONTH(DATE(K185,VALUE(MID(C185,3,2)),VALUE(MID(C185,1,2))))=VALUE(MID(C185,3,2))),DATE(K185,VALUE(MID(C185,3,2)),VALUE(MID(C185,1,2))),"")),"")</f>
+      <c r="M185">
+        <f>IFERROR(IF(L185="","",IF(AND(DAY(DATE(L185,VALUE(MID(C185,3,2)),VALUE(MID(C185,1,2))))=VALUE(MID(C185,1,2)),MONTH(DATE(L185,VALUE(MID(C185,3,2)),VALUE(MID(C185,1,2))))=VALUE(MID(C185,3,2))),DATE(L185,VALUE(MID(C185,3,2)),VALUE(MID(C185,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6042,27 +6782,31 @@
       <c r="B186" s="2" t="n"/>
       <c r="C186" s="3" t="n"/>
       <c r="D186" s="2" t="n"/>
-      <c r="E186" s="4" t="n"/>
-      <c r="F186" s="2" t="n"/>
+      <c r="E186" s="4">
+        <f>IF(A186="","",5)</f>
+        <v/>
+      </c>
+      <c r="F186" s="4" t="n"/>
       <c r="G186" s="2" t="n"/>
-      <c r="H186" s="2">
-        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(J186="","JMBG sadrži nešto što nije cifra",IF(L186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;J186,"Pogrešna kontrolna cifra — treba "&amp;J186,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I186">
+      <c r="H186" s="2" t="n"/>
+      <c r="I186" s="2">
+        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(K186="","JMBG sadrži nešto što nije cifra",IF(M186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;K186,"Pogrešna kontrolna cifra — treba "&amp;K186,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J186">
         <f>IFERROR(IF(LEN(C186)&lt;&gt;13,"",7*(VALUE(MID(C186,1,1))+VALUE(MID(C186,7,1)))+6*(VALUE(MID(C186,2,1))+VALUE(MID(C186,8,1)))+5*(VALUE(MID(C186,3,1))+VALUE(MID(C186,9,1)))+4*(VALUE(MID(C186,4,1))+VALUE(MID(C186,10,1)))+3*(VALUE(MID(C186,5,1))+VALUE(MID(C186,11,1)))+2*(VALUE(MID(C186,6,1))+VALUE(MID(C186,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J186">
-        <f>IF(I186="","",IF(11-MOD(I186,11)&gt;9,0,11-MOD(I186,11)))</f>
-        <v/>
-      </c>
       <c r="K186">
+        <f>IF(J186="","",IF(11-MOD(J186,11)&gt;9,0,11-MOD(J186,11)))</f>
+        <v/>
+      </c>
+      <c r="L186">
         <f>IFERROR(IF(LEN(C186)&lt;&gt;13,"",IF(VALUE(MID(C186,5,3))&gt;=800,1000,2000)+VALUE(MID(C186,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L186">
-        <f>IFERROR(IF(K186="","",IF(AND(DAY(DATE(K186,VALUE(MID(C186,3,2)),VALUE(MID(C186,1,2))))=VALUE(MID(C186,1,2)),MONTH(DATE(K186,VALUE(MID(C186,3,2)),VALUE(MID(C186,1,2))))=VALUE(MID(C186,3,2))),DATE(K186,VALUE(MID(C186,3,2)),VALUE(MID(C186,1,2))),"")),"")</f>
+      <c r="M186">
+        <f>IFERROR(IF(L186="","",IF(AND(DAY(DATE(L186,VALUE(MID(C186,3,2)),VALUE(MID(C186,1,2))))=VALUE(MID(C186,1,2)),MONTH(DATE(L186,VALUE(MID(C186,3,2)),VALUE(MID(C186,1,2))))=VALUE(MID(C186,3,2))),DATE(L186,VALUE(MID(C186,3,2)),VALUE(MID(C186,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6071,27 +6815,31 @@
       <c r="B187" s="2" t="n"/>
       <c r="C187" s="3" t="n"/>
       <c r="D187" s="2" t="n"/>
-      <c r="E187" s="4" t="n"/>
-      <c r="F187" s="2" t="n"/>
+      <c r="E187" s="4">
+        <f>IF(A187="","",5)</f>
+        <v/>
+      </c>
+      <c r="F187" s="4" t="n"/>
       <c r="G187" s="2" t="n"/>
-      <c r="H187" s="2">
-        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(J187="","JMBG sadrži nešto što nije cifra",IF(L187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;J187,"Pogrešna kontrolna cifra — treba "&amp;J187,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I187">
+      <c r="H187" s="2" t="n"/>
+      <c r="I187" s="2">
+        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(K187="","JMBG sadrži nešto što nije cifra",IF(M187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;K187,"Pogrešna kontrolna cifra — treba "&amp;K187,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J187">
         <f>IFERROR(IF(LEN(C187)&lt;&gt;13,"",7*(VALUE(MID(C187,1,1))+VALUE(MID(C187,7,1)))+6*(VALUE(MID(C187,2,1))+VALUE(MID(C187,8,1)))+5*(VALUE(MID(C187,3,1))+VALUE(MID(C187,9,1)))+4*(VALUE(MID(C187,4,1))+VALUE(MID(C187,10,1)))+3*(VALUE(MID(C187,5,1))+VALUE(MID(C187,11,1)))+2*(VALUE(MID(C187,6,1))+VALUE(MID(C187,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J187">
-        <f>IF(I187="","",IF(11-MOD(I187,11)&gt;9,0,11-MOD(I187,11)))</f>
-        <v/>
-      </c>
       <c r="K187">
+        <f>IF(J187="","",IF(11-MOD(J187,11)&gt;9,0,11-MOD(J187,11)))</f>
+        <v/>
+      </c>
+      <c r="L187">
         <f>IFERROR(IF(LEN(C187)&lt;&gt;13,"",IF(VALUE(MID(C187,5,3))&gt;=800,1000,2000)+VALUE(MID(C187,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L187">
-        <f>IFERROR(IF(K187="","",IF(AND(DAY(DATE(K187,VALUE(MID(C187,3,2)),VALUE(MID(C187,1,2))))=VALUE(MID(C187,1,2)),MONTH(DATE(K187,VALUE(MID(C187,3,2)),VALUE(MID(C187,1,2))))=VALUE(MID(C187,3,2))),DATE(K187,VALUE(MID(C187,3,2)),VALUE(MID(C187,1,2))),"")),"")</f>
+      <c r="M187">
+        <f>IFERROR(IF(L187="","",IF(AND(DAY(DATE(L187,VALUE(MID(C187,3,2)),VALUE(MID(C187,1,2))))=VALUE(MID(C187,1,2)),MONTH(DATE(L187,VALUE(MID(C187,3,2)),VALUE(MID(C187,1,2))))=VALUE(MID(C187,3,2))),DATE(L187,VALUE(MID(C187,3,2)),VALUE(MID(C187,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6100,27 +6848,31 @@
       <c r="B188" s="2" t="n"/>
       <c r="C188" s="3" t="n"/>
       <c r="D188" s="2" t="n"/>
-      <c r="E188" s="4" t="n"/>
-      <c r="F188" s="2" t="n"/>
+      <c r="E188" s="4">
+        <f>IF(A188="","",5)</f>
+        <v/>
+      </c>
+      <c r="F188" s="4" t="n"/>
       <c r="G188" s="2" t="n"/>
-      <c r="H188" s="2">
-        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(J188="","JMBG sadrži nešto što nije cifra",IF(L188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;J188,"Pogrešna kontrolna cifra — treba "&amp;J188,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I188">
+      <c r="H188" s="2" t="n"/>
+      <c r="I188" s="2">
+        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(K188="","JMBG sadrži nešto što nije cifra",IF(M188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;K188,"Pogrešna kontrolna cifra — treba "&amp;K188,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J188">
         <f>IFERROR(IF(LEN(C188)&lt;&gt;13,"",7*(VALUE(MID(C188,1,1))+VALUE(MID(C188,7,1)))+6*(VALUE(MID(C188,2,1))+VALUE(MID(C188,8,1)))+5*(VALUE(MID(C188,3,1))+VALUE(MID(C188,9,1)))+4*(VALUE(MID(C188,4,1))+VALUE(MID(C188,10,1)))+3*(VALUE(MID(C188,5,1))+VALUE(MID(C188,11,1)))+2*(VALUE(MID(C188,6,1))+VALUE(MID(C188,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J188">
-        <f>IF(I188="","",IF(11-MOD(I188,11)&gt;9,0,11-MOD(I188,11)))</f>
-        <v/>
-      </c>
       <c r="K188">
+        <f>IF(J188="","",IF(11-MOD(J188,11)&gt;9,0,11-MOD(J188,11)))</f>
+        <v/>
+      </c>
+      <c r="L188">
         <f>IFERROR(IF(LEN(C188)&lt;&gt;13,"",IF(VALUE(MID(C188,5,3))&gt;=800,1000,2000)+VALUE(MID(C188,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L188">
-        <f>IFERROR(IF(K188="","",IF(AND(DAY(DATE(K188,VALUE(MID(C188,3,2)),VALUE(MID(C188,1,2))))=VALUE(MID(C188,1,2)),MONTH(DATE(K188,VALUE(MID(C188,3,2)),VALUE(MID(C188,1,2))))=VALUE(MID(C188,3,2))),DATE(K188,VALUE(MID(C188,3,2)),VALUE(MID(C188,1,2))),"")),"")</f>
+      <c r="M188">
+        <f>IFERROR(IF(L188="","",IF(AND(DAY(DATE(L188,VALUE(MID(C188,3,2)),VALUE(MID(C188,1,2))))=VALUE(MID(C188,1,2)),MONTH(DATE(L188,VALUE(MID(C188,3,2)),VALUE(MID(C188,1,2))))=VALUE(MID(C188,3,2))),DATE(L188,VALUE(MID(C188,3,2)),VALUE(MID(C188,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6129,27 +6881,31 @@
       <c r="B189" s="2" t="n"/>
       <c r="C189" s="3" t="n"/>
       <c r="D189" s="2" t="n"/>
-      <c r="E189" s="4" t="n"/>
-      <c r="F189" s="2" t="n"/>
+      <c r="E189" s="4">
+        <f>IF(A189="","",5)</f>
+        <v/>
+      </c>
+      <c r="F189" s="4" t="n"/>
       <c r="G189" s="2" t="n"/>
-      <c r="H189" s="2">
-        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(J189="","JMBG sadrži nešto što nije cifra",IF(L189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;J189,"Pogrešna kontrolna cifra — treba "&amp;J189,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I189">
+      <c r="H189" s="2" t="n"/>
+      <c r="I189" s="2">
+        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(K189="","JMBG sadrži nešto što nije cifra",IF(M189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;K189,"Pogrešna kontrolna cifra — treba "&amp;K189,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J189">
         <f>IFERROR(IF(LEN(C189)&lt;&gt;13,"",7*(VALUE(MID(C189,1,1))+VALUE(MID(C189,7,1)))+6*(VALUE(MID(C189,2,1))+VALUE(MID(C189,8,1)))+5*(VALUE(MID(C189,3,1))+VALUE(MID(C189,9,1)))+4*(VALUE(MID(C189,4,1))+VALUE(MID(C189,10,1)))+3*(VALUE(MID(C189,5,1))+VALUE(MID(C189,11,1)))+2*(VALUE(MID(C189,6,1))+VALUE(MID(C189,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J189">
-        <f>IF(I189="","",IF(11-MOD(I189,11)&gt;9,0,11-MOD(I189,11)))</f>
-        <v/>
-      </c>
       <c r="K189">
+        <f>IF(J189="","",IF(11-MOD(J189,11)&gt;9,0,11-MOD(J189,11)))</f>
+        <v/>
+      </c>
+      <c r="L189">
         <f>IFERROR(IF(LEN(C189)&lt;&gt;13,"",IF(VALUE(MID(C189,5,3))&gt;=800,1000,2000)+VALUE(MID(C189,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L189">
-        <f>IFERROR(IF(K189="","",IF(AND(DAY(DATE(K189,VALUE(MID(C189,3,2)),VALUE(MID(C189,1,2))))=VALUE(MID(C189,1,2)),MONTH(DATE(K189,VALUE(MID(C189,3,2)),VALUE(MID(C189,1,2))))=VALUE(MID(C189,3,2))),DATE(K189,VALUE(MID(C189,3,2)),VALUE(MID(C189,1,2))),"")),"")</f>
+      <c r="M189">
+        <f>IFERROR(IF(L189="","",IF(AND(DAY(DATE(L189,VALUE(MID(C189,3,2)),VALUE(MID(C189,1,2))))=VALUE(MID(C189,1,2)),MONTH(DATE(L189,VALUE(MID(C189,3,2)),VALUE(MID(C189,1,2))))=VALUE(MID(C189,3,2))),DATE(L189,VALUE(MID(C189,3,2)),VALUE(MID(C189,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6158,27 +6914,31 @@
       <c r="B190" s="2" t="n"/>
       <c r="C190" s="3" t="n"/>
       <c r="D190" s="2" t="n"/>
-      <c r="E190" s="4" t="n"/>
-      <c r="F190" s="2" t="n"/>
+      <c r="E190" s="4">
+        <f>IF(A190="","",5)</f>
+        <v/>
+      </c>
+      <c r="F190" s="4" t="n"/>
       <c r="G190" s="2" t="n"/>
-      <c r="H190" s="2">
-        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(J190="","JMBG sadrži nešto što nije cifra",IF(L190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;J190,"Pogrešna kontrolna cifra — treba "&amp;J190,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I190">
+      <c r="H190" s="2" t="n"/>
+      <c r="I190" s="2">
+        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(K190="","JMBG sadrži nešto što nije cifra",IF(M190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;K190,"Pogrešna kontrolna cifra — treba "&amp;K190,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J190">
         <f>IFERROR(IF(LEN(C190)&lt;&gt;13,"",7*(VALUE(MID(C190,1,1))+VALUE(MID(C190,7,1)))+6*(VALUE(MID(C190,2,1))+VALUE(MID(C190,8,1)))+5*(VALUE(MID(C190,3,1))+VALUE(MID(C190,9,1)))+4*(VALUE(MID(C190,4,1))+VALUE(MID(C190,10,1)))+3*(VALUE(MID(C190,5,1))+VALUE(MID(C190,11,1)))+2*(VALUE(MID(C190,6,1))+VALUE(MID(C190,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J190">
-        <f>IF(I190="","",IF(11-MOD(I190,11)&gt;9,0,11-MOD(I190,11)))</f>
-        <v/>
-      </c>
       <c r="K190">
+        <f>IF(J190="","",IF(11-MOD(J190,11)&gt;9,0,11-MOD(J190,11)))</f>
+        <v/>
+      </c>
+      <c r="L190">
         <f>IFERROR(IF(LEN(C190)&lt;&gt;13,"",IF(VALUE(MID(C190,5,3))&gt;=800,1000,2000)+VALUE(MID(C190,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L190">
-        <f>IFERROR(IF(K190="","",IF(AND(DAY(DATE(K190,VALUE(MID(C190,3,2)),VALUE(MID(C190,1,2))))=VALUE(MID(C190,1,2)),MONTH(DATE(K190,VALUE(MID(C190,3,2)),VALUE(MID(C190,1,2))))=VALUE(MID(C190,3,2))),DATE(K190,VALUE(MID(C190,3,2)),VALUE(MID(C190,1,2))),"")),"")</f>
+      <c r="M190">
+        <f>IFERROR(IF(L190="","",IF(AND(DAY(DATE(L190,VALUE(MID(C190,3,2)),VALUE(MID(C190,1,2))))=VALUE(MID(C190,1,2)),MONTH(DATE(L190,VALUE(MID(C190,3,2)),VALUE(MID(C190,1,2))))=VALUE(MID(C190,3,2))),DATE(L190,VALUE(MID(C190,3,2)),VALUE(MID(C190,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6187,27 +6947,31 @@
       <c r="B191" s="2" t="n"/>
       <c r="C191" s="3" t="n"/>
       <c r="D191" s="2" t="n"/>
-      <c r="E191" s="4" t="n"/>
-      <c r="F191" s="2" t="n"/>
+      <c r="E191" s="4">
+        <f>IF(A191="","",5)</f>
+        <v/>
+      </c>
+      <c r="F191" s="4" t="n"/>
       <c r="G191" s="2" t="n"/>
-      <c r="H191" s="2">
-        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(J191="","JMBG sadrži nešto što nije cifra",IF(L191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;J191,"Pogrešna kontrolna cifra — treba "&amp;J191,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I191">
+      <c r="H191" s="2" t="n"/>
+      <c r="I191" s="2">
+        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(K191="","JMBG sadrži nešto što nije cifra",IF(M191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;K191,"Pogrešna kontrolna cifra — treba "&amp;K191,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J191">
         <f>IFERROR(IF(LEN(C191)&lt;&gt;13,"",7*(VALUE(MID(C191,1,1))+VALUE(MID(C191,7,1)))+6*(VALUE(MID(C191,2,1))+VALUE(MID(C191,8,1)))+5*(VALUE(MID(C191,3,1))+VALUE(MID(C191,9,1)))+4*(VALUE(MID(C191,4,1))+VALUE(MID(C191,10,1)))+3*(VALUE(MID(C191,5,1))+VALUE(MID(C191,11,1)))+2*(VALUE(MID(C191,6,1))+VALUE(MID(C191,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J191">
-        <f>IF(I191="","",IF(11-MOD(I191,11)&gt;9,0,11-MOD(I191,11)))</f>
-        <v/>
-      </c>
       <c r="K191">
+        <f>IF(J191="","",IF(11-MOD(J191,11)&gt;9,0,11-MOD(J191,11)))</f>
+        <v/>
+      </c>
+      <c r="L191">
         <f>IFERROR(IF(LEN(C191)&lt;&gt;13,"",IF(VALUE(MID(C191,5,3))&gt;=800,1000,2000)+VALUE(MID(C191,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L191">
-        <f>IFERROR(IF(K191="","",IF(AND(DAY(DATE(K191,VALUE(MID(C191,3,2)),VALUE(MID(C191,1,2))))=VALUE(MID(C191,1,2)),MONTH(DATE(K191,VALUE(MID(C191,3,2)),VALUE(MID(C191,1,2))))=VALUE(MID(C191,3,2))),DATE(K191,VALUE(MID(C191,3,2)),VALUE(MID(C191,1,2))),"")),"")</f>
+      <c r="M191">
+        <f>IFERROR(IF(L191="","",IF(AND(DAY(DATE(L191,VALUE(MID(C191,3,2)),VALUE(MID(C191,1,2))))=VALUE(MID(C191,1,2)),MONTH(DATE(L191,VALUE(MID(C191,3,2)),VALUE(MID(C191,1,2))))=VALUE(MID(C191,3,2))),DATE(L191,VALUE(MID(C191,3,2)),VALUE(MID(C191,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6216,27 +6980,31 @@
       <c r="B192" s="2" t="n"/>
       <c r="C192" s="3" t="n"/>
       <c r="D192" s="2" t="n"/>
-      <c r="E192" s="4" t="n"/>
-      <c r="F192" s="2" t="n"/>
+      <c r="E192" s="4">
+        <f>IF(A192="","",5)</f>
+        <v/>
+      </c>
+      <c r="F192" s="4" t="n"/>
       <c r="G192" s="2" t="n"/>
-      <c r="H192" s="2">
-        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(J192="","JMBG sadrži nešto što nije cifra",IF(L192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;J192,"Pogrešna kontrolna cifra — treba "&amp;J192,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I192">
+      <c r="H192" s="2" t="n"/>
+      <c r="I192" s="2">
+        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(K192="","JMBG sadrži nešto što nije cifra",IF(M192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;K192,"Pogrešna kontrolna cifra — treba "&amp;K192,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J192">
         <f>IFERROR(IF(LEN(C192)&lt;&gt;13,"",7*(VALUE(MID(C192,1,1))+VALUE(MID(C192,7,1)))+6*(VALUE(MID(C192,2,1))+VALUE(MID(C192,8,1)))+5*(VALUE(MID(C192,3,1))+VALUE(MID(C192,9,1)))+4*(VALUE(MID(C192,4,1))+VALUE(MID(C192,10,1)))+3*(VALUE(MID(C192,5,1))+VALUE(MID(C192,11,1)))+2*(VALUE(MID(C192,6,1))+VALUE(MID(C192,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J192">
-        <f>IF(I192="","",IF(11-MOD(I192,11)&gt;9,0,11-MOD(I192,11)))</f>
-        <v/>
-      </c>
       <c r="K192">
+        <f>IF(J192="","",IF(11-MOD(J192,11)&gt;9,0,11-MOD(J192,11)))</f>
+        <v/>
+      </c>
+      <c r="L192">
         <f>IFERROR(IF(LEN(C192)&lt;&gt;13,"",IF(VALUE(MID(C192,5,3))&gt;=800,1000,2000)+VALUE(MID(C192,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L192">
-        <f>IFERROR(IF(K192="","",IF(AND(DAY(DATE(K192,VALUE(MID(C192,3,2)),VALUE(MID(C192,1,2))))=VALUE(MID(C192,1,2)),MONTH(DATE(K192,VALUE(MID(C192,3,2)),VALUE(MID(C192,1,2))))=VALUE(MID(C192,3,2))),DATE(K192,VALUE(MID(C192,3,2)),VALUE(MID(C192,1,2))),"")),"")</f>
+      <c r="M192">
+        <f>IFERROR(IF(L192="","",IF(AND(DAY(DATE(L192,VALUE(MID(C192,3,2)),VALUE(MID(C192,1,2))))=VALUE(MID(C192,1,2)),MONTH(DATE(L192,VALUE(MID(C192,3,2)),VALUE(MID(C192,1,2))))=VALUE(MID(C192,3,2))),DATE(L192,VALUE(MID(C192,3,2)),VALUE(MID(C192,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6245,27 +7013,31 @@
       <c r="B193" s="2" t="n"/>
       <c r="C193" s="3" t="n"/>
       <c r="D193" s="2" t="n"/>
-      <c r="E193" s="4" t="n"/>
-      <c r="F193" s="2" t="n"/>
+      <c r="E193" s="4">
+        <f>IF(A193="","",5)</f>
+        <v/>
+      </c>
+      <c r="F193" s="4" t="n"/>
       <c r="G193" s="2" t="n"/>
-      <c r="H193" s="2">
-        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(J193="","JMBG sadrži nešto što nije cifra",IF(L193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;J193,"Pogrešna kontrolna cifra — treba "&amp;J193,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I193">
+      <c r="H193" s="2" t="n"/>
+      <c r="I193" s="2">
+        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(K193="","JMBG sadrži nešto što nije cifra",IF(M193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;K193,"Pogrešna kontrolna cifra — treba "&amp;K193,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J193">
         <f>IFERROR(IF(LEN(C193)&lt;&gt;13,"",7*(VALUE(MID(C193,1,1))+VALUE(MID(C193,7,1)))+6*(VALUE(MID(C193,2,1))+VALUE(MID(C193,8,1)))+5*(VALUE(MID(C193,3,1))+VALUE(MID(C193,9,1)))+4*(VALUE(MID(C193,4,1))+VALUE(MID(C193,10,1)))+3*(VALUE(MID(C193,5,1))+VALUE(MID(C193,11,1)))+2*(VALUE(MID(C193,6,1))+VALUE(MID(C193,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J193">
-        <f>IF(I193="","",IF(11-MOD(I193,11)&gt;9,0,11-MOD(I193,11)))</f>
-        <v/>
-      </c>
       <c r="K193">
+        <f>IF(J193="","",IF(11-MOD(J193,11)&gt;9,0,11-MOD(J193,11)))</f>
+        <v/>
+      </c>
+      <c r="L193">
         <f>IFERROR(IF(LEN(C193)&lt;&gt;13,"",IF(VALUE(MID(C193,5,3))&gt;=800,1000,2000)+VALUE(MID(C193,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L193">
-        <f>IFERROR(IF(K193="","",IF(AND(DAY(DATE(K193,VALUE(MID(C193,3,2)),VALUE(MID(C193,1,2))))=VALUE(MID(C193,1,2)),MONTH(DATE(K193,VALUE(MID(C193,3,2)),VALUE(MID(C193,1,2))))=VALUE(MID(C193,3,2))),DATE(K193,VALUE(MID(C193,3,2)),VALUE(MID(C193,1,2))),"")),"")</f>
+      <c r="M193">
+        <f>IFERROR(IF(L193="","",IF(AND(DAY(DATE(L193,VALUE(MID(C193,3,2)),VALUE(MID(C193,1,2))))=VALUE(MID(C193,1,2)),MONTH(DATE(L193,VALUE(MID(C193,3,2)),VALUE(MID(C193,1,2))))=VALUE(MID(C193,3,2))),DATE(L193,VALUE(MID(C193,3,2)),VALUE(MID(C193,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6274,27 +7046,31 @@
       <c r="B194" s="2" t="n"/>
       <c r="C194" s="3" t="n"/>
       <c r="D194" s="2" t="n"/>
-      <c r="E194" s="4" t="n"/>
-      <c r="F194" s="2" t="n"/>
+      <c r="E194" s="4">
+        <f>IF(A194="","",5)</f>
+        <v/>
+      </c>
+      <c r="F194" s="4" t="n"/>
       <c r="G194" s="2" t="n"/>
-      <c r="H194" s="2">
-        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(J194="","JMBG sadrži nešto što nije cifra",IF(L194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;J194,"Pogrešna kontrolna cifra — treba "&amp;J194,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I194">
+      <c r="H194" s="2" t="n"/>
+      <c r="I194" s="2">
+        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(K194="","JMBG sadrži nešto što nije cifra",IF(M194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;K194,"Pogrešna kontrolna cifra — treba "&amp;K194,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J194">
         <f>IFERROR(IF(LEN(C194)&lt;&gt;13,"",7*(VALUE(MID(C194,1,1))+VALUE(MID(C194,7,1)))+6*(VALUE(MID(C194,2,1))+VALUE(MID(C194,8,1)))+5*(VALUE(MID(C194,3,1))+VALUE(MID(C194,9,1)))+4*(VALUE(MID(C194,4,1))+VALUE(MID(C194,10,1)))+3*(VALUE(MID(C194,5,1))+VALUE(MID(C194,11,1)))+2*(VALUE(MID(C194,6,1))+VALUE(MID(C194,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J194">
-        <f>IF(I194="","",IF(11-MOD(I194,11)&gt;9,0,11-MOD(I194,11)))</f>
-        <v/>
-      </c>
       <c r="K194">
+        <f>IF(J194="","",IF(11-MOD(J194,11)&gt;9,0,11-MOD(J194,11)))</f>
+        <v/>
+      </c>
+      <c r="L194">
         <f>IFERROR(IF(LEN(C194)&lt;&gt;13,"",IF(VALUE(MID(C194,5,3))&gt;=800,1000,2000)+VALUE(MID(C194,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L194">
-        <f>IFERROR(IF(K194="","",IF(AND(DAY(DATE(K194,VALUE(MID(C194,3,2)),VALUE(MID(C194,1,2))))=VALUE(MID(C194,1,2)),MONTH(DATE(K194,VALUE(MID(C194,3,2)),VALUE(MID(C194,1,2))))=VALUE(MID(C194,3,2))),DATE(K194,VALUE(MID(C194,3,2)),VALUE(MID(C194,1,2))),"")),"")</f>
+      <c r="M194">
+        <f>IFERROR(IF(L194="","",IF(AND(DAY(DATE(L194,VALUE(MID(C194,3,2)),VALUE(MID(C194,1,2))))=VALUE(MID(C194,1,2)),MONTH(DATE(L194,VALUE(MID(C194,3,2)),VALUE(MID(C194,1,2))))=VALUE(MID(C194,3,2))),DATE(L194,VALUE(MID(C194,3,2)),VALUE(MID(C194,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6303,27 +7079,31 @@
       <c r="B195" s="2" t="n"/>
       <c r="C195" s="3" t="n"/>
       <c r="D195" s="2" t="n"/>
-      <c r="E195" s="4" t="n"/>
-      <c r="F195" s="2" t="n"/>
+      <c r="E195" s="4">
+        <f>IF(A195="","",5)</f>
+        <v/>
+      </c>
+      <c r="F195" s="4" t="n"/>
       <c r="G195" s="2" t="n"/>
-      <c r="H195" s="2">
-        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(J195="","JMBG sadrži nešto što nije cifra",IF(L195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;J195,"Pogrešna kontrolna cifra — treba "&amp;J195,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I195">
+      <c r="H195" s="2" t="n"/>
+      <c r="I195" s="2">
+        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(K195="","JMBG sadrži nešto što nije cifra",IF(M195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;K195,"Pogrešna kontrolna cifra — treba "&amp;K195,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J195">
         <f>IFERROR(IF(LEN(C195)&lt;&gt;13,"",7*(VALUE(MID(C195,1,1))+VALUE(MID(C195,7,1)))+6*(VALUE(MID(C195,2,1))+VALUE(MID(C195,8,1)))+5*(VALUE(MID(C195,3,1))+VALUE(MID(C195,9,1)))+4*(VALUE(MID(C195,4,1))+VALUE(MID(C195,10,1)))+3*(VALUE(MID(C195,5,1))+VALUE(MID(C195,11,1)))+2*(VALUE(MID(C195,6,1))+VALUE(MID(C195,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J195">
-        <f>IF(I195="","",IF(11-MOD(I195,11)&gt;9,0,11-MOD(I195,11)))</f>
-        <v/>
-      </c>
       <c r="K195">
+        <f>IF(J195="","",IF(11-MOD(J195,11)&gt;9,0,11-MOD(J195,11)))</f>
+        <v/>
+      </c>
+      <c r="L195">
         <f>IFERROR(IF(LEN(C195)&lt;&gt;13,"",IF(VALUE(MID(C195,5,3))&gt;=800,1000,2000)+VALUE(MID(C195,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L195">
-        <f>IFERROR(IF(K195="","",IF(AND(DAY(DATE(K195,VALUE(MID(C195,3,2)),VALUE(MID(C195,1,2))))=VALUE(MID(C195,1,2)),MONTH(DATE(K195,VALUE(MID(C195,3,2)),VALUE(MID(C195,1,2))))=VALUE(MID(C195,3,2))),DATE(K195,VALUE(MID(C195,3,2)),VALUE(MID(C195,1,2))),"")),"")</f>
+      <c r="M195">
+        <f>IFERROR(IF(L195="","",IF(AND(DAY(DATE(L195,VALUE(MID(C195,3,2)),VALUE(MID(C195,1,2))))=VALUE(MID(C195,1,2)),MONTH(DATE(L195,VALUE(MID(C195,3,2)),VALUE(MID(C195,1,2))))=VALUE(MID(C195,3,2))),DATE(L195,VALUE(MID(C195,3,2)),VALUE(MID(C195,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6332,27 +7112,31 @@
       <c r="B196" s="2" t="n"/>
       <c r="C196" s="3" t="n"/>
       <c r="D196" s="2" t="n"/>
-      <c r="E196" s="4" t="n"/>
-      <c r="F196" s="2" t="n"/>
+      <c r="E196" s="4">
+        <f>IF(A196="","",5)</f>
+        <v/>
+      </c>
+      <c r="F196" s="4" t="n"/>
       <c r="G196" s="2" t="n"/>
-      <c r="H196" s="2">
-        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(J196="","JMBG sadrži nešto što nije cifra",IF(L196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;J196,"Pogrešna kontrolna cifra — treba "&amp;J196,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I196">
+      <c r="H196" s="2" t="n"/>
+      <c r="I196" s="2">
+        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(K196="","JMBG sadrži nešto što nije cifra",IF(M196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;K196,"Pogrešna kontrolna cifra — treba "&amp;K196,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J196">
         <f>IFERROR(IF(LEN(C196)&lt;&gt;13,"",7*(VALUE(MID(C196,1,1))+VALUE(MID(C196,7,1)))+6*(VALUE(MID(C196,2,1))+VALUE(MID(C196,8,1)))+5*(VALUE(MID(C196,3,1))+VALUE(MID(C196,9,1)))+4*(VALUE(MID(C196,4,1))+VALUE(MID(C196,10,1)))+3*(VALUE(MID(C196,5,1))+VALUE(MID(C196,11,1)))+2*(VALUE(MID(C196,6,1))+VALUE(MID(C196,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J196">
-        <f>IF(I196="","",IF(11-MOD(I196,11)&gt;9,0,11-MOD(I196,11)))</f>
-        <v/>
-      </c>
       <c r="K196">
+        <f>IF(J196="","",IF(11-MOD(J196,11)&gt;9,0,11-MOD(J196,11)))</f>
+        <v/>
+      </c>
+      <c r="L196">
         <f>IFERROR(IF(LEN(C196)&lt;&gt;13,"",IF(VALUE(MID(C196,5,3))&gt;=800,1000,2000)+VALUE(MID(C196,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L196">
-        <f>IFERROR(IF(K196="","",IF(AND(DAY(DATE(K196,VALUE(MID(C196,3,2)),VALUE(MID(C196,1,2))))=VALUE(MID(C196,1,2)),MONTH(DATE(K196,VALUE(MID(C196,3,2)),VALUE(MID(C196,1,2))))=VALUE(MID(C196,3,2))),DATE(K196,VALUE(MID(C196,3,2)),VALUE(MID(C196,1,2))),"")),"")</f>
+      <c r="M196">
+        <f>IFERROR(IF(L196="","",IF(AND(DAY(DATE(L196,VALUE(MID(C196,3,2)),VALUE(MID(C196,1,2))))=VALUE(MID(C196,1,2)),MONTH(DATE(L196,VALUE(MID(C196,3,2)),VALUE(MID(C196,1,2))))=VALUE(MID(C196,3,2))),DATE(L196,VALUE(MID(C196,3,2)),VALUE(MID(C196,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6361,27 +7145,31 @@
       <c r="B197" s="2" t="n"/>
       <c r="C197" s="3" t="n"/>
       <c r="D197" s="2" t="n"/>
-      <c r="E197" s="4" t="n"/>
-      <c r="F197" s="2" t="n"/>
+      <c r="E197" s="4">
+        <f>IF(A197="","",5)</f>
+        <v/>
+      </c>
+      <c r="F197" s="4" t="n"/>
       <c r="G197" s="2" t="n"/>
-      <c r="H197" s="2">
-        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(J197="","JMBG sadrži nešto što nije cifra",IF(L197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;J197,"Pogrešna kontrolna cifra — treba "&amp;J197,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I197">
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2">
+        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(K197="","JMBG sadrži nešto što nije cifra",IF(M197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;K197,"Pogrešna kontrolna cifra — treba "&amp;K197,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J197">
         <f>IFERROR(IF(LEN(C197)&lt;&gt;13,"",7*(VALUE(MID(C197,1,1))+VALUE(MID(C197,7,1)))+6*(VALUE(MID(C197,2,1))+VALUE(MID(C197,8,1)))+5*(VALUE(MID(C197,3,1))+VALUE(MID(C197,9,1)))+4*(VALUE(MID(C197,4,1))+VALUE(MID(C197,10,1)))+3*(VALUE(MID(C197,5,1))+VALUE(MID(C197,11,1)))+2*(VALUE(MID(C197,6,1))+VALUE(MID(C197,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J197">
-        <f>IF(I197="","",IF(11-MOD(I197,11)&gt;9,0,11-MOD(I197,11)))</f>
-        <v/>
-      </c>
       <c r="K197">
+        <f>IF(J197="","",IF(11-MOD(J197,11)&gt;9,0,11-MOD(J197,11)))</f>
+        <v/>
+      </c>
+      <c r="L197">
         <f>IFERROR(IF(LEN(C197)&lt;&gt;13,"",IF(VALUE(MID(C197,5,3))&gt;=800,1000,2000)+VALUE(MID(C197,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L197">
-        <f>IFERROR(IF(K197="","",IF(AND(DAY(DATE(K197,VALUE(MID(C197,3,2)),VALUE(MID(C197,1,2))))=VALUE(MID(C197,1,2)),MONTH(DATE(K197,VALUE(MID(C197,3,2)),VALUE(MID(C197,1,2))))=VALUE(MID(C197,3,2))),DATE(K197,VALUE(MID(C197,3,2)),VALUE(MID(C197,1,2))),"")),"")</f>
+      <c r="M197">
+        <f>IFERROR(IF(L197="","",IF(AND(DAY(DATE(L197,VALUE(MID(C197,3,2)),VALUE(MID(C197,1,2))))=VALUE(MID(C197,1,2)),MONTH(DATE(L197,VALUE(MID(C197,3,2)),VALUE(MID(C197,1,2))))=VALUE(MID(C197,3,2))),DATE(L197,VALUE(MID(C197,3,2)),VALUE(MID(C197,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6390,27 +7178,31 @@
       <c r="B198" s="2" t="n"/>
       <c r="C198" s="3" t="n"/>
       <c r="D198" s="2" t="n"/>
-      <c r="E198" s="4" t="n"/>
-      <c r="F198" s="2" t="n"/>
+      <c r="E198" s="4">
+        <f>IF(A198="","",5)</f>
+        <v/>
+      </c>
+      <c r="F198" s="4" t="n"/>
       <c r="G198" s="2" t="n"/>
-      <c r="H198" s="2">
-        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(J198="","JMBG sadrži nešto što nije cifra",IF(L198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;J198,"Pogrešna kontrolna cifra — treba "&amp;J198,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I198">
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2">
+        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(K198="","JMBG sadrži nešto što nije cifra",IF(M198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;K198,"Pogrešna kontrolna cifra — treba "&amp;K198,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J198">
         <f>IFERROR(IF(LEN(C198)&lt;&gt;13,"",7*(VALUE(MID(C198,1,1))+VALUE(MID(C198,7,1)))+6*(VALUE(MID(C198,2,1))+VALUE(MID(C198,8,1)))+5*(VALUE(MID(C198,3,1))+VALUE(MID(C198,9,1)))+4*(VALUE(MID(C198,4,1))+VALUE(MID(C198,10,1)))+3*(VALUE(MID(C198,5,1))+VALUE(MID(C198,11,1)))+2*(VALUE(MID(C198,6,1))+VALUE(MID(C198,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J198">
-        <f>IF(I198="","",IF(11-MOD(I198,11)&gt;9,0,11-MOD(I198,11)))</f>
-        <v/>
-      </c>
       <c r="K198">
+        <f>IF(J198="","",IF(11-MOD(J198,11)&gt;9,0,11-MOD(J198,11)))</f>
+        <v/>
+      </c>
+      <c r="L198">
         <f>IFERROR(IF(LEN(C198)&lt;&gt;13,"",IF(VALUE(MID(C198,5,3))&gt;=800,1000,2000)+VALUE(MID(C198,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L198">
-        <f>IFERROR(IF(K198="","",IF(AND(DAY(DATE(K198,VALUE(MID(C198,3,2)),VALUE(MID(C198,1,2))))=VALUE(MID(C198,1,2)),MONTH(DATE(K198,VALUE(MID(C198,3,2)),VALUE(MID(C198,1,2))))=VALUE(MID(C198,3,2))),DATE(K198,VALUE(MID(C198,3,2)),VALUE(MID(C198,1,2))),"")),"")</f>
+      <c r="M198">
+        <f>IFERROR(IF(L198="","",IF(AND(DAY(DATE(L198,VALUE(MID(C198,3,2)),VALUE(MID(C198,1,2))))=VALUE(MID(C198,1,2)),MONTH(DATE(L198,VALUE(MID(C198,3,2)),VALUE(MID(C198,1,2))))=VALUE(MID(C198,3,2))),DATE(L198,VALUE(MID(C198,3,2)),VALUE(MID(C198,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6419,27 +7211,31 @@
       <c r="B199" s="2" t="n"/>
       <c r="C199" s="3" t="n"/>
       <c r="D199" s="2" t="n"/>
-      <c r="E199" s="4" t="n"/>
-      <c r="F199" s="2" t="n"/>
+      <c r="E199" s="4">
+        <f>IF(A199="","",5)</f>
+        <v/>
+      </c>
+      <c r="F199" s="4" t="n"/>
       <c r="G199" s="2" t="n"/>
-      <c r="H199" s="2">
-        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(J199="","JMBG sadrži nešto što nije cifra",IF(L199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;J199,"Pogrešna kontrolna cifra — treba "&amp;J199,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I199">
+      <c r="H199" s="2" t="n"/>
+      <c r="I199" s="2">
+        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(K199="","JMBG sadrži nešto što nije cifra",IF(M199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;K199,"Pogrešna kontrolna cifra — treba "&amp;K199,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J199">
         <f>IFERROR(IF(LEN(C199)&lt;&gt;13,"",7*(VALUE(MID(C199,1,1))+VALUE(MID(C199,7,1)))+6*(VALUE(MID(C199,2,1))+VALUE(MID(C199,8,1)))+5*(VALUE(MID(C199,3,1))+VALUE(MID(C199,9,1)))+4*(VALUE(MID(C199,4,1))+VALUE(MID(C199,10,1)))+3*(VALUE(MID(C199,5,1))+VALUE(MID(C199,11,1)))+2*(VALUE(MID(C199,6,1))+VALUE(MID(C199,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J199">
-        <f>IF(I199="","",IF(11-MOD(I199,11)&gt;9,0,11-MOD(I199,11)))</f>
-        <v/>
-      </c>
       <c r="K199">
+        <f>IF(J199="","",IF(11-MOD(J199,11)&gt;9,0,11-MOD(J199,11)))</f>
+        <v/>
+      </c>
+      <c r="L199">
         <f>IFERROR(IF(LEN(C199)&lt;&gt;13,"",IF(VALUE(MID(C199,5,3))&gt;=800,1000,2000)+VALUE(MID(C199,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L199">
-        <f>IFERROR(IF(K199="","",IF(AND(DAY(DATE(K199,VALUE(MID(C199,3,2)),VALUE(MID(C199,1,2))))=VALUE(MID(C199,1,2)),MONTH(DATE(K199,VALUE(MID(C199,3,2)),VALUE(MID(C199,1,2))))=VALUE(MID(C199,3,2))),DATE(K199,VALUE(MID(C199,3,2)),VALUE(MID(C199,1,2))),"")),"")</f>
+      <c r="M199">
+        <f>IFERROR(IF(L199="","",IF(AND(DAY(DATE(L199,VALUE(MID(C199,3,2)),VALUE(MID(C199,1,2))))=VALUE(MID(C199,1,2)),MONTH(DATE(L199,VALUE(MID(C199,3,2)),VALUE(MID(C199,1,2))))=VALUE(MID(C199,3,2))),DATE(L199,VALUE(MID(C199,3,2)),VALUE(MID(C199,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6448,27 +7244,31 @@
       <c r="B200" s="2" t="n"/>
       <c r="C200" s="3" t="n"/>
       <c r="D200" s="2" t="n"/>
-      <c r="E200" s="4" t="n"/>
-      <c r="F200" s="2" t="n"/>
+      <c r="E200" s="4">
+        <f>IF(A200="","",5)</f>
+        <v/>
+      </c>
+      <c r="F200" s="4" t="n"/>
       <c r="G200" s="2" t="n"/>
-      <c r="H200" s="2">
-        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(J200="","JMBG sadrži nešto što nije cifra",IF(L200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;J200,"Pogrešna kontrolna cifra — treba "&amp;J200,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I200">
+      <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2">
+        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(K200="","JMBG sadrži nešto što nije cifra",IF(M200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;K200,"Pogrešna kontrolna cifra — treba "&amp;K200,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J200">
         <f>IFERROR(IF(LEN(C200)&lt;&gt;13,"",7*(VALUE(MID(C200,1,1))+VALUE(MID(C200,7,1)))+6*(VALUE(MID(C200,2,1))+VALUE(MID(C200,8,1)))+5*(VALUE(MID(C200,3,1))+VALUE(MID(C200,9,1)))+4*(VALUE(MID(C200,4,1))+VALUE(MID(C200,10,1)))+3*(VALUE(MID(C200,5,1))+VALUE(MID(C200,11,1)))+2*(VALUE(MID(C200,6,1))+VALUE(MID(C200,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J200">
-        <f>IF(I200="","",IF(11-MOD(I200,11)&gt;9,0,11-MOD(I200,11)))</f>
-        <v/>
-      </c>
       <c r="K200">
+        <f>IF(J200="","",IF(11-MOD(J200,11)&gt;9,0,11-MOD(J200,11)))</f>
+        <v/>
+      </c>
+      <c r="L200">
         <f>IFERROR(IF(LEN(C200)&lt;&gt;13,"",IF(VALUE(MID(C200,5,3))&gt;=800,1000,2000)+VALUE(MID(C200,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L200">
-        <f>IFERROR(IF(K200="","",IF(AND(DAY(DATE(K200,VALUE(MID(C200,3,2)),VALUE(MID(C200,1,2))))=VALUE(MID(C200,1,2)),MONTH(DATE(K200,VALUE(MID(C200,3,2)),VALUE(MID(C200,1,2))))=VALUE(MID(C200,3,2))),DATE(K200,VALUE(MID(C200,3,2)),VALUE(MID(C200,1,2))),"")),"")</f>
+      <c r="M200">
+        <f>IFERROR(IF(L200="","",IF(AND(DAY(DATE(L200,VALUE(MID(C200,3,2)),VALUE(MID(C200,1,2))))=VALUE(MID(C200,1,2)),MONTH(DATE(L200,VALUE(MID(C200,3,2)),VALUE(MID(C200,1,2))))=VALUE(MID(C200,3,2))),DATE(L200,VALUE(MID(C200,3,2)),VALUE(MID(C200,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
@@ -6477,41 +7277,45 @@
       <c r="B201" s="2" t="n"/>
       <c r="C201" s="3" t="n"/>
       <c r="D201" s="2" t="n"/>
-      <c r="E201" s="4" t="n"/>
-      <c r="F201" s="2" t="n"/>
+      <c r="E201" s="4">
+        <f>IF(A201="","",5)</f>
+        <v/>
+      </c>
+      <c r="F201" s="4" t="n"/>
       <c r="G201" s="2" t="n"/>
-      <c r="H201" s="2">
-        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(J201="","JMBG sadrži nešto što nije cifra",IF(L201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;J201,"Pogrešna kontrolna cifra — treba "&amp;J201,"✓ ispravan")))))</f>
-        <v/>
-      </c>
-      <c r="I201">
+      <c r="H201" s="2" t="n"/>
+      <c r="I201" s="2">
+        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(K201="","JMBG sadrži nešto što nije cifra",IF(M201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;K201,"Pogrešna kontrolna cifra — treba "&amp;K201,"✓ ispravan")))))</f>
+        <v/>
+      </c>
+      <c r="J201">
         <f>IFERROR(IF(LEN(C201)&lt;&gt;13,"",7*(VALUE(MID(C201,1,1))+VALUE(MID(C201,7,1)))+6*(VALUE(MID(C201,2,1))+VALUE(MID(C201,8,1)))+5*(VALUE(MID(C201,3,1))+VALUE(MID(C201,9,1)))+4*(VALUE(MID(C201,4,1))+VALUE(MID(C201,10,1)))+3*(VALUE(MID(C201,5,1))+VALUE(MID(C201,11,1)))+2*(VALUE(MID(C201,6,1))+VALUE(MID(C201,12,1)))),"")</f>
         <v/>
       </c>
-      <c r="J201">
-        <f>IF(I201="","",IF(11-MOD(I201,11)&gt;9,0,11-MOD(I201,11)))</f>
-        <v/>
-      </c>
       <c r="K201">
+        <f>IF(J201="","",IF(11-MOD(J201,11)&gt;9,0,11-MOD(J201,11)))</f>
+        <v/>
+      </c>
+      <c r="L201">
         <f>IFERROR(IF(LEN(C201)&lt;&gt;13,"",IF(VALUE(MID(C201,5,3))&gt;=800,1000,2000)+VALUE(MID(C201,5,3))),"")</f>
         <v/>
       </c>
-      <c r="L201">
-        <f>IFERROR(IF(K201="","",IF(AND(DAY(DATE(K201,VALUE(MID(C201,3,2)),VALUE(MID(C201,1,2))))=VALUE(MID(C201,1,2)),MONTH(DATE(K201,VALUE(MID(C201,3,2)),VALUE(MID(C201,1,2))))=VALUE(MID(C201,3,2))),DATE(K201,VALUE(MID(C201,3,2)),VALUE(MID(C201,1,2))),"")),"")</f>
+      <c r="M201">
+        <f>IFERROR(IF(L201="","",IF(AND(DAY(DATE(L201,VALUE(MID(C201,3,2)),VALUE(MID(C201,1,2))))=VALUE(MID(C201,1,2)),MONTH(DATE(L201,VALUE(MID(C201,3,2)),VALUE(MID(C201,1,2))))=VALUE(MID(C201,3,2))),DATE(L201,VALUE(MID(C201,3,2)),VALUE(MID(C201,1,2))),"")),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H201"/>
-  <conditionalFormatting sqref="H2:H201">
+  <autoFilter ref="A1:I201"/>
+  <conditionalFormatting sqref="I2:I201">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>LEFT($H2,1)="✓"</formula>
+      <formula>LEFT($I2,1)="✓"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$H2&lt;&gt;""</formula>
+      <formula>$I2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E201">
+  <conditionalFormatting sqref="F2:F201">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"OK"</formula>
     </cfRule>
@@ -6525,12 +7329,12 @@
       <formula>"ČEKA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:D201">
+  <conditionalFormatting sqref="A2:E201">
     <cfRule type="expression" priority="7" dxfId="3">
-      <formula>$E2="GREŠKA"</formula>
+      <formula>$F2="GREŠKA"</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="2">
-      <formula>$E2="OK"</formula>
+      <formula>$F2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6543,7 +7347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B30"/>
+  <dimension ref="B1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6570,7 +7374,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>Popunjavaj kolone A-D: Ime, Prezime, JMBG, Datum.</t>
+          <t>Popunjavaj kolone A-E: Ime, Prezime, JMBG, Dolazak, Dana.</t>
         </is>
       </c>
     </row>
@@ -6591,146 +7395,160 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Datum piši kao 05.10-10.10 ili 05.10.2026-10.10.2026 — oba se prepoznaju.</t>
+          <t>Dolazak piši kao 05.10 ili 05.10.2026 — oba se prepoznaju.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dana se popunjava samo od sebe na 5; prekucaj ako je boravak duži.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
-          <t>2. Provera JMBG-a (kolona H)</t>
+          <t>'5 dana' znači 5 noćenja: dolazak 05.10 -&gt; odlazak 10.10.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2. Provera JMBG-a (kolona I)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Računa se automatski, po zvaničnoj formuli za kontrolnu cifru.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Zeleno '✓ ispravan' znači da broj matematički može da postoji.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Crveno kaže tačno šta ne valja, npr. 'Pogrešna kontrolna cifra — treba 8'.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
-          <t>Kolone I-L su pomoćne (sakrivene) — služe samo formuli u koloni H. Ne diraj ih.</t>
+          <t>Kolone J-M su pomoćne (sakrivene) — služe samo formuli u koloni I. Ne diraj ih.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Provera hvata tipfelere, ali ne može da zna da li broj zaista pripada tom čoveku.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>To utvrđuje tek portal — i to se posle vidi u koloni RAZLOG.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>3. Slanje u aplikaciju</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
-          <t>Označi kolone A-D za grupu gostiju koju prijavljuješ (5, 10, 30 — koliko hoćeš),</t>
+          <t>Označi kolone A-E za grupu gostiju koju prijavljuješ (5, 10, 30 — koliko hoćeš),</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Ctrl+C, pa u aplikaciji Ctrl+V.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>4. Vraćanje rezultata</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Kad se tura završi, u aplikaciji Ctrl+C i ovde zalepi preko kolone A za te goste.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
+    <row r="26">
+      <c r="B26" t="inlineStr">
         <is>
-          <t>Popuniće se i E (STATUS), F (RAZLOG) i G (PDF). Bojenje je već podešeno:</t>
+          <t>Popuniće se i F (STATUS), G (RAZLOG) i H (PDF). Bojenje je već podešeno:</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>OK = zeleno, GREŠKA = crveno, PRESKOČEN = sivo.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
-          <t>Kolone H-L su formule i ostaju netaknute jer su desno od zalepljenog.</t>
+          <t>Kolone I-M su formule i ostaju netaknute jer su desno od zalepljenog.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Napomena</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Redovi 2-8 su izmišljeni primeri — obriši ih pre pravog rada.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Poslednja dva su namerno pokvarena da se vidi kako provera reaguje.</t>
         </is>

--- a/primer/primer_gosti.xlsx
+++ b/primer/primer_gosti.xlsx
@@ -621,7 +621,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2">
-        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra — treba "&amp;L2,"✓ ispravan")))))</f>
+        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra - treba "&amp;L2,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K2">
@@ -655,7 +655,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2">
-        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra — treba "&amp;L3,"✓ ispravan")))))</f>
+        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra - treba "&amp;L3,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K3">
@@ -689,7 +689,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2">
-        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra — treba "&amp;L4,"✓ ispravan")))))</f>
+        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra - treba "&amp;L4,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K4">
@@ -723,7 +723,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2">
-        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra — treba "&amp;L5,"✓ ispravan")))))</f>
+        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra - treba "&amp;L5,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K5">
@@ -757,7 +757,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2">
-        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra — treba "&amp;L6,"✓ ispravan")))))</f>
+        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra - treba "&amp;L6,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K6">
@@ -791,7 +791,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2">
-        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra — treba "&amp;L7,"✓ ispravan")))))</f>
+        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra - treba "&amp;L7,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K7">
@@ -825,7 +825,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2">
-        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra — treba "&amp;L8,"✓ ispravan")))))</f>
+        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra - treba "&amp;L8,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K8">
@@ -859,7 +859,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2">
-        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra — treba "&amp;L9,"✓ ispravan")))))</f>
+        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra - treba "&amp;L9,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K9">
@@ -893,7 +893,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2">
-        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra — treba "&amp;L10,"✓ ispravan")))))</f>
+        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra - treba "&amp;L10,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K10">
@@ -927,7 +927,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2">
-        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra — treba "&amp;L11,"✓ ispravan")))))</f>
+        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra - treba "&amp;L11,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K11">
@@ -961,7 +961,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2">
-        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra — treba "&amp;L12,"✓ ispravan")))))</f>
+        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra - treba "&amp;L12,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K12">
@@ -995,7 +995,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2">
-        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra — treba "&amp;L13,"✓ ispravan")))))</f>
+        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra - treba "&amp;L13,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K13">
@@ -1029,7 +1029,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2">
-        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra — treba "&amp;L14,"✓ ispravan")))))</f>
+        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra - treba "&amp;L14,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K14">
@@ -1063,7 +1063,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2">
-        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra — treba "&amp;L15,"✓ ispravan")))))</f>
+        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra - treba "&amp;L15,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K15">
@@ -1097,7 +1097,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2">
-        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra — treba "&amp;L16,"✓ ispravan")))))</f>
+        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra - treba "&amp;L16,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K16">
@@ -1131,7 +1131,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2">
-        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra — treba "&amp;L17,"✓ ispravan")))))</f>
+        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra - treba "&amp;L17,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K17">
@@ -1165,7 +1165,7 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2">
-        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra — treba "&amp;L18,"✓ ispravan")))))</f>
+        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra - treba "&amp;L18,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K18">
@@ -1199,7 +1199,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2">
-        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra — treba "&amp;L19,"✓ ispravan")))))</f>
+        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra - treba "&amp;L19,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K19">
@@ -1233,7 +1233,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2">
-        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra — treba "&amp;L20,"✓ ispravan")))))</f>
+        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra - treba "&amp;L20,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K20">
@@ -1267,7 +1267,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2">
-        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra — treba "&amp;L21,"✓ ispravan")))))</f>
+        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra - treba "&amp;L21,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K21">
@@ -1301,7 +1301,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2">
-        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra — treba "&amp;L22,"✓ ispravan")))))</f>
+        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra - treba "&amp;L22,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K22">
@@ -1335,7 +1335,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2">
-        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra — treba "&amp;L23,"✓ ispravan")))))</f>
+        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra - treba "&amp;L23,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K23">
@@ -1369,7 +1369,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2">
-        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra — treba "&amp;L24,"✓ ispravan")))))</f>
+        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra - treba "&amp;L24,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K24">
@@ -1403,7 +1403,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2">
-        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra — treba "&amp;L25,"✓ ispravan")))))</f>
+        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra - treba "&amp;L25,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K25">
@@ -1437,7 +1437,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2">
-        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra — treba "&amp;L26,"✓ ispravan")))))</f>
+        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra - treba "&amp;L26,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K26">
@@ -1471,7 +1471,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2">
-        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra — treba "&amp;L27,"✓ ispravan")))))</f>
+        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra - treba "&amp;L27,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K27">
@@ -1505,7 +1505,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2">
-        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra — treba "&amp;L28,"✓ ispravan")))))</f>
+        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra - treba "&amp;L28,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K28">
@@ -1539,7 +1539,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2">
-        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra — treba "&amp;L29,"✓ ispravan")))))</f>
+        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra - treba "&amp;L29,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K29">
@@ -1573,7 +1573,7 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2">
-        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra — treba "&amp;L30,"✓ ispravan")))))</f>
+        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra - treba "&amp;L30,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K30">
@@ -1607,7 +1607,7 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2">
-        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra — treba "&amp;L31,"✓ ispravan")))))</f>
+        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra - treba "&amp;L31,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K31">
@@ -1641,7 +1641,7 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2">
-        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra — treba "&amp;L32,"✓ ispravan")))))</f>
+        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra - treba "&amp;L32,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K32">
@@ -1675,7 +1675,7 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2">
-        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra — treba "&amp;L33,"✓ ispravan")))))</f>
+        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra - treba "&amp;L33,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K33">
@@ -1709,7 +1709,7 @@
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2">
-        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra — treba "&amp;L34,"✓ ispravan")))))</f>
+        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra - treba "&amp;L34,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K34">
@@ -1743,7 +1743,7 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2">
-        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra — treba "&amp;L35,"✓ ispravan")))))</f>
+        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra - treba "&amp;L35,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K35">
@@ -1777,7 +1777,7 @@
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2">
-        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra — treba "&amp;L36,"✓ ispravan")))))</f>
+        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra - treba "&amp;L36,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K36">
@@ -1811,7 +1811,7 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2">
-        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra — treba "&amp;L37,"✓ ispravan")))))</f>
+        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra - treba "&amp;L37,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K37">
@@ -1845,7 +1845,7 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2">
-        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra — treba "&amp;L38,"✓ ispravan")))))</f>
+        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra - treba "&amp;L38,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K38">
@@ -1879,7 +1879,7 @@
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2">
-        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra — treba "&amp;L39,"✓ ispravan")))))</f>
+        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra - treba "&amp;L39,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K39">
@@ -1913,7 +1913,7 @@
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2">
-        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra — treba "&amp;L40,"✓ ispravan")))))</f>
+        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra - treba "&amp;L40,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K40">
@@ -1947,7 +1947,7 @@
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2">
-        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra — treba "&amp;L41,"✓ ispravan")))))</f>
+        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra - treba "&amp;L41,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K41">
@@ -1981,7 +1981,7 @@
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2">
-        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra — treba "&amp;L42,"✓ ispravan")))))</f>
+        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra - treba "&amp;L42,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K42">
@@ -2015,7 +2015,7 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2">
-        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra — treba "&amp;L43,"✓ ispravan")))))</f>
+        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra - treba "&amp;L43,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K43">
@@ -2049,7 +2049,7 @@
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2">
-        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra — treba "&amp;L44,"✓ ispravan")))))</f>
+        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra - treba "&amp;L44,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K44">
@@ -2083,7 +2083,7 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2">
-        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra — treba "&amp;L45,"✓ ispravan")))))</f>
+        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra - treba "&amp;L45,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K45">
@@ -2117,7 +2117,7 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2">
-        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra — treba "&amp;L46,"✓ ispravan")))))</f>
+        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra - treba "&amp;L46,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K46">
@@ -2151,7 +2151,7 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2">
-        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra — treba "&amp;L47,"✓ ispravan")))))</f>
+        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra - treba "&amp;L47,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K47">
@@ -2185,7 +2185,7 @@
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2">
-        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra — treba "&amp;L48,"✓ ispravan")))))</f>
+        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra - treba "&amp;L48,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K48">
@@ -2219,7 +2219,7 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2">
-        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra — treba "&amp;L49,"✓ ispravan")))))</f>
+        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra - treba "&amp;L49,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K49">
@@ -2253,7 +2253,7 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2">
-        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra — treba "&amp;L50,"✓ ispravan")))))</f>
+        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra - treba "&amp;L50,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K50">
@@ -2287,7 +2287,7 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2">
-        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra — treba "&amp;L51,"✓ ispravan")))))</f>
+        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra - treba "&amp;L51,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K51">
@@ -2321,7 +2321,7 @@
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2">
-        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra — treba "&amp;L52,"✓ ispravan")))))</f>
+        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra - treba "&amp;L52,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K52">
@@ -2355,7 +2355,7 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2">
-        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra — treba "&amp;L53,"✓ ispravan")))))</f>
+        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra - treba "&amp;L53,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K53">
@@ -2389,7 +2389,7 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2">
-        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra — treba "&amp;L54,"✓ ispravan")))))</f>
+        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra - treba "&amp;L54,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K54">
@@ -2423,7 +2423,7 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2">
-        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra — treba "&amp;L55,"✓ ispravan")))))</f>
+        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra - treba "&amp;L55,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K55">
@@ -2457,7 +2457,7 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
       <c r="J56" s="2">
-        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra — treba "&amp;L56,"✓ ispravan")))))</f>
+        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra - treba "&amp;L56,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K56">
@@ -2491,7 +2491,7 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2">
-        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra — treba "&amp;L57,"✓ ispravan")))))</f>
+        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra - treba "&amp;L57,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K57">
@@ -2525,7 +2525,7 @@
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2">
-        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra — treba "&amp;L58,"✓ ispravan")))))</f>
+        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra - treba "&amp;L58,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K58">
@@ -2559,7 +2559,7 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
       <c r="J59" s="2">
-        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra — treba "&amp;L59,"✓ ispravan")))))</f>
+        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra - treba "&amp;L59,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K59">
@@ -2593,7 +2593,7 @@
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
       <c r="J60" s="2">
-        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra — treba "&amp;L60,"✓ ispravan")))))</f>
+        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra - treba "&amp;L60,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K60">
@@ -2627,7 +2627,7 @@
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2">
-        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra — treba "&amp;L61,"✓ ispravan")))))</f>
+        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra - treba "&amp;L61,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K61">
@@ -2661,7 +2661,7 @@
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
       <c r="J62" s="2">
-        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra — treba "&amp;L62,"✓ ispravan")))))</f>
+        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra - treba "&amp;L62,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K62">
@@ -2695,7 +2695,7 @@
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2">
-        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra — treba "&amp;L63,"✓ ispravan")))))</f>
+        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra - treba "&amp;L63,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K63">
@@ -2729,7 +2729,7 @@
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2">
-        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra — treba "&amp;L64,"✓ ispravan")))))</f>
+        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra - treba "&amp;L64,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K64">
@@ -2763,7 +2763,7 @@
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
       <c r="J65" s="2">
-        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra — treba "&amp;L65,"✓ ispravan")))))</f>
+        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra - treba "&amp;L65,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K65">
@@ -2797,7 +2797,7 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2">
-        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra — treba "&amp;L66,"✓ ispravan")))))</f>
+        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra - treba "&amp;L66,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K66">
@@ -2831,7 +2831,7 @@
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
       <c r="J67" s="2">
-        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra — treba "&amp;L67,"✓ ispravan")))))</f>
+        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra - treba "&amp;L67,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K67">
@@ -2865,7 +2865,7 @@
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
       <c r="J68" s="2">
-        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra — treba "&amp;L68,"✓ ispravan")))))</f>
+        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra - treba "&amp;L68,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K68">
@@ -2899,7 +2899,7 @@
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
       <c r="J69" s="2">
-        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra — treba "&amp;L69,"✓ ispravan")))))</f>
+        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra - treba "&amp;L69,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K69">
@@ -2933,7 +2933,7 @@
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2">
-        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra — treba "&amp;L70,"✓ ispravan")))))</f>
+        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra - treba "&amp;L70,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K70">
@@ -2967,7 +2967,7 @@
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
       <c r="J71" s="2">
-        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra — treba "&amp;L71,"✓ ispravan")))))</f>
+        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra - treba "&amp;L71,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K71">
@@ -3001,7 +3001,7 @@
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2">
-        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra — treba "&amp;L72,"✓ ispravan")))))</f>
+        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra - treba "&amp;L72,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K72">
@@ -3035,7 +3035,7 @@
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
       <c r="J73" s="2">
-        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra — treba "&amp;L73,"✓ ispravan")))))</f>
+        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra - treba "&amp;L73,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K73">
@@ -3069,7 +3069,7 @@
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
       <c r="J74" s="2">
-        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra — treba "&amp;L74,"✓ ispravan")))))</f>
+        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra - treba "&amp;L74,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K74">
@@ -3103,7 +3103,7 @@
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2">
-        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra — treba "&amp;L75,"✓ ispravan")))))</f>
+        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra - treba "&amp;L75,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K75">
@@ -3137,7 +3137,7 @@
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
       <c r="J76" s="2">
-        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra — treba "&amp;L76,"✓ ispravan")))))</f>
+        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra - treba "&amp;L76,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K76">
@@ -3171,7 +3171,7 @@
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
       <c r="J77" s="2">
-        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra — treba "&amp;L77,"✓ ispravan")))))</f>
+        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra - treba "&amp;L77,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K77">
@@ -3205,7 +3205,7 @@
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
       <c r="J78" s="2">
-        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra — treba "&amp;L78,"✓ ispravan")))))</f>
+        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra - treba "&amp;L78,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K78">
@@ -3239,7 +3239,7 @@
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
       <c r="J79" s="2">
-        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra — treba "&amp;L79,"✓ ispravan")))))</f>
+        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra - treba "&amp;L79,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K79">
@@ -3273,7 +3273,7 @@
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
       <c r="J80" s="2">
-        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra — treba "&amp;L80,"✓ ispravan")))))</f>
+        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra - treba "&amp;L80,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K80">
@@ -3307,7 +3307,7 @@
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
       <c r="J81" s="2">
-        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra — treba "&amp;L81,"✓ ispravan")))))</f>
+        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra - treba "&amp;L81,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K81">
@@ -3341,7 +3341,7 @@
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
       <c r="J82" s="2">
-        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra — treba "&amp;L82,"✓ ispravan")))))</f>
+        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra - treba "&amp;L82,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K82">
@@ -3375,7 +3375,7 @@
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
       <c r="J83" s="2">
-        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra — treba "&amp;L83,"✓ ispravan")))))</f>
+        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra - treba "&amp;L83,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K83">
@@ -3409,7 +3409,7 @@
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2">
-        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra — treba "&amp;L84,"✓ ispravan")))))</f>
+        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra - treba "&amp;L84,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K84">
@@ -3443,7 +3443,7 @@
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
       <c r="J85" s="2">
-        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra — treba "&amp;L85,"✓ ispravan")))))</f>
+        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra - treba "&amp;L85,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K85">
@@ -3477,7 +3477,7 @@
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
       <c r="J86" s="2">
-        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra — treba "&amp;L86,"✓ ispravan")))))</f>
+        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra - treba "&amp;L86,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K86">
@@ -3511,7 +3511,7 @@
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
       <c r="J87" s="2">
-        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra — treba "&amp;L87,"✓ ispravan")))))</f>
+        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra - treba "&amp;L87,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K87">
@@ -3545,7 +3545,7 @@
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
       <c r="J88" s="2">
-        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra — treba "&amp;L88,"✓ ispravan")))))</f>
+        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra - treba "&amp;L88,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K88">
@@ -3579,7 +3579,7 @@
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
       <c r="J89" s="2">
-        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra — treba "&amp;L89,"✓ ispravan")))))</f>
+        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra - treba "&amp;L89,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K89">
@@ -3613,7 +3613,7 @@
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
       <c r="J90" s="2">
-        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra — treba "&amp;L90,"✓ ispravan")))))</f>
+        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra - treba "&amp;L90,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K90">
@@ -3647,7 +3647,7 @@
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="n"/>
       <c r="J91" s="2">
-        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra — treba "&amp;L91,"✓ ispravan")))))</f>
+        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra - treba "&amp;L91,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K91">
@@ -3681,7 +3681,7 @@
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
       <c r="J92" s="2">
-        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra — treba "&amp;L92,"✓ ispravan")))))</f>
+        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra - treba "&amp;L92,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K92">
@@ -3715,7 +3715,7 @@
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="n"/>
       <c r="J93" s="2">
-        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra — treba "&amp;L93,"✓ ispravan")))))</f>
+        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra - treba "&amp;L93,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K93">
@@ -3749,7 +3749,7 @@
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
       <c r="J94" s="2">
-        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra — treba "&amp;L94,"✓ ispravan")))))</f>
+        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra - treba "&amp;L94,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K94">
@@ -3783,7 +3783,7 @@
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="n"/>
       <c r="J95" s="2">
-        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra — treba "&amp;L95,"✓ ispravan")))))</f>
+        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra - treba "&amp;L95,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K95">
@@ -3817,7 +3817,7 @@
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="n"/>
       <c r="J96" s="2">
-        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra — treba "&amp;L96,"✓ ispravan")))))</f>
+        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra - treba "&amp;L96,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K96">
@@ -3851,7 +3851,7 @@
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
       <c r="J97" s="2">
-        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra — treba "&amp;L97,"✓ ispravan")))))</f>
+        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra - treba "&amp;L97,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K97">
@@ -3885,7 +3885,7 @@
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
       <c r="J98" s="2">
-        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra — treba "&amp;L98,"✓ ispravan")))))</f>
+        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra - treba "&amp;L98,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K98">
@@ -3919,7 +3919,7 @@
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
       <c r="J99" s="2">
-        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra — treba "&amp;L99,"✓ ispravan")))))</f>
+        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra - treba "&amp;L99,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K99">
@@ -3953,7 +3953,7 @@
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="n"/>
       <c r="J100" s="2">
-        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra — treba "&amp;L100,"✓ ispravan")))))</f>
+        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra - treba "&amp;L100,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K100">
@@ -3987,7 +3987,7 @@
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="n"/>
       <c r="J101" s="2">
-        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra — treba "&amp;L101,"✓ ispravan")))))</f>
+        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra - treba "&amp;L101,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K101">
@@ -4021,7 +4021,7 @@
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="n"/>
       <c r="J102" s="2">
-        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra — treba "&amp;L102,"✓ ispravan")))))</f>
+        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra - treba "&amp;L102,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K102">
@@ -4055,7 +4055,7 @@
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
       <c r="J103" s="2">
-        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra — treba "&amp;L103,"✓ ispravan")))))</f>
+        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra - treba "&amp;L103,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K103">
@@ -4089,7 +4089,7 @@
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="n"/>
       <c r="J104" s="2">
-        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra — treba "&amp;L104,"✓ ispravan")))))</f>
+        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra - treba "&amp;L104,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K104">
@@ -4123,7 +4123,7 @@
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
       <c r="J105" s="2">
-        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra — treba "&amp;L105,"✓ ispravan")))))</f>
+        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra - treba "&amp;L105,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K105">
@@ -4157,7 +4157,7 @@
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="n"/>
       <c r="J106" s="2">
-        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra — treba "&amp;L106,"✓ ispravan")))))</f>
+        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra - treba "&amp;L106,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K106">
@@ -4191,7 +4191,7 @@
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
       <c r="J107" s="2">
-        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra — treba "&amp;L107,"✓ ispravan")))))</f>
+        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra - treba "&amp;L107,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K107">
@@ -4225,7 +4225,7 @@
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
       <c r="J108" s="2">
-        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra — treba "&amp;L108,"✓ ispravan")))))</f>
+        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra - treba "&amp;L108,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K108">
@@ -4259,7 +4259,7 @@
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
       <c r="J109" s="2">
-        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra — treba "&amp;L109,"✓ ispravan")))))</f>
+        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra - treba "&amp;L109,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K109">
@@ -4293,7 +4293,7 @@
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
       <c r="J110" s="2">
-        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra — treba "&amp;L110,"✓ ispravan")))))</f>
+        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra - treba "&amp;L110,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K110">
@@ -4327,7 +4327,7 @@
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
       <c r="J111" s="2">
-        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra — treba "&amp;L111,"✓ ispravan")))))</f>
+        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra - treba "&amp;L111,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K111">
@@ -4361,7 +4361,7 @@
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
       <c r="J112" s="2">
-        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra — treba "&amp;L112,"✓ ispravan")))))</f>
+        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra - treba "&amp;L112,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K112">
@@ -4395,7 +4395,7 @@
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
       <c r="J113" s="2">
-        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra — treba "&amp;L113,"✓ ispravan")))))</f>
+        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra - treba "&amp;L113,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K113">
@@ -4429,7 +4429,7 @@
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
       <c r="J114" s="2">
-        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra — treba "&amp;L114,"✓ ispravan")))))</f>
+        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra - treba "&amp;L114,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K114">
@@ -4463,7 +4463,7 @@
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
       <c r="J115" s="2">
-        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra — treba "&amp;L115,"✓ ispravan")))))</f>
+        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra - treba "&amp;L115,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K115">
@@ -4497,7 +4497,7 @@
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="n"/>
       <c r="J116" s="2">
-        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra — treba "&amp;L116,"✓ ispravan")))))</f>
+        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra - treba "&amp;L116,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K116">
@@ -4531,7 +4531,7 @@
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
       <c r="J117" s="2">
-        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra — treba "&amp;L117,"✓ ispravan")))))</f>
+        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra - treba "&amp;L117,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K117">
@@ -4565,7 +4565,7 @@
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="n"/>
       <c r="J118" s="2">
-        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra — treba "&amp;L118,"✓ ispravan")))))</f>
+        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra - treba "&amp;L118,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K118">
@@ -4599,7 +4599,7 @@
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
       <c r="J119" s="2">
-        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra — treba "&amp;L119,"✓ ispravan")))))</f>
+        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra - treba "&amp;L119,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K119">
@@ -4633,7 +4633,7 @@
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
       <c r="J120" s="2">
-        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra — treba "&amp;L120,"✓ ispravan")))))</f>
+        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra - treba "&amp;L120,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K120">
@@ -4667,7 +4667,7 @@
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="n"/>
       <c r="J121" s="2">
-        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra — treba "&amp;L121,"✓ ispravan")))))</f>
+        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra - treba "&amp;L121,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K121">
@@ -4701,7 +4701,7 @@
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="n"/>
       <c r="J122" s="2">
-        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra — treba "&amp;L122,"✓ ispravan")))))</f>
+        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra - treba "&amp;L122,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K122">
@@ -4735,7 +4735,7 @@
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
       <c r="J123" s="2">
-        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra — treba "&amp;L123,"✓ ispravan")))))</f>
+        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra - treba "&amp;L123,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K123">
@@ -4769,7 +4769,7 @@
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
       <c r="J124" s="2">
-        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra — treba "&amp;L124,"✓ ispravan")))))</f>
+        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra - treba "&amp;L124,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K124">
@@ -4803,7 +4803,7 @@
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
       <c r="J125" s="2">
-        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra — treba "&amp;L125,"✓ ispravan")))))</f>
+        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra - treba "&amp;L125,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K125">
@@ -4837,7 +4837,7 @@
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
       <c r="J126" s="2">
-        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra — treba "&amp;L126,"✓ ispravan")))))</f>
+        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra - treba "&amp;L126,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K126">
@@ -4871,7 +4871,7 @@
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
       <c r="J127" s="2">
-        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra — treba "&amp;L127,"✓ ispravan")))))</f>
+        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra - treba "&amp;L127,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K127">
@@ -4905,7 +4905,7 @@
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="2" t="n"/>
       <c r="J128" s="2">
-        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra — treba "&amp;L128,"✓ ispravan")))))</f>
+        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra - treba "&amp;L128,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K128">
@@ -4939,7 +4939,7 @@
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
       <c r="J129" s="2">
-        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra — treba "&amp;L129,"✓ ispravan")))))</f>
+        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra - treba "&amp;L129,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K129">
@@ -4973,7 +4973,7 @@
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
       <c r="J130" s="2">
-        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra — treba "&amp;L130,"✓ ispravan")))))</f>
+        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra - treba "&amp;L130,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K130">
@@ -5007,7 +5007,7 @@
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
       <c r="J131" s="2">
-        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra — treba "&amp;L131,"✓ ispravan")))))</f>
+        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra - treba "&amp;L131,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K131">
@@ -5041,7 +5041,7 @@
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="n"/>
       <c r="J132" s="2">
-        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra — treba "&amp;L132,"✓ ispravan")))))</f>
+        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra - treba "&amp;L132,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K132">
@@ -5075,7 +5075,7 @@
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="n"/>
       <c r="J133" s="2">
-        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra — treba "&amp;L133,"✓ ispravan")))))</f>
+        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra - treba "&amp;L133,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K133">
@@ -5109,7 +5109,7 @@
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
       <c r="J134" s="2">
-        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra — treba "&amp;L134,"✓ ispravan")))))</f>
+        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra - treba "&amp;L134,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K134">
@@ -5143,7 +5143,7 @@
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
       <c r="J135" s="2">
-        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra — treba "&amp;L135,"✓ ispravan")))))</f>
+        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra - treba "&amp;L135,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K135">
@@ -5177,7 +5177,7 @@
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
       <c r="J136" s="2">
-        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra — treba "&amp;L136,"✓ ispravan")))))</f>
+        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra - treba "&amp;L136,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K136">
@@ -5211,7 +5211,7 @@
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="n"/>
       <c r="J137" s="2">
-        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra — treba "&amp;L137,"✓ ispravan")))))</f>
+        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra - treba "&amp;L137,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K137">
@@ -5245,7 +5245,7 @@
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
       <c r="J138" s="2">
-        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra — treba "&amp;L138,"✓ ispravan")))))</f>
+        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra - treba "&amp;L138,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K138">
@@ -5279,7 +5279,7 @@
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2">
-        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra — treba "&amp;L139,"✓ ispravan")))))</f>
+        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra - treba "&amp;L139,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K139">
@@ -5313,7 +5313,7 @@
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
       <c r="J140" s="2">
-        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra — treba "&amp;L140,"✓ ispravan")))))</f>
+        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra - treba "&amp;L140,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K140">
@@ -5347,7 +5347,7 @@
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
       <c r="J141" s="2">
-        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra — treba "&amp;L141,"✓ ispravan")))))</f>
+        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra - treba "&amp;L141,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K141">
@@ -5381,7 +5381,7 @@
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="2" t="n"/>
       <c r="J142" s="2">
-        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra — treba "&amp;L142,"✓ ispravan")))))</f>
+        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra - treba "&amp;L142,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K142">
@@ -5415,7 +5415,7 @@
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
       <c r="J143" s="2">
-        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra — treba "&amp;L143,"✓ ispravan")))))</f>
+        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra - treba "&amp;L143,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K143">
@@ -5449,7 +5449,7 @@
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
       <c r="J144" s="2">
-        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra — treba "&amp;L144,"✓ ispravan")))))</f>
+        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra - treba "&amp;L144,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K144">
@@ -5483,7 +5483,7 @@
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
       <c r="J145" s="2">
-        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra — treba "&amp;L145,"✓ ispravan")))))</f>
+        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra - treba "&amp;L145,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K145">
@@ -5517,7 +5517,7 @@
       <c r="H146" s="2" t="n"/>
       <c r="I146" s="2" t="n"/>
       <c r="J146" s="2">
-        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra — treba "&amp;L146,"✓ ispravan")))))</f>
+        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra - treba "&amp;L146,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K146">
@@ -5551,7 +5551,7 @@
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="n"/>
       <c r="J147" s="2">
-        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra — treba "&amp;L147,"✓ ispravan")))))</f>
+        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra - treba "&amp;L147,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K147">
@@ -5585,7 +5585,7 @@
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="n"/>
       <c r="J148" s="2">
-        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra — treba "&amp;L148,"✓ ispravan")))))</f>
+        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra - treba "&amp;L148,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K148">
@@ -5619,7 +5619,7 @@
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="n"/>
       <c r="J149" s="2">
-        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra — treba "&amp;L149,"✓ ispravan")))))</f>
+        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra - treba "&amp;L149,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K149">
@@ -5653,7 +5653,7 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2">
-        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra — treba "&amp;L150,"✓ ispravan")))))</f>
+        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra - treba "&amp;L150,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K150">
@@ -5687,7 +5687,7 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2">
-        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra — treba "&amp;L151,"✓ ispravan")))))</f>
+        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra - treba "&amp;L151,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K151">
@@ -5721,7 +5721,7 @@
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="n"/>
       <c r="J152" s="2">
-        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra — treba "&amp;L152,"✓ ispravan")))))</f>
+        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra - treba "&amp;L152,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K152">
@@ -5755,7 +5755,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
       <c r="J153" s="2">
-        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra — treba "&amp;L153,"✓ ispravan")))))</f>
+        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra - treba "&amp;L153,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K153">
@@ -5789,7 +5789,7 @@
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
       <c r="J154" s="2">
-        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra — treba "&amp;L154,"✓ ispravan")))))</f>
+        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra - treba "&amp;L154,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K154">
@@ -5823,7 +5823,7 @@
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
       <c r="J155" s="2">
-        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra — treba "&amp;L155,"✓ ispravan")))))</f>
+        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra - treba "&amp;L155,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K155">
@@ -5857,7 +5857,7 @@
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
       <c r="J156" s="2">
-        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra — treba "&amp;L156,"✓ ispravan")))))</f>
+        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra - treba "&amp;L156,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K156">
@@ -5891,7 +5891,7 @@
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
       <c r="J157" s="2">
-        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra — treba "&amp;L157,"✓ ispravan")))))</f>
+        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra - treba "&amp;L157,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K157">
@@ -5925,7 +5925,7 @@
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="2" t="n"/>
       <c r="J158" s="2">
-        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra — treba "&amp;L158,"✓ ispravan")))))</f>
+        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra - treba "&amp;L158,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K158">
@@ -5959,7 +5959,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
       <c r="J159" s="2">
-        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra — treba "&amp;L159,"✓ ispravan")))))</f>
+        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra - treba "&amp;L159,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K159">
@@ -5993,7 +5993,7 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2">
-        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra — treba "&amp;L160,"✓ ispravan")))))</f>
+        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra - treba "&amp;L160,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K160">
@@ -6027,7 +6027,7 @@
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
       <c r="J161" s="2">
-        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra — treba "&amp;L161,"✓ ispravan")))))</f>
+        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra - treba "&amp;L161,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K161">
@@ -6061,7 +6061,7 @@
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
       <c r="J162" s="2">
-        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra — treba "&amp;L162,"✓ ispravan")))))</f>
+        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra - treba "&amp;L162,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K162">
@@ -6095,7 +6095,7 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
       <c r="J163" s="2">
-        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra — treba "&amp;L163,"✓ ispravan")))))</f>
+        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra - treba "&amp;L163,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K163">
@@ -6129,7 +6129,7 @@
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="2" t="n"/>
       <c r="J164" s="2">
-        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra — treba "&amp;L164,"✓ ispravan")))))</f>
+        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra - treba "&amp;L164,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K164">
@@ -6163,7 +6163,7 @@
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
       <c r="J165" s="2">
-        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra — treba "&amp;L165,"✓ ispravan")))))</f>
+        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra - treba "&amp;L165,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K165">
@@ -6197,7 +6197,7 @@
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="n"/>
       <c r="J166" s="2">
-        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra — treba "&amp;L166,"✓ ispravan")))))</f>
+        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra - treba "&amp;L166,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K166">
@@ -6231,7 +6231,7 @@
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
       <c r="J167" s="2">
-        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra — treba "&amp;L167,"✓ ispravan")))))</f>
+        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra - treba "&amp;L167,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K167">
@@ -6265,7 +6265,7 @@
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
       <c r="J168" s="2">
-        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra — treba "&amp;L168,"✓ ispravan")))))</f>
+        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra - treba "&amp;L168,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K168">
@@ -6299,7 +6299,7 @@
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="n"/>
       <c r="J169" s="2">
-        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra — treba "&amp;L169,"✓ ispravan")))))</f>
+        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra - treba "&amp;L169,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K169">
@@ -6333,7 +6333,7 @@
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
       <c r="J170" s="2">
-        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra — treba "&amp;L170,"✓ ispravan")))))</f>
+        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra - treba "&amp;L170,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K170">
@@ -6367,7 +6367,7 @@
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
       <c r="J171" s="2">
-        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra — treba "&amp;L171,"✓ ispravan")))))</f>
+        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra - treba "&amp;L171,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K171">
@@ -6401,7 +6401,7 @@
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
       <c r="J172" s="2">
-        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra — treba "&amp;L172,"✓ ispravan")))))</f>
+        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra - treba "&amp;L172,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K172">
@@ -6435,7 +6435,7 @@
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="n"/>
       <c r="J173" s="2">
-        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra — treba "&amp;L173,"✓ ispravan")))))</f>
+        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra - treba "&amp;L173,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K173">
@@ -6469,7 +6469,7 @@
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
       <c r="J174" s="2">
-        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra — treba "&amp;L174,"✓ ispravan")))))</f>
+        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra - treba "&amp;L174,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K174">
@@ -6503,7 +6503,7 @@
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
       <c r="J175" s="2">
-        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra — treba "&amp;L175,"✓ ispravan")))))</f>
+        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra - treba "&amp;L175,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K175">
@@ -6537,7 +6537,7 @@
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
       <c r="J176" s="2">
-        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra — treba "&amp;L176,"✓ ispravan")))))</f>
+        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra - treba "&amp;L176,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K176">
@@ -6571,7 +6571,7 @@
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
       <c r="J177" s="2">
-        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra — treba "&amp;L177,"✓ ispravan")))))</f>
+        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra - treba "&amp;L177,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K177">
@@ -6605,7 +6605,7 @@
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
       <c r="J178" s="2">
-        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra — treba "&amp;L178,"✓ ispravan")))))</f>
+        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra - treba "&amp;L178,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K178">
@@ -6639,7 +6639,7 @@
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="2" t="n"/>
       <c r="J179" s="2">
-        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra — treba "&amp;L179,"✓ ispravan")))))</f>
+        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra - treba "&amp;L179,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K179">
@@ -6673,7 +6673,7 @@
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
       <c r="J180" s="2">
-        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra — treba "&amp;L180,"✓ ispravan")))))</f>
+        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra - treba "&amp;L180,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K180">
@@ -6707,7 +6707,7 @@
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="2" t="n"/>
       <c r="J181" s="2">
-        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra — treba "&amp;L181,"✓ ispravan")))))</f>
+        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra - treba "&amp;L181,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K181">
@@ -6741,7 +6741,7 @@
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="n"/>
       <c r="J182" s="2">
-        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra — treba "&amp;L182,"✓ ispravan")))))</f>
+        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra - treba "&amp;L182,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K182">
@@ -6775,7 +6775,7 @@
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="2" t="n"/>
       <c r="J183" s="2">
-        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra — treba "&amp;L183,"✓ ispravan")))))</f>
+        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra - treba "&amp;L183,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K183">
@@ -6809,7 +6809,7 @@
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
       <c r="J184" s="2">
-        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra — treba "&amp;L184,"✓ ispravan")))))</f>
+        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra - treba "&amp;L184,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K184">
@@ -6843,7 +6843,7 @@
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="n"/>
       <c r="J185" s="2">
-        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra — treba "&amp;L185,"✓ ispravan")))))</f>
+        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra - treba "&amp;L185,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K185">
@@ -6877,7 +6877,7 @@
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="n"/>
       <c r="J186" s="2">
-        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra — treba "&amp;L186,"✓ ispravan")))))</f>
+        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra - treba "&amp;L186,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K186">
@@ -6911,7 +6911,7 @@
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="2" t="n"/>
       <c r="J187" s="2">
-        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra — treba "&amp;L187,"✓ ispravan")))))</f>
+        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra - treba "&amp;L187,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K187">
@@ -6945,7 +6945,7 @@
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
       <c r="J188" s="2">
-        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra — treba "&amp;L188,"✓ ispravan")))))</f>
+        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra - treba "&amp;L188,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K188">
@@ -6979,7 +6979,7 @@
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="n"/>
       <c r="J189" s="2">
-        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra — treba "&amp;L189,"✓ ispravan")))))</f>
+        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra - treba "&amp;L189,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K189">
@@ -7013,7 +7013,7 @@
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="2" t="n"/>
       <c r="J190" s="2">
-        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra — treba "&amp;L190,"✓ ispravan")))))</f>
+        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra - treba "&amp;L190,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K190">
@@ -7047,7 +7047,7 @@
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="n"/>
       <c r="J191" s="2">
-        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra — treba "&amp;L191,"✓ ispravan")))))</f>
+        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra - treba "&amp;L191,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K191">
@@ -7081,7 +7081,7 @@
       <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="n"/>
       <c r="J192" s="2">
-        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra — treba "&amp;L192,"✓ ispravan")))))</f>
+        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra - treba "&amp;L192,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K192">
@@ -7115,7 +7115,7 @@
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="n"/>
       <c r="J193" s="2">
-        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra — treba "&amp;L193,"✓ ispravan")))))</f>
+        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra - treba "&amp;L193,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K193">
@@ -7149,7 +7149,7 @@
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
       <c r="J194" s="2">
-        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra — treba "&amp;L194,"✓ ispravan")))))</f>
+        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra - treba "&amp;L194,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K194">
@@ -7183,7 +7183,7 @@
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="n"/>
       <c r="J195" s="2">
-        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra — treba "&amp;L195,"✓ ispravan")))))</f>
+        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra - treba "&amp;L195,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K195">
@@ -7217,7 +7217,7 @@
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
       <c r="J196" s="2">
-        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra — treba "&amp;L196,"✓ ispravan")))))</f>
+        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra - treba "&amp;L196,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K196">
@@ -7251,7 +7251,7 @@
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="n"/>
       <c r="J197" s="2">
-        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra — treba "&amp;L197,"✓ ispravan")))))</f>
+        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra - treba "&amp;L197,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K197">
@@ -7285,7 +7285,7 @@
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
       <c r="J198" s="2">
-        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra — treba "&amp;L198,"✓ ispravan")))))</f>
+        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra - treba "&amp;L198,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K198">
@@ -7319,7 +7319,7 @@
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="n"/>
       <c r="J199" s="2">
-        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra — treba "&amp;L199,"✓ ispravan")))))</f>
+        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra - treba "&amp;L199,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K199">
@@ -7353,7 +7353,7 @@
       <c r="H200" s="2" t="n"/>
       <c r="I200" s="2" t="n"/>
       <c r="J200" s="2">
-        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra — treba "&amp;L200,"✓ ispravan")))))</f>
+        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra - treba "&amp;L200,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K200">
@@ -7387,7 +7387,7 @@
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="n"/>
       <c r="J201" s="2">
-        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra — treba "&amp;L201,"✓ ispravan")))))</f>
+        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra - treba "&amp;L201,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K201">
@@ -7551,7 +7551,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2">
-        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra — treba "&amp;L2,"✓ ispravan")))))</f>
+        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra - treba "&amp;L2,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K2">
@@ -7585,7 +7585,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2">
-        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra — treba "&amp;L3,"✓ ispravan")))))</f>
+        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra - treba "&amp;L3,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K3">
@@ -7619,7 +7619,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2">
-        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra — treba "&amp;L4,"✓ ispravan")))))</f>
+        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra - treba "&amp;L4,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K4">
@@ -7653,7 +7653,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2">
-        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra — treba "&amp;L5,"✓ ispravan")))))</f>
+        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra - treba "&amp;L5,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K5">
@@ -7687,7 +7687,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2">
-        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra — treba "&amp;L6,"✓ ispravan")))))</f>
+        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra - treba "&amp;L6,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K6">
@@ -7721,7 +7721,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2">
-        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra — treba "&amp;L7,"✓ ispravan")))))</f>
+        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra - treba "&amp;L7,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K7">
@@ -7755,7 +7755,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2">
-        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra — treba "&amp;L8,"✓ ispravan")))))</f>
+        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra - treba "&amp;L8,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K8">
@@ -7789,7 +7789,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2">
-        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra — treba "&amp;L9,"✓ ispravan")))))</f>
+        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra - treba "&amp;L9,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K9">
@@ -7823,7 +7823,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2">
-        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra — treba "&amp;L10,"✓ ispravan")))))</f>
+        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra - treba "&amp;L10,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K10">
@@ -7857,7 +7857,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2">
-        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra — treba "&amp;L11,"✓ ispravan")))))</f>
+        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra - treba "&amp;L11,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K11">
@@ -7891,7 +7891,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2">
-        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra — treba "&amp;L12,"✓ ispravan")))))</f>
+        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra - treba "&amp;L12,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K12">
@@ -7925,7 +7925,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2">
-        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra — treba "&amp;L13,"✓ ispravan")))))</f>
+        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra - treba "&amp;L13,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K13">
@@ -7959,7 +7959,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2">
-        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra — treba "&amp;L14,"✓ ispravan")))))</f>
+        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra - treba "&amp;L14,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K14">
@@ -7993,7 +7993,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2">
-        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra — treba "&amp;L15,"✓ ispravan")))))</f>
+        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra - treba "&amp;L15,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K15">
@@ -8027,7 +8027,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2">
-        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra — treba "&amp;L16,"✓ ispravan")))))</f>
+        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra - treba "&amp;L16,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K16">
@@ -8061,7 +8061,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2">
-        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra — treba "&amp;L17,"✓ ispravan")))))</f>
+        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra - treba "&amp;L17,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K17">
@@ -8095,7 +8095,7 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2">
-        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra — treba "&amp;L18,"✓ ispravan")))))</f>
+        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra - treba "&amp;L18,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K18">
@@ -8129,7 +8129,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2">
-        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra — treba "&amp;L19,"✓ ispravan")))))</f>
+        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra - treba "&amp;L19,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K19">
@@ -8163,7 +8163,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2">
-        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra — treba "&amp;L20,"✓ ispravan")))))</f>
+        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra - treba "&amp;L20,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K20">
@@ -8197,7 +8197,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2">
-        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra — treba "&amp;L21,"✓ ispravan")))))</f>
+        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra - treba "&amp;L21,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K21">
@@ -8231,7 +8231,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2">
-        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra — treba "&amp;L22,"✓ ispravan")))))</f>
+        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra - treba "&amp;L22,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K22">
@@ -8265,7 +8265,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2">
-        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra — treba "&amp;L23,"✓ ispravan")))))</f>
+        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra - treba "&amp;L23,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K23">
@@ -8299,7 +8299,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2">
-        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra — treba "&amp;L24,"✓ ispravan")))))</f>
+        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra - treba "&amp;L24,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K24">
@@ -8333,7 +8333,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2">
-        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra — treba "&amp;L25,"✓ ispravan")))))</f>
+        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra - treba "&amp;L25,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K25">
@@ -8367,7 +8367,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2">
-        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra — treba "&amp;L26,"✓ ispravan")))))</f>
+        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra - treba "&amp;L26,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K26">
@@ -8401,7 +8401,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2">
-        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra — treba "&amp;L27,"✓ ispravan")))))</f>
+        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra - treba "&amp;L27,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K27">
@@ -8435,7 +8435,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2">
-        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra — treba "&amp;L28,"✓ ispravan")))))</f>
+        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra - treba "&amp;L28,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K28">
@@ -8469,7 +8469,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2">
-        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra — treba "&amp;L29,"✓ ispravan")))))</f>
+        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra - treba "&amp;L29,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K29">
@@ -8503,7 +8503,7 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2">
-        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra — treba "&amp;L30,"✓ ispravan")))))</f>
+        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra - treba "&amp;L30,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K30">
@@ -8537,7 +8537,7 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2">
-        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra — treba "&amp;L31,"✓ ispravan")))))</f>
+        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra - treba "&amp;L31,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K31">
@@ -8571,7 +8571,7 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2">
-        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra — treba "&amp;L32,"✓ ispravan")))))</f>
+        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra - treba "&amp;L32,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K32">
@@ -8605,7 +8605,7 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2">
-        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra — treba "&amp;L33,"✓ ispravan")))))</f>
+        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra - treba "&amp;L33,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K33">
@@ -8639,7 +8639,7 @@
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2">
-        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra — treba "&amp;L34,"✓ ispravan")))))</f>
+        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra - treba "&amp;L34,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K34">
@@ -8673,7 +8673,7 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2">
-        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra — treba "&amp;L35,"✓ ispravan")))))</f>
+        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra - treba "&amp;L35,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K35">
@@ -8707,7 +8707,7 @@
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2">
-        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra — treba "&amp;L36,"✓ ispravan")))))</f>
+        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra - treba "&amp;L36,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K36">
@@ -8741,7 +8741,7 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2">
-        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra — treba "&amp;L37,"✓ ispravan")))))</f>
+        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra - treba "&amp;L37,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K37">
@@ -8775,7 +8775,7 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2">
-        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra — treba "&amp;L38,"✓ ispravan")))))</f>
+        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra - treba "&amp;L38,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K38">
@@ -8809,7 +8809,7 @@
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2">
-        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra — treba "&amp;L39,"✓ ispravan")))))</f>
+        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra - treba "&amp;L39,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K39">
@@ -8843,7 +8843,7 @@
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2">
-        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra — treba "&amp;L40,"✓ ispravan")))))</f>
+        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra - treba "&amp;L40,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K40">
@@ -8877,7 +8877,7 @@
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2">
-        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra — treba "&amp;L41,"✓ ispravan")))))</f>
+        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra - treba "&amp;L41,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K41">
@@ -8911,7 +8911,7 @@
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2">
-        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra — treba "&amp;L42,"✓ ispravan")))))</f>
+        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra - treba "&amp;L42,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K42">
@@ -8945,7 +8945,7 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2">
-        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra — treba "&amp;L43,"✓ ispravan")))))</f>
+        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra - treba "&amp;L43,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K43">
@@ -8979,7 +8979,7 @@
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2">
-        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra — treba "&amp;L44,"✓ ispravan")))))</f>
+        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra - treba "&amp;L44,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K44">
@@ -9013,7 +9013,7 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2">
-        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra — treba "&amp;L45,"✓ ispravan")))))</f>
+        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra - treba "&amp;L45,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K45">
@@ -9047,7 +9047,7 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2">
-        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra — treba "&amp;L46,"✓ ispravan")))))</f>
+        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra - treba "&amp;L46,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K46">
@@ -9081,7 +9081,7 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2">
-        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra — treba "&amp;L47,"✓ ispravan")))))</f>
+        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra - treba "&amp;L47,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K47">
@@ -9115,7 +9115,7 @@
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2">
-        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra — treba "&amp;L48,"✓ ispravan")))))</f>
+        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra - treba "&amp;L48,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K48">
@@ -9149,7 +9149,7 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2">
-        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra — treba "&amp;L49,"✓ ispravan")))))</f>
+        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra - treba "&amp;L49,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K49">
@@ -9183,7 +9183,7 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2">
-        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra — treba "&amp;L50,"✓ ispravan")))))</f>
+        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra - treba "&amp;L50,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K50">
@@ -9217,7 +9217,7 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2">
-        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra — treba "&amp;L51,"✓ ispravan")))))</f>
+        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra - treba "&amp;L51,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K51">
@@ -9251,7 +9251,7 @@
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2">
-        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra — treba "&amp;L52,"✓ ispravan")))))</f>
+        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra - treba "&amp;L52,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K52">
@@ -9285,7 +9285,7 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2">
-        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra — treba "&amp;L53,"✓ ispravan")))))</f>
+        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra - treba "&amp;L53,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K53">
@@ -9319,7 +9319,7 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2">
-        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra — treba "&amp;L54,"✓ ispravan")))))</f>
+        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra - treba "&amp;L54,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K54">
@@ -9353,7 +9353,7 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2">
-        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra — treba "&amp;L55,"✓ ispravan")))))</f>
+        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra - treba "&amp;L55,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K55">
@@ -9387,7 +9387,7 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
       <c r="J56" s="2">
-        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra — treba "&amp;L56,"✓ ispravan")))))</f>
+        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra - treba "&amp;L56,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K56">
@@ -9421,7 +9421,7 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2">
-        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra — treba "&amp;L57,"✓ ispravan")))))</f>
+        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra - treba "&amp;L57,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K57">
@@ -9455,7 +9455,7 @@
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2">
-        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra — treba "&amp;L58,"✓ ispravan")))))</f>
+        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra - treba "&amp;L58,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K58">
@@ -9489,7 +9489,7 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
       <c r="J59" s="2">
-        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra — treba "&amp;L59,"✓ ispravan")))))</f>
+        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra - treba "&amp;L59,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K59">
@@ -9523,7 +9523,7 @@
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
       <c r="J60" s="2">
-        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra — treba "&amp;L60,"✓ ispravan")))))</f>
+        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra - treba "&amp;L60,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K60">
@@ -9557,7 +9557,7 @@
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2">
-        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra — treba "&amp;L61,"✓ ispravan")))))</f>
+        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra - treba "&amp;L61,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K61">
@@ -9591,7 +9591,7 @@
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
       <c r="J62" s="2">
-        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra — treba "&amp;L62,"✓ ispravan")))))</f>
+        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra - treba "&amp;L62,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K62">
@@ -9625,7 +9625,7 @@
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2">
-        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra — treba "&amp;L63,"✓ ispravan")))))</f>
+        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra - treba "&amp;L63,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K63">
@@ -9659,7 +9659,7 @@
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2">
-        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra — treba "&amp;L64,"✓ ispravan")))))</f>
+        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra - treba "&amp;L64,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K64">
@@ -9693,7 +9693,7 @@
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
       <c r="J65" s="2">
-        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra — treba "&amp;L65,"✓ ispravan")))))</f>
+        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra - treba "&amp;L65,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K65">
@@ -9727,7 +9727,7 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2">
-        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra — treba "&amp;L66,"✓ ispravan")))))</f>
+        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra - treba "&amp;L66,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K66">
@@ -9761,7 +9761,7 @@
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
       <c r="J67" s="2">
-        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra — treba "&amp;L67,"✓ ispravan")))))</f>
+        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra - treba "&amp;L67,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K67">
@@ -9795,7 +9795,7 @@
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
       <c r="J68" s="2">
-        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra — treba "&amp;L68,"✓ ispravan")))))</f>
+        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra - treba "&amp;L68,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K68">
@@ -9829,7 +9829,7 @@
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
       <c r="J69" s="2">
-        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra — treba "&amp;L69,"✓ ispravan")))))</f>
+        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra - treba "&amp;L69,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K69">
@@ -9863,7 +9863,7 @@
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2">
-        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra — treba "&amp;L70,"✓ ispravan")))))</f>
+        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra - treba "&amp;L70,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K70">
@@ -9897,7 +9897,7 @@
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
       <c r="J71" s="2">
-        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra — treba "&amp;L71,"✓ ispravan")))))</f>
+        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra - treba "&amp;L71,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K71">
@@ -9931,7 +9931,7 @@
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2">
-        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra — treba "&amp;L72,"✓ ispravan")))))</f>
+        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra - treba "&amp;L72,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K72">
@@ -9965,7 +9965,7 @@
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
       <c r="J73" s="2">
-        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra — treba "&amp;L73,"✓ ispravan")))))</f>
+        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra - treba "&amp;L73,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K73">
@@ -9999,7 +9999,7 @@
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
       <c r="J74" s="2">
-        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra — treba "&amp;L74,"✓ ispravan")))))</f>
+        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra - treba "&amp;L74,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K74">
@@ -10033,7 +10033,7 @@
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2">
-        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra — treba "&amp;L75,"✓ ispravan")))))</f>
+        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra - treba "&amp;L75,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K75">
@@ -10067,7 +10067,7 @@
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
       <c r="J76" s="2">
-        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra — treba "&amp;L76,"✓ ispravan")))))</f>
+        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra - treba "&amp;L76,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K76">
@@ -10101,7 +10101,7 @@
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
       <c r="J77" s="2">
-        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra — treba "&amp;L77,"✓ ispravan")))))</f>
+        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra - treba "&amp;L77,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K77">
@@ -10135,7 +10135,7 @@
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
       <c r="J78" s="2">
-        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra — treba "&amp;L78,"✓ ispravan")))))</f>
+        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra - treba "&amp;L78,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K78">
@@ -10169,7 +10169,7 @@
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
       <c r="J79" s="2">
-        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra — treba "&amp;L79,"✓ ispravan")))))</f>
+        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra - treba "&amp;L79,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K79">
@@ -10203,7 +10203,7 @@
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
       <c r="J80" s="2">
-        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra — treba "&amp;L80,"✓ ispravan")))))</f>
+        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra - treba "&amp;L80,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K80">
@@ -10237,7 +10237,7 @@
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
       <c r="J81" s="2">
-        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra — treba "&amp;L81,"✓ ispravan")))))</f>
+        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra - treba "&amp;L81,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K81">
@@ -10271,7 +10271,7 @@
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
       <c r="J82" s="2">
-        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra — treba "&amp;L82,"✓ ispravan")))))</f>
+        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra - treba "&amp;L82,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K82">
@@ -10305,7 +10305,7 @@
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
       <c r="J83" s="2">
-        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra — treba "&amp;L83,"✓ ispravan")))))</f>
+        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra - treba "&amp;L83,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K83">
@@ -10339,7 +10339,7 @@
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2">
-        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra — treba "&amp;L84,"✓ ispravan")))))</f>
+        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra - treba "&amp;L84,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K84">
@@ -10373,7 +10373,7 @@
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
       <c r="J85" s="2">
-        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra — treba "&amp;L85,"✓ ispravan")))))</f>
+        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra - treba "&amp;L85,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K85">
@@ -10407,7 +10407,7 @@
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
       <c r="J86" s="2">
-        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra — treba "&amp;L86,"✓ ispravan")))))</f>
+        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra - treba "&amp;L86,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K86">
@@ -10441,7 +10441,7 @@
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
       <c r="J87" s="2">
-        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra — treba "&amp;L87,"✓ ispravan")))))</f>
+        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra - treba "&amp;L87,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K87">
@@ -10475,7 +10475,7 @@
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
       <c r="J88" s="2">
-        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra — treba "&amp;L88,"✓ ispravan")))))</f>
+        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra - treba "&amp;L88,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K88">
@@ -10509,7 +10509,7 @@
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
       <c r="J89" s="2">
-        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra — treba "&amp;L89,"✓ ispravan")))))</f>
+        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra - treba "&amp;L89,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K89">
@@ -10543,7 +10543,7 @@
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
       <c r="J90" s="2">
-        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra — treba "&amp;L90,"✓ ispravan")))))</f>
+        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra - treba "&amp;L90,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K90">
@@ -10577,7 +10577,7 @@
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="n"/>
       <c r="J91" s="2">
-        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra — treba "&amp;L91,"✓ ispravan")))))</f>
+        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra - treba "&amp;L91,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K91">
@@ -10611,7 +10611,7 @@
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
       <c r="J92" s="2">
-        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra — treba "&amp;L92,"✓ ispravan")))))</f>
+        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra - treba "&amp;L92,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K92">
@@ -10645,7 +10645,7 @@
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="n"/>
       <c r="J93" s="2">
-        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra — treba "&amp;L93,"✓ ispravan")))))</f>
+        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra - treba "&amp;L93,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K93">
@@ -10679,7 +10679,7 @@
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
       <c r="J94" s="2">
-        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra — treba "&amp;L94,"✓ ispravan")))))</f>
+        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra - treba "&amp;L94,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K94">
@@ -10713,7 +10713,7 @@
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="n"/>
       <c r="J95" s="2">
-        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra — treba "&amp;L95,"✓ ispravan")))))</f>
+        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra - treba "&amp;L95,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K95">
@@ -10747,7 +10747,7 @@
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="n"/>
       <c r="J96" s="2">
-        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra — treba "&amp;L96,"✓ ispravan")))))</f>
+        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra - treba "&amp;L96,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K96">
@@ -10781,7 +10781,7 @@
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
       <c r="J97" s="2">
-        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra — treba "&amp;L97,"✓ ispravan")))))</f>
+        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra - treba "&amp;L97,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K97">
@@ -10815,7 +10815,7 @@
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
       <c r="J98" s="2">
-        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra — treba "&amp;L98,"✓ ispravan")))))</f>
+        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra - treba "&amp;L98,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K98">
@@ -10849,7 +10849,7 @@
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
       <c r="J99" s="2">
-        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra — treba "&amp;L99,"✓ ispravan")))))</f>
+        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra - treba "&amp;L99,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K99">
@@ -10883,7 +10883,7 @@
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="n"/>
       <c r="J100" s="2">
-        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra — treba "&amp;L100,"✓ ispravan")))))</f>
+        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra - treba "&amp;L100,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K100">
@@ -10917,7 +10917,7 @@
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="n"/>
       <c r="J101" s="2">
-        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra — treba "&amp;L101,"✓ ispravan")))))</f>
+        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra - treba "&amp;L101,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K101">
@@ -10951,7 +10951,7 @@
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="n"/>
       <c r="J102" s="2">
-        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra — treba "&amp;L102,"✓ ispravan")))))</f>
+        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra - treba "&amp;L102,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K102">
@@ -10985,7 +10985,7 @@
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
       <c r="J103" s="2">
-        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra — treba "&amp;L103,"✓ ispravan")))))</f>
+        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra - treba "&amp;L103,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K103">
@@ -11019,7 +11019,7 @@
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="n"/>
       <c r="J104" s="2">
-        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra — treba "&amp;L104,"✓ ispravan")))))</f>
+        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra - treba "&amp;L104,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K104">
@@ -11053,7 +11053,7 @@
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
       <c r="J105" s="2">
-        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra — treba "&amp;L105,"✓ ispravan")))))</f>
+        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra - treba "&amp;L105,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K105">
@@ -11087,7 +11087,7 @@
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="n"/>
       <c r="J106" s="2">
-        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra — treba "&amp;L106,"✓ ispravan")))))</f>
+        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra - treba "&amp;L106,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K106">
@@ -11121,7 +11121,7 @@
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
       <c r="J107" s="2">
-        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra — treba "&amp;L107,"✓ ispravan")))))</f>
+        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra - treba "&amp;L107,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K107">
@@ -11155,7 +11155,7 @@
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
       <c r="J108" s="2">
-        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra — treba "&amp;L108,"✓ ispravan")))))</f>
+        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra - treba "&amp;L108,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K108">
@@ -11189,7 +11189,7 @@
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
       <c r="J109" s="2">
-        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra — treba "&amp;L109,"✓ ispravan")))))</f>
+        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra - treba "&amp;L109,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K109">
@@ -11223,7 +11223,7 @@
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
       <c r="J110" s="2">
-        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra — treba "&amp;L110,"✓ ispravan")))))</f>
+        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra - treba "&amp;L110,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K110">
@@ -11257,7 +11257,7 @@
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
       <c r="J111" s="2">
-        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra — treba "&amp;L111,"✓ ispravan")))))</f>
+        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra - treba "&amp;L111,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K111">
@@ -11291,7 +11291,7 @@
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
       <c r="J112" s="2">
-        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra — treba "&amp;L112,"✓ ispravan")))))</f>
+        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra - treba "&amp;L112,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K112">
@@ -11325,7 +11325,7 @@
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
       <c r="J113" s="2">
-        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra — treba "&amp;L113,"✓ ispravan")))))</f>
+        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra - treba "&amp;L113,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K113">
@@ -11359,7 +11359,7 @@
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
       <c r="J114" s="2">
-        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra — treba "&amp;L114,"✓ ispravan")))))</f>
+        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra - treba "&amp;L114,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K114">
@@ -11393,7 +11393,7 @@
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
       <c r="J115" s="2">
-        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra — treba "&amp;L115,"✓ ispravan")))))</f>
+        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra - treba "&amp;L115,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K115">
@@ -11427,7 +11427,7 @@
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="n"/>
       <c r="J116" s="2">
-        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra — treba "&amp;L116,"✓ ispravan")))))</f>
+        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra - treba "&amp;L116,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K116">
@@ -11461,7 +11461,7 @@
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
       <c r="J117" s="2">
-        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra — treba "&amp;L117,"✓ ispravan")))))</f>
+        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra - treba "&amp;L117,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K117">
@@ -11495,7 +11495,7 @@
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="n"/>
       <c r="J118" s="2">
-        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra — treba "&amp;L118,"✓ ispravan")))))</f>
+        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra - treba "&amp;L118,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K118">
@@ -11529,7 +11529,7 @@
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
       <c r="J119" s="2">
-        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra — treba "&amp;L119,"✓ ispravan")))))</f>
+        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra - treba "&amp;L119,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K119">
@@ -11563,7 +11563,7 @@
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
       <c r="J120" s="2">
-        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra — treba "&amp;L120,"✓ ispravan")))))</f>
+        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra - treba "&amp;L120,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K120">
@@ -11597,7 +11597,7 @@
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="n"/>
       <c r="J121" s="2">
-        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra — treba "&amp;L121,"✓ ispravan")))))</f>
+        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra - treba "&amp;L121,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K121">
@@ -11631,7 +11631,7 @@
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="n"/>
       <c r="J122" s="2">
-        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra — treba "&amp;L122,"✓ ispravan")))))</f>
+        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra - treba "&amp;L122,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K122">
@@ -11665,7 +11665,7 @@
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
       <c r="J123" s="2">
-        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra — treba "&amp;L123,"✓ ispravan")))))</f>
+        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra - treba "&amp;L123,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K123">
@@ -11699,7 +11699,7 @@
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
       <c r="J124" s="2">
-        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra — treba "&amp;L124,"✓ ispravan")))))</f>
+        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra - treba "&amp;L124,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K124">
@@ -11733,7 +11733,7 @@
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
       <c r="J125" s="2">
-        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra — treba "&amp;L125,"✓ ispravan")))))</f>
+        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra - treba "&amp;L125,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K125">
@@ -11767,7 +11767,7 @@
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
       <c r="J126" s="2">
-        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra — treba "&amp;L126,"✓ ispravan")))))</f>
+        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra - treba "&amp;L126,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K126">
@@ -11801,7 +11801,7 @@
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
       <c r="J127" s="2">
-        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra — treba "&amp;L127,"✓ ispravan")))))</f>
+        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra - treba "&amp;L127,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K127">
@@ -11835,7 +11835,7 @@
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="2" t="n"/>
       <c r="J128" s="2">
-        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra — treba "&amp;L128,"✓ ispravan")))))</f>
+        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra - treba "&amp;L128,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K128">
@@ -11869,7 +11869,7 @@
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
       <c r="J129" s="2">
-        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra — treba "&amp;L129,"✓ ispravan")))))</f>
+        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra - treba "&amp;L129,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K129">
@@ -11903,7 +11903,7 @@
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
       <c r="J130" s="2">
-        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra — treba "&amp;L130,"✓ ispravan")))))</f>
+        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra - treba "&amp;L130,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K130">
@@ -11937,7 +11937,7 @@
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
       <c r="J131" s="2">
-        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra — treba "&amp;L131,"✓ ispravan")))))</f>
+        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra - treba "&amp;L131,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K131">
@@ -11971,7 +11971,7 @@
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="n"/>
       <c r="J132" s="2">
-        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra — treba "&amp;L132,"✓ ispravan")))))</f>
+        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra - treba "&amp;L132,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K132">
@@ -12005,7 +12005,7 @@
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="n"/>
       <c r="J133" s="2">
-        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra — treba "&amp;L133,"✓ ispravan")))))</f>
+        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra - treba "&amp;L133,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K133">
@@ -12039,7 +12039,7 @@
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
       <c r="J134" s="2">
-        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra — treba "&amp;L134,"✓ ispravan")))))</f>
+        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra - treba "&amp;L134,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K134">
@@ -12073,7 +12073,7 @@
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
       <c r="J135" s="2">
-        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra — treba "&amp;L135,"✓ ispravan")))))</f>
+        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra - treba "&amp;L135,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K135">
@@ -12107,7 +12107,7 @@
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
       <c r="J136" s="2">
-        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra — treba "&amp;L136,"✓ ispravan")))))</f>
+        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra - treba "&amp;L136,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K136">
@@ -12141,7 +12141,7 @@
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="n"/>
       <c r="J137" s="2">
-        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra — treba "&amp;L137,"✓ ispravan")))))</f>
+        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra - treba "&amp;L137,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K137">
@@ -12175,7 +12175,7 @@
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
       <c r="J138" s="2">
-        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra — treba "&amp;L138,"✓ ispravan")))))</f>
+        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra - treba "&amp;L138,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K138">
@@ -12209,7 +12209,7 @@
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2">
-        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra — treba "&amp;L139,"✓ ispravan")))))</f>
+        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra - treba "&amp;L139,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K139">
@@ -12243,7 +12243,7 @@
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
       <c r="J140" s="2">
-        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra — treba "&amp;L140,"✓ ispravan")))))</f>
+        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra - treba "&amp;L140,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K140">
@@ -12277,7 +12277,7 @@
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
       <c r="J141" s="2">
-        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra — treba "&amp;L141,"✓ ispravan")))))</f>
+        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra - treba "&amp;L141,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K141">
@@ -12311,7 +12311,7 @@
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="2" t="n"/>
       <c r="J142" s="2">
-        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra — treba "&amp;L142,"✓ ispravan")))))</f>
+        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra - treba "&amp;L142,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K142">
@@ -12345,7 +12345,7 @@
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
       <c r="J143" s="2">
-        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra — treba "&amp;L143,"✓ ispravan")))))</f>
+        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra - treba "&amp;L143,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K143">
@@ -12379,7 +12379,7 @@
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
       <c r="J144" s="2">
-        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra — treba "&amp;L144,"✓ ispravan")))))</f>
+        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra - treba "&amp;L144,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K144">
@@ -12413,7 +12413,7 @@
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
       <c r="J145" s="2">
-        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra — treba "&amp;L145,"✓ ispravan")))))</f>
+        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra - treba "&amp;L145,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K145">
@@ -12447,7 +12447,7 @@
       <c r="H146" s="2" t="n"/>
       <c r="I146" s="2" t="n"/>
       <c r="J146" s="2">
-        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra — treba "&amp;L146,"✓ ispravan")))))</f>
+        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra - treba "&amp;L146,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K146">
@@ -12481,7 +12481,7 @@
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="n"/>
       <c r="J147" s="2">
-        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra — treba "&amp;L147,"✓ ispravan")))))</f>
+        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra - treba "&amp;L147,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K147">
@@ -12515,7 +12515,7 @@
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="n"/>
       <c r="J148" s="2">
-        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra — treba "&amp;L148,"✓ ispravan")))))</f>
+        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra - treba "&amp;L148,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K148">
@@ -12549,7 +12549,7 @@
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="n"/>
       <c r="J149" s="2">
-        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra — treba "&amp;L149,"✓ ispravan")))))</f>
+        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra - treba "&amp;L149,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K149">
@@ -12583,7 +12583,7 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2">
-        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra — treba "&amp;L150,"✓ ispravan")))))</f>
+        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra - treba "&amp;L150,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K150">
@@ -12617,7 +12617,7 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2">
-        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra — treba "&amp;L151,"✓ ispravan")))))</f>
+        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra - treba "&amp;L151,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K151">
@@ -12651,7 +12651,7 @@
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="n"/>
       <c r="J152" s="2">
-        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra — treba "&amp;L152,"✓ ispravan")))))</f>
+        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra - treba "&amp;L152,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K152">
@@ -12685,7 +12685,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
       <c r="J153" s="2">
-        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra — treba "&amp;L153,"✓ ispravan")))))</f>
+        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra - treba "&amp;L153,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K153">
@@ -12719,7 +12719,7 @@
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
       <c r="J154" s="2">
-        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra — treba "&amp;L154,"✓ ispravan")))))</f>
+        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra - treba "&amp;L154,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K154">
@@ -12753,7 +12753,7 @@
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
       <c r="J155" s="2">
-        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra — treba "&amp;L155,"✓ ispravan")))))</f>
+        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra - treba "&amp;L155,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K155">
@@ -12787,7 +12787,7 @@
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
       <c r="J156" s="2">
-        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra — treba "&amp;L156,"✓ ispravan")))))</f>
+        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra - treba "&amp;L156,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K156">
@@ -12821,7 +12821,7 @@
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
       <c r="J157" s="2">
-        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra — treba "&amp;L157,"✓ ispravan")))))</f>
+        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra - treba "&amp;L157,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K157">
@@ -12855,7 +12855,7 @@
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="2" t="n"/>
       <c r="J158" s="2">
-        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra — treba "&amp;L158,"✓ ispravan")))))</f>
+        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra - treba "&amp;L158,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K158">
@@ -12889,7 +12889,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
       <c r="J159" s="2">
-        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra — treba "&amp;L159,"✓ ispravan")))))</f>
+        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra - treba "&amp;L159,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K159">
@@ -12923,7 +12923,7 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2">
-        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra — treba "&amp;L160,"✓ ispravan")))))</f>
+        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra - treba "&amp;L160,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K160">
@@ -12957,7 +12957,7 @@
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
       <c r="J161" s="2">
-        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra — treba "&amp;L161,"✓ ispravan")))))</f>
+        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra - treba "&amp;L161,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K161">
@@ -12991,7 +12991,7 @@
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
       <c r="J162" s="2">
-        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra — treba "&amp;L162,"✓ ispravan")))))</f>
+        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra - treba "&amp;L162,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K162">
@@ -13025,7 +13025,7 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
       <c r="J163" s="2">
-        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra — treba "&amp;L163,"✓ ispravan")))))</f>
+        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra - treba "&amp;L163,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K163">
@@ -13059,7 +13059,7 @@
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="2" t="n"/>
       <c r="J164" s="2">
-        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra — treba "&amp;L164,"✓ ispravan")))))</f>
+        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra - treba "&amp;L164,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K164">
@@ -13093,7 +13093,7 @@
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
       <c r="J165" s="2">
-        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra — treba "&amp;L165,"✓ ispravan")))))</f>
+        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra - treba "&amp;L165,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K165">
@@ -13127,7 +13127,7 @@
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="n"/>
       <c r="J166" s="2">
-        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra — treba "&amp;L166,"✓ ispravan")))))</f>
+        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra - treba "&amp;L166,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K166">
@@ -13161,7 +13161,7 @@
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
       <c r="J167" s="2">
-        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra — treba "&amp;L167,"✓ ispravan")))))</f>
+        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra - treba "&amp;L167,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K167">
@@ -13195,7 +13195,7 @@
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
       <c r="J168" s="2">
-        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra — treba "&amp;L168,"✓ ispravan")))))</f>
+        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra - treba "&amp;L168,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K168">
@@ -13229,7 +13229,7 @@
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="n"/>
       <c r="J169" s="2">
-        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra — treba "&amp;L169,"✓ ispravan")))))</f>
+        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra - treba "&amp;L169,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K169">
@@ -13263,7 +13263,7 @@
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
       <c r="J170" s="2">
-        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra — treba "&amp;L170,"✓ ispravan")))))</f>
+        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra - treba "&amp;L170,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K170">
@@ -13297,7 +13297,7 @@
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
       <c r="J171" s="2">
-        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra — treba "&amp;L171,"✓ ispravan")))))</f>
+        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra - treba "&amp;L171,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K171">
@@ -13331,7 +13331,7 @@
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
       <c r="J172" s="2">
-        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra — treba "&amp;L172,"✓ ispravan")))))</f>
+        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra - treba "&amp;L172,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K172">
@@ -13365,7 +13365,7 @@
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="n"/>
       <c r="J173" s="2">
-        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra — treba "&amp;L173,"✓ ispravan")))))</f>
+        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra - treba "&amp;L173,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K173">
@@ -13399,7 +13399,7 @@
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
       <c r="J174" s="2">
-        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra — treba "&amp;L174,"✓ ispravan")))))</f>
+        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra - treba "&amp;L174,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K174">
@@ -13433,7 +13433,7 @@
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
       <c r="J175" s="2">
-        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra — treba "&amp;L175,"✓ ispravan")))))</f>
+        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra - treba "&amp;L175,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K175">
@@ -13467,7 +13467,7 @@
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
       <c r="J176" s="2">
-        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra — treba "&amp;L176,"✓ ispravan")))))</f>
+        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra - treba "&amp;L176,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K176">
@@ -13501,7 +13501,7 @@
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
       <c r="J177" s="2">
-        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra — treba "&amp;L177,"✓ ispravan")))))</f>
+        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra - treba "&amp;L177,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K177">
@@ -13535,7 +13535,7 @@
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
       <c r="J178" s="2">
-        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra — treba "&amp;L178,"✓ ispravan")))))</f>
+        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra - treba "&amp;L178,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K178">
@@ -13569,7 +13569,7 @@
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="2" t="n"/>
       <c r="J179" s="2">
-        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra — treba "&amp;L179,"✓ ispravan")))))</f>
+        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra - treba "&amp;L179,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K179">
@@ -13603,7 +13603,7 @@
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
       <c r="J180" s="2">
-        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra — treba "&amp;L180,"✓ ispravan")))))</f>
+        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra - treba "&amp;L180,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K180">
@@ -13637,7 +13637,7 @@
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="2" t="n"/>
       <c r="J181" s="2">
-        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra — treba "&amp;L181,"✓ ispravan")))))</f>
+        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra - treba "&amp;L181,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K181">
@@ -13671,7 +13671,7 @@
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="n"/>
       <c r="J182" s="2">
-        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra — treba "&amp;L182,"✓ ispravan")))))</f>
+        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra - treba "&amp;L182,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K182">
@@ -13705,7 +13705,7 @@
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="2" t="n"/>
       <c r="J183" s="2">
-        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra — treba "&amp;L183,"✓ ispravan")))))</f>
+        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra - treba "&amp;L183,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K183">
@@ -13739,7 +13739,7 @@
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
       <c r="J184" s="2">
-        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra — treba "&amp;L184,"✓ ispravan")))))</f>
+        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra - treba "&amp;L184,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K184">
@@ -13773,7 +13773,7 @@
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="n"/>
       <c r="J185" s="2">
-        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra — treba "&amp;L185,"✓ ispravan")))))</f>
+        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra - treba "&amp;L185,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K185">
@@ -13807,7 +13807,7 @@
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="n"/>
       <c r="J186" s="2">
-        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra — treba "&amp;L186,"✓ ispravan")))))</f>
+        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra - treba "&amp;L186,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K186">
@@ -13841,7 +13841,7 @@
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="2" t="n"/>
       <c r="J187" s="2">
-        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra — treba "&amp;L187,"✓ ispravan")))))</f>
+        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra - treba "&amp;L187,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K187">
@@ -13875,7 +13875,7 @@
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
       <c r="J188" s="2">
-        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra — treba "&amp;L188,"✓ ispravan")))))</f>
+        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra - treba "&amp;L188,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K188">
@@ -13909,7 +13909,7 @@
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="n"/>
       <c r="J189" s="2">
-        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra — treba "&amp;L189,"✓ ispravan")))))</f>
+        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra - treba "&amp;L189,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K189">
@@ -13943,7 +13943,7 @@
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="2" t="n"/>
       <c r="J190" s="2">
-        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra — treba "&amp;L190,"✓ ispravan")))))</f>
+        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra - treba "&amp;L190,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K190">
@@ -13977,7 +13977,7 @@
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="n"/>
       <c r="J191" s="2">
-        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra — treba "&amp;L191,"✓ ispravan")))))</f>
+        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra - treba "&amp;L191,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K191">
@@ -14011,7 +14011,7 @@
       <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="n"/>
       <c r="J192" s="2">
-        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra — treba "&amp;L192,"✓ ispravan")))))</f>
+        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra - treba "&amp;L192,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K192">
@@ -14045,7 +14045,7 @@
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="n"/>
       <c r="J193" s="2">
-        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra — treba "&amp;L193,"✓ ispravan")))))</f>
+        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra - treba "&amp;L193,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K193">
@@ -14079,7 +14079,7 @@
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
       <c r="J194" s="2">
-        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra — treba "&amp;L194,"✓ ispravan")))))</f>
+        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra - treba "&amp;L194,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K194">
@@ -14113,7 +14113,7 @@
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="n"/>
       <c r="J195" s="2">
-        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra — treba "&amp;L195,"✓ ispravan")))))</f>
+        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra - treba "&amp;L195,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K195">
@@ -14147,7 +14147,7 @@
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
       <c r="J196" s="2">
-        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra — treba "&amp;L196,"✓ ispravan")))))</f>
+        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra - treba "&amp;L196,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K196">
@@ -14181,7 +14181,7 @@
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="n"/>
       <c r="J197" s="2">
-        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra — treba "&amp;L197,"✓ ispravan")))))</f>
+        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra - treba "&amp;L197,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K197">
@@ -14215,7 +14215,7 @@
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
       <c r="J198" s="2">
-        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra — treba "&amp;L198,"✓ ispravan")))))</f>
+        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra - treba "&amp;L198,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K198">
@@ -14249,7 +14249,7 @@
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="n"/>
       <c r="J199" s="2">
-        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra — treba "&amp;L199,"✓ ispravan")))))</f>
+        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra - treba "&amp;L199,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K199">
@@ -14283,7 +14283,7 @@
       <c r="H200" s="2" t="n"/>
       <c r="I200" s="2" t="n"/>
       <c r="J200" s="2">
-        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra — treba "&amp;L200,"✓ ispravan")))))</f>
+        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra - treba "&amp;L200,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K200">
@@ -14317,7 +14317,7 @@
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="n"/>
       <c r="J201" s="2">
-        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra — treba "&amp;L201,"✓ ispravan")))))</f>
+        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra - treba "&amp;L201,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K201">
@@ -14481,7 +14481,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2">
-        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra — treba "&amp;L2,"✓ ispravan")))))</f>
+        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra - treba "&amp;L2,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K2">
@@ -14515,7 +14515,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2">
-        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra — treba "&amp;L3,"✓ ispravan")))))</f>
+        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra - treba "&amp;L3,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K3">
@@ -14549,7 +14549,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2">
-        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra — treba "&amp;L4,"✓ ispravan")))))</f>
+        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra - treba "&amp;L4,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K4">
@@ -14583,7 +14583,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2">
-        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra — treba "&amp;L5,"✓ ispravan")))))</f>
+        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra - treba "&amp;L5,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K5">
@@ -14617,7 +14617,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2">
-        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra — treba "&amp;L6,"✓ ispravan")))))</f>
+        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra - treba "&amp;L6,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K6">
@@ -14651,7 +14651,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2">
-        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra — treba "&amp;L7,"✓ ispravan")))))</f>
+        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra - treba "&amp;L7,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K7">
@@ -14685,7 +14685,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2">
-        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra — treba "&amp;L8,"✓ ispravan")))))</f>
+        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra - treba "&amp;L8,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K8">
@@ -14719,7 +14719,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2">
-        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra — treba "&amp;L9,"✓ ispravan")))))</f>
+        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra - treba "&amp;L9,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K9">
@@ -14753,7 +14753,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2">
-        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra — treba "&amp;L10,"✓ ispravan")))))</f>
+        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra - treba "&amp;L10,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K10">
@@ -14787,7 +14787,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2">
-        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra — treba "&amp;L11,"✓ ispravan")))))</f>
+        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra - treba "&amp;L11,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K11">
@@ -14821,7 +14821,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2">
-        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra — treba "&amp;L12,"✓ ispravan")))))</f>
+        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra - treba "&amp;L12,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K12">
@@ -14855,7 +14855,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2">
-        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra — treba "&amp;L13,"✓ ispravan")))))</f>
+        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra - treba "&amp;L13,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K13">
@@ -14889,7 +14889,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2">
-        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra — treba "&amp;L14,"✓ ispravan")))))</f>
+        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra - treba "&amp;L14,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K14">
@@ -14923,7 +14923,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2">
-        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra — treba "&amp;L15,"✓ ispravan")))))</f>
+        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra - treba "&amp;L15,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K15">
@@ -14957,7 +14957,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2">
-        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra — treba "&amp;L16,"✓ ispravan")))))</f>
+        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra - treba "&amp;L16,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K16">
@@ -14991,7 +14991,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2">
-        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra — treba "&amp;L17,"✓ ispravan")))))</f>
+        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra - treba "&amp;L17,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K17">
@@ -15025,7 +15025,7 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2">
-        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra — treba "&amp;L18,"✓ ispravan")))))</f>
+        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra - treba "&amp;L18,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K18">
@@ -15059,7 +15059,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2">
-        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra — treba "&amp;L19,"✓ ispravan")))))</f>
+        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra - treba "&amp;L19,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K19">
@@ -15093,7 +15093,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2">
-        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra — treba "&amp;L20,"✓ ispravan")))))</f>
+        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra - treba "&amp;L20,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K20">
@@ -15127,7 +15127,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2">
-        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra — treba "&amp;L21,"✓ ispravan")))))</f>
+        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra - treba "&amp;L21,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K21">
@@ -15161,7 +15161,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2">
-        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra — treba "&amp;L22,"✓ ispravan")))))</f>
+        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra - treba "&amp;L22,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K22">
@@ -15195,7 +15195,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2">
-        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra — treba "&amp;L23,"✓ ispravan")))))</f>
+        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra - treba "&amp;L23,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K23">
@@ -15229,7 +15229,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2">
-        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra — treba "&amp;L24,"✓ ispravan")))))</f>
+        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra - treba "&amp;L24,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K24">
@@ -15263,7 +15263,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2">
-        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra — treba "&amp;L25,"✓ ispravan")))))</f>
+        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra - treba "&amp;L25,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K25">
@@ -15297,7 +15297,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2">
-        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra — treba "&amp;L26,"✓ ispravan")))))</f>
+        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra - treba "&amp;L26,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K26">
@@ -15331,7 +15331,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2">
-        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra — treba "&amp;L27,"✓ ispravan")))))</f>
+        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra - treba "&amp;L27,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K27">
@@ -15365,7 +15365,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2">
-        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra — treba "&amp;L28,"✓ ispravan")))))</f>
+        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra - treba "&amp;L28,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K28">
@@ -15399,7 +15399,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2">
-        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra — treba "&amp;L29,"✓ ispravan")))))</f>
+        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra - treba "&amp;L29,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K29">
@@ -15433,7 +15433,7 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2">
-        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra — treba "&amp;L30,"✓ ispravan")))))</f>
+        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra - treba "&amp;L30,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K30">
@@ -15467,7 +15467,7 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2">
-        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra — treba "&amp;L31,"✓ ispravan")))))</f>
+        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra - treba "&amp;L31,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K31">
@@ -15501,7 +15501,7 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2">
-        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra — treba "&amp;L32,"✓ ispravan")))))</f>
+        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra - treba "&amp;L32,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K32">
@@ -15535,7 +15535,7 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2">
-        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra — treba "&amp;L33,"✓ ispravan")))))</f>
+        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra - treba "&amp;L33,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K33">
@@ -15569,7 +15569,7 @@
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2">
-        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra — treba "&amp;L34,"✓ ispravan")))))</f>
+        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra - treba "&amp;L34,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K34">
@@ -15603,7 +15603,7 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2">
-        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra — treba "&amp;L35,"✓ ispravan")))))</f>
+        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra - treba "&amp;L35,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K35">
@@ -15637,7 +15637,7 @@
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2">
-        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra — treba "&amp;L36,"✓ ispravan")))))</f>
+        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra - treba "&amp;L36,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K36">
@@ -15671,7 +15671,7 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2">
-        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra — treba "&amp;L37,"✓ ispravan")))))</f>
+        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra - treba "&amp;L37,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K37">
@@ -15705,7 +15705,7 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2">
-        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra — treba "&amp;L38,"✓ ispravan")))))</f>
+        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra - treba "&amp;L38,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K38">
@@ -15739,7 +15739,7 @@
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2">
-        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra — treba "&amp;L39,"✓ ispravan")))))</f>
+        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra - treba "&amp;L39,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K39">
@@ -15773,7 +15773,7 @@
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2">
-        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra — treba "&amp;L40,"✓ ispravan")))))</f>
+        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra - treba "&amp;L40,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K40">
@@ -15807,7 +15807,7 @@
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2">
-        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra — treba "&amp;L41,"✓ ispravan")))))</f>
+        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra - treba "&amp;L41,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K41">
@@ -15841,7 +15841,7 @@
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2">
-        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra — treba "&amp;L42,"✓ ispravan")))))</f>
+        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra - treba "&amp;L42,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K42">
@@ -15875,7 +15875,7 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2">
-        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra — treba "&amp;L43,"✓ ispravan")))))</f>
+        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra - treba "&amp;L43,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K43">
@@ -15909,7 +15909,7 @@
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2">
-        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra — treba "&amp;L44,"✓ ispravan")))))</f>
+        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra - treba "&amp;L44,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K44">
@@ -15943,7 +15943,7 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2">
-        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra — treba "&amp;L45,"✓ ispravan")))))</f>
+        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra - treba "&amp;L45,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K45">
@@ -15977,7 +15977,7 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2">
-        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra — treba "&amp;L46,"✓ ispravan")))))</f>
+        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra - treba "&amp;L46,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K46">
@@ -16011,7 +16011,7 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2">
-        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra — treba "&amp;L47,"✓ ispravan")))))</f>
+        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra - treba "&amp;L47,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K47">
@@ -16045,7 +16045,7 @@
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2">
-        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra — treba "&amp;L48,"✓ ispravan")))))</f>
+        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra - treba "&amp;L48,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K48">
@@ -16079,7 +16079,7 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2">
-        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra — treba "&amp;L49,"✓ ispravan")))))</f>
+        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra - treba "&amp;L49,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K49">
@@ -16113,7 +16113,7 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2">
-        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra — treba "&amp;L50,"✓ ispravan")))))</f>
+        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra - treba "&amp;L50,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K50">
@@ -16147,7 +16147,7 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2">
-        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra — treba "&amp;L51,"✓ ispravan")))))</f>
+        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra - treba "&amp;L51,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K51">
@@ -16181,7 +16181,7 @@
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2">
-        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra — treba "&amp;L52,"✓ ispravan")))))</f>
+        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra - treba "&amp;L52,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K52">
@@ -16215,7 +16215,7 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2">
-        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra — treba "&amp;L53,"✓ ispravan")))))</f>
+        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra - treba "&amp;L53,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K53">
@@ -16249,7 +16249,7 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2">
-        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra — treba "&amp;L54,"✓ ispravan")))))</f>
+        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra - treba "&amp;L54,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K54">
@@ -16283,7 +16283,7 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2">
-        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra — treba "&amp;L55,"✓ ispravan")))))</f>
+        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra - treba "&amp;L55,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K55">
@@ -16317,7 +16317,7 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
       <c r="J56" s="2">
-        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra — treba "&amp;L56,"✓ ispravan")))))</f>
+        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra - treba "&amp;L56,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K56">
@@ -16351,7 +16351,7 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2">
-        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra — treba "&amp;L57,"✓ ispravan")))))</f>
+        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra - treba "&amp;L57,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K57">
@@ -16385,7 +16385,7 @@
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2">
-        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra — treba "&amp;L58,"✓ ispravan")))))</f>
+        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra - treba "&amp;L58,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K58">
@@ -16419,7 +16419,7 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
       <c r="J59" s="2">
-        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra — treba "&amp;L59,"✓ ispravan")))))</f>
+        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra - treba "&amp;L59,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K59">
@@ -16453,7 +16453,7 @@
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
       <c r="J60" s="2">
-        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra — treba "&amp;L60,"✓ ispravan")))))</f>
+        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra - treba "&amp;L60,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K60">
@@ -16487,7 +16487,7 @@
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2">
-        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra — treba "&amp;L61,"✓ ispravan")))))</f>
+        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra - treba "&amp;L61,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K61">
@@ -16521,7 +16521,7 @@
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
       <c r="J62" s="2">
-        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra — treba "&amp;L62,"✓ ispravan")))))</f>
+        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra - treba "&amp;L62,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K62">
@@ -16555,7 +16555,7 @@
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2">
-        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra — treba "&amp;L63,"✓ ispravan")))))</f>
+        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra - treba "&amp;L63,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K63">
@@ -16589,7 +16589,7 @@
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2">
-        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra — treba "&amp;L64,"✓ ispravan")))))</f>
+        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra - treba "&amp;L64,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K64">
@@ -16623,7 +16623,7 @@
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
       <c r="J65" s="2">
-        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra — treba "&amp;L65,"✓ ispravan")))))</f>
+        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra - treba "&amp;L65,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K65">
@@ -16657,7 +16657,7 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2">
-        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra — treba "&amp;L66,"✓ ispravan")))))</f>
+        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra - treba "&amp;L66,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K66">
@@ -16691,7 +16691,7 @@
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
       <c r="J67" s="2">
-        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra — treba "&amp;L67,"✓ ispravan")))))</f>
+        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra - treba "&amp;L67,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K67">
@@ -16725,7 +16725,7 @@
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
       <c r="J68" s="2">
-        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra — treba "&amp;L68,"✓ ispravan")))))</f>
+        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra - treba "&amp;L68,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K68">
@@ -16759,7 +16759,7 @@
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
       <c r="J69" s="2">
-        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra — treba "&amp;L69,"✓ ispravan")))))</f>
+        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra - treba "&amp;L69,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K69">
@@ -16793,7 +16793,7 @@
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2">
-        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra — treba "&amp;L70,"✓ ispravan")))))</f>
+        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra - treba "&amp;L70,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K70">
@@ -16827,7 +16827,7 @@
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
       <c r="J71" s="2">
-        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra — treba "&amp;L71,"✓ ispravan")))))</f>
+        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra - treba "&amp;L71,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K71">
@@ -16861,7 +16861,7 @@
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2">
-        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra — treba "&amp;L72,"✓ ispravan")))))</f>
+        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra - treba "&amp;L72,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K72">
@@ -16895,7 +16895,7 @@
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
       <c r="J73" s="2">
-        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra — treba "&amp;L73,"✓ ispravan")))))</f>
+        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra - treba "&amp;L73,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K73">
@@ -16929,7 +16929,7 @@
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
       <c r="J74" s="2">
-        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra — treba "&amp;L74,"✓ ispravan")))))</f>
+        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra - treba "&amp;L74,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K74">
@@ -16963,7 +16963,7 @@
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2">
-        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra — treba "&amp;L75,"✓ ispravan")))))</f>
+        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra - treba "&amp;L75,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K75">
@@ -16997,7 +16997,7 @@
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
       <c r="J76" s="2">
-        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra — treba "&amp;L76,"✓ ispravan")))))</f>
+        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra - treba "&amp;L76,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K76">
@@ -17031,7 +17031,7 @@
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
       <c r="J77" s="2">
-        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra — treba "&amp;L77,"✓ ispravan")))))</f>
+        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra - treba "&amp;L77,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K77">
@@ -17065,7 +17065,7 @@
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
       <c r="J78" s="2">
-        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra — treba "&amp;L78,"✓ ispravan")))))</f>
+        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra - treba "&amp;L78,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K78">
@@ -17099,7 +17099,7 @@
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
       <c r="J79" s="2">
-        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra — treba "&amp;L79,"✓ ispravan")))))</f>
+        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra - treba "&amp;L79,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K79">
@@ -17133,7 +17133,7 @@
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
       <c r="J80" s="2">
-        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra — treba "&amp;L80,"✓ ispravan")))))</f>
+        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra - treba "&amp;L80,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K80">
@@ -17167,7 +17167,7 @@
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
       <c r="J81" s="2">
-        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra — treba "&amp;L81,"✓ ispravan")))))</f>
+        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra - treba "&amp;L81,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K81">
@@ -17201,7 +17201,7 @@
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
       <c r="J82" s="2">
-        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra — treba "&amp;L82,"✓ ispravan")))))</f>
+        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra - treba "&amp;L82,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K82">
@@ -17235,7 +17235,7 @@
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
       <c r="J83" s="2">
-        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra — treba "&amp;L83,"✓ ispravan")))))</f>
+        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra - treba "&amp;L83,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K83">
@@ -17269,7 +17269,7 @@
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2">
-        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra — treba "&amp;L84,"✓ ispravan")))))</f>
+        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra - treba "&amp;L84,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K84">
@@ -17303,7 +17303,7 @@
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
       <c r="J85" s="2">
-        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra — treba "&amp;L85,"✓ ispravan")))))</f>
+        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra - treba "&amp;L85,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K85">
@@ -17337,7 +17337,7 @@
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
       <c r="J86" s="2">
-        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra — treba "&amp;L86,"✓ ispravan")))))</f>
+        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra - treba "&amp;L86,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K86">
@@ -17371,7 +17371,7 @@
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
       <c r="J87" s="2">
-        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra — treba "&amp;L87,"✓ ispravan")))))</f>
+        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra - treba "&amp;L87,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K87">
@@ -17405,7 +17405,7 @@
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
       <c r="J88" s="2">
-        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra — treba "&amp;L88,"✓ ispravan")))))</f>
+        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra - treba "&amp;L88,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K88">
@@ -17439,7 +17439,7 @@
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
       <c r="J89" s="2">
-        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra — treba "&amp;L89,"✓ ispravan")))))</f>
+        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra - treba "&amp;L89,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K89">
@@ -17473,7 +17473,7 @@
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
       <c r="J90" s="2">
-        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra — treba "&amp;L90,"✓ ispravan")))))</f>
+        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra - treba "&amp;L90,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K90">
@@ -17507,7 +17507,7 @@
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="n"/>
       <c r="J91" s="2">
-        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra — treba "&amp;L91,"✓ ispravan")))))</f>
+        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra - treba "&amp;L91,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K91">
@@ -17541,7 +17541,7 @@
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
       <c r="J92" s="2">
-        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra — treba "&amp;L92,"✓ ispravan")))))</f>
+        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra - treba "&amp;L92,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K92">
@@ -17575,7 +17575,7 @@
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="n"/>
       <c r="J93" s="2">
-        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra — treba "&amp;L93,"✓ ispravan")))))</f>
+        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra - treba "&amp;L93,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K93">
@@ -17609,7 +17609,7 @@
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
       <c r="J94" s="2">
-        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra — treba "&amp;L94,"✓ ispravan")))))</f>
+        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra - treba "&amp;L94,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K94">
@@ -17643,7 +17643,7 @@
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="n"/>
       <c r="J95" s="2">
-        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra — treba "&amp;L95,"✓ ispravan")))))</f>
+        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra - treba "&amp;L95,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K95">
@@ -17677,7 +17677,7 @@
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="n"/>
       <c r="J96" s="2">
-        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra — treba "&amp;L96,"✓ ispravan")))))</f>
+        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra - treba "&amp;L96,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K96">
@@ -17711,7 +17711,7 @@
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
       <c r="J97" s="2">
-        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra — treba "&amp;L97,"✓ ispravan")))))</f>
+        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra - treba "&amp;L97,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K97">
@@ -17745,7 +17745,7 @@
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
       <c r="J98" s="2">
-        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra — treba "&amp;L98,"✓ ispravan")))))</f>
+        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra - treba "&amp;L98,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K98">
@@ -17779,7 +17779,7 @@
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
       <c r="J99" s="2">
-        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra — treba "&amp;L99,"✓ ispravan")))))</f>
+        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra - treba "&amp;L99,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K99">
@@ -17813,7 +17813,7 @@
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="n"/>
       <c r="J100" s="2">
-        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra — treba "&amp;L100,"✓ ispravan")))))</f>
+        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra - treba "&amp;L100,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K100">
@@ -17847,7 +17847,7 @@
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="n"/>
       <c r="J101" s="2">
-        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra — treba "&amp;L101,"✓ ispravan")))))</f>
+        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra - treba "&amp;L101,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K101">
@@ -17881,7 +17881,7 @@
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="n"/>
       <c r="J102" s="2">
-        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra — treba "&amp;L102,"✓ ispravan")))))</f>
+        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra - treba "&amp;L102,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K102">
@@ -17915,7 +17915,7 @@
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
       <c r="J103" s="2">
-        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra — treba "&amp;L103,"✓ ispravan")))))</f>
+        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra - treba "&amp;L103,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K103">
@@ -17949,7 +17949,7 @@
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="n"/>
       <c r="J104" s="2">
-        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra — treba "&amp;L104,"✓ ispravan")))))</f>
+        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra - treba "&amp;L104,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K104">
@@ -17983,7 +17983,7 @@
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
       <c r="J105" s="2">
-        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra — treba "&amp;L105,"✓ ispravan")))))</f>
+        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra - treba "&amp;L105,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K105">
@@ -18017,7 +18017,7 @@
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="n"/>
       <c r="J106" s="2">
-        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra — treba "&amp;L106,"✓ ispravan")))))</f>
+        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra - treba "&amp;L106,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K106">
@@ -18051,7 +18051,7 @@
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
       <c r="J107" s="2">
-        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra — treba "&amp;L107,"✓ ispravan")))))</f>
+        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra - treba "&amp;L107,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K107">
@@ -18085,7 +18085,7 @@
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
       <c r="J108" s="2">
-        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra — treba "&amp;L108,"✓ ispravan")))))</f>
+        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra - treba "&amp;L108,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K108">
@@ -18119,7 +18119,7 @@
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
       <c r="J109" s="2">
-        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra — treba "&amp;L109,"✓ ispravan")))))</f>
+        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra - treba "&amp;L109,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K109">
@@ -18153,7 +18153,7 @@
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
       <c r="J110" s="2">
-        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra — treba "&amp;L110,"✓ ispravan")))))</f>
+        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra - treba "&amp;L110,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K110">
@@ -18187,7 +18187,7 @@
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
       <c r="J111" s="2">
-        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra — treba "&amp;L111,"✓ ispravan")))))</f>
+        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra - treba "&amp;L111,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K111">
@@ -18221,7 +18221,7 @@
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
       <c r="J112" s="2">
-        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra — treba "&amp;L112,"✓ ispravan")))))</f>
+        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra - treba "&amp;L112,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K112">
@@ -18255,7 +18255,7 @@
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
       <c r="J113" s="2">
-        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra — treba "&amp;L113,"✓ ispravan")))))</f>
+        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra - treba "&amp;L113,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K113">
@@ -18289,7 +18289,7 @@
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
       <c r="J114" s="2">
-        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra — treba "&amp;L114,"✓ ispravan")))))</f>
+        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra - treba "&amp;L114,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K114">
@@ -18323,7 +18323,7 @@
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
       <c r="J115" s="2">
-        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra — treba "&amp;L115,"✓ ispravan")))))</f>
+        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra - treba "&amp;L115,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K115">
@@ -18357,7 +18357,7 @@
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="n"/>
       <c r="J116" s="2">
-        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra — treba "&amp;L116,"✓ ispravan")))))</f>
+        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra - treba "&amp;L116,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K116">
@@ -18391,7 +18391,7 @@
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
       <c r="J117" s="2">
-        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra — treba "&amp;L117,"✓ ispravan")))))</f>
+        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra - treba "&amp;L117,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K117">
@@ -18425,7 +18425,7 @@
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="n"/>
       <c r="J118" s="2">
-        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra — treba "&amp;L118,"✓ ispravan")))))</f>
+        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra - treba "&amp;L118,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K118">
@@ -18459,7 +18459,7 @@
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
       <c r="J119" s="2">
-        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra — treba "&amp;L119,"✓ ispravan")))))</f>
+        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra - treba "&amp;L119,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K119">
@@ -18493,7 +18493,7 @@
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
       <c r="J120" s="2">
-        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra — treba "&amp;L120,"✓ ispravan")))))</f>
+        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra - treba "&amp;L120,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K120">
@@ -18527,7 +18527,7 @@
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="n"/>
       <c r="J121" s="2">
-        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra — treba "&amp;L121,"✓ ispravan")))))</f>
+        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra - treba "&amp;L121,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K121">
@@ -18561,7 +18561,7 @@
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="n"/>
       <c r="J122" s="2">
-        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra — treba "&amp;L122,"✓ ispravan")))))</f>
+        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra - treba "&amp;L122,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K122">
@@ -18595,7 +18595,7 @@
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
       <c r="J123" s="2">
-        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra — treba "&amp;L123,"✓ ispravan")))))</f>
+        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra - treba "&amp;L123,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K123">
@@ -18629,7 +18629,7 @@
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
       <c r="J124" s="2">
-        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra — treba "&amp;L124,"✓ ispravan")))))</f>
+        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra - treba "&amp;L124,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K124">
@@ -18663,7 +18663,7 @@
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
       <c r="J125" s="2">
-        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra — treba "&amp;L125,"✓ ispravan")))))</f>
+        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra - treba "&amp;L125,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K125">
@@ -18697,7 +18697,7 @@
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
       <c r="J126" s="2">
-        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra — treba "&amp;L126,"✓ ispravan")))))</f>
+        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra - treba "&amp;L126,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K126">
@@ -18731,7 +18731,7 @@
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
       <c r="J127" s="2">
-        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra — treba "&amp;L127,"✓ ispravan")))))</f>
+        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra - treba "&amp;L127,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K127">
@@ -18765,7 +18765,7 @@
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="2" t="n"/>
       <c r="J128" s="2">
-        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra — treba "&amp;L128,"✓ ispravan")))))</f>
+        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra - treba "&amp;L128,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K128">
@@ -18799,7 +18799,7 @@
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
       <c r="J129" s="2">
-        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra — treba "&amp;L129,"✓ ispravan")))))</f>
+        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra - treba "&amp;L129,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K129">
@@ -18833,7 +18833,7 @@
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
       <c r="J130" s="2">
-        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra — treba "&amp;L130,"✓ ispravan")))))</f>
+        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra - treba "&amp;L130,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K130">
@@ -18867,7 +18867,7 @@
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
       <c r="J131" s="2">
-        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra — treba "&amp;L131,"✓ ispravan")))))</f>
+        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra - treba "&amp;L131,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K131">
@@ -18901,7 +18901,7 @@
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="n"/>
       <c r="J132" s="2">
-        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra — treba "&amp;L132,"✓ ispravan")))))</f>
+        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra - treba "&amp;L132,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K132">
@@ -18935,7 +18935,7 @@
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="n"/>
       <c r="J133" s="2">
-        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra — treba "&amp;L133,"✓ ispravan")))))</f>
+        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra - treba "&amp;L133,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K133">
@@ -18969,7 +18969,7 @@
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
       <c r="J134" s="2">
-        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra — treba "&amp;L134,"✓ ispravan")))))</f>
+        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra - treba "&amp;L134,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K134">
@@ -19003,7 +19003,7 @@
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
       <c r="J135" s="2">
-        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra — treba "&amp;L135,"✓ ispravan")))))</f>
+        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra - treba "&amp;L135,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K135">
@@ -19037,7 +19037,7 @@
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
       <c r="J136" s="2">
-        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra — treba "&amp;L136,"✓ ispravan")))))</f>
+        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra - treba "&amp;L136,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K136">
@@ -19071,7 +19071,7 @@
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="n"/>
       <c r="J137" s="2">
-        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra — treba "&amp;L137,"✓ ispravan")))))</f>
+        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra - treba "&amp;L137,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K137">
@@ -19105,7 +19105,7 @@
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
       <c r="J138" s="2">
-        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra — treba "&amp;L138,"✓ ispravan")))))</f>
+        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra - treba "&amp;L138,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K138">
@@ -19139,7 +19139,7 @@
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2">
-        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra — treba "&amp;L139,"✓ ispravan")))))</f>
+        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra - treba "&amp;L139,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K139">
@@ -19173,7 +19173,7 @@
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
       <c r="J140" s="2">
-        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra — treba "&amp;L140,"✓ ispravan")))))</f>
+        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra - treba "&amp;L140,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K140">
@@ -19207,7 +19207,7 @@
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
       <c r="J141" s="2">
-        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra — treba "&amp;L141,"✓ ispravan")))))</f>
+        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra - treba "&amp;L141,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K141">
@@ -19241,7 +19241,7 @@
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="2" t="n"/>
       <c r="J142" s="2">
-        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra — treba "&amp;L142,"✓ ispravan")))))</f>
+        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra - treba "&amp;L142,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K142">
@@ -19275,7 +19275,7 @@
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
       <c r="J143" s="2">
-        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra — treba "&amp;L143,"✓ ispravan")))))</f>
+        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra - treba "&amp;L143,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K143">
@@ -19309,7 +19309,7 @@
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
       <c r="J144" s="2">
-        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra — treba "&amp;L144,"✓ ispravan")))))</f>
+        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra - treba "&amp;L144,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K144">
@@ -19343,7 +19343,7 @@
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
       <c r="J145" s="2">
-        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra — treba "&amp;L145,"✓ ispravan")))))</f>
+        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra - treba "&amp;L145,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K145">
@@ -19377,7 +19377,7 @@
       <c r="H146" s="2" t="n"/>
       <c r="I146" s="2" t="n"/>
       <c r="J146" s="2">
-        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra — treba "&amp;L146,"✓ ispravan")))))</f>
+        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra - treba "&amp;L146,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K146">
@@ -19411,7 +19411,7 @@
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="n"/>
       <c r="J147" s="2">
-        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra — treba "&amp;L147,"✓ ispravan")))))</f>
+        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra - treba "&amp;L147,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K147">
@@ -19445,7 +19445,7 @@
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="n"/>
       <c r="J148" s="2">
-        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra — treba "&amp;L148,"✓ ispravan")))))</f>
+        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra - treba "&amp;L148,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K148">
@@ -19479,7 +19479,7 @@
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="n"/>
       <c r="J149" s="2">
-        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra — treba "&amp;L149,"✓ ispravan")))))</f>
+        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra - treba "&amp;L149,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K149">
@@ -19513,7 +19513,7 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2">
-        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra — treba "&amp;L150,"✓ ispravan")))))</f>
+        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra - treba "&amp;L150,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K150">
@@ -19547,7 +19547,7 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2">
-        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra — treba "&amp;L151,"✓ ispravan")))))</f>
+        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra - treba "&amp;L151,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K151">
@@ -19581,7 +19581,7 @@
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="n"/>
       <c r="J152" s="2">
-        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra — treba "&amp;L152,"✓ ispravan")))))</f>
+        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra - treba "&amp;L152,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K152">
@@ -19615,7 +19615,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
       <c r="J153" s="2">
-        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra — treba "&amp;L153,"✓ ispravan")))))</f>
+        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra - treba "&amp;L153,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K153">
@@ -19649,7 +19649,7 @@
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
       <c r="J154" s="2">
-        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra — treba "&amp;L154,"✓ ispravan")))))</f>
+        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra - treba "&amp;L154,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K154">
@@ -19683,7 +19683,7 @@
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
       <c r="J155" s="2">
-        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra — treba "&amp;L155,"✓ ispravan")))))</f>
+        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra - treba "&amp;L155,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K155">
@@ -19717,7 +19717,7 @@
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
       <c r="J156" s="2">
-        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra — treba "&amp;L156,"✓ ispravan")))))</f>
+        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra - treba "&amp;L156,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K156">
@@ -19751,7 +19751,7 @@
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
       <c r="J157" s="2">
-        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra — treba "&amp;L157,"✓ ispravan")))))</f>
+        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra - treba "&amp;L157,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K157">
@@ -19785,7 +19785,7 @@
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="2" t="n"/>
       <c r="J158" s="2">
-        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra — treba "&amp;L158,"✓ ispravan")))))</f>
+        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra - treba "&amp;L158,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K158">
@@ -19819,7 +19819,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
       <c r="J159" s="2">
-        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra — treba "&amp;L159,"✓ ispravan")))))</f>
+        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra - treba "&amp;L159,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K159">
@@ -19853,7 +19853,7 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2">
-        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra — treba "&amp;L160,"✓ ispravan")))))</f>
+        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra - treba "&amp;L160,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K160">
@@ -19887,7 +19887,7 @@
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
       <c r="J161" s="2">
-        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra — treba "&amp;L161,"✓ ispravan")))))</f>
+        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra - treba "&amp;L161,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K161">
@@ -19921,7 +19921,7 @@
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
       <c r="J162" s="2">
-        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra — treba "&amp;L162,"✓ ispravan")))))</f>
+        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra - treba "&amp;L162,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K162">
@@ -19955,7 +19955,7 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
       <c r="J163" s="2">
-        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra — treba "&amp;L163,"✓ ispravan")))))</f>
+        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra - treba "&amp;L163,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K163">
@@ -19989,7 +19989,7 @@
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="2" t="n"/>
       <c r="J164" s="2">
-        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra — treba "&amp;L164,"✓ ispravan")))))</f>
+        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra - treba "&amp;L164,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K164">
@@ -20023,7 +20023,7 @@
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
       <c r="J165" s="2">
-        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra — treba "&amp;L165,"✓ ispravan")))))</f>
+        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra - treba "&amp;L165,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K165">
@@ -20057,7 +20057,7 @@
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="n"/>
       <c r="J166" s="2">
-        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra — treba "&amp;L166,"✓ ispravan")))))</f>
+        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra - treba "&amp;L166,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K166">
@@ -20091,7 +20091,7 @@
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
       <c r="J167" s="2">
-        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra — treba "&amp;L167,"✓ ispravan")))))</f>
+        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra - treba "&amp;L167,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K167">
@@ -20125,7 +20125,7 @@
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
       <c r="J168" s="2">
-        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra — treba "&amp;L168,"✓ ispravan")))))</f>
+        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra - treba "&amp;L168,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K168">
@@ -20159,7 +20159,7 @@
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="n"/>
       <c r="J169" s="2">
-        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra — treba "&amp;L169,"✓ ispravan")))))</f>
+        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra - treba "&amp;L169,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K169">
@@ -20193,7 +20193,7 @@
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
       <c r="J170" s="2">
-        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra — treba "&amp;L170,"✓ ispravan")))))</f>
+        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra - treba "&amp;L170,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K170">
@@ -20227,7 +20227,7 @@
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
       <c r="J171" s="2">
-        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra — treba "&amp;L171,"✓ ispravan")))))</f>
+        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra - treba "&amp;L171,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K171">
@@ -20261,7 +20261,7 @@
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
       <c r="J172" s="2">
-        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra — treba "&amp;L172,"✓ ispravan")))))</f>
+        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra - treba "&amp;L172,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K172">
@@ -20295,7 +20295,7 @@
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="n"/>
       <c r="J173" s="2">
-        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra — treba "&amp;L173,"✓ ispravan")))))</f>
+        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra - treba "&amp;L173,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K173">
@@ -20329,7 +20329,7 @@
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
       <c r="J174" s="2">
-        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra — treba "&amp;L174,"✓ ispravan")))))</f>
+        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra - treba "&amp;L174,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K174">
@@ -20363,7 +20363,7 @@
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
       <c r="J175" s="2">
-        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra — treba "&amp;L175,"✓ ispravan")))))</f>
+        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra - treba "&amp;L175,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K175">
@@ -20397,7 +20397,7 @@
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
       <c r="J176" s="2">
-        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra — treba "&amp;L176,"✓ ispravan")))))</f>
+        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra - treba "&amp;L176,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K176">
@@ -20431,7 +20431,7 @@
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
       <c r="J177" s="2">
-        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra — treba "&amp;L177,"✓ ispravan")))))</f>
+        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra - treba "&amp;L177,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K177">
@@ -20465,7 +20465,7 @@
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
       <c r="J178" s="2">
-        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra — treba "&amp;L178,"✓ ispravan")))))</f>
+        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra - treba "&amp;L178,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K178">
@@ -20499,7 +20499,7 @@
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="2" t="n"/>
       <c r="J179" s="2">
-        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra — treba "&amp;L179,"✓ ispravan")))))</f>
+        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra - treba "&amp;L179,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K179">
@@ -20533,7 +20533,7 @@
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
       <c r="J180" s="2">
-        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra — treba "&amp;L180,"✓ ispravan")))))</f>
+        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra - treba "&amp;L180,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K180">
@@ -20567,7 +20567,7 @@
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="2" t="n"/>
       <c r="J181" s="2">
-        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra — treba "&amp;L181,"✓ ispravan")))))</f>
+        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra - treba "&amp;L181,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K181">
@@ -20601,7 +20601,7 @@
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="n"/>
       <c r="J182" s="2">
-        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra — treba "&amp;L182,"✓ ispravan")))))</f>
+        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra - treba "&amp;L182,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K182">
@@ -20635,7 +20635,7 @@
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="2" t="n"/>
       <c r="J183" s="2">
-        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra — treba "&amp;L183,"✓ ispravan")))))</f>
+        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra - treba "&amp;L183,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K183">
@@ -20669,7 +20669,7 @@
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
       <c r="J184" s="2">
-        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra — treba "&amp;L184,"✓ ispravan")))))</f>
+        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra - treba "&amp;L184,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K184">
@@ -20703,7 +20703,7 @@
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="n"/>
       <c r="J185" s="2">
-        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra — treba "&amp;L185,"✓ ispravan")))))</f>
+        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra - treba "&amp;L185,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K185">
@@ -20737,7 +20737,7 @@
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="n"/>
       <c r="J186" s="2">
-        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra — treba "&amp;L186,"✓ ispravan")))))</f>
+        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra - treba "&amp;L186,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K186">
@@ -20771,7 +20771,7 @@
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="2" t="n"/>
       <c r="J187" s="2">
-        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra — treba "&amp;L187,"✓ ispravan")))))</f>
+        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra - treba "&amp;L187,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K187">
@@ -20805,7 +20805,7 @@
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
       <c r="J188" s="2">
-        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra — treba "&amp;L188,"✓ ispravan")))))</f>
+        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra - treba "&amp;L188,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K188">
@@ -20839,7 +20839,7 @@
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="n"/>
       <c r="J189" s="2">
-        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra — treba "&amp;L189,"✓ ispravan")))))</f>
+        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra - treba "&amp;L189,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K189">
@@ -20873,7 +20873,7 @@
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="2" t="n"/>
       <c r="J190" s="2">
-        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra — treba "&amp;L190,"✓ ispravan")))))</f>
+        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra - treba "&amp;L190,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K190">
@@ -20907,7 +20907,7 @@
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="n"/>
       <c r="J191" s="2">
-        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra — treba "&amp;L191,"✓ ispravan")))))</f>
+        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra - treba "&amp;L191,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K191">
@@ -20941,7 +20941,7 @@
       <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="n"/>
       <c r="J192" s="2">
-        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra — treba "&amp;L192,"✓ ispravan")))))</f>
+        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra - treba "&amp;L192,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K192">
@@ -20975,7 +20975,7 @@
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="n"/>
       <c r="J193" s="2">
-        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra — treba "&amp;L193,"✓ ispravan")))))</f>
+        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra - treba "&amp;L193,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K193">
@@ -21009,7 +21009,7 @@
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
       <c r="J194" s="2">
-        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra — treba "&amp;L194,"✓ ispravan")))))</f>
+        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra - treba "&amp;L194,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K194">
@@ -21043,7 +21043,7 @@
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="n"/>
       <c r="J195" s="2">
-        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra — treba "&amp;L195,"✓ ispravan")))))</f>
+        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra - treba "&amp;L195,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K195">
@@ -21077,7 +21077,7 @@
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
       <c r="J196" s="2">
-        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra — treba "&amp;L196,"✓ ispravan")))))</f>
+        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra - treba "&amp;L196,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K196">
@@ -21111,7 +21111,7 @@
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="n"/>
       <c r="J197" s="2">
-        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra — treba "&amp;L197,"✓ ispravan")))))</f>
+        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra - treba "&amp;L197,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K197">
@@ -21145,7 +21145,7 @@
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
       <c r="J198" s="2">
-        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra — treba "&amp;L198,"✓ ispravan")))))</f>
+        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra - treba "&amp;L198,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K198">
@@ -21179,7 +21179,7 @@
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="n"/>
       <c r="J199" s="2">
-        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra — treba "&amp;L199,"✓ ispravan")))))</f>
+        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra - treba "&amp;L199,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K199">
@@ -21213,7 +21213,7 @@
       <c r="H200" s="2" t="n"/>
       <c r="I200" s="2" t="n"/>
       <c r="J200" s="2">
-        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra — treba "&amp;L200,"✓ ispravan")))))</f>
+        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra - treba "&amp;L200,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K200">
@@ -21247,7 +21247,7 @@
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="n"/>
       <c r="J201" s="2">
-        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra — treba "&amp;L201,"✓ ispravan")))))</f>
+        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra - treba "&amp;L201,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K201">
@@ -21427,7 +21427,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2">
-        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra — treba "&amp;L2,"✓ ispravan")))))</f>
+        <f>IF(C2="","",IF(LEN(C2)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C2)&amp;")",IF(L2="","JMBG sadrži nešto što nije cifra",IF(N2="","Nepostojeći datum rođenja",IF(VALUE(MID(C2,13,1))&lt;&gt;L2,"Pogrešna kontrolna cifra - treba "&amp;L2,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K2">
@@ -21477,7 +21477,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2">
-        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra — treba "&amp;L3,"✓ ispravan")))))</f>
+        <f>IF(C3="","",IF(LEN(C3)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C3)&amp;")",IF(L3="","JMBG sadrži nešto što nije cifra",IF(N3="","Nepostojeći datum rođenja",IF(VALUE(MID(C3,13,1))&lt;&gt;L3,"Pogrešna kontrolna cifra - treba "&amp;L3,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K3">
@@ -21526,7 +21526,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2">
-        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra — treba "&amp;L4,"✓ ispravan")))))</f>
+        <f>IF(C4="","",IF(LEN(C4)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C4)&amp;")",IF(L4="","JMBG sadrži nešto što nije cifra",IF(N4="","Nepostojeći datum rođenja",IF(VALUE(MID(C4,13,1))&lt;&gt;L4,"Pogrešna kontrolna cifra - treba "&amp;L4,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K4">
@@ -21576,7 +21576,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2">
-        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra — treba "&amp;L5,"✓ ispravan")))))</f>
+        <f>IF(C5="","",IF(LEN(C5)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C5)&amp;")",IF(L5="","JMBG sadrži nešto što nije cifra",IF(N5="","Nepostojeći datum rođenja",IF(VALUE(MID(C5,13,1))&lt;&gt;L5,"Pogrešna kontrolna cifra - treba "&amp;L5,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K5">
@@ -21625,7 +21625,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2">
-        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra — treba "&amp;L6,"✓ ispravan")))))</f>
+        <f>IF(C6="","",IF(LEN(C6)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C6)&amp;")",IF(L6="","JMBG sadrži nešto što nije cifra",IF(N6="","Nepostojeći datum rođenja",IF(VALUE(MID(C6,13,1))&lt;&gt;L6,"Pogrešna kontrolna cifra - treba "&amp;L6,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K6">
@@ -21675,7 +21675,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2">
-        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra — treba "&amp;L7,"✓ ispravan")))))</f>
+        <f>IF(C7="","",IF(LEN(C7)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C7)&amp;")",IF(L7="","JMBG sadrži nešto što nije cifra",IF(N7="","Nepostojeći datum rođenja",IF(VALUE(MID(C7,13,1))&lt;&gt;L7,"Pogrešna kontrolna cifra - treba "&amp;L7,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K7">
@@ -21725,7 +21725,7 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2">
-        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra — treba "&amp;L8,"✓ ispravan")))))</f>
+        <f>IF(C8="","",IF(LEN(C8)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C8)&amp;")",IF(L8="","JMBG sadrži nešto što nije cifra",IF(N8="","Nepostojeći datum rođenja",IF(VALUE(MID(C8,13,1))&lt;&gt;L8,"Pogrešna kontrolna cifra - treba "&amp;L8,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K8">
@@ -21759,7 +21759,7 @@
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
       <c r="J9" s="2">
-        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra — treba "&amp;L9,"✓ ispravan")))))</f>
+        <f>IF(C9="","",IF(LEN(C9)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C9)&amp;")",IF(L9="","JMBG sadrži nešto što nije cifra",IF(N9="","Nepostojeći datum rođenja",IF(VALUE(MID(C9,13,1))&lt;&gt;L9,"Pogrešna kontrolna cifra - treba "&amp;L9,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K9">
@@ -21793,7 +21793,7 @@
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
       <c r="J10" s="2">
-        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra — treba "&amp;L10,"✓ ispravan")))))</f>
+        <f>IF(C10="","",IF(LEN(C10)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C10)&amp;")",IF(L10="","JMBG sadrži nešto što nije cifra",IF(N10="","Nepostojeći datum rođenja",IF(VALUE(MID(C10,13,1))&lt;&gt;L10,"Pogrešna kontrolna cifra - treba "&amp;L10,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K10">
@@ -21827,7 +21827,7 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2">
-        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra — treba "&amp;L11,"✓ ispravan")))))</f>
+        <f>IF(C11="","",IF(LEN(C11)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C11)&amp;")",IF(L11="","JMBG sadrži nešto što nije cifra",IF(N11="","Nepostojeći datum rođenja",IF(VALUE(MID(C11,13,1))&lt;&gt;L11,"Pogrešna kontrolna cifra - treba "&amp;L11,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K11">
@@ -21861,7 +21861,7 @@
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2">
-        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra — treba "&amp;L12,"✓ ispravan")))))</f>
+        <f>IF(C12="","",IF(LEN(C12)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C12)&amp;")",IF(L12="","JMBG sadrži nešto što nije cifra",IF(N12="","Nepostojeći datum rođenja",IF(VALUE(MID(C12,13,1))&lt;&gt;L12,"Pogrešna kontrolna cifra - treba "&amp;L12,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K12">
@@ -21895,7 +21895,7 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2">
-        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra — treba "&amp;L13,"✓ ispravan")))))</f>
+        <f>IF(C13="","",IF(LEN(C13)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C13)&amp;")",IF(L13="","JMBG sadrži nešto što nije cifra",IF(N13="","Nepostojeći datum rođenja",IF(VALUE(MID(C13,13,1))&lt;&gt;L13,"Pogrešna kontrolna cifra - treba "&amp;L13,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K13">
@@ -21929,7 +21929,7 @@
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2">
-        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra — treba "&amp;L14,"✓ ispravan")))))</f>
+        <f>IF(C14="","",IF(LEN(C14)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C14)&amp;")",IF(L14="","JMBG sadrži nešto što nije cifra",IF(N14="","Nepostojeći datum rođenja",IF(VALUE(MID(C14,13,1))&lt;&gt;L14,"Pogrešna kontrolna cifra - treba "&amp;L14,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K14">
@@ -21963,7 +21963,7 @@
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
       <c r="J15" s="2">
-        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra — treba "&amp;L15,"✓ ispravan")))))</f>
+        <f>IF(C15="","",IF(LEN(C15)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C15)&amp;")",IF(L15="","JMBG sadrži nešto što nije cifra",IF(N15="","Nepostojeći datum rođenja",IF(VALUE(MID(C15,13,1))&lt;&gt;L15,"Pogrešna kontrolna cifra - treba "&amp;L15,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K15">
@@ -21997,7 +21997,7 @@
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2">
-        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra — treba "&amp;L16,"✓ ispravan")))))</f>
+        <f>IF(C16="","",IF(LEN(C16)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C16)&amp;")",IF(L16="","JMBG sadrži nešto što nije cifra",IF(N16="","Nepostojeći datum rođenja",IF(VALUE(MID(C16,13,1))&lt;&gt;L16,"Pogrešna kontrolna cifra - treba "&amp;L16,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K16">
@@ -22031,7 +22031,7 @@
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
       <c r="J17" s="2">
-        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra — treba "&amp;L17,"✓ ispravan")))))</f>
+        <f>IF(C17="","",IF(LEN(C17)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C17)&amp;")",IF(L17="","JMBG sadrži nešto što nije cifra",IF(N17="","Nepostojeći datum rođenja",IF(VALUE(MID(C17,13,1))&lt;&gt;L17,"Pogrešna kontrolna cifra - treba "&amp;L17,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K17">
@@ -22065,7 +22065,7 @@
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2">
-        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra — treba "&amp;L18,"✓ ispravan")))))</f>
+        <f>IF(C18="","",IF(LEN(C18)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C18)&amp;")",IF(L18="","JMBG sadrži nešto što nije cifra",IF(N18="","Nepostojeći datum rođenja",IF(VALUE(MID(C18,13,1))&lt;&gt;L18,"Pogrešna kontrolna cifra - treba "&amp;L18,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K18">
@@ -22099,7 +22099,7 @@
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
       <c r="J19" s="2">
-        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra — treba "&amp;L19,"✓ ispravan")))))</f>
+        <f>IF(C19="","",IF(LEN(C19)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C19)&amp;")",IF(L19="","JMBG sadrži nešto što nije cifra",IF(N19="","Nepostojeći datum rođenja",IF(VALUE(MID(C19,13,1))&lt;&gt;L19,"Pogrešna kontrolna cifra - treba "&amp;L19,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K19">
@@ -22133,7 +22133,7 @@
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2">
-        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra — treba "&amp;L20,"✓ ispravan")))))</f>
+        <f>IF(C20="","",IF(LEN(C20)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C20)&amp;")",IF(L20="","JMBG sadrži nešto što nije cifra",IF(N20="","Nepostojeći datum rođenja",IF(VALUE(MID(C20,13,1))&lt;&gt;L20,"Pogrešna kontrolna cifra - treba "&amp;L20,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K20">
@@ -22167,7 +22167,7 @@
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2">
-        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra — treba "&amp;L21,"✓ ispravan")))))</f>
+        <f>IF(C21="","",IF(LEN(C21)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C21)&amp;")",IF(L21="","JMBG sadrži nešto što nije cifra",IF(N21="","Nepostojeći datum rođenja",IF(VALUE(MID(C21,13,1))&lt;&gt;L21,"Pogrešna kontrolna cifra - treba "&amp;L21,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K21">
@@ -22201,7 +22201,7 @@
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2">
-        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra — treba "&amp;L22,"✓ ispravan")))))</f>
+        <f>IF(C22="","",IF(LEN(C22)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C22)&amp;")",IF(L22="","JMBG sadrži nešto što nije cifra",IF(N22="","Nepostojeći datum rođenja",IF(VALUE(MID(C22,13,1))&lt;&gt;L22,"Pogrešna kontrolna cifra - treba "&amp;L22,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K22">
@@ -22235,7 +22235,7 @@
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2">
-        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra — treba "&amp;L23,"✓ ispravan")))))</f>
+        <f>IF(C23="","",IF(LEN(C23)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C23)&amp;")",IF(L23="","JMBG sadrži nešto što nije cifra",IF(N23="","Nepostojeći datum rođenja",IF(VALUE(MID(C23,13,1))&lt;&gt;L23,"Pogrešna kontrolna cifra - treba "&amp;L23,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K23">
@@ -22269,7 +22269,7 @@
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2">
-        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra — treba "&amp;L24,"✓ ispravan")))))</f>
+        <f>IF(C24="","",IF(LEN(C24)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C24)&amp;")",IF(L24="","JMBG sadrži nešto što nije cifra",IF(N24="","Nepostojeći datum rođenja",IF(VALUE(MID(C24,13,1))&lt;&gt;L24,"Pogrešna kontrolna cifra - treba "&amp;L24,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K24">
@@ -22303,7 +22303,7 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2">
-        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra — treba "&amp;L25,"✓ ispravan")))))</f>
+        <f>IF(C25="","",IF(LEN(C25)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C25)&amp;")",IF(L25="","JMBG sadrži nešto što nije cifra",IF(N25="","Nepostojeći datum rođenja",IF(VALUE(MID(C25,13,1))&lt;&gt;L25,"Pogrešna kontrolna cifra - treba "&amp;L25,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K25">
@@ -22337,7 +22337,7 @@
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2">
-        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra — treba "&amp;L26,"✓ ispravan")))))</f>
+        <f>IF(C26="","",IF(LEN(C26)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C26)&amp;")",IF(L26="","JMBG sadrži nešto što nije cifra",IF(N26="","Nepostojeći datum rođenja",IF(VALUE(MID(C26,13,1))&lt;&gt;L26,"Pogrešna kontrolna cifra - treba "&amp;L26,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K26">
@@ -22371,7 +22371,7 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2">
-        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra — treba "&amp;L27,"✓ ispravan")))))</f>
+        <f>IF(C27="","",IF(LEN(C27)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C27)&amp;")",IF(L27="","JMBG sadrži nešto što nije cifra",IF(N27="","Nepostojeći datum rođenja",IF(VALUE(MID(C27,13,1))&lt;&gt;L27,"Pogrešna kontrolna cifra - treba "&amp;L27,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K27">
@@ -22405,7 +22405,7 @@
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2">
-        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra — treba "&amp;L28,"✓ ispravan")))))</f>
+        <f>IF(C28="","",IF(LEN(C28)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C28)&amp;")",IF(L28="","JMBG sadrži nešto što nije cifra",IF(N28="","Nepostojeći datum rođenja",IF(VALUE(MID(C28,13,1))&lt;&gt;L28,"Pogrešna kontrolna cifra - treba "&amp;L28,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K28">
@@ -22439,7 +22439,7 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2">
-        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra — treba "&amp;L29,"✓ ispravan")))))</f>
+        <f>IF(C29="","",IF(LEN(C29)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C29)&amp;")",IF(L29="","JMBG sadrži nešto što nije cifra",IF(N29="","Nepostojeći datum rođenja",IF(VALUE(MID(C29,13,1))&lt;&gt;L29,"Pogrešna kontrolna cifra - treba "&amp;L29,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K29">
@@ -22473,7 +22473,7 @@
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2">
-        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra — treba "&amp;L30,"✓ ispravan")))))</f>
+        <f>IF(C30="","",IF(LEN(C30)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C30)&amp;")",IF(L30="","JMBG sadrži nešto što nije cifra",IF(N30="","Nepostojeći datum rođenja",IF(VALUE(MID(C30,13,1))&lt;&gt;L30,"Pogrešna kontrolna cifra - treba "&amp;L30,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K30">
@@ -22507,7 +22507,7 @@
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
       <c r="J31" s="2">
-        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra — treba "&amp;L31,"✓ ispravan")))))</f>
+        <f>IF(C31="","",IF(LEN(C31)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C31)&amp;")",IF(L31="","JMBG sadrži nešto što nije cifra",IF(N31="","Nepostojeći datum rođenja",IF(VALUE(MID(C31,13,1))&lt;&gt;L31,"Pogrešna kontrolna cifra - treba "&amp;L31,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K31">
@@ -22541,7 +22541,7 @@
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
       <c r="J32" s="2">
-        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra — treba "&amp;L32,"✓ ispravan")))))</f>
+        <f>IF(C32="","",IF(LEN(C32)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C32)&amp;")",IF(L32="","JMBG sadrži nešto što nije cifra",IF(N32="","Nepostojeći datum rođenja",IF(VALUE(MID(C32,13,1))&lt;&gt;L32,"Pogrešna kontrolna cifra - treba "&amp;L32,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K32">
@@ -22575,7 +22575,7 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
       <c r="J33" s="2">
-        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra — treba "&amp;L33,"✓ ispravan")))))</f>
+        <f>IF(C33="","",IF(LEN(C33)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C33)&amp;")",IF(L33="","JMBG sadrži nešto što nije cifra",IF(N33="","Nepostojeći datum rođenja",IF(VALUE(MID(C33,13,1))&lt;&gt;L33,"Pogrešna kontrolna cifra - treba "&amp;L33,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K33">
@@ -22609,7 +22609,7 @@
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
       <c r="J34" s="2">
-        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra — treba "&amp;L34,"✓ ispravan")))))</f>
+        <f>IF(C34="","",IF(LEN(C34)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C34)&amp;")",IF(L34="","JMBG sadrži nešto što nije cifra",IF(N34="","Nepostojeći datum rođenja",IF(VALUE(MID(C34,13,1))&lt;&gt;L34,"Pogrešna kontrolna cifra - treba "&amp;L34,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K34">
@@ -22643,7 +22643,7 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2">
-        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra — treba "&amp;L35,"✓ ispravan")))))</f>
+        <f>IF(C35="","",IF(LEN(C35)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C35)&amp;")",IF(L35="","JMBG sadrži nešto što nije cifra",IF(N35="","Nepostojeći datum rođenja",IF(VALUE(MID(C35,13,1))&lt;&gt;L35,"Pogrešna kontrolna cifra - treba "&amp;L35,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K35">
@@ -22677,7 +22677,7 @@
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2">
-        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra — treba "&amp;L36,"✓ ispravan")))))</f>
+        <f>IF(C36="","",IF(LEN(C36)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C36)&amp;")",IF(L36="","JMBG sadrži nešto što nije cifra",IF(N36="","Nepostojeći datum rođenja",IF(VALUE(MID(C36,13,1))&lt;&gt;L36,"Pogrešna kontrolna cifra - treba "&amp;L36,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K36">
@@ -22711,7 +22711,7 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2">
-        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra — treba "&amp;L37,"✓ ispravan")))))</f>
+        <f>IF(C37="","",IF(LEN(C37)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C37)&amp;")",IF(L37="","JMBG sadrži nešto što nije cifra",IF(N37="","Nepostojeći datum rođenja",IF(VALUE(MID(C37,13,1))&lt;&gt;L37,"Pogrešna kontrolna cifra - treba "&amp;L37,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K37">
@@ -22745,7 +22745,7 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2">
-        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra — treba "&amp;L38,"✓ ispravan")))))</f>
+        <f>IF(C38="","",IF(LEN(C38)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C38)&amp;")",IF(L38="","JMBG sadrži nešto što nije cifra",IF(N38="","Nepostojeći datum rođenja",IF(VALUE(MID(C38,13,1))&lt;&gt;L38,"Pogrešna kontrolna cifra - treba "&amp;L38,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K38">
@@ -22779,7 +22779,7 @@
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2">
-        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra — treba "&amp;L39,"✓ ispravan")))))</f>
+        <f>IF(C39="","",IF(LEN(C39)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C39)&amp;")",IF(L39="","JMBG sadrži nešto što nije cifra",IF(N39="","Nepostojeći datum rođenja",IF(VALUE(MID(C39,13,1))&lt;&gt;L39,"Pogrešna kontrolna cifra - treba "&amp;L39,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K39">
@@ -22813,7 +22813,7 @@
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2">
-        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra — treba "&amp;L40,"✓ ispravan")))))</f>
+        <f>IF(C40="","",IF(LEN(C40)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C40)&amp;")",IF(L40="","JMBG sadrži nešto što nije cifra",IF(N40="","Nepostojeći datum rođenja",IF(VALUE(MID(C40,13,1))&lt;&gt;L40,"Pogrešna kontrolna cifra - treba "&amp;L40,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K40">
@@ -22847,7 +22847,7 @@
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2">
-        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra — treba "&amp;L41,"✓ ispravan")))))</f>
+        <f>IF(C41="","",IF(LEN(C41)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C41)&amp;")",IF(L41="","JMBG sadrži nešto što nije cifra",IF(N41="","Nepostojeći datum rođenja",IF(VALUE(MID(C41,13,1))&lt;&gt;L41,"Pogrešna kontrolna cifra - treba "&amp;L41,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K41">
@@ -22881,7 +22881,7 @@
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2">
-        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra — treba "&amp;L42,"✓ ispravan")))))</f>
+        <f>IF(C42="","",IF(LEN(C42)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C42)&amp;")",IF(L42="","JMBG sadrži nešto što nije cifra",IF(N42="","Nepostojeći datum rođenja",IF(VALUE(MID(C42,13,1))&lt;&gt;L42,"Pogrešna kontrolna cifra - treba "&amp;L42,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K42">
@@ -22915,7 +22915,7 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2">
-        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra — treba "&amp;L43,"✓ ispravan")))))</f>
+        <f>IF(C43="","",IF(LEN(C43)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C43)&amp;")",IF(L43="","JMBG sadrži nešto što nije cifra",IF(N43="","Nepostojeći datum rođenja",IF(VALUE(MID(C43,13,1))&lt;&gt;L43,"Pogrešna kontrolna cifra - treba "&amp;L43,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K43">
@@ -22949,7 +22949,7 @@
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2">
-        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra — treba "&amp;L44,"✓ ispravan")))))</f>
+        <f>IF(C44="","",IF(LEN(C44)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C44)&amp;")",IF(L44="","JMBG sadrži nešto što nije cifra",IF(N44="","Nepostojeći datum rođenja",IF(VALUE(MID(C44,13,1))&lt;&gt;L44,"Pogrešna kontrolna cifra - treba "&amp;L44,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K44">
@@ -22983,7 +22983,7 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2">
-        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra — treba "&amp;L45,"✓ ispravan")))))</f>
+        <f>IF(C45="","",IF(LEN(C45)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C45)&amp;")",IF(L45="","JMBG sadrži nešto što nije cifra",IF(N45="","Nepostojeći datum rođenja",IF(VALUE(MID(C45,13,1))&lt;&gt;L45,"Pogrešna kontrolna cifra - treba "&amp;L45,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K45">
@@ -23017,7 +23017,7 @@
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2">
-        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra — treba "&amp;L46,"✓ ispravan")))))</f>
+        <f>IF(C46="","",IF(LEN(C46)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C46)&amp;")",IF(L46="","JMBG sadrži nešto što nije cifra",IF(N46="","Nepostojeći datum rođenja",IF(VALUE(MID(C46,13,1))&lt;&gt;L46,"Pogrešna kontrolna cifra - treba "&amp;L46,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K46">
@@ -23051,7 +23051,7 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2">
-        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra — treba "&amp;L47,"✓ ispravan")))))</f>
+        <f>IF(C47="","",IF(LEN(C47)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C47)&amp;")",IF(L47="","JMBG sadrži nešto što nije cifra",IF(N47="","Nepostojeći datum rođenja",IF(VALUE(MID(C47,13,1))&lt;&gt;L47,"Pogrešna kontrolna cifra - treba "&amp;L47,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K47">
@@ -23085,7 +23085,7 @@
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2">
-        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra — treba "&amp;L48,"✓ ispravan")))))</f>
+        <f>IF(C48="","",IF(LEN(C48)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C48)&amp;")",IF(L48="","JMBG sadrži nešto što nije cifra",IF(N48="","Nepostojeći datum rođenja",IF(VALUE(MID(C48,13,1))&lt;&gt;L48,"Pogrešna kontrolna cifra - treba "&amp;L48,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K48">
@@ -23119,7 +23119,7 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2">
-        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra — treba "&amp;L49,"✓ ispravan")))))</f>
+        <f>IF(C49="","",IF(LEN(C49)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C49)&amp;")",IF(L49="","JMBG sadrži nešto što nije cifra",IF(N49="","Nepostojeći datum rođenja",IF(VALUE(MID(C49,13,1))&lt;&gt;L49,"Pogrešna kontrolna cifra - treba "&amp;L49,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K49">
@@ -23153,7 +23153,7 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2">
-        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra — treba "&amp;L50,"✓ ispravan")))))</f>
+        <f>IF(C50="","",IF(LEN(C50)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C50)&amp;")",IF(L50="","JMBG sadrži nešto što nije cifra",IF(N50="","Nepostojeći datum rođenja",IF(VALUE(MID(C50,13,1))&lt;&gt;L50,"Pogrešna kontrolna cifra - treba "&amp;L50,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K50">
@@ -23187,7 +23187,7 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2">
-        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra — treba "&amp;L51,"✓ ispravan")))))</f>
+        <f>IF(C51="","",IF(LEN(C51)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C51)&amp;")",IF(L51="","JMBG sadrži nešto što nije cifra",IF(N51="","Nepostojeći datum rođenja",IF(VALUE(MID(C51,13,1))&lt;&gt;L51,"Pogrešna kontrolna cifra - treba "&amp;L51,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K51">
@@ -23221,7 +23221,7 @@
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2">
-        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra — treba "&amp;L52,"✓ ispravan")))))</f>
+        <f>IF(C52="","",IF(LEN(C52)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C52)&amp;")",IF(L52="","JMBG sadrži nešto što nije cifra",IF(N52="","Nepostojeći datum rođenja",IF(VALUE(MID(C52,13,1))&lt;&gt;L52,"Pogrešna kontrolna cifra - treba "&amp;L52,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K52">
@@ -23255,7 +23255,7 @@
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2">
-        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra — treba "&amp;L53,"✓ ispravan")))))</f>
+        <f>IF(C53="","",IF(LEN(C53)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C53)&amp;")",IF(L53="","JMBG sadrži nešto što nije cifra",IF(N53="","Nepostojeći datum rođenja",IF(VALUE(MID(C53,13,1))&lt;&gt;L53,"Pogrešna kontrolna cifra - treba "&amp;L53,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K53">
@@ -23289,7 +23289,7 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
       <c r="J54" s="2">
-        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra — treba "&amp;L54,"✓ ispravan")))))</f>
+        <f>IF(C54="","",IF(LEN(C54)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C54)&amp;")",IF(L54="","JMBG sadrži nešto što nije cifra",IF(N54="","Nepostojeći datum rođenja",IF(VALUE(MID(C54,13,1))&lt;&gt;L54,"Pogrešna kontrolna cifra - treba "&amp;L54,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K54">
@@ -23323,7 +23323,7 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2">
-        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra — treba "&amp;L55,"✓ ispravan")))))</f>
+        <f>IF(C55="","",IF(LEN(C55)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C55)&amp;")",IF(L55="","JMBG sadrži nešto što nije cifra",IF(N55="","Nepostojeći datum rođenja",IF(VALUE(MID(C55,13,1))&lt;&gt;L55,"Pogrešna kontrolna cifra - treba "&amp;L55,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K55">
@@ -23357,7 +23357,7 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="n"/>
       <c r="J56" s="2">
-        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra — treba "&amp;L56,"✓ ispravan")))))</f>
+        <f>IF(C56="","",IF(LEN(C56)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C56)&amp;")",IF(L56="","JMBG sadrži nešto što nije cifra",IF(N56="","Nepostojeći datum rođenja",IF(VALUE(MID(C56,13,1))&lt;&gt;L56,"Pogrešna kontrolna cifra - treba "&amp;L56,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K56">
@@ -23391,7 +23391,7 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2">
-        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra — treba "&amp;L57,"✓ ispravan")))))</f>
+        <f>IF(C57="","",IF(LEN(C57)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C57)&amp;")",IF(L57="","JMBG sadrži nešto što nije cifra",IF(N57="","Nepostojeći datum rođenja",IF(VALUE(MID(C57,13,1))&lt;&gt;L57,"Pogrešna kontrolna cifra - treba "&amp;L57,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K57">
@@ -23425,7 +23425,7 @@
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2">
-        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra — treba "&amp;L58,"✓ ispravan")))))</f>
+        <f>IF(C58="","",IF(LEN(C58)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C58)&amp;")",IF(L58="","JMBG sadrži nešto što nije cifra",IF(N58="","Nepostojeći datum rođenja",IF(VALUE(MID(C58,13,1))&lt;&gt;L58,"Pogrešna kontrolna cifra - treba "&amp;L58,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K58">
@@ -23459,7 +23459,7 @@
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
       <c r="J59" s="2">
-        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra — treba "&amp;L59,"✓ ispravan")))))</f>
+        <f>IF(C59="","",IF(LEN(C59)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C59)&amp;")",IF(L59="","JMBG sadrži nešto što nije cifra",IF(N59="","Nepostojeći datum rođenja",IF(VALUE(MID(C59,13,1))&lt;&gt;L59,"Pogrešna kontrolna cifra - treba "&amp;L59,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K59">
@@ -23493,7 +23493,7 @@
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n"/>
       <c r="J60" s="2">
-        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra — treba "&amp;L60,"✓ ispravan")))))</f>
+        <f>IF(C60="","",IF(LEN(C60)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C60)&amp;")",IF(L60="","JMBG sadrži nešto što nije cifra",IF(N60="","Nepostojeći datum rođenja",IF(VALUE(MID(C60,13,1))&lt;&gt;L60,"Pogrešna kontrolna cifra - treba "&amp;L60,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K60">
@@ -23527,7 +23527,7 @@
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="n"/>
       <c r="J61" s="2">
-        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra — treba "&amp;L61,"✓ ispravan")))))</f>
+        <f>IF(C61="","",IF(LEN(C61)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C61)&amp;")",IF(L61="","JMBG sadrži nešto što nije cifra",IF(N61="","Nepostojeći datum rođenja",IF(VALUE(MID(C61,13,1))&lt;&gt;L61,"Pogrešna kontrolna cifra - treba "&amp;L61,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K61">
@@ -23561,7 +23561,7 @@
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="n"/>
       <c r="J62" s="2">
-        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra — treba "&amp;L62,"✓ ispravan")))))</f>
+        <f>IF(C62="","",IF(LEN(C62)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C62)&amp;")",IF(L62="","JMBG sadrži nešto što nije cifra",IF(N62="","Nepostojeći datum rođenja",IF(VALUE(MID(C62,13,1))&lt;&gt;L62,"Pogrešna kontrolna cifra - treba "&amp;L62,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K62">
@@ -23595,7 +23595,7 @@
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2">
-        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra — treba "&amp;L63,"✓ ispravan")))))</f>
+        <f>IF(C63="","",IF(LEN(C63)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C63)&amp;")",IF(L63="","JMBG sadrži nešto što nije cifra",IF(N63="","Nepostojeći datum rođenja",IF(VALUE(MID(C63,13,1))&lt;&gt;L63,"Pogrešna kontrolna cifra - treba "&amp;L63,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K63">
@@ -23629,7 +23629,7 @@
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2">
-        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra — treba "&amp;L64,"✓ ispravan")))))</f>
+        <f>IF(C64="","",IF(LEN(C64)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C64)&amp;")",IF(L64="","JMBG sadrži nešto što nije cifra",IF(N64="","Nepostojeći datum rođenja",IF(VALUE(MID(C64,13,1))&lt;&gt;L64,"Pogrešna kontrolna cifra - treba "&amp;L64,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K64">
@@ -23663,7 +23663,7 @@
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="n"/>
       <c r="J65" s="2">
-        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra — treba "&amp;L65,"✓ ispravan")))))</f>
+        <f>IF(C65="","",IF(LEN(C65)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C65)&amp;")",IF(L65="","JMBG sadrži nešto što nije cifra",IF(N65="","Nepostojeći datum rođenja",IF(VALUE(MID(C65,13,1))&lt;&gt;L65,"Pogrešna kontrolna cifra - treba "&amp;L65,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K65">
@@ -23697,7 +23697,7 @@
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2">
-        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra — treba "&amp;L66,"✓ ispravan")))))</f>
+        <f>IF(C66="","",IF(LEN(C66)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C66)&amp;")",IF(L66="","JMBG sadrži nešto što nije cifra",IF(N66="","Nepostojeći datum rođenja",IF(VALUE(MID(C66,13,1))&lt;&gt;L66,"Pogrešna kontrolna cifra - treba "&amp;L66,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K66">
@@ -23731,7 +23731,7 @@
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="n"/>
       <c r="J67" s="2">
-        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra — treba "&amp;L67,"✓ ispravan")))))</f>
+        <f>IF(C67="","",IF(LEN(C67)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C67)&amp;")",IF(L67="","JMBG sadrži nešto što nije cifra",IF(N67="","Nepostojeći datum rođenja",IF(VALUE(MID(C67,13,1))&lt;&gt;L67,"Pogrešna kontrolna cifra - treba "&amp;L67,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K67">
@@ -23765,7 +23765,7 @@
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="n"/>
       <c r="J68" s="2">
-        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra — treba "&amp;L68,"✓ ispravan")))))</f>
+        <f>IF(C68="","",IF(LEN(C68)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C68)&amp;")",IF(L68="","JMBG sadrži nešto što nije cifra",IF(N68="","Nepostojeći datum rođenja",IF(VALUE(MID(C68,13,1))&lt;&gt;L68,"Pogrešna kontrolna cifra - treba "&amp;L68,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K68">
@@ -23799,7 +23799,7 @@
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="n"/>
       <c r="J69" s="2">
-        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra — treba "&amp;L69,"✓ ispravan")))))</f>
+        <f>IF(C69="","",IF(LEN(C69)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C69)&amp;")",IF(L69="","JMBG sadrži nešto što nije cifra",IF(N69="","Nepostojeći datum rođenja",IF(VALUE(MID(C69,13,1))&lt;&gt;L69,"Pogrešna kontrolna cifra - treba "&amp;L69,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K69">
@@ -23833,7 +23833,7 @@
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2">
-        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra — treba "&amp;L70,"✓ ispravan")))))</f>
+        <f>IF(C70="","",IF(LEN(C70)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C70)&amp;")",IF(L70="","JMBG sadrži nešto što nije cifra",IF(N70="","Nepostojeći datum rođenja",IF(VALUE(MID(C70,13,1))&lt;&gt;L70,"Pogrešna kontrolna cifra - treba "&amp;L70,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K70">
@@ -23867,7 +23867,7 @@
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="n"/>
       <c r="J71" s="2">
-        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra — treba "&amp;L71,"✓ ispravan")))))</f>
+        <f>IF(C71="","",IF(LEN(C71)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C71)&amp;")",IF(L71="","JMBG sadrži nešto što nije cifra",IF(N71="","Nepostojeći datum rođenja",IF(VALUE(MID(C71,13,1))&lt;&gt;L71,"Pogrešna kontrolna cifra - treba "&amp;L71,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K71">
@@ -23901,7 +23901,7 @@
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="n"/>
       <c r="J72" s="2">
-        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra — treba "&amp;L72,"✓ ispravan")))))</f>
+        <f>IF(C72="","",IF(LEN(C72)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C72)&amp;")",IF(L72="","JMBG sadrži nešto što nije cifra",IF(N72="","Nepostojeći datum rođenja",IF(VALUE(MID(C72,13,1))&lt;&gt;L72,"Pogrešna kontrolna cifra - treba "&amp;L72,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K72">
@@ -23935,7 +23935,7 @@
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="n"/>
       <c r="J73" s="2">
-        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra — treba "&amp;L73,"✓ ispravan")))))</f>
+        <f>IF(C73="","",IF(LEN(C73)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C73)&amp;")",IF(L73="","JMBG sadrži nešto što nije cifra",IF(N73="","Nepostojeći datum rođenja",IF(VALUE(MID(C73,13,1))&lt;&gt;L73,"Pogrešna kontrolna cifra - treba "&amp;L73,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K73">
@@ -23969,7 +23969,7 @@
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="n"/>
       <c r="J74" s="2">
-        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra — treba "&amp;L74,"✓ ispravan")))))</f>
+        <f>IF(C74="","",IF(LEN(C74)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C74)&amp;")",IF(L74="","JMBG sadrži nešto što nije cifra",IF(N74="","Nepostojeći datum rođenja",IF(VALUE(MID(C74,13,1))&lt;&gt;L74,"Pogrešna kontrolna cifra - treba "&amp;L74,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K74">
@@ -24003,7 +24003,7 @@
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="n"/>
       <c r="J75" s="2">
-        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra — treba "&amp;L75,"✓ ispravan")))))</f>
+        <f>IF(C75="","",IF(LEN(C75)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C75)&amp;")",IF(L75="","JMBG sadrži nešto što nije cifra",IF(N75="","Nepostojeći datum rođenja",IF(VALUE(MID(C75,13,1))&lt;&gt;L75,"Pogrešna kontrolna cifra - treba "&amp;L75,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K75">
@@ -24037,7 +24037,7 @@
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="n"/>
       <c r="J76" s="2">
-        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra — treba "&amp;L76,"✓ ispravan")))))</f>
+        <f>IF(C76="","",IF(LEN(C76)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C76)&amp;")",IF(L76="","JMBG sadrži nešto što nije cifra",IF(N76="","Nepostojeći datum rođenja",IF(VALUE(MID(C76,13,1))&lt;&gt;L76,"Pogrešna kontrolna cifra - treba "&amp;L76,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K76">
@@ -24071,7 +24071,7 @@
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="n"/>
       <c r="J77" s="2">
-        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra — treba "&amp;L77,"✓ ispravan")))))</f>
+        <f>IF(C77="","",IF(LEN(C77)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C77)&amp;")",IF(L77="","JMBG sadrži nešto što nije cifra",IF(N77="","Nepostojeći datum rođenja",IF(VALUE(MID(C77,13,1))&lt;&gt;L77,"Pogrešna kontrolna cifra - treba "&amp;L77,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K77">
@@ -24105,7 +24105,7 @@
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="n"/>
       <c r="J78" s="2">
-        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra — treba "&amp;L78,"✓ ispravan")))))</f>
+        <f>IF(C78="","",IF(LEN(C78)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C78)&amp;")",IF(L78="","JMBG sadrži nešto što nije cifra",IF(N78="","Nepostojeći datum rođenja",IF(VALUE(MID(C78,13,1))&lt;&gt;L78,"Pogrešna kontrolna cifra - treba "&amp;L78,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K78">
@@ -24139,7 +24139,7 @@
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="n"/>
       <c r="J79" s="2">
-        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra — treba "&amp;L79,"✓ ispravan")))))</f>
+        <f>IF(C79="","",IF(LEN(C79)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C79)&amp;")",IF(L79="","JMBG sadrži nešto što nije cifra",IF(N79="","Nepostojeći datum rođenja",IF(VALUE(MID(C79,13,1))&lt;&gt;L79,"Pogrešna kontrolna cifra - treba "&amp;L79,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K79">
@@ -24173,7 +24173,7 @@
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="n"/>
       <c r="J80" s="2">
-        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra — treba "&amp;L80,"✓ ispravan")))))</f>
+        <f>IF(C80="","",IF(LEN(C80)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C80)&amp;")",IF(L80="","JMBG sadrži nešto što nije cifra",IF(N80="","Nepostojeći datum rođenja",IF(VALUE(MID(C80,13,1))&lt;&gt;L80,"Pogrešna kontrolna cifra - treba "&amp;L80,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K80">
@@ -24207,7 +24207,7 @@
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="n"/>
       <c r="J81" s="2">
-        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra — treba "&amp;L81,"✓ ispravan")))))</f>
+        <f>IF(C81="","",IF(LEN(C81)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C81)&amp;")",IF(L81="","JMBG sadrži nešto što nije cifra",IF(N81="","Nepostojeći datum rođenja",IF(VALUE(MID(C81,13,1))&lt;&gt;L81,"Pogrešna kontrolna cifra - treba "&amp;L81,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K81">
@@ -24241,7 +24241,7 @@
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="n"/>
       <c r="J82" s="2">
-        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra — treba "&amp;L82,"✓ ispravan")))))</f>
+        <f>IF(C82="","",IF(LEN(C82)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C82)&amp;")",IF(L82="","JMBG sadrži nešto što nije cifra",IF(N82="","Nepostojeći datum rođenja",IF(VALUE(MID(C82,13,1))&lt;&gt;L82,"Pogrešna kontrolna cifra - treba "&amp;L82,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K82">
@@ -24275,7 +24275,7 @@
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="n"/>
       <c r="J83" s="2">
-        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra — treba "&amp;L83,"✓ ispravan")))))</f>
+        <f>IF(C83="","",IF(LEN(C83)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C83)&amp;")",IF(L83="","JMBG sadrži nešto što nije cifra",IF(N83="","Nepostojeći datum rođenja",IF(VALUE(MID(C83,13,1))&lt;&gt;L83,"Pogrešna kontrolna cifra - treba "&amp;L83,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K83">
@@ -24309,7 +24309,7 @@
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="n"/>
       <c r="J84" s="2">
-        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra — treba "&amp;L84,"✓ ispravan")))))</f>
+        <f>IF(C84="","",IF(LEN(C84)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C84)&amp;")",IF(L84="","JMBG sadrži nešto što nije cifra",IF(N84="","Nepostojeći datum rođenja",IF(VALUE(MID(C84,13,1))&lt;&gt;L84,"Pogrešna kontrolna cifra - treba "&amp;L84,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K84">
@@ -24343,7 +24343,7 @@
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="n"/>
       <c r="J85" s="2">
-        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra — treba "&amp;L85,"✓ ispravan")))))</f>
+        <f>IF(C85="","",IF(LEN(C85)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C85)&amp;")",IF(L85="","JMBG sadrži nešto što nije cifra",IF(N85="","Nepostojeći datum rođenja",IF(VALUE(MID(C85,13,1))&lt;&gt;L85,"Pogrešna kontrolna cifra - treba "&amp;L85,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K85">
@@ -24377,7 +24377,7 @@
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="n"/>
       <c r="J86" s="2">
-        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra — treba "&amp;L86,"✓ ispravan")))))</f>
+        <f>IF(C86="","",IF(LEN(C86)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C86)&amp;")",IF(L86="","JMBG sadrži nešto što nije cifra",IF(N86="","Nepostojeći datum rođenja",IF(VALUE(MID(C86,13,1))&lt;&gt;L86,"Pogrešna kontrolna cifra - treba "&amp;L86,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K86">
@@ -24411,7 +24411,7 @@
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="n"/>
       <c r="J87" s="2">
-        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra — treba "&amp;L87,"✓ ispravan")))))</f>
+        <f>IF(C87="","",IF(LEN(C87)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C87)&amp;")",IF(L87="","JMBG sadrži nešto što nije cifra",IF(N87="","Nepostojeći datum rođenja",IF(VALUE(MID(C87,13,1))&lt;&gt;L87,"Pogrešna kontrolna cifra - treba "&amp;L87,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K87">
@@ -24445,7 +24445,7 @@
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="n"/>
       <c r="J88" s="2">
-        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra — treba "&amp;L88,"✓ ispravan")))))</f>
+        <f>IF(C88="","",IF(LEN(C88)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C88)&amp;")",IF(L88="","JMBG sadrži nešto što nije cifra",IF(N88="","Nepostojeći datum rođenja",IF(VALUE(MID(C88,13,1))&lt;&gt;L88,"Pogrešna kontrolna cifra - treba "&amp;L88,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K88">
@@ -24479,7 +24479,7 @@
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="n"/>
       <c r="J89" s="2">
-        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra — treba "&amp;L89,"✓ ispravan")))))</f>
+        <f>IF(C89="","",IF(LEN(C89)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C89)&amp;")",IF(L89="","JMBG sadrži nešto što nije cifra",IF(N89="","Nepostojeći datum rođenja",IF(VALUE(MID(C89,13,1))&lt;&gt;L89,"Pogrešna kontrolna cifra - treba "&amp;L89,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K89">
@@ -24513,7 +24513,7 @@
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="n"/>
       <c r="J90" s="2">
-        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra — treba "&amp;L90,"✓ ispravan")))))</f>
+        <f>IF(C90="","",IF(LEN(C90)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C90)&amp;")",IF(L90="","JMBG sadrži nešto što nije cifra",IF(N90="","Nepostojeći datum rođenja",IF(VALUE(MID(C90,13,1))&lt;&gt;L90,"Pogrešna kontrolna cifra - treba "&amp;L90,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K90">
@@ -24547,7 +24547,7 @@
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="n"/>
       <c r="J91" s="2">
-        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra — treba "&amp;L91,"✓ ispravan")))))</f>
+        <f>IF(C91="","",IF(LEN(C91)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C91)&amp;")",IF(L91="","JMBG sadrži nešto što nije cifra",IF(N91="","Nepostojeći datum rođenja",IF(VALUE(MID(C91,13,1))&lt;&gt;L91,"Pogrešna kontrolna cifra - treba "&amp;L91,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K91">
@@ -24581,7 +24581,7 @@
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="n"/>
       <c r="J92" s="2">
-        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra — treba "&amp;L92,"✓ ispravan")))))</f>
+        <f>IF(C92="","",IF(LEN(C92)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C92)&amp;")",IF(L92="","JMBG sadrži nešto što nije cifra",IF(N92="","Nepostojeći datum rođenja",IF(VALUE(MID(C92,13,1))&lt;&gt;L92,"Pogrešna kontrolna cifra - treba "&amp;L92,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K92">
@@ -24615,7 +24615,7 @@
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="n"/>
       <c r="J93" s="2">
-        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra — treba "&amp;L93,"✓ ispravan")))))</f>
+        <f>IF(C93="","",IF(LEN(C93)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C93)&amp;")",IF(L93="","JMBG sadrži nešto što nije cifra",IF(N93="","Nepostojeći datum rođenja",IF(VALUE(MID(C93,13,1))&lt;&gt;L93,"Pogrešna kontrolna cifra - treba "&amp;L93,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K93">
@@ -24649,7 +24649,7 @@
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="n"/>
       <c r="J94" s="2">
-        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra — treba "&amp;L94,"✓ ispravan")))))</f>
+        <f>IF(C94="","",IF(LEN(C94)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C94)&amp;")",IF(L94="","JMBG sadrži nešto što nije cifra",IF(N94="","Nepostojeći datum rođenja",IF(VALUE(MID(C94,13,1))&lt;&gt;L94,"Pogrešna kontrolna cifra - treba "&amp;L94,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K94">
@@ -24683,7 +24683,7 @@
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="n"/>
       <c r="J95" s="2">
-        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra — treba "&amp;L95,"✓ ispravan")))))</f>
+        <f>IF(C95="","",IF(LEN(C95)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C95)&amp;")",IF(L95="","JMBG sadrži nešto što nije cifra",IF(N95="","Nepostojeći datum rođenja",IF(VALUE(MID(C95,13,1))&lt;&gt;L95,"Pogrešna kontrolna cifra - treba "&amp;L95,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K95">
@@ -24717,7 +24717,7 @@
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="n"/>
       <c r="J96" s="2">
-        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra — treba "&amp;L96,"✓ ispravan")))))</f>
+        <f>IF(C96="","",IF(LEN(C96)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C96)&amp;")",IF(L96="","JMBG sadrži nešto što nije cifra",IF(N96="","Nepostojeći datum rođenja",IF(VALUE(MID(C96,13,1))&lt;&gt;L96,"Pogrešna kontrolna cifra - treba "&amp;L96,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K96">
@@ -24751,7 +24751,7 @@
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="n"/>
       <c r="J97" s="2">
-        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra — treba "&amp;L97,"✓ ispravan")))))</f>
+        <f>IF(C97="","",IF(LEN(C97)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C97)&amp;")",IF(L97="","JMBG sadrži nešto što nije cifra",IF(N97="","Nepostojeći datum rođenja",IF(VALUE(MID(C97,13,1))&lt;&gt;L97,"Pogrešna kontrolna cifra - treba "&amp;L97,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K97">
@@ -24785,7 +24785,7 @@
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="n"/>
       <c r="J98" s="2">
-        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra — treba "&amp;L98,"✓ ispravan")))))</f>
+        <f>IF(C98="","",IF(LEN(C98)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C98)&amp;")",IF(L98="","JMBG sadrži nešto što nije cifra",IF(N98="","Nepostojeći datum rođenja",IF(VALUE(MID(C98,13,1))&lt;&gt;L98,"Pogrešna kontrolna cifra - treba "&amp;L98,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K98">
@@ -24819,7 +24819,7 @@
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="n"/>
       <c r="J99" s="2">
-        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra — treba "&amp;L99,"✓ ispravan")))))</f>
+        <f>IF(C99="","",IF(LEN(C99)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C99)&amp;")",IF(L99="","JMBG sadrži nešto što nije cifra",IF(N99="","Nepostojeći datum rođenja",IF(VALUE(MID(C99,13,1))&lt;&gt;L99,"Pogrešna kontrolna cifra - treba "&amp;L99,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K99">
@@ -24853,7 +24853,7 @@
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="n"/>
       <c r="J100" s="2">
-        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra — treba "&amp;L100,"✓ ispravan")))))</f>
+        <f>IF(C100="","",IF(LEN(C100)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C100)&amp;")",IF(L100="","JMBG sadrži nešto što nije cifra",IF(N100="","Nepostojeći datum rođenja",IF(VALUE(MID(C100,13,1))&lt;&gt;L100,"Pogrešna kontrolna cifra - treba "&amp;L100,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K100">
@@ -24887,7 +24887,7 @@
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="n"/>
       <c r="J101" s="2">
-        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra — treba "&amp;L101,"✓ ispravan")))))</f>
+        <f>IF(C101="","",IF(LEN(C101)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C101)&amp;")",IF(L101="","JMBG sadrži nešto što nije cifra",IF(N101="","Nepostojeći datum rođenja",IF(VALUE(MID(C101,13,1))&lt;&gt;L101,"Pogrešna kontrolna cifra - treba "&amp;L101,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K101">
@@ -24921,7 +24921,7 @@
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="n"/>
       <c r="J102" s="2">
-        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra — treba "&amp;L102,"✓ ispravan")))))</f>
+        <f>IF(C102="","",IF(LEN(C102)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C102)&amp;")",IF(L102="","JMBG sadrži nešto što nije cifra",IF(N102="","Nepostojeći datum rođenja",IF(VALUE(MID(C102,13,1))&lt;&gt;L102,"Pogrešna kontrolna cifra - treba "&amp;L102,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K102">
@@ -24955,7 +24955,7 @@
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="n"/>
       <c r="J103" s="2">
-        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra — treba "&amp;L103,"✓ ispravan")))))</f>
+        <f>IF(C103="","",IF(LEN(C103)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C103)&amp;")",IF(L103="","JMBG sadrži nešto što nije cifra",IF(N103="","Nepostojeći datum rođenja",IF(VALUE(MID(C103,13,1))&lt;&gt;L103,"Pogrešna kontrolna cifra - treba "&amp;L103,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K103">
@@ -24989,7 +24989,7 @@
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="n"/>
       <c r="J104" s="2">
-        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra — treba "&amp;L104,"✓ ispravan")))))</f>
+        <f>IF(C104="","",IF(LEN(C104)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C104)&amp;")",IF(L104="","JMBG sadrži nešto što nije cifra",IF(N104="","Nepostojeći datum rođenja",IF(VALUE(MID(C104,13,1))&lt;&gt;L104,"Pogrešna kontrolna cifra - treba "&amp;L104,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K104">
@@ -25023,7 +25023,7 @@
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="n"/>
       <c r="J105" s="2">
-        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra — treba "&amp;L105,"✓ ispravan")))))</f>
+        <f>IF(C105="","",IF(LEN(C105)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C105)&amp;")",IF(L105="","JMBG sadrži nešto što nije cifra",IF(N105="","Nepostojeći datum rođenja",IF(VALUE(MID(C105,13,1))&lt;&gt;L105,"Pogrešna kontrolna cifra - treba "&amp;L105,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K105">
@@ -25057,7 +25057,7 @@
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="n"/>
       <c r="J106" s="2">
-        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra — treba "&amp;L106,"✓ ispravan")))))</f>
+        <f>IF(C106="","",IF(LEN(C106)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C106)&amp;")",IF(L106="","JMBG sadrži nešto što nije cifra",IF(N106="","Nepostojeći datum rođenja",IF(VALUE(MID(C106,13,1))&lt;&gt;L106,"Pogrešna kontrolna cifra - treba "&amp;L106,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K106">
@@ -25091,7 +25091,7 @@
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="n"/>
       <c r="J107" s="2">
-        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra — treba "&amp;L107,"✓ ispravan")))))</f>
+        <f>IF(C107="","",IF(LEN(C107)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C107)&amp;")",IF(L107="","JMBG sadrži nešto što nije cifra",IF(N107="","Nepostojeći datum rođenja",IF(VALUE(MID(C107,13,1))&lt;&gt;L107,"Pogrešna kontrolna cifra - treba "&amp;L107,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K107">
@@ -25125,7 +25125,7 @@
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="n"/>
       <c r="J108" s="2">
-        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra — treba "&amp;L108,"✓ ispravan")))))</f>
+        <f>IF(C108="","",IF(LEN(C108)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C108)&amp;")",IF(L108="","JMBG sadrži nešto što nije cifra",IF(N108="","Nepostojeći datum rođenja",IF(VALUE(MID(C108,13,1))&lt;&gt;L108,"Pogrešna kontrolna cifra - treba "&amp;L108,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K108">
@@ -25159,7 +25159,7 @@
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
       <c r="J109" s="2">
-        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra — treba "&amp;L109,"✓ ispravan")))))</f>
+        <f>IF(C109="","",IF(LEN(C109)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C109)&amp;")",IF(L109="","JMBG sadrži nešto što nije cifra",IF(N109="","Nepostojeći datum rođenja",IF(VALUE(MID(C109,13,1))&lt;&gt;L109,"Pogrešna kontrolna cifra - treba "&amp;L109,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K109">
@@ -25193,7 +25193,7 @@
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="n"/>
       <c r="J110" s="2">
-        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra — treba "&amp;L110,"✓ ispravan")))))</f>
+        <f>IF(C110="","",IF(LEN(C110)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C110)&amp;")",IF(L110="","JMBG sadrži nešto što nije cifra",IF(N110="","Nepostojeći datum rođenja",IF(VALUE(MID(C110,13,1))&lt;&gt;L110,"Pogrešna kontrolna cifra - treba "&amp;L110,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K110">
@@ -25227,7 +25227,7 @@
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="n"/>
       <c r="J111" s="2">
-        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra — treba "&amp;L111,"✓ ispravan")))))</f>
+        <f>IF(C111="","",IF(LEN(C111)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C111)&amp;")",IF(L111="","JMBG sadrži nešto što nije cifra",IF(N111="","Nepostojeći datum rođenja",IF(VALUE(MID(C111,13,1))&lt;&gt;L111,"Pogrešna kontrolna cifra - treba "&amp;L111,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K111">
@@ -25261,7 +25261,7 @@
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="n"/>
       <c r="J112" s="2">
-        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra — treba "&amp;L112,"✓ ispravan")))))</f>
+        <f>IF(C112="","",IF(LEN(C112)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C112)&amp;")",IF(L112="","JMBG sadrži nešto što nije cifra",IF(N112="","Nepostojeći datum rođenja",IF(VALUE(MID(C112,13,1))&lt;&gt;L112,"Pogrešna kontrolna cifra - treba "&amp;L112,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K112">
@@ -25295,7 +25295,7 @@
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="n"/>
       <c r="J113" s="2">
-        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra — treba "&amp;L113,"✓ ispravan")))))</f>
+        <f>IF(C113="","",IF(LEN(C113)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C113)&amp;")",IF(L113="","JMBG sadrži nešto što nije cifra",IF(N113="","Nepostojeći datum rođenja",IF(VALUE(MID(C113,13,1))&lt;&gt;L113,"Pogrešna kontrolna cifra - treba "&amp;L113,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K113">
@@ -25329,7 +25329,7 @@
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="n"/>
       <c r="J114" s="2">
-        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra — treba "&amp;L114,"✓ ispravan")))))</f>
+        <f>IF(C114="","",IF(LEN(C114)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C114)&amp;")",IF(L114="","JMBG sadrži nešto što nije cifra",IF(N114="","Nepostojeći datum rođenja",IF(VALUE(MID(C114,13,1))&lt;&gt;L114,"Pogrešna kontrolna cifra - treba "&amp;L114,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K114">
@@ -25363,7 +25363,7 @@
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="n"/>
       <c r="J115" s="2">
-        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra — treba "&amp;L115,"✓ ispravan")))))</f>
+        <f>IF(C115="","",IF(LEN(C115)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C115)&amp;")",IF(L115="","JMBG sadrži nešto što nije cifra",IF(N115="","Nepostojeći datum rođenja",IF(VALUE(MID(C115,13,1))&lt;&gt;L115,"Pogrešna kontrolna cifra - treba "&amp;L115,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K115">
@@ -25397,7 +25397,7 @@
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="n"/>
       <c r="J116" s="2">
-        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra — treba "&amp;L116,"✓ ispravan")))))</f>
+        <f>IF(C116="","",IF(LEN(C116)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C116)&amp;")",IF(L116="","JMBG sadrži nešto što nije cifra",IF(N116="","Nepostojeći datum rođenja",IF(VALUE(MID(C116,13,1))&lt;&gt;L116,"Pogrešna kontrolna cifra - treba "&amp;L116,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K116">
@@ -25431,7 +25431,7 @@
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="n"/>
       <c r="J117" s="2">
-        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra — treba "&amp;L117,"✓ ispravan")))))</f>
+        <f>IF(C117="","",IF(LEN(C117)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C117)&amp;")",IF(L117="","JMBG sadrži nešto što nije cifra",IF(N117="","Nepostojeći datum rođenja",IF(VALUE(MID(C117,13,1))&lt;&gt;L117,"Pogrešna kontrolna cifra - treba "&amp;L117,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K117">
@@ -25465,7 +25465,7 @@
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="n"/>
       <c r="J118" s="2">
-        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra — treba "&amp;L118,"✓ ispravan")))))</f>
+        <f>IF(C118="","",IF(LEN(C118)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C118)&amp;")",IF(L118="","JMBG sadrži nešto što nije cifra",IF(N118="","Nepostojeći datum rođenja",IF(VALUE(MID(C118,13,1))&lt;&gt;L118,"Pogrešna kontrolna cifra - treba "&amp;L118,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K118">
@@ -25499,7 +25499,7 @@
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="n"/>
       <c r="J119" s="2">
-        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra — treba "&amp;L119,"✓ ispravan")))))</f>
+        <f>IF(C119="","",IF(LEN(C119)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C119)&amp;")",IF(L119="","JMBG sadrži nešto što nije cifra",IF(N119="","Nepostojeći datum rođenja",IF(VALUE(MID(C119,13,1))&lt;&gt;L119,"Pogrešna kontrolna cifra - treba "&amp;L119,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K119">
@@ -25533,7 +25533,7 @@
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="n"/>
       <c r="J120" s="2">
-        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra — treba "&amp;L120,"✓ ispravan")))))</f>
+        <f>IF(C120="","",IF(LEN(C120)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C120)&amp;")",IF(L120="","JMBG sadrži nešto što nije cifra",IF(N120="","Nepostojeći datum rođenja",IF(VALUE(MID(C120,13,1))&lt;&gt;L120,"Pogrešna kontrolna cifra - treba "&amp;L120,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K120">
@@ -25567,7 +25567,7 @@
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="n"/>
       <c r="J121" s="2">
-        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra — treba "&amp;L121,"✓ ispravan")))))</f>
+        <f>IF(C121="","",IF(LEN(C121)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C121)&amp;")",IF(L121="","JMBG sadrži nešto što nije cifra",IF(N121="","Nepostojeći datum rođenja",IF(VALUE(MID(C121,13,1))&lt;&gt;L121,"Pogrešna kontrolna cifra - treba "&amp;L121,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K121">
@@ -25601,7 +25601,7 @@
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="n"/>
       <c r="J122" s="2">
-        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra — treba "&amp;L122,"✓ ispravan")))))</f>
+        <f>IF(C122="","",IF(LEN(C122)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C122)&amp;")",IF(L122="","JMBG sadrži nešto što nije cifra",IF(N122="","Nepostojeći datum rođenja",IF(VALUE(MID(C122,13,1))&lt;&gt;L122,"Pogrešna kontrolna cifra - treba "&amp;L122,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K122">
@@ -25635,7 +25635,7 @@
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="n"/>
       <c r="J123" s="2">
-        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra — treba "&amp;L123,"✓ ispravan")))))</f>
+        <f>IF(C123="","",IF(LEN(C123)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C123)&amp;")",IF(L123="","JMBG sadrži nešto što nije cifra",IF(N123="","Nepostojeći datum rođenja",IF(VALUE(MID(C123,13,1))&lt;&gt;L123,"Pogrešna kontrolna cifra - treba "&amp;L123,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K123">
@@ -25669,7 +25669,7 @@
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="n"/>
       <c r="J124" s="2">
-        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra — treba "&amp;L124,"✓ ispravan")))))</f>
+        <f>IF(C124="","",IF(LEN(C124)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C124)&amp;")",IF(L124="","JMBG sadrži nešto što nije cifra",IF(N124="","Nepostojeći datum rođenja",IF(VALUE(MID(C124,13,1))&lt;&gt;L124,"Pogrešna kontrolna cifra - treba "&amp;L124,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K124">
@@ -25703,7 +25703,7 @@
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="n"/>
       <c r="J125" s="2">
-        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra — treba "&amp;L125,"✓ ispravan")))))</f>
+        <f>IF(C125="","",IF(LEN(C125)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C125)&amp;")",IF(L125="","JMBG sadrži nešto što nije cifra",IF(N125="","Nepostojeći datum rođenja",IF(VALUE(MID(C125,13,1))&lt;&gt;L125,"Pogrešna kontrolna cifra - treba "&amp;L125,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K125">
@@ -25737,7 +25737,7 @@
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="n"/>
       <c r="J126" s="2">
-        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra — treba "&amp;L126,"✓ ispravan")))))</f>
+        <f>IF(C126="","",IF(LEN(C126)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C126)&amp;")",IF(L126="","JMBG sadrži nešto što nije cifra",IF(N126="","Nepostojeći datum rođenja",IF(VALUE(MID(C126,13,1))&lt;&gt;L126,"Pogrešna kontrolna cifra - treba "&amp;L126,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K126">
@@ -25771,7 +25771,7 @@
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="n"/>
       <c r="J127" s="2">
-        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra — treba "&amp;L127,"✓ ispravan")))))</f>
+        <f>IF(C127="","",IF(LEN(C127)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C127)&amp;")",IF(L127="","JMBG sadrži nešto što nije cifra",IF(N127="","Nepostojeći datum rođenja",IF(VALUE(MID(C127,13,1))&lt;&gt;L127,"Pogrešna kontrolna cifra - treba "&amp;L127,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K127">
@@ -25805,7 +25805,7 @@
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="2" t="n"/>
       <c r="J128" s="2">
-        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra — treba "&amp;L128,"✓ ispravan")))))</f>
+        <f>IF(C128="","",IF(LEN(C128)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C128)&amp;")",IF(L128="","JMBG sadrži nešto što nije cifra",IF(N128="","Nepostojeći datum rođenja",IF(VALUE(MID(C128,13,1))&lt;&gt;L128,"Pogrešna kontrolna cifra - treba "&amp;L128,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K128">
@@ -25839,7 +25839,7 @@
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="n"/>
       <c r="J129" s="2">
-        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra — treba "&amp;L129,"✓ ispravan")))))</f>
+        <f>IF(C129="","",IF(LEN(C129)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C129)&amp;")",IF(L129="","JMBG sadrži nešto što nije cifra",IF(N129="","Nepostojeći datum rođenja",IF(VALUE(MID(C129,13,1))&lt;&gt;L129,"Pogrešna kontrolna cifra - treba "&amp;L129,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K129">
@@ -25873,7 +25873,7 @@
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="n"/>
       <c r="J130" s="2">
-        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra — treba "&amp;L130,"✓ ispravan")))))</f>
+        <f>IF(C130="","",IF(LEN(C130)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C130)&amp;")",IF(L130="","JMBG sadrži nešto što nije cifra",IF(N130="","Nepostojeći datum rođenja",IF(VALUE(MID(C130,13,1))&lt;&gt;L130,"Pogrešna kontrolna cifra - treba "&amp;L130,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K130">
@@ -25907,7 +25907,7 @@
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
       <c r="J131" s="2">
-        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra — treba "&amp;L131,"✓ ispravan")))))</f>
+        <f>IF(C131="","",IF(LEN(C131)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C131)&amp;")",IF(L131="","JMBG sadrži nešto što nije cifra",IF(N131="","Nepostojeći datum rođenja",IF(VALUE(MID(C131,13,1))&lt;&gt;L131,"Pogrešna kontrolna cifra - treba "&amp;L131,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K131">
@@ -25941,7 +25941,7 @@
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="n"/>
       <c r="J132" s="2">
-        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra — treba "&amp;L132,"✓ ispravan")))))</f>
+        <f>IF(C132="","",IF(LEN(C132)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C132)&amp;")",IF(L132="","JMBG sadrži nešto što nije cifra",IF(N132="","Nepostojeći datum rođenja",IF(VALUE(MID(C132,13,1))&lt;&gt;L132,"Pogrešna kontrolna cifra - treba "&amp;L132,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K132">
@@ -25975,7 +25975,7 @@
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="n"/>
       <c r="J133" s="2">
-        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra — treba "&amp;L133,"✓ ispravan")))))</f>
+        <f>IF(C133="","",IF(LEN(C133)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C133)&amp;")",IF(L133="","JMBG sadrži nešto što nije cifra",IF(N133="","Nepostojeći datum rođenja",IF(VALUE(MID(C133,13,1))&lt;&gt;L133,"Pogrešna kontrolna cifra - treba "&amp;L133,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K133">
@@ -26009,7 +26009,7 @@
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="n"/>
       <c r="J134" s="2">
-        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra — treba "&amp;L134,"✓ ispravan")))))</f>
+        <f>IF(C134="","",IF(LEN(C134)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C134)&amp;")",IF(L134="","JMBG sadrži nešto što nije cifra",IF(N134="","Nepostojeći datum rođenja",IF(VALUE(MID(C134,13,1))&lt;&gt;L134,"Pogrešna kontrolna cifra - treba "&amp;L134,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K134">
@@ -26043,7 +26043,7 @@
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
       <c r="J135" s="2">
-        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra — treba "&amp;L135,"✓ ispravan")))))</f>
+        <f>IF(C135="","",IF(LEN(C135)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C135)&amp;")",IF(L135="","JMBG sadrži nešto što nije cifra",IF(N135="","Nepostojeći datum rođenja",IF(VALUE(MID(C135,13,1))&lt;&gt;L135,"Pogrešna kontrolna cifra - treba "&amp;L135,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K135">
@@ -26077,7 +26077,7 @@
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
       <c r="J136" s="2">
-        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra — treba "&amp;L136,"✓ ispravan")))))</f>
+        <f>IF(C136="","",IF(LEN(C136)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C136)&amp;")",IF(L136="","JMBG sadrži nešto što nije cifra",IF(N136="","Nepostojeći datum rođenja",IF(VALUE(MID(C136,13,1))&lt;&gt;L136,"Pogrešna kontrolna cifra - treba "&amp;L136,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K136">
@@ -26111,7 +26111,7 @@
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="n"/>
       <c r="J137" s="2">
-        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra — treba "&amp;L137,"✓ ispravan")))))</f>
+        <f>IF(C137="","",IF(LEN(C137)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C137)&amp;")",IF(L137="","JMBG sadrži nešto što nije cifra",IF(N137="","Nepostojeći datum rođenja",IF(VALUE(MID(C137,13,1))&lt;&gt;L137,"Pogrešna kontrolna cifra - treba "&amp;L137,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K137">
@@ -26145,7 +26145,7 @@
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="n"/>
       <c r="J138" s="2">
-        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra — treba "&amp;L138,"✓ ispravan")))))</f>
+        <f>IF(C138="","",IF(LEN(C138)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C138)&amp;")",IF(L138="","JMBG sadrži nešto što nije cifra",IF(N138="","Nepostojeći datum rođenja",IF(VALUE(MID(C138,13,1))&lt;&gt;L138,"Pogrešna kontrolna cifra - treba "&amp;L138,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K138">
@@ -26179,7 +26179,7 @@
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2">
-        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra — treba "&amp;L139,"✓ ispravan")))))</f>
+        <f>IF(C139="","",IF(LEN(C139)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C139)&amp;")",IF(L139="","JMBG sadrži nešto što nije cifra",IF(N139="","Nepostojeći datum rođenja",IF(VALUE(MID(C139,13,1))&lt;&gt;L139,"Pogrešna kontrolna cifra - treba "&amp;L139,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K139">
@@ -26213,7 +26213,7 @@
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
       <c r="J140" s="2">
-        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra — treba "&amp;L140,"✓ ispravan")))))</f>
+        <f>IF(C140="","",IF(LEN(C140)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C140)&amp;")",IF(L140="","JMBG sadrži nešto što nije cifra",IF(N140="","Nepostojeći datum rođenja",IF(VALUE(MID(C140,13,1))&lt;&gt;L140,"Pogrešna kontrolna cifra - treba "&amp;L140,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K140">
@@ -26247,7 +26247,7 @@
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
       <c r="J141" s="2">
-        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra — treba "&amp;L141,"✓ ispravan")))))</f>
+        <f>IF(C141="","",IF(LEN(C141)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C141)&amp;")",IF(L141="","JMBG sadrži nešto što nije cifra",IF(N141="","Nepostojeći datum rođenja",IF(VALUE(MID(C141,13,1))&lt;&gt;L141,"Pogrešna kontrolna cifra - treba "&amp;L141,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K141">
@@ -26281,7 +26281,7 @@
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="2" t="n"/>
       <c r="J142" s="2">
-        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra — treba "&amp;L142,"✓ ispravan")))))</f>
+        <f>IF(C142="","",IF(LEN(C142)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C142)&amp;")",IF(L142="","JMBG sadrži nešto što nije cifra",IF(N142="","Nepostojeći datum rođenja",IF(VALUE(MID(C142,13,1))&lt;&gt;L142,"Pogrešna kontrolna cifra - treba "&amp;L142,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K142">
@@ -26315,7 +26315,7 @@
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
       <c r="J143" s="2">
-        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra — treba "&amp;L143,"✓ ispravan")))))</f>
+        <f>IF(C143="","",IF(LEN(C143)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C143)&amp;")",IF(L143="","JMBG sadrži nešto što nije cifra",IF(N143="","Nepostojeći datum rođenja",IF(VALUE(MID(C143,13,1))&lt;&gt;L143,"Pogrešna kontrolna cifra - treba "&amp;L143,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K143">
@@ -26349,7 +26349,7 @@
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
       <c r="J144" s="2">
-        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra — treba "&amp;L144,"✓ ispravan")))))</f>
+        <f>IF(C144="","",IF(LEN(C144)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C144)&amp;")",IF(L144="","JMBG sadrži nešto što nije cifra",IF(N144="","Nepostojeći datum rođenja",IF(VALUE(MID(C144,13,1))&lt;&gt;L144,"Pogrešna kontrolna cifra - treba "&amp;L144,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K144">
@@ -26383,7 +26383,7 @@
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
       <c r="J145" s="2">
-        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra — treba "&amp;L145,"✓ ispravan")))))</f>
+        <f>IF(C145="","",IF(LEN(C145)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C145)&amp;")",IF(L145="","JMBG sadrži nešto što nije cifra",IF(N145="","Nepostojeći datum rođenja",IF(VALUE(MID(C145,13,1))&lt;&gt;L145,"Pogrešna kontrolna cifra - treba "&amp;L145,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K145">
@@ -26417,7 +26417,7 @@
       <c r="H146" s="2" t="n"/>
       <c r="I146" s="2" t="n"/>
       <c r="J146" s="2">
-        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra — treba "&amp;L146,"✓ ispravan")))))</f>
+        <f>IF(C146="","",IF(LEN(C146)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C146)&amp;")",IF(L146="","JMBG sadrži nešto što nije cifra",IF(N146="","Nepostojeći datum rođenja",IF(VALUE(MID(C146,13,1))&lt;&gt;L146,"Pogrešna kontrolna cifra - treba "&amp;L146,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K146">
@@ -26451,7 +26451,7 @@
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="n"/>
       <c r="J147" s="2">
-        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra — treba "&amp;L147,"✓ ispravan")))))</f>
+        <f>IF(C147="","",IF(LEN(C147)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C147)&amp;")",IF(L147="","JMBG sadrži nešto što nije cifra",IF(N147="","Nepostojeći datum rođenja",IF(VALUE(MID(C147,13,1))&lt;&gt;L147,"Pogrešna kontrolna cifra - treba "&amp;L147,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K147">
@@ -26485,7 +26485,7 @@
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="n"/>
       <c r="J148" s="2">
-        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra — treba "&amp;L148,"✓ ispravan")))))</f>
+        <f>IF(C148="","",IF(LEN(C148)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C148)&amp;")",IF(L148="","JMBG sadrži nešto što nije cifra",IF(N148="","Nepostojeći datum rođenja",IF(VALUE(MID(C148,13,1))&lt;&gt;L148,"Pogrešna kontrolna cifra - treba "&amp;L148,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K148">
@@ -26519,7 +26519,7 @@
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="n"/>
       <c r="J149" s="2">
-        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra — treba "&amp;L149,"✓ ispravan")))))</f>
+        <f>IF(C149="","",IF(LEN(C149)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C149)&amp;")",IF(L149="","JMBG sadrži nešto što nije cifra",IF(N149="","Nepostojeći datum rođenja",IF(VALUE(MID(C149,13,1))&lt;&gt;L149,"Pogrešna kontrolna cifra - treba "&amp;L149,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K149">
@@ -26553,7 +26553,7 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2">
-        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra — treba "&amp;L150,"✓ ispravan")))))</f>
+        <f>IF(C150="","",IF(LEN(C150)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C150)&amp;")",IF(L150="","JMBG sadrži nešto što nije cifra",IF(N150="","Nepostojeći datum rođenja",IF(VALUE(MID(C150,13,1))&lt;&gt;L150,"Pogrešna kontrolna cifra - treba "&amp;L150,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K150">
@@ -26587,7 +26587,7 @@
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="n"/>
       <c r="J151" s="2">
-        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra — treba "&amp;L151,"✓ ispravan")))))</f>
+        <f>IF(C151="","",IF(LEN(C151)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C151)&amp;")",IF(L151="","JMBG sadrži nešto što nije cifra",IF(N151="","Nepostojeći datum rođenja",IF(VALUE(MID(C151,13,1))&lt;&gt;L151,"Pogrešna kontrolna cifra - treba "&amp;L151,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K151">
@@ -26621,7 +26621,7 @@
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="n"/>
       <c r="J152" s="2">
-        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra — treba "&amp;L152,"✓ ispravan")))))</f>
+        <f>IF(C152="","",IF(LEN(C152)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C152)&amp;")",IF(L152="","JMBG sadrži nešto što nije cifra",IF(N152="","Nepostojeći datum rođenja",IF(VALUE(MID(C152,13,1))&lt;&gt;L152,"Pogrešna kontrolna cifra - treba "&amp;L152,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K152">
@@ -26655,7 +26655,7 @@
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="n"/>
       <c r="J153" s="2">
-        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra — treba "&amp;L153,"✓ ispravan")))))</f>
+        <f>IF(C153="","",IF(LEN(C153)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C153)&amp;")",IF(L153="","JMBG sadrži nešto što nije cifra",IF(N153="","Nepostojeći datum rođenja",IF(VALUE(MID(C153,13,1))&lt;&gt;L153,"Pogrešna kontrolna cifra - treba "&amp;L153,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K153">
@@ -26689,7 +26689,7 @@
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="n"/>
       <c r="J154" s="2">
-        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra — treba "&amp;L154,"✓ ispravan")))))</f>
+        <f>IF(C154="","",IF(LEN(C154)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C154)&amp;")",IF(L154="","JMBG sadrži nešto što nije cifra",IF(N154="","Nepostojeći datum rođenja",IF(VALUE(MID(C154,13,1))&lt;&gt;L154,"Pogrešna kontrolna cifra - treba "&amp;L154,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K154">
@@ -26723,7 +26723,7 @@
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="n"/>
       <c r="J155" s="2">
-        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra — treba "&amp;L155,"✓ ispravan")))))</f>
+        <f>IF(C155="","",IF(LEN(C155)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C155)&amp;")",IF(L155="","JMBG sadrži nešto što nije cifra",IF(N155="","Nepostojeći datum rođenja",IF(VALUE(MID(C155,13,1))&lt;&gt;L155,"Pogrešna kontrolna cifra - treba "&amp;L155,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K155">
@@ -26757,7 +26757,7 @@
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
       <c r="J156" s="2">
-        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra — treba "&amp;L156,"✓ ispravan")))))</f>
+        <f>IF(C156="","",IF(LEN(C156)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C156)&amp;")",IF(L156="","JMBG sadrži nešto što nije cifra",IF(N156="","Nepostojeći datum rođenja",IF(VALUE(MID(C156,13,1))&lt;&gt;L156,"Pogrešna kontrolna cifra - treba "&amp;L156,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K156">
@@ -26791,7 +26791,7 @@
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
       <c r="J157" s="2">
-        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra — treba "&amp;L157,"✓ ispravan")))))</f>
+        <f>IF(C157="","",IF(LEN(C157)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C157)&amp;")",IF(L157="","JMBG sadrži nešto što nije cifra",IF(N157="","Nepostojeći datum rođenja",IF(VALUE(MID(C157,13,1))&lt;&gt;L157,"Pogrešna kontrolna cifra - treba "&amp;L157,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K157">
@@ -26825,7 +26825,7 @@
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="2" t="n"/>
       <c r="J158" s="2">
-        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra — treba "&amp;L158,"✓ ispravan")))))</f>
+        <f>IF(C158="","",IF(LEN(C158)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C158)&amp;")",IF(L158="","JMBG sadrži nešto što nije cifra",IF(N158="","Nepostojeći datum rođenja",IF(VALUE(MID(C158,13,1))&lt;&gt;L158,"Pogrešna kontrolna cifra - treba "&amp;L158,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K158">
@@ -26859,7 +26859,7 @@
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="n"/>
       <c r="J159" s="2">
-        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra — treba "&amp;L159,"✓ ispravan")))))</f>
+        <f>IF(C159="","",IF(LEN(C159)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C159)&amp;")",IF(L159="","JMBG sadrži nešto što nije cifra",IF(N159="","Nepostojeći datum rođenja",IF(VALUE(MID(C159,13,1))&lt;&gt;L159,"Pogrešna kontrolna cifra - treba "&amp;L159,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K159">
@@ -26893,7 +26893,7 @@
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="n"/>
       <c r="J160" s="2">
-        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra — treba "&amp;L160,"✓ ispravan")))))</f>
+        <f>IF(C160="","",IF(LEN(C160)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C160)&amp;")",IF(L160="","JMBG sadrži nešto što nije cifra",IF(N160="","Nepostojeći datum rođenja",IF(VALUE(MID(C160,13,1))&lt;&gt;L160,"Pogrešna kontrolna cifra - treba "&amp;L160,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K160">
@@ -26927,7 +26927,7 @@
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="n"/>
       <c r="J161" s="2">
-        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra — treba "&amp;L161,"✓ ispravan")))))</f>
+        <f>IF(C161="","",IF(LEN(C161)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C161)&amp;")",IF(L161="","JMBG sadrži nešto što nije cifra",IF(N161="","Nepostojeći datum rođenja",IF(VALUE(MID(C161,13,1))&lt;&gt;L161,"Pogrešna kontrolna cifra - treba "&amp;L161,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K161">
@@ -26961,7 +26961,7 @@
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="n"/>
       <c r="J162" s="2">
-        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra — treba "&amp;L162,"✓ ispravan")))))</f>
+        <f>IF(C162="","",IF(LEN(C162)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C162)&amp;")",IF(L162="","JMBG sadrži nešto što nije cifra",IF(N162="","Nepostojeći datum rođenja",IF(VALUE(MID(C162,13,1))&lt;&gt;L162,"Pogrešna kontrolna cifra - treba "&amp;L162,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K162">
@@ -26995,7 +26995,7 @@
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="n"/>
       <c r="J163" s="2">
-        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra — treba "&amp;L163,"✓ ispravan")))))</f>
+        <f>IF(C163="","",IF(LEN(C163)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C163)&amp;")",IF(L163="","JMBG sadrži nešto što nije cifra",IF(N163="","Nepostojeći datum rođenja",IF(VALUE(MID(C163,13,1))&lt;&gt;L163,"Pogrešna kontrolna cifra - treba "&amp;L163,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K163">
@@ -27029,7 +27029,7 @@
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="2" t="n"/>
       <c r="J164" s="2">
-        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra — treba "&amp;L164,"✓ ispravan")))))</f>
+        <f>IF(C164="","",IF(LEN(C164)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C164)&amp;")",IF(L164="","JMBG sadrži nešto što nije cifra",IF(N164="","Nepostojeći datum rođenja",IF(VALUE(MID(C164,13,1))&lt;&gt;L164,"Pogrešna kontrolna cifra - treba "&amp;L164,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K164">
@@ -27063,7 +27063,7 @@
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="n"/>
       <c r="J165" s="2">
-        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra — treba "&amp;L165,"✓ ispravan")))))</f>
+        <f>IF(C165="","",IF(LEN(C165)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C165)&amp;")",IF(L165="","JMBG sadrži nešto što nije cifra",IF(N165="","Nepostojeći datum rođenja",IF(VALUE(MID(C165,13,1))&lt;&gt;L165,"Pogrešna kontrolna cifra - treba "&amp;L165,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K165">
@@ -27097,7 +27097,7 @@
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="n"/>
       <c r="J166" s="2">
-        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra — treba "&amp;L166,"✓ ispravan")))))</f>
+        <f>IF(C166="","",IF(LEN(C166)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C166)&amp;")",IF(L166="","JMBG sadrži nešto što nije cifra",IF(N166="","Nepostojeći datum rođenja",IF(VALUE(MID(C166,13,1))&lt;&gt;L166,"Pogrešna kontrolna cifra - treba "&amp;L166,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K166">
@@ -27131,7 +27131,7 @@
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="n"/>
       <c r="J167" s="2">
-        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra — treba "&amp;L167,"✓ ispravan")))))</f>
+        <f>IF(C167="","",IF(LEN(C167)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C167)&amp;")",IF(L167="","JMBG sadrži nešto što nije cifra",IF(N167="","Nepostojeći datum rođenja",IF(VALUE(MID(C167,13,1))&lt;&gt;L167,"Pogrešna kontrolna cifra - treba "&amp;L167,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K167">
@@ -27165,7 +27165,7 @@
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="n"/>
       <c r="J168" s="2">
-        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra — treba "&amp;L168,"✓ ispravan")))))</f>
+        <f>IF(C168="","",IF(LEN(C168)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C168)&amp;")",IF(L168="","JMBG sadrži nešto što nije cifra",IF(N168="","Nepostojeći datum rođenja",IF(VALUE(MID(C168,13,1))&lt;&gt;L168,"Pogrešna kontrolna cifra - treba "&amp;L168,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K168">
@@ -27199,7 +27199,7 @@
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="n"/>
       <c r="J169" s="2">
-        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra — treba "&amp;L169,"✓ ispravan")))))</f>
+        <f>IF(C169="","",IF(LEN(C169)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C169)&amp;")",IF(L169="","JMBG sadrži nešto što nije cifra",IF(N169="","Nepostojeći datum rođenja",IF(VALUE(MID(C169,13,1))&lt;&gt;L169,"Pogrešna kontrolna cifra - treba "&amp;L169,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K169">
@@ -27233,7 +27233,7 @@
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
       <c r="J170" s="2">
-        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra — treba "&amp;L170,"✓ ispravan")))))</f>
+        <f>IF(C170="","",IF(LEN(C170)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C170)&amp;")",IF(L170="","JMBG sadrži nešto što nije cifra",IF(N170="","Nepostojeći datum rođenja",IF(VALUE(MID(C170,13,1))&lt;&gt;L170,"Pogrešna kontrolna cifra - treba "&amp;L170,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K170">
@@ -27267,7 +27267,7 @@
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
       <c r="J171" s="2">
-        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra — treba "&amp;L171,"✓ ispravan")))))</f>
+        <f>IF(C171="","",IF(LEN(C171)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C171)&amp;")",IF(L171="","JMBG sadrži nešto što nije cifra",IF(N171="","Nepostojeći datum rođenja",IF(VALUE(MID(C171,13,1))&lt;&gt;L171,"Pogrešna kontrolna cifra - treba "&amp;L171,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K171">
@@ -27301,7 +27301,7 @@
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
       <c r="J172" s="2">
-        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra — treba "&amp;L172,"✓ ispravan")))))</f>
+        <f>IF(C172="","",IF(LEN(C172)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C172)&amp;")",IF(L172="","JMBG sadrži nešto što nije cifra",IF(N172="","Nepostojeći datum rođenja",IF(VALUE(MID(C172,13,1))&lt;&gt;L172,"Pogrešna kontrolna cifra - treba "&amp;L172,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K172">
@@ -27335,7 +27335,7 @@
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="n"/>
       <c r="J173" s="2">
-        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra — treba "&amp;L173,"✓ ispravan")))))</f>
+        <f>IF(C173="","",IF(LEN(C173)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C173)&amp;")",IF(L173="","JMBG sadrži nešto što nije cifra",IF(N173="","Nepostojeći datum rođenja",IF(VALUE(MID(C173,13,1))&lt;&gt;L173,"Pogrešna kontrolna cifra - treba "&amp;L173,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K173">
@@ -27369,7 +27369,7 @@
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="n"/>
       <c r="J174" s="2">
-        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra — treba "&amp;L174,"✓ ispravan")))))</f>
+        <f>IF(C174="","",IF(LEN(C174)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C174)&amp;")",IF(L174="","JMBG sadrži nešto što nije cifra",IF(N174="","Nepostojeći datum rođenja",IF(VALUE(MID(C174,13,1))&lt;&gt;L174,"Pogrešna kontrolna cifra - treba "&amp;L174,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K174">
@@ -27403,7 +27403,7 @@
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
       <c r="J175" s="2">
-        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra — treba "&amp;L175,"✓ ispravan")))))</f>
+        <f>IF(C175="","",IF(LEN(C175)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C175)&amp;")",IF(L175="","JMBG sadrži nešto što nije cifra",IF(N175="","Nepostojeći datum rođenja",IF(VALUE(MID(C175,13,1))&lt;&gt;L175,"Pogrešna kontrolna cifra - treba "&amp;L175,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K175">
@@ -27437,7 +27437,7 @@
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
       <c r="J176" s="2">
-        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra — treba "&amp;L176,"✓ ispravan")))))</f>
+        <f>IF(C176="","",IF(LEN(C176)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C176)&amp;")",IF(L176="","JMBG sadrži nešto što nije cifra",IF(N176="","Nepostojeći datum rođenja",IF(VALUE(MID(C176,13,1))&lt;&gt;L176,"Pogrešna kontrolna cifra - treba "&amp;L176,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K176">
@@ -27471,7 +27471,7 @@
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
       <c r="J177" s="2">
-        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra — treba "&amp;L177,"✓ ispravan")))))</f>
+        <f>IF(C177="","",IF(LEN(C177)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C177)&amp;")",IF(L177="","JMBG sadrži nešto što nije cifra",IF(N177="","Nepostojeći datum rođenja",IF(VALUE(MID(C177,13,1))&lt;&gt;L177,"Pogrešna kontrolna cifra - treba "&amp;L177,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K177">
@@ -27505,7 +27505,7 @@
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
       <c r="J178" s="2">
-        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra — treba "&amp;L178,"✓ ispravan")))))</f>
+        <f>IF(C178="","",IF(LEN(C178)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C178)&amp;")",IF(L178="","JMBG sadrži nešto što nije cifra",IF(N178="","Nepostojeći datum rođenja",IF(VALUE(MID(C178,13,1))&lt;&gt;L178,"Pogrešna kontrolna cifra - treba "&amp;L178,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K178">
@@ -27539,7 +27539,7 @@
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="2" t="n"/>
       <c r="J179" s="2">
-        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra — treba "&amp;L179,"✓ ispravan")))))</f>
+        <f>IF(C179="","",IF(LEN(C179)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C179)&amp;")",IF(L179="","JMBG sadrži nešto što nije cifra",IF(N179="","Nepostojeći datum rođenja",IF(VALUE(MID(C179,13,1))&lt;&gt;L179,"Pogrešna kontrolna cifra - treba "&amp;L179,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K179">
@@ -27573,7 +27573,7 @@
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
       <c r="J180" s="2">
-        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra — treba "&amp;L180,"✓ ispravan")))))</f>
+        <f>IF(C180="","",IF(LEN(C180)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C180)&amp;")",IF(L180="","JMBG sadrži nešto što nije cifra",IF(N180="","Nepostojeći datum rođenja",IF(VALUE(MID(C180,13,1))&lt;&gt;L180,"Pogrešna kontrolna cifra - treba "&amp;L180,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K180">
@@ -27607,7 +27607,7 @@
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="2" t="n"/>
       <c r="J181" s="2">
-        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra — treba "&amp;L181,"✓ ispravan")))))</f>
+        <f>IF(C181="","",IF(LEN(C181)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C181)&amp;")",IF(L181="","JMBG sadrži nešto što nije cifra",IF(N181="","Nepostojeći datum rođenja",IF(VALUE(MID(C181,13,1))&lt;&gt;L181,"Pogrešna kontrolna cifra - treba "&amp;L181,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K181">
@@ -27641,7 +27641,7 @@
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="n"/>
       <c r="J182" s="2">
-        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra — treba "&amp;L182,"✓ ispravan")))))</f>
+        <f>IF(C182="","",IF(LEN(C182)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C182)&amp;")",IF(L182="","JMBG sadrži nešto što nije cifra",IF(N182="","Nepostojeći datum rođenja",IF(VALUE(MID(C182,13,1))&lt;&gt;L182,"Pogrešna kontrolna cifra - treba "&amp;L182,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K182">
@@ -27675,7 +27675,7 @@
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="2" t="n"/>
       <c r="J183" s="2">
-        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra — treba "&amp;L183,"✓ ispravan")))))</f>
+        <f>IF(C183="","",IF(LEN(C183)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C183)&amp;")",IF(L183="","JMBG sadrži nešto što nije cifra",IF(N183="","Nepostojeći datum rođenja",IF(VALUE(MID(C183,13,1))&lt;&gt;L183,"Pogrešna kontrolna cifra - treba "&amp;L183,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K183">
@@ -27709,7 +27709,7 @@
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="n"/>
       <c r="J184" s="2">
-        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra — treba "&amp;L184,"✓ ispravan")))))</f>
+        <f>IF(C184="","",IF(LEN(C184)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C184)&amp;")",IF(L184="","JMBG sadrži nešto što nije cifra",IF(N184="","Nepostojeći datum rođenja",IF(VALUE(MID(C184,13,1))&lt;&gt;L184,"Pogrešna kontrolna cifra - treba "&amp;L184,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K184">
@@ -27743,7 +27743,7 @@
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="n"/>
       <c r="J185" s="2">
-        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra — treba "&amp;L185,"✓ ispravan")))))</f>
+        <f>IF(C185="","",IF(LEN(C185)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C185)&amp;")",IF(L185="","JMBG sadrži nešto što nije cifra",IF(N185="","Nepostojeći datum rođenja",IF(VALUE(MID(C185,13,1))&lt;&gt;L185,"Pogrešna kontrolna cifra - treba "&amp;L185,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K185">
@@ -27777,7 +27777,7 @@
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="n"/>
       <c r="J186" s="2">
-        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra — treba "&amp;L186,"✓ ispravan")))))</f>
+        <f>IF(C186="","",IF(LEN(C186)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C186)&amp;")",IF(L186="","JMBG sadrži nešto što nije cifra",IF(N186="","Nepostojeći datum rođenja",IF(VALUE(MID(C186,13,1))&lt;&gt;L186,"Pogrešna kontrolna cifra - treba "&amp;L186,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K186">
@@ -27811,7 +27811,7 @@
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="2" t="n"/>
       <c r="J187" s="2">
-        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra — treba "&amp;L187,"✓ ispravan")))))</f>
+        <f>IF(C187="","",IF(LEN(C187)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C187)&amp;")",IF(L187="","JMBG sadrži nešto što nije cifra",IF(N187="","Nepostojeći datum rođenja",IF(VALUE(MID(C187,13,1))&lt;&gt;L187,"Pogrešna kontrolna cifra - treba "&amp;L187,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K187">
@@ -27845,7 +27845,7 @@
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="n"/>
       <c r="J188" s="2">
-        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra — treba "&amp;L188,"✓ ispravan")))))</f>
+        <f>IF(C188="","",IF(LEN(C188)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C188)&amp;")",IF(L188="","JMBG sadrži nešto što nije cifra",IF(N188="","Nepostojeći datum rođenja",IF(VALUE(MID(C188,13,1))&lt;&gt;L188,"Pogrešna kontrolna cifra - treba "&amp;L188,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K188">
@@ -27879,7 +27879,7 @@
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="n"/>
       <c r="J189" s="2">
-        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra — treba "&amp;L189,"✓ ispravan")))))</f>
+        <f>IF(C189="","",IF(LEN(C189)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C189)&amp;")",IF(L189="","JMBG sadrži nešto što nije cifra",IF(N189="","Nepostojeći datum rođenja",IF(VALUE(MID(C189,13,1))&lt;&gt;L189,"Pogrešna kontrolna cifra - treba "&amp;L189,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K189">
@@ -27913,7 +27913,7 @@
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="2" t="n"/>
       <c r="J190" s="2">
-        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra — treba "&amp;L190,"✓ ispravan")))))</f>
+        <f>IF(C190="","",IF(LEN(C190)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C190)&amp;")",IF(L190="","JMBG sadrži nešto što nije cifra",IF(N190="","Nepostojeći datum rođenja",IF(VALUE(MID(C190,13,1))&lt;&gt;L190,"Pogrešna kontrolna cifra - treba "&amp;L190,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K190">
@@ -27947,7 +27947,7 @@
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="n"/>
       <c r="J191" s="2">
-        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra — treba "&amp;L191,"✓ ispravan")))))</f>
+        <f>IF(C191="","",IF(LEN(C191)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C191)&amp;")",IF(L191="","JMBG sadrži nešto što nije cifra",IF(N191="","Nepostojeći datum rođenja",IF(VALUE(MID(C191,13,1))&lt;&gt;L191,"Pogrešna kontrolna cifra - treba "&amp;L191,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K191">
@@ -27981,7 +27981,7 @@
       <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="n"/>
       <c r="J192" s="2">
-        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra — treba "&amp;L192,"✓ ispravan")))))</f>
+        <f>IF(C192="","",IF(LEN(C192)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C192)&amp;")",IF(L192="","JMBG sadrži nešto što nije cifra",IF(N192="","Nepostojeći datum rođenja",IF(VALUE(MID(C192,13,1))&lt;&gt;L192,"Pogrešna kontrolna cifra - treba "&amp;L192,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K192">
@@ -28015,7 +28015,7 @@
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="n"/>
       <c r="J193" s="2">
-        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra — treba "&amp;L193,"✓ ispravan")))))</f>
+        <f>IF(C193="","",IF(LEN(C193)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C193)&amp;")",IF(L193="","JMBG sadrži nešto što nije cifra",IF(N193="","Nepostojeći datum rođenja",IF(VALUE(MID(C193,13,1))&lt;&gt;L193,"Pogrešna kontrolna cifra - treba "&amp;L193,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K193">
@@ -28049,7 +28049,7 @@
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="n"/>
       <c r="J194" s="2">
-        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra — treba "&amp;L194,"✓ ispravan")))))</f>
+        <f>IF(C194="","",IF(LEN(C194)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C194)&amp;")",IF(L194="","JMBG sadrži nešto što nije cifra",IF(N194="","Nepostojeći datum rođenja",IF(VALUE(MID(C194,13,1))&lt;&gt;L194,"Pogrešna kontrolna cifra - treba "&amp;L194,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K194">
@@ -28083,7 +28083,7 @@
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="n"/>
       <c r="J195" s="2">
-        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra — treba "&amp;L195,"✓ ispravan")))))</f>
+        <f>IF(C195="","",IF(LEN(C195)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C195)&amp;")",IF(L195="","JMBG sadrži nešto što nije cifra",IF(N195="","Nepostojeći datum rođenja",IF(VALUE(MID(C195,13,1))&lt;&gt;L195,"Pogrešna kontrolna cifra - treba "&amp;L195,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K195">
@@ -28117,7 +28117,7 @@
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="n"/>
       <c r="J196" s="2">
-        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra — treba "&amp;L196,"✓ ispravan")))))</f>
+        <f>IF(C196="","",IF(LEN(C196)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C196)&amp;")",IF(L196="","JMBG sadrži nešto što nije cifra",IF(N196="","Nepostojeći datum rođenja",IF(VALUE(MID(C196,13,1))&lt;&gt;L196,"Pogrešna kontrolna cifra - treba "&amp;L196,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K196">
@@ -28151,7 +28151,7 @@
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="n"/>
       <c r="J197" s="2">
-        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra — treba "&amp;L197,"✓ ispravan")))))</f>
+        <f>IF(C197="","",IF(LEN(C197)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C197)&amp;")",IF(L197="","JMBG sadrži nešto što nije cifra",IF(N197="","Nepostojeći datum rođenja",IF(VALUE(MID(C197,13,1))&lt;&gt;L197,"Pogrešna kontrolna cifra - treba "&amp;L197,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K197">
@@ -28185,7 +28185,7 @@
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="n"/>
       <c r="J198" s="2">
-        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra — treba "&amp;L198,"✓ ispravan")))))</f>
+        <f>IF(C198="","",IF(LEN(C198)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C198)&amp;")",IF(L198="","JMBG sadrži nešto što nije cifra",IF(N198="","Nepostojeći datum rođenja",IF(VALUE(MID(C198,13,1))&lt;&gt;L198,"Pogrešna kontrolna cifra - treba "&amp;L198,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K198">
@@ -28219,7 +28219,7 @@
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="n"/>
       <c r="J199" s="2">
-        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra — treba "&amp;L199,"✓ ispravan")))))</f>
+        <f>IF(C199="","",IF(LEN(C199)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C199)&amp;")",IF(L199="","JMBG sadrži nešto što nije cifra",IF(N199="","Nepostojeći datum rođenja",IF(VALUE(MID(C199,13,1))&lt;&gt;L199,"Pogrešna kontrolna cifra - treba "&amp;L199,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K199">
@@ -28253,7 +28253,7 @@
       <c r="H200" s="2" t="n"/>
       <c r="I200" s="2" t="n"/>
       <c r="J200" s="2">
-        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra — treba "&amp;L200,"✓ ispravan")))))</f>
+        <f>IF(C200="","",IF(LEN(C200)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C200)&amp;")",IF(L200="","JMBG sadrži nešto što nije cifra",IF(N200="","Nepostojeći datum rođenja",IF(VALUE(MID(C200,13,1))&lt;&gt;L200,"Pogrešna kontrolna cifra - treba "&amp;L200,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K200">
@@ -28287,7 +28287,7 @@
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="n"/>
       <c r="J201" s="2">
-        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra — treba "&amp;L201,"✓ ispravan")))))</f>
+        <f>IF(C201="","",IF(LEN(C201)&lt;&gt;13,"Nema 13 cifara (ima "&amp;LEN(C201)&amp;")",IF(L201="","JMBG sadrži nešto što nije cifra",IF(N201="","Nepostojeći datum rođenja",IF(VALUE(MID(C201,13,1))&lt;&gt;L201,"Pogrešna kontrolna cifra - treba "&amp;L201,"✓ ispravan")))))</f>
         <v/>
       </c>
       <c r="K201">
@@ -28397,7 +28397,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>List 'Primeri' su izmišljeni primeri — tu se vidi kako radi provera</t>
+          <t>List 'Primeri' su izmišljeni primeri - tu se vidi kako radi provera</t>
         </is>
       </c>
     </row>
@@ -28428,7 +28428,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>JMBG kolona je formatirana kao TEKST — bez toga Excel pojede vodeću nulu kod</t>
+          <t>JMBG kolona je formatirana kao TEKST - bez toga Excel pojede vodeću nulu kod</t>
         </is>
       </c>
     </row>
@@ -28442,7 +28442,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dolazak piši kao 05.10 ili 05.10.2026 — oba se prepoznaju.</t>
+          <t>Dolazak piši kao 05.10 ili 05.10.2026 - oba se prepoznaju.</t>
         </is>
       </c>
     </row>
@@ -28456,7 +28456,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>E-mail popunjavaj samo za goste čiji vaučeri idu na drugu adresu nego ostali —</t>
+          <t>E-mail popunjavaj samo za goste čiji vaučeri idu na drugu adresu nego ostali -</t>
         </is>
       </c>
     </row>
@@ -28501,14 +28501,14 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crveno kaže tačno šta ne valja, npr. 'Pogrešna kontrolna cifra — treba 8'.</t>
+          <t>Crveno kaže tačno šta ne valja, npr. 'Pogrešna kontrolna cifra - treba 8'.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kolone K-N su pomoćne (sakrivene) — služe samo formuli u koloni J. Ne diraj ih.</t>
+          <t>Kolone K-N su pomoćne (sakrivene) - služe samo formuli u koloni J. Ne diraj ih.</t>
         </is>
       </c>
     </row>
@@ -28525,7 +28525,7 @@
     <row r="27">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>To utvrđuje tek portal — i to se posle vidi u koloni RAZLOG.</t>
+          <t>To utvrđuje tek portal - i to se posle vidi u koloni RAZLOG.</t>
         </is>
       </c>
     </row>
@@ -28542,7 +28542,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Označi kolone A-F za grupu gostiju koju prijavljuješ (5, 10, 30 — koliko hoćeš),</t>
+          <t>Označi kolone A-F za grupu gostiju koju prijavljuješ (5, 10, 30 - koliko hoćeš),</t>
         </is>
       </c>
     </row>
@@ -28604,7 +28604,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>Na listu 'Primeri' su izmišljeni gosti — ne pripadaju nikome.</t>
+          <t>Na listu 'Primeri' su izmišljeni gosti - ne pripadaju nikome.</t>
         </is>
       </c>
     </row>
